--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgmcm\OneDrive\Desktop\QA Portfolio\Qa-Portfolio\Automation Exercise Project\Test Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E684311F-19D6-43DF-8B80-5B32975CC4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DDFB38-743B-497B-8492-E6442DAD1736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5950" yWindow="3530" windowWidth="28800" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="3730" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="432">
   <si>
     <t>Automation Exercise | Requirements Traceability Matrix</t>
   </si>
@@ -1557,12 +1557,54 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>API-PRODUCT-001</t>
+  </si>
+  <si>
+    <t>API-BRAND-001</t>
+  </si>
+  <si>
+    <t>API-SEARCH-001</t>
+  </si>
+  <si>
+    <t>API-SEARCH-002</t>
+  </si>
+  <si>
+    <t>API-AUTH-001</t>
+  </si>
+  <si>
+    <t>API-AUTH-002</t>
+  </si>
+  <si>
+    <t>API-PRODUCT-002</t>
+  </si>
+  <si>
+    <t>API-BRAND-002</t>
+  </si>
+  <si>
+    <t>API-AUTH-004</t>
+  </si>
+  <si>
+    <t>API-AUTH-003</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-001</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-002</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-003</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-004</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1620,6 +1662,10 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1992,6 +2038,43 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2067,43 +2150,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2111,13 +2157,69 @@
   </cellStyles>
   <dxfs count="17">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2256,69 +2358,13 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF595959"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2393,13 +2439,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>13</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2573,17 +2619,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OfficialApiScenarios" displayName="OfficialApiScenarios" ref="A4:H18" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OfficialApiScenarios" displayName="OfficialApiScenarios" ref="A4:H18" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
   <autoFilter ref="A4:H18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Source API ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Exact Scenario Title" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="API URL" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Request Method" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Exact Request Parameter(s)" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Response Code" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Response Type" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Exact Expected Response" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Source API ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Exact Scenario Title" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="API URL" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Request Method" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Exact Request Parameter(s)" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Response Code" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Response Type" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Exact Expected Response" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2748,341 +2794,341 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="E4" s="29" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="E4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="I4" s="29" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="I4" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="M4" s="29" t="s">
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="M4" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="29"/>
+      <c r="N4" s="42"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="30">
+      <c r="A5" s="43">
         <f>COUNTA(RTM!A8:A107)</f>
         <v>44</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="E5" s="30">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="E5" s="43">
         <f>COUNTIF(RTM!G8:G107,"Fully Covered")</f>
-        <v>13</v>
-      </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
-      <c r="I5" s="30">
+        <v>27</v>
+      </c>
+      <c r="F5" s="44"/>
+      <c r="G5" s="45"/>
+      <c r="I5" s="43">
         <f>COUNTIF(RTM!G8:G107,"Partially Covered")</f>
         <v>1</v>
       </c>
-      <c r="J5" s="31"/>
-      <c r="K5" s="32"/>
-      <c r="M5" s="30">
+      <c r="J5" s="44"/>
+      <c r="K5" s="45"/>
+      <c r="M5" s="43">
         <f>COUNTIF(RTM!G8:G107,"Not Covered")</f>
-        <v>30</v>
-      </c>
-      <c r="N5" s="32"/>
+        <v>16</v>
+      </c>
+      <c r="N5" s="45"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="33"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="35"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="35"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="48"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="48"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="17" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="18">
         <f>COUNTIF(RTM!G8:G107,"Fully Covered")</f>
-        <v>13</v>
-      </c>
-      <c r="C9" s="45">
+        <v>27</v>
+      </c>
+      <c r="C9" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Fully Covered")</f>
         <v>9</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Fully Covered")</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="45">
+        <v>14</v>
+      </c>
+      <c r="E9" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Fully Covered")</f>
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="18">
         <f>COUNTIF(RTM!G8:G107,"Partially Covered")</f>
         <v>1</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Partially Covered")</f>
         <v>1</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Partially Covered")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Partially Covered")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="18">
         <f>COUNTIF(RTM!G8:G107,"Not Covered")</f>
-        <v>30</v>
-      </c>
-      <c r="C11" s="45">
+        <v>16</v>
+      </c>
+      <c r="C11" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Not Covered")</f>
         <v>16</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Not Covered")</f>
-        <v>14</v>
-      </c>
-      <c r="E11" s="45">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Not Covered")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="37.5">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="20">
         <f>COUNTIF(RTM!K8:K107,"Pass")</f>
         <v>11</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="20">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="37.5">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="20">
         <f>COUNTIF(RTM!K8:K107,"Fail")</f>
         <v>3</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="20">
         <f>COUNTIF(RTM!K8:K107,"Fail")</f>
         <v>3</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="20">
         <f>COUNTIF(RTM!K8:K107,"Not Run")</f>
         <v>30</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="20">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.5">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="33"/>
     </row>
     <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="23"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="36"/>
     </row>
     <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="23"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="36"/>
     </row>
     <row r="24" spans="1:14" ht="30" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="23"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="36"/>
     </row>
     <row r="25" spans="1:14" ht="30" customHeight="1">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="26"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3123,70 +3169,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="38"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="51"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="41"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="54"/>
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -4374,570 +4420,598 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="57" customHeight="1">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D38" s="50" t="s">
+      <c r="D38" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="E38" s="50" t="s">
+      <c r="E38" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="F38" s="51"/>
-      <c r="G38" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H38" s="52" t="s">
+      <c r="F38" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="I38" s="50" t="s">
+      <c r="I38" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J38" s="50" t="s">
+      <c r="J38" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K38" s="50" t="s">
+      <c r="K38" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L38" s="51"/>
-      <c r="M38" s="50" t="s">
+      <c r="L38" s="24"/>
+      <c r="M38" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="N38" s="53"/>
-      <c r="O38" s="53"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:15" ht="57" customHeight="1">
-      <c r="A39" s="50" t="s">
+      <c r="A39" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="B39" s="50" t="s">
+      <c r="B39" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D39" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="E39" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="F39" s="51"/>
-      <c r="G39" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H39" s="51" t="s">
+      <c r="F39" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="I39" s="50" t="s">
+      <c r="I39" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J39" s="50" t="s">
+      <c r="J39" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="K39" s="50" t="s">
+      <c r="K39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L39" s="51"/>
-      <c r="M39" s="50" t="s">
+      <c r="L39" s="24"/>
+      <c r="M39" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:15" ht="57" customHeight="1">
-      <c r="A40" s="50" t="s">
+      <c r="A40" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="B40" s="50" t="s">
+      <c r="B40" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="E40" s="50" t="s">
+      <c r="E40" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="F40" s="51"/>
-      <c r="G40" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H40" s="52" t="s">
+      <c r="F40" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="I40" s="50" t="s">
+      <c r="I40" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J40" s="50" t="s">
+      <c r="J40" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K40" s="50" t="s">
+      <c r="K40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L40" s="51"/>
-      <c r="M40" s="50" t="s">
+      <c r="L40" s="24"/>
+      <c r="M40" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="N40" s="53"/>
-      <c r="O40" s="53"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
     </row>
     <row r="41" spans="1:15" ht="57" customHeight="1">
-      <c r="A41" s="50" t="s">
+      <c r="A41" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="E41" s="50" t="s">
+      <c r="E41" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="F41" s="51"/>
-      <c r="G41" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="51" t="s">
+      <c r="F41" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J41" s="50" t="s">
+      <c r="J41" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="K41" s="50" t="s">
+      <c r="K41" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L41" s="51"/>
-      <c r="M41" s="50" t="s">
+      <c r="L41" s="24"/>
+      <c r="M41" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
     </row>
     <row r="42" spans="1:15" ht="57" customHeight="1">
-      <c r="A42" s="50" t="s">
+      <c r="A42" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="D42" s="50" t="s">
+      <c r="D42" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="E42" s="50" t="s">
+      <c r="E42" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="F42" s="51"/>
-      <c r="G42" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="51" t="s">
+      <c r="F42" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H42" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="I42" s="50" t="s">
+      <c r="I42" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J42" s="50" t="s">
+      <c r="J42" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="50" t="s">
+      <c r="K42" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L42" s="51"/>
-      <c r="M42" s="50" t="s">
+      <c r="L42" s="24"/>
+      <c r="M42" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
     </row>
     <row r="43" spans="1:15" ht="57" customHeight="1">
-      <c r="A43" s="50" t="s">
+      <c r="A43" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="B43" s="50" t="s">
+      <c r="B43" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="D43" s="50" t="s">
+      <c r="D43" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="E43" s="54" t="s">
+      <c r="E43" s="27" t="s">
         <v>411</v>
       </c>
-      <c r="F43" s="51"/>
-      <c r="G43" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="52" t="s">
+      <c r="F43" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="I43" s="50" t="s">
+      <c r="I43" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J43" s="50" t="s">
+      <c r="J43" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K43" s="50" t="s">
+      <c r="K43" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L43" s="51"/>
-      <c r="M43" s="54" t="s">
+      <c r="L43" s="24"/>
+      <c r="M43" s="27" t="s">
         <v>415</v>
       </c>
-      <c r="N43" s="53"/>
-      <c r="O43" s="53"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
     </row>
     <row r="44" spans="1:15" ht="57" customHeight="1">
-      <c r="A44" s="50" t="s">
+      <c r="A44" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="E44" s="50" t="s">
+      <c r="E44" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="F44" s="51"/>
-      <c r="G44" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="51" t="s">
+      <c r="F44" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H44" s="24" t="s">
         <v>320</v>
       </c>
-      <c r="I44" s="50" t="s">
+      <c r="I44" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J44" s="50" t="s">
+      <c r="J44" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="K44" s="50" t="s">
+      <c r="K44" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L44" s="51"/>
-      <c r="M44" s="50" t="s">
+      <c r="L44" s="24"/>
+      <c r="M44" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="N44" s="53"/>
-      <c r="O44" s="53"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
     </row>
     <row r="45" spans="1:15" ht="57" customHeight="1">
-      <c r="A45" s="50" t="s">
+      <c r="A45" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="B45" s="50" t="s">
+      <c r="B45" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="D45" s="50" t="s">
+      <c r="D45" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="E45" s="50" t="s">
+      <c r="E45" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="F45" s="51"/>
-      <c r="G45" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="51" t="s">
+      <c r="F45" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H45" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="I45" s="50" t="s">
+      <c r="I45" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J45" s="50" t="s">
+      <c r="J45" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K45" s="50" t="s">
+      <c r="K45" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L45" s="51"/>
-      <c r="M45" s="50" t="s">
+      <c r="L45" s="24"/>
+      <c r="M45" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
     </row>
     <row r="46" spans="1:15" ht="57" customHeight="1">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="B46" s="50" t="s">
+      <c r="B46" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="D46" s="50" t="s">
+      <c r="D46" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="F46" s="51"/>
-      <c r="G46" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="52" t="s">
+      <c r="F46" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="I46" s="50" t="s">
+      <c r="I46" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J46" s="50" t="s">
+      <c r="J46" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="K46" s="50" t="s">
+      <c r="K46" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L46" s="51"/>
-      <c r="M46" s="50" t="s">
+      <c r="L46" s="24"/>
+      <c r="M46" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="N46" s="53"/>
-      <c r="O46" s="53"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
     </row>
     <row r="47" spans="1:15" ht="57" customHeight="1">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="B47" s="50" t="s">
+      <c r="B47" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="E47" s="50" t="s">
+      <c r="E47" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="F47" s="51"/>
-      <c r="G47" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="51" t="s">
+      <c r="F47" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="G47" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H47" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="I47" s="50" t="s">
+      <c r="I47" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="J47" s="50" t="s">
+      <c r="J47" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K47" s="50" t="s">
+      <c r="K47" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L47" s="51"/>
-      <c r="M47" s="50" t="s">
+      <c r="L47" s="24"/>
+      <c r="M47" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="N47" s="53"/>
-      <c r="O47" s="53"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
     </row>
     <row r="48" spans="1:15" ht="57" customHeight="1">
-      <c r="A48" s="50" t="s">
+      <c r="A48" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="B48" s="50" t="s">
+      <c r="B48" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E48" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="F48" s="51"/>
-      <c r="G48" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="51" t="s">
+      <c r="F48" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="G48" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="I48" s="50" t="s">
+      <c r="I48" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J48" s="50" t="s">
+      <c r="J48" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="K48" s="50" t="s">
+      <c r="K48" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L48" s="51"/>
-      <c r="M48" s="50" t="s">
+      <c r="L48" s="24"/>
+      <c r="M48" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="N48" s="53"/>
-      <c r="O48" s="53"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
     </row>
     <row r="49" spans="1:15" ht="57" customHeight="1">
-      <c r="A49" s="50" t="s">
+      <c r="A49" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="B49" s="50" t="s">
+      <c r="B49" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="D49" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="E49" s="50" t="s">
+      <c r="E49" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="F49" s="51"/>
-      <c r="G49" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="51" t="s">
+      <c r="F49" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="I49" s="50" t="s">
+      <c r="I49" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J49" s="50" t="s">
+      <c r="J49" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="K49" s="50" t="s">
+      <c r="K49" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L49" s="51"/>
-      <c r="M49" s="50" t="s">
+      <c r="L49" s="24"/>
+      <c r="M49" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
     </row>
     <row r="50" spans="1:15" ht="57" customHeight="1">
-      <c r="A50" s="50" t="s">
+      <c r="A50" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="B50" s="50" t="s">
+      <c r="B50" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="23" t="s">
         <v>348</v>
       </c>
-      <c r="D50" s="50" t="s">
+      <c r="D50" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="E50" s="50" t="s">
+      <c r="E50" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="F50" s="51"/>
-      <c r="G50" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H50" s="51" t="s">
+      <c r="F50" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="I50" s="50" t="s">
+      <c r="I50" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J50" s="50" t="s">
+      <c r="J50" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K50" s="50" t="s">
+      <c r="K50" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L50" s="51"/>
-      <c r="M50" s="50" t="s">
+      <c r="L50" s="24"/>
+      <c r="M50" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="N50" s="53"/>
-      <c r="O50" s="53"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
     </row>
     <row r="51" spans="1:15" ht="57" customHeight="1">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="B51" s="50" t="s">
+      <c r="B51" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="D51" s="50" t="s">
+      <c r="D51" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="E51" s="50" t="s">
+      <c r="E51" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="F51" s="51"/>
-      <c r="G51" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="51" t="s">
+      <c r="F51" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="I51" s="50" t="s">
+      <c r="I51" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J51" s="50" t="s">
+      <c r="J51" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K51" s="50" t="s">
+      <c r="K51" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="L51" s="51"/>
-      <c r="M51" s="50" t="s">
+      <c r="L51" s="24"/>
+      <c r="M51" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="N51" s="53"/>
-      <c r="O51" s="53"/>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
     </row>
     <row r="52" spans="1:15" ht="57" customHeight="1">
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="48"/>
-      <c r="M52" s="48"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
     </row>
     <row r="53" spans="1:15" ht="57" customHeight="1">
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
-      <c r="L53" s="48"/>
-      <c r="M53" s="48"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4945,15 +5019,16 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A4:M5"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="G8:G107">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="Fully Covered"/>
-    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Partially Covered"/>
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Not Covered"/>
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Fully Covered"/>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Partially Covered"/>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Not Covered"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:K107">
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Pass"/>
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="Fail"/>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="Not Run"/>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Pass"/>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Fail"/>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Not Run"/>
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation type="list" sqref="G8:G107" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -4991,20 +5066,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
     </row>
     <row r="4" spans="1:4" ht="38" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -5412,28 +5487,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="28" t="s">
         <v>357</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1">
       <c r="A4" s="16" t="s">

--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kgmcm\OneDrive\Desktop\QA Portfolio\Qa-Portfolio\Automation Exercise Project\Test Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DDFB38-743B-497B-8492-E6442DAD1736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C29A31F-3802-4417-A583-49C4CEE3C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="3730" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="436">
   <si>
     <t>Automation Exercise | Requirements Traceability Matrix</t>
   </si>
@@ -53,12 +53,24 @@
     <t>Not Covered</t>
   </si>
   <si>
+    <t>Coverage Status</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>UI Scenarios</t>
+  </si>
+  <si>
+    <t>API Scenarios</t>
+  </si>
+  <si>
+    <t>Tester-Derived</t>
+  </si>
+  <si>
     <t>Execution Status</t>
   </si>
   <si>
-    <t>Count</t>
-  </si>
-  <si>
     <t>Defect-Linked</t>
   </si>
   <si>
@@ -89,9 +101,6 @@
     <t>Requirements Traceability Matrix</t>
   </si>
   <si>
-    <t>Coverage is synchronized with the 17-case test repository and four-defect log. Source scenario wording and exact steps are preserved on the Source Scenarios worksheet.</t>
-  </si>
-  <si>
     <t>Coverage rule: Fully Covered means every material behavior in the requirement is mapped to one or more existing test cases. Partially Covered means some, but not all material behavior is mapped. Not Covered means no existing case verifies the requirement.</t>
   </si>
   <si>
@@ -111,9 +120,6 @@
   </si>
   <si>
     <t>Mapped Test Case ID(s)</t>
-  </si>
-  <si>
-    <t>Coverage Status</t>
   </si>
   <si>
     <t>Coverage Rationale</t>
@@ -268,15 +274,9 @@
     <t>Contact Us Form</t>
   </si>
   <si>
-    <t>No contact-form test exists.</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Create a contact-form case covering file upload, confirmation dialog, success message, and return to Home.</t>
-  </si>
-  <si>
     <t>REQ-NAV-001</t>
   </si>
   <si>
@@ -289,15 +289,9 @@
     <t>Verify Test Cases Page</t>
   </si>
   <si>
-    <t>No navigation test covers the Test Cases page.</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>Create a navigation case for the Test Cases page.</t>
-  </si>
-  <si>
     <t>REQ-PRODUCT-001</t>
   </si>
   <si>
@@ -349,12 +343,6 @@
     <t>Verify Subscription in home page</t>
   </si>
   <si>
-    <t>No homepage subscription test exists.</t>
-  </si>
-  <si>
-    <t>Create homepage subscription coverage.</t>
-  </si>
-  <si>
     <t>REQ-SUB-002</t>
   </si>
   <si>
@@ -364,12 +352,6 @@
     <t>Verify Subscription in Cart page</t>
   </si>
   <si>
-    <t>No cart-page subscription test exists.</t>
-  </si>
-  <si>
-    <t>Create cart-page subscription coverage.</t>
-  </si>
-  <si>
     <t>REQ-CART-001</t>
   </si>
   <si>
@@ -637,9 +619,6 @@
     <t>REQ-EXT-001</t>
   </si>
   <si>
-    <t>Tester-Derived</t>
-  </si>
-  <si>
     <t>CUSTOM-01</t>
   </si>
   <si>
@@ -716,6 +695,281 @@
   </si>
   <si>
     <t>Retain as enhanced account-lifecycle coverage.</t>
+  </si>
+  <si>
+    <t>REQ-API-001</t>
+  </si>
+  <si>
+    <t>Site API Scenario</t>
+  </si>
+  <si>
+    <t>SRC-API-01</t>
+  </si>
+  <si>
+    <t>Product API</t>
+  </si>
+  <si>
+    <t>Get All Products List</t>
+  </si>
+  <si>
+    <t>API-PRODUCT-001</t>
+  </si>
+  <si>
+    <t>Official API scenario is documented, but no portfolio API
+ test has been executed.</t>
+  </si>
+  <si>
+    <t>API — Positive</t>
+  </si>
+  <si>
+    <t>Create API-PRODUCT-001 and verify the product-list response.</t>
+  </si>
+  <si>
+    <t>REQ-API-002</t>
+  </si>
+  <si>
+    <t>SRC-API-02</t>
+  </si>
+  <si>
+    <t>POST To All Products List</t>
+  </si>
+  <si>
+    <t>API-PRODUCT-002</t>
+  </si>
+  <si>
+    <t>Unsupported-method handling has not been tested.</t>
+  </si>
+  <si>
+    <t>API — Negative</t>
+  </si>
+  <si>
+    <t>Create API-PRODUCT-002 and verify the 405 response behavior.</t>
+  </si>
+  <si>
+    <t>REQ-API-003</t>
+  </si>
+  <si>
+    <t>SRC-API-03</t>
+  </si>
+  <si>
+    <t>Brand API</t>
+  </si>
+  <si>
+    <t>Get All Brands List</t>
+  </si>
+  <si>
+    <t>API-BRAND-001</t>
+  </si>
+  <si>
+    <t>Create API-BRAND-001 and verify the brand-list response.</t>
+  </si>
+  <si>
+    <t>REQ-API-004</t>
+  </si>
+  <si>
+    <t>SRC-API-04</t>
+  </si>
+  <si>
+    <t>PUT To All Brands List</t>
+  </si>
+  <si>
+    <t>API-BRAND-002</t>
+  </si>
+  <si>
+    <t>Create API-BRAND-002 and verify the 405 response behavior.</t>
+  </si>
+  <si>
+    <t>REQ-API-005</t>
+  </si>
+  <si>
+    <t>SRC-API-05</t>
+  </si>
+  <si>
+    <t>Search API</t>
+  </si>
+  <si>
+    <t>POST To Search Product</t>
+  </si>
+  <si>
+    <t>API-SEARCH-001</t>
+  </si>
+  <si>
+    <t>Valid product-search API behavior has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-SEARCH-001 using a valid search_product parameter.</t>
+  </si>
+  <si>
+    <t>REQ-API-006</t>
+  </si>
+  <si>
+    <t>SRC-API-06</t>
+  </si>
+  <si>
+    <t>POST To Search Product without search_product 
+parameter</t>
+  </si>
+  <si>
+    <t>API-SEARCH-002</t>
+  </si>
+  <si>
+    <t>Missing-parameter validation for product search has not
+ been tested.</t>
+  </si>
+  <si>
+    <t>Create API-SEARCH-002 without the required search_product 
+parameter.</t>
+  </si>
+  <si>
+    <t>REQ-API-007</t>
+  </si>
+  <si>
+    <t>SRC-API-07</t>
+  </si>
+  <si>
+    <t>Authentication API</t>
+  </si>
+  <si>
+    <t>POST To Verify Login with valid details</t>
+  </si>
+  <si>
+    <t>API-AUTH-001</t>
+  </si>
+  <si>
+    <t>Valid API login verification has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-AUTH-001 using valid test credentials.</t>
+  </si>
+  <si>
+    <t>REQ-API-008</t>
+  </si>
+  <si>
+    <t>SRC-API-08</t>
+  </si>
+  <si>
+    <t>POST To Verify Login without email parameter</t>
+  </si>
+  <si>
+    <t>API-AUTH-002</t>
+  </si>
+  <si>
+    <t>Missing-email validation for API login has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-AUTH-002 with only the password parameter.</t>
+  </si>
+  <si>
+    <t>REQ-API-009</t>
+  </si>
+  <si>
+    <t>SRC-API-09</t>
+  </si>
+  <si>
+    <t>DELETE To Verify Login</t>
+  </si>
+  <si>
+    <t>API-AUTH-003</t>
+  </si>
+  <si>
+    <t>Unsupported DELETE handling for login verification 
+has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-AUTH-003 and verify the 405 response behavior.</t>
+  </si>
+  <si>
+    <t>REQ-API-010</t>
+  </si>
+  <si>
+    <t>SRC-API-10</t>
+  </si>
+  <si>
+    <t>POST To Verify Login with invalid details</t>
+  </si>
+  <si>
+    <t>API-AUTH-004</t>
+  </si>
+  <si>
+    <t>Invalid API login behavior has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-AUTH-004 using invalid test credentials.</t>
+  </si>
+  <si>
+    <t>REQ-API-011</t>
+  </si>
+  <si>
+    <t>SRC-API-11</t>
+  </si>
+  <si>
+    <t>Account API</t>
+  </si>
+  <si>
+    <t>POST To Create/Register User Account</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-001</t>
+  </si>
+  <si>
+    <t>API account creation has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-ACCOUNT-001 using a disposable test account.</t>
+  </si>
+  <si>
+    <t>REQ-API-012</t>
+  </si>
+  <si>
+    <t>SRC-API-12</t>
+  </si>
+  <si>
+    <t>DELETE METHOD To Delete User Account</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-002</t>
+  </si>
+  <si>
+    <t>API account deletion has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-ACCOUNT-002 and delete only a disposable test account.</t>
+  </si>
+  <si>
+    <t>REQ-API-013</t>
+  </si>
+  <si>
+    <t>SRC-API-13</t>
+  </si>
+  <si>
+    <t>PUT METHOD To Update User Account</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-003</t>
+  </si>
+  <si>
+    <t>API account updates have not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-ACCOUNT-003 and verify the updated account values.</t>
+  </si>
+  <si>
+    <t>REQ-API-014</t>
+  </si>
+  <si>
+    <t>SRC-API-14</t>
+  </si>
+  <si>
+    <t>GET user account detail by email</t>
+  </si>
+  <si>
+    <t>API-ACCOUNT-004</t>
+  </si>
+  <si>
+    <t>API account-detail retrieval has not been tested.</t>
+  </si>
+  <si>
+    <t>Create API-ACCOUNT-004 using a dedicated QA account email.</t>
   </si>
   <si>
     <t>Authoritative Source Scenarios</t>
@@ -1142,237 +1396,12 @@
 7. Verify that page is scrolled up and 'Full-Fledged practice website for Automation Engineers' text is visible on screen</t>
   </si>
   <si>
-    <t>Cross-reference of 26 official UI scenarios, 14 official API scenarios, and 4 tester-derived requirements against the current 17 executed manual UI test cases</t>
-  </si>
-  <si>
-    <t>UI Scenarios</t>
-  </si>
-  <si>
-    <t>API Scenarios</t>
-  </si>
-  <si>
-    <t>Current strength: registration, login, account lifecycle, product discovery, and foundational cart behavior are covered by 17 executed UI test cases.
-API scope added: all 14 official Automation Exercise API scenarios are now documented as traceable requirements and preserved verbatim on the Source APIs worksheet.
-Current API gap: no Postman API cases have been executed yet, so all 14 API requirements remain Not Covered.
-Recommended next action: execute API-PRODUCT-001, API-BRAND-001, API-SEARCH-001, and API-SEARCH-002 in Postman; record both the HTTP status and any responseCode returned inside the JSON; then map the results back to this RTM.</t>
-  </si>
-  <si>
-    <t>REQ-API-001</t>
-  </si>
-  <si>
-    <t>Site API Scenario</t>
-  </si>
-  <si>
-    <t>SRC-API-01</t>
-  </si>
-  <si>
-    <t>Product API</t>
-  </si>
-  <si>
-    <t>Get All Products List</t>
-  </si>
-  <si>
-    <t>API — Positive</t>
-  </si>
-  <si>
-    <t>Create API-PRODUCT-001 and verify the product-list response.</t>
-  </si>
-  <si>
-    <t>REQ-API-002</t>
-  </si>
-  <si>
-    <t>SRC-API-02</t>
-  </si>
-  <si>
-    <t>POST To All Products List</t>
-  </si>
-  <si>
-    <t>Unsupported-method handling has not been tested.</t>
-  </si>
-  <si>
-    <t>API — Negative</t>
-  </si>
-  <si>
-    <t>Create API-PRODUCT-002 and verify the 405 response behavior.</t>
-  </si>
-  <si>
-    <t>REQ-API-003</t>
-  </si>
-  <si>
-    <t>SRC-API-03</t>
-  </si>
-  <si>
-    <t>Brand API</t>
-  </si>
-  <si>
-    <t>Get All Brands List</t>
-  </si>
-  <si>
-    <t>Create API-BRAND-001 and verify the brand-list response.</t>
-  </si>
-  <si>
-    <t>REQ-API-004</t>
-  </si>
-  <si>
-    <t>SRC-API-04</t>
-  </si>
-  <si>
-    <t>PUT To All Brands List</t>
-  </si>
-  <si>
-    <t>Create API-BRAND-002 and verify the 405 response behavior.</t>
-  </si>
-  <si>
-    <t>REQ-API-005</t>
-  </si>
-  <si>
-    <t>SRC-API-05</t>
-  </si>
-  <si>
-    <t>Search API</t>
-  </si>
-  <si>
-    <t>POST To Search Product</t>
-  </si>
-  <si>
-    <t>Valid product-search API behavior has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-SEARCH-001 using a valid search_product parameter.</t>
-  </si>
-  <si>
-    <t>REQ-API-006</t>
-  </si>
-  <si>
-    <t>SRC-API-06</t>
-  </si>
-  <si>
-    <t>REQ-API-007</t>
-  </si>
-  <si>
-    <t>SRC-API-07</t>
-  </si>
-  <si>
-    <t>Authentication API</t>
-  </si>
-  <si>
-    <t>POST To Verify Login with valid details</t>
-  </si>
-  <si>
-    <t>Valid API login verification has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-AUTH-001 using valid test credentials.</t>
-  </si>
-  <si>
-    <t>REQ-API-008</t>
-  </si>
-  <si>
-    <t>SRC-API-08</t>
-  </si>
-  <si>
-    <t>POST To Verify Login without email parameter</t>
-  </si>
-  <si>
-    <t>Missing-email validation for API login has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-AUTH-002 with only the password parameter.</t>
-  </si>
-  <si>
-    <t>REQ-API-009</t>
-  </si>
-  <si>
-    <t>SRC-API-09</t>
-  </si>
-  <si>
-    <t>DELETE To Verify Login</t>
-  </si>
-  <si>
-    <t>Create API-AUTH-003 and verify the 405 response behavior.</t>
-  </si>
-  <si>
-    <t>REQ-API-010</t>
-  </si>
-  <si>
-    <t>SRC-API-10</t>
-  </si>
-  <si>
-    <t>POST To Verify Login with invalid details</t>
-  </si>
-  <si>
-    <t>Invalid API login behavior has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-AUTH-004 using invalid test credentials.</t>
-  </si>
-  <si>
-    <t>REQ-API-011</t>
-  </si>
-  <si>
-    <t>SRC-API-11</t>
-  </si>
-  <si>
-    <t>Account API</t>
-  </si>
-  <si>
-    <t>POST To Create/Register User Account</t>
-  </si>
-  <si>
-    <t>API account creation has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-ACCOUNT-001 using a disposable test account.</t>
-  </si>
-  <si>
-    <t>REQ-API-012</t>
-  </si>
-  <si>
-    <t>SRC-API-12</t>
-  </si>
-  <si>
-    <t>DELETE METHOD To Delete User Account</t>
-  </si>
-  <si>
-    <t>API account deletion has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-ACCOUNT-002 and delete only a disposable test account.</t>
-  </si>
-  <si>
-    <t>REQ-API-013</t>
-  </si>
-  <si>
-    <t>SRC-API-13</t>
-  </si>
-  <si>
-    <t>PUT METHOD To Update User Account</t>
-  </si>
-  <si>
-    <t>API account updates have not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-ACCOUNT-003 and verify the updated account values.</t>
-  </si>
-  <si>
-    <t>REQ-API-014</t>
-  </si>
-  <si>
-    <t>SRC-API-14</t>
-  </si>
-  <si>
-    <t>GET user account detail by email</t>
-  </si>
-  <si>
-    <t>API account-detail retrieval has not been tested.</t>
-  </si>
-  <si>
-    <t>Create API-ACCOUNT-004 using a dedicated QA account email.</t>
-  </si>
-  <si>
     <t>Automation Exercise — Official API Source Scenarios</t>
   </si>
   <si>
+    <t>Exact scenario details transcribed from Automation Exercise Web Application</t>
+  </si>
+  <si>
     <t>Source API ID</t>
   </si>
   <si>
@@ -1520,6 +1549,9 @@
     <t>User updated!</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>API 14: GET user account detail by email</t>
   </si>
   <si>
@@ -1532,79 +1564,59 @@
     <t>User Detail</t>
   </si>
   <si>
-    <t>POST To Search Product without search_product 
-parameter</t>
-  </si>
-  <si>
-    <t>Unsupported DELETE handling for login verification 
-has not been tested.</t>
-  </si>
-  <si>
-    <t>Missing-parameter validation for product search has not
- been tested.</t>
-  </si>
-  <si>
-    <t>Official API scenario is documented, but no portfolio API
- test has been executed.</t>
-  </si>
-  <si>
-    <t>Create API-SEARCH-002 without the required search_product 
-parameter.</t>
-  </si>
-  <si>
-    <t>Exact scenario details transcribed from Automation Exercise Web Application</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>API-PRODUCT-001</t>
-  </si>
-  <si>
-    <t>API-BRAND-001</t>
-  </si>
-  <si>
-    <t>API-SEARCH-001</t>
-  </si>
-  <si>
-    <t>API-SEARCH-002</t>
-  </si>
-  <si>
-    <t>API-AUTH-001</t>
-  </si>
-  <si>
-    <t>API-AUTH-002</t>
-  </si>
-  <si>
-    <t>API-PRODUCT-002</t>
-  </si>
-  <si>
-    <t>API-BRAND-002</t>
-  </si>
-  <si>
-    <t>API-AUTH-004</t>
-  </si>
-  <si>
-    <t>API-AUTH-003</t>
-  </si>
-  <si>
-    <t>API-ACCOUNT-001</t>
-  </si>
-  <si>
-    <t>API-ACCOUNT-002</t>
-  </si>
-  <si>
-    <t>API-ACCOUNT-003</t>
-  </si>
-  <si>
-    <t>API-ACCOUNT-004</t>
+    <t>Cross-reference of 26 official UI scenarios, 14 official API scenarios, and 4 tester-derived requirements against the current 21-case manual UI test repository</t>
+  </si>
+  <si>
+    <t>Current strength: registration, login, account lifecycle, product discovery, foundational cart behavior, contact-form submission, Test Cases navigation, and subscription coverage are mapped across 21 manual UI cases.
+Batch 3 execution is complete: AE-CONTACT-001, AE-NAV-001, AE-SUB-001, and AE-SUB-002 all passed with evidence recorded in the test repository.
+The manual repository now contains 18 passed cases, 3 failed cases, and 0 cases remaining Not Run.
+Recommended next action: retain the Batch 3 evidence for regression coverage and continue creating cases for the remaining uncovered checkout, catalog, review, recommendation, and scroll-navigation requirements.</t>
+  </si>
+  <si>
+    <t>Coverage is synchronized with the 21-case manual test repository and current defect log. Source scenario wording and exact steps are preserved on the Source Scenarios worksheet.</t>
+  </si>
+  <si>
+    <t>AE-CONTACT-001</t>
+  </si>
+  <si>
+    <t>No immediate gap. Preserve the sanitized AE-CONTACT-001 screenshot and successful return-to-Home observation for regression evidence.</t>
+  </si>
+  <si>
+    <t>AE-NAV-001</t>
+  </si>
+  <si>
+    <t>No immediate gap. Retain AE-NAV-001 evidence showing both successful navigation and the published Test Cases page content.</t>
+  </si>
+  <si>
+    <t>AE-SUB-001</t>
+  </si>
+  <si>
+    <t>No immediate gap. Retain the sanitized AE-SUB-001 screenshot and reuse a controlled email value during regression testing.</t>
+  </si>
+  <si>
+    <t>AE-SUB-002</t>
+  </si>
+  <si>
+    <t>No immediate gap. Retain AE-SUB-002 evidence confirming both the success message and continued cart-page context.</t>
+  </si>
+  <si>
+    <t>The home-page footer displayed the subscription heading, accepted the sanitized email, and showed the expected success message.</t>
+  </si>
+  <si>
+    <t>The cart-page footer displayed the subscription heading, accepted the sanitized email, showed the expected success message, and remained on the cart page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navigation to the Test Cases page completed without error and the published scenarios were visible as expected.</t>
+  </si>
+  <si>
+    <t>Text entry, permitted file upload, the confirmation dialog, success messaging, and return to Home all matched the expected result.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1662,10 +1674,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -2069,12 +2077,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2150,12 +2152,18 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF595959"/>
@@ -2220,151 +2228,6 @@
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2439,20 +2302,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5753-4948-94F8-7D0C6B4BB87D}"/>
+              <c16:uniqueId val="{00000000-9EFE-469B-8359-D8AD469DDEA2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2619,17 +2482,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OfficialApiScenarios" displayName="OfficialApiScenarios" ref="A4:H18" headerRowDxfId="16" dataDxfId="15" totalsRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OfficialApiScenarios" displayName="OfficialApiScenarios" ref="A4:H18">
   <autoFilter ref="A4:H18" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Source API ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Exact Scenario Title" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="API URL" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Request Method" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Exact Request Parameter(s)" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Response Code" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Response Type" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Exact Expected Response" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Source API ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Exact Scenario Title"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="API URL"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Request Method"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Exact Request Parameter(s)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Response Code"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Response Type"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Exact Expected Response"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2794,115 +2657,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1">
-      <c r="A2" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
+      <c r="A2" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="E4" s="42" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="E4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="I4" s="42" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="I4" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="M4" s="42" t="s">
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="M4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="42"/>
+      <c r="N4" s="40"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="43">
+      <c r="A5" s="41">
         <f>COUNTA(RTM!A8:A107)</f>
         <v>44</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="E5" s="43">
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="E5" s="41">
         <f>COUNTIF(RTM!G8:G107,"Fully Covered")</f>
-        <v>27</v>
-      </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="45"/>
-      <c r="I5" s="43">
+        <v>31</v>
+      </c>
+      <c r="F5" s="42"/>
+      <c r="G5" s="43"/>
+      <c r="I5" s="41">
         <f>COUNTIF(RTM!G8:G107,"Partially Covered")</f>
         <v>1</v>
       </c>
-      <c r="J5" s="44"/>
-      <c r="K5" s="45"/>
-      <c r="M5" s="43">
+      <c r="J5" s="42"/>
+      <c r="K5" s="43"/>
+      <c r="M5" s="41">
         <f>COUNTIF(RTM!G8:G107,"Not Covered")</f>
-        <v>16</v>
-      </c>
-      <c r="N5" s="45"/>
+        <v>12</v>
+      </c>
+      <c r="N5" s="43"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="46"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="48"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="48"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="48"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="46"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="46"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="17" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>283</v>
+        <v>7</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>284</v>
+        <v>8</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -2911,11 +2774,11 @@
       </c>
       <c r="B9" s="18">
         <f>COUNTIF(RTM!G8:G107,"Fully Covered")</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Fully Covered")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Fully Covered")</f>
@@ -2953,11 +2816,11 @@
       </c>
       <c r="B11" s="18">
         <f>COUNTIF(RTM!G8:G107,"Not Covered")</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Not Covered")</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D11" s="18">
         <f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Not Covered")</f>
@@ -2970,37 +2833,37 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="37.5">
       <c r="A15" s="20" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B15" s="20">
         <f>COUNTIF(RTM!K8:K107,"Pass")</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C15" s="20">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="37.5">
       <c r="A16" s="20" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B16" s="20">
         <f>COUNTIF(RTM!K8:K107,"Fail")</f>
@@ -3011,124 +2874,124 @@
         <v>3</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25">
       <c r="A17" s="20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" s="20">
         <f>COUNTIF(RTM!K8:K107,"Not Run")</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C17" s="20">
         <f>0</f>
         <v>0</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15.5">
-      <c r="A20" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
+      <c r="A20" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="33"/>
+      <c r="A21" s="29" t="s">
+        <v>422</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="31"/>
     </row>
     <row r="22" spans="1:14" ht="30" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="36"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="30" customHeight="1">
-      <c r="A23" s="34"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="36"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="30" customHeight="1">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="36"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="34"/>
     </row>
     <row r="25" spans="1:14" ht="30" customHeight="1">
-      <c r="A25" s="37"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="39"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3169,344 +3032,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1">
-      <c r="A1" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
+      <c r="A1" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
     </row>
     <row r="2" spans="1:13" ht="24" customHeight="1">
-      <c r="A2" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
+      <c r="A2" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="51"/>
+      <c r="A4" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="49"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="54"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="52"/>
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="57" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="57" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="57" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="57" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="57" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="57" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>424</v>
+      </c>
       <c r="G13" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>75</v>
+        <v>435</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="8" t="s">
-        <v>77</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="57" customHeight="1">
@@ -3514,7 +3379,7 @@
         <v>78</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>79</v>
@@ -3525,1470 +3390,1476 @@
       <c r="E14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>426</v>
+      </c>
       <c r="G14" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="8" t="s">
-        <v>84</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="57" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="57" customHeight="1">
       <c r="A16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L16" s="6"/>
       <c r="M16" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="57" customHeight="1">
       <c r="A17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>428</v>
+      </c>
       <c r="G17" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>102</v>
+        <v>432</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="8" t="s">
-        <v>103</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="57" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>430</v>
+      </c>
       <c r="G18" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>107</v>
+        <v>433</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="8" t="s">
-        <v>108</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="57" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="57" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="57" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="57" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="57" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="57" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="57" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="57" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L26" s="6"/>
       <c r="M26" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="57" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="8" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="57" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L28" s="6"/>
       <c r="M28" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="57" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L29" s="6"/>
       <c r="M29" s="8" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="57" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="57" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="8" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="57" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="57" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>80</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="8" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="57" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="8" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="57" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>205</v>
-      </c>
       <c r="D35" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="8" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="57" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="8" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="57" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>198</v>
+        <v>9</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>2</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="12" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="57" customHeight="1">
       <c r="A38" s="23" t="s">
-        <v>286</v>
+        <v>218</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>418</v>
+        <v>223</v>
       </c>
       <c r="G38" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>414</v>
+        <v>224</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J38" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K38" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L38" s="24"/>
       <c r="M38" s="23" t="s">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="N38" s="26"/>
       <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:15" ht="57" customHeight="1">
       <c r="A39" s="23" t="s">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>295</v>
+        <v>229</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>424</v>
+        <v>230</v>
       </c>
       <c r="G39" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>296</v>
+        <v>231</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J39" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K39" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L39" s="24"/>
       <c r="M39" s="23" t="s">
-        <v>298</v>
+        <v>233</v>
       </c>
       <c r="N39" s="26"/>
       <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:15" ht="57" customHeight="1">
       <c r="A40" s="23" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>301</v>
+        <v>236</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>419</v>
+        <v>238</v>
       </c>
       <c r="G40" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>414</v>
+        <v>224</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J40" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L40" s="24"/>
       <c r="M40" s="23" t="s">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="N40" s="26"/>
       <c r="O40" s="26"/>
     </row>
     <row r="41" spans="1:15" ht="57" customHeight="1">
       <c r="A41" s="23" t="s">
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>301</v>
+        <v>236</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>425</v>
+        <v>243</v>
       </c>
       <c r="G41" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>296</v>
+        <v>231</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J41" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L41" s="24"/>
       <c r="M41" s="23" t="s">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="N41" s="26"/>
       <c r="O41" s="26"/>
     </row>
     <row r="42" spans="1:15" ht="57" customHeight="1">
       <c r="A42" s="23" t="s">
-        <v>308</v>
+        <v>245</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>420</v>
+        <v>249</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="I42" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J42" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K42" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L42" s="24"/>
       <c r="M42" s="23" t="s">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="N42" s="26"/>
       <c r="O42" s="26"/>
     </row>
     <row r="43" spans="1:15" ht="57" customHeight="1">
       <c r="A43" s="23" t="s">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>310</v>
+        <v>247</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>411</v>
+        <v>254</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>421</v>
+        <v>255</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>413</v>
+        <v>256</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J43" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L43" s="24"/>
       <c r="M43" s="27" t="s">
-        <v>415</v>
+        <v>257</v>
       </c>
       <c r="N43" s="26"/>
       <c r="O43" s="26"/>
     </row>
     <row r="44" spans="1:15" ht="57" customHeight="1">
       <c r="A44" s="23" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>319</v>
+        <v>261</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>422</v>
+        <v>262</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>320</v>
+        <v>263</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J44" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K44" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L44" s="24"/>
       <c r="M44" s="23" t="s">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="N44" s="26"/>
       <c r="O44" s="26"/>
     </row>
     <row r="45" spans="1:15" ht="57" customHeight="1">
       <c r="A45" s="23" t="s">
-        <v>322</v>
+        <v>265</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>324</v>
+        <v>267</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>423</v>
+        <v>268</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J45" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K45" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L45" s="24"/>
       <c r="M45" s="23" t="s">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="N45" s="26"/>
       <c r="O45" s="26"/>
     </row>
     <row r="46" spans="1:15" ht="57" customHeight="1">
       <c r="A46" s="23" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>427</v>
+        <v>274</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>412</v>
+        <v>275</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J46" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K46" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L46" s="24"/>
       <c r="M46" s="23" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="N46" s="26"/>
       <c r="O46" s="26"/>
     </row>
     <row r="47" spans="1:15" ht="57" customHeight="1">
       <c r="A47" s="23" t="s">
-        <v>331</v>
+        <v>277</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>426</v>
+        <v>280</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>297</v>
+        <v>232</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K47" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L47" s="24"/>
       <c r="M47" s="23" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="N47" s="26"/>
       <c r="O47" s="26"/>
     </row>
     <row r="48" spans="1:15" ht="57" customHeight="1">
       <c r="A48" s="23" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="B48" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="F48" s="23" t="s">
         <v>287</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F48" s="23" t="s">
-        <v>428</v>
       </c>
       <c r="G48" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J48" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K48" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L48" s="24"/>
       <c r="M48" s="23" t="s">
-        <v>341</v>
+        <v>289</v>
       </c>
       <c r="N48" s="26"/>
       <c r="O48" s="26"/>
     </row>
     <row r="49" spans="1:15" ht="57" customHeight="1">
       <c r="A49" s="23" t="s">
-        <v>342</v>
+        <v>290</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>429</v>
+        <v>293</v>
       </c>
       <c r="G49" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K49" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="23" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="N49" s="26"/>
       <c r="O49" s="26"/>
     </row>
     <row r="50" spans="1:15" ht="57" customHeight="1">
       <c r="A50" s="23" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="G50" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J50" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K50" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L50" s="24"/>
       <c r="M50" s="23" t="s">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="N50" s="26"/>
       <c r="O50" s="26"/>
     </row>
     <row r="51" spans="1:15" ht="57" customHeight="1">
       <c r="A51" s="23" t="s">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>287</v>
+        <v>219</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>431</v>
+        <v>305</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>2</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>291</v>
+        <v>225</v>
       </c>
       <c r="J51" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K51" s="23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L51" s="24"/>
       <c r="M51" s="23" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="N51" s="26"/>
       <c r="O51" s="26"/>
@@ -5019,7 +4890,6 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A4:M5"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="G8:G107">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Fully Covered"/>
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Partially Covered"/>
@@ -5066,117 +4936,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
-      <c r="A1" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="A1" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="A2" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
     </row>
     <row r="4" spans="1:4" ht="38" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>227</v>
+        <v>310</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>228</v>
+        <v>311</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="264.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="C5" s="5">
         <v>18</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>231</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="264.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="C6" s="5">
         <v>10</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="264.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
       <c r="C7" s="5">
         <v>8</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>235</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="264.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>236</v>
+        <v>319</v>
       </c>
       <c r="C8" s="5">
         <v>10</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>237</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="264.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>238</v>
+        <v>321</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>239</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="264.5" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
+        <v>323</v>
       </c>
       <c r="C10" s="5">
         <v>11</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="264.5" customHeight="1">
@@ -5184,279 +5054,279 @@
         <v>79</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>242</v>
+        <v>325</v>
       </c>
       <c r="C11" s="5">
         <v>5</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>243</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="264.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>244</v>
+        <v>327</v>
       </c>
       <c r="C12" s="5">
         <v>9</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>245</v>
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="264.5" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>246</v>
+        <v>329</v>
       </c>
       <c r="C13" s="5">
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>247</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="264.5" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="C14" s="5">
         <v>7</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>249</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="264.5" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>250</v>
+        <v>333</v>
       </c>
       <c r="C15" s="5">
         <v>8</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>251</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="264.5" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>252</v>
+        <v>335</v>
       </c>
       <c r="C16" s="5">
         <v>10</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="264.5" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>254</v>
+        <v>337</v>
       </c>
       <c r="C17" s="5">
         <v>9</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>255</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="264.5" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="C18" s="5">
         <v>20</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>257</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="264.5" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>258</v>
+        <v>341</v>
       </c>
       <c r="C19" s="5">
         <v>18</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="264.5" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="C20" s="5">
         <v>17</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>261</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="264.5" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>262</v>
+        <v>345</v>
       </c>
       <c r="C21" s="5">
         <v>8</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>263</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="264.5" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>264</v>
+        <v>347</v>
       </c>
       <c r="C22" s="5">
         <v>8</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>265</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="264.5" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="C23" s="5">
         <v>8</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>267</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="264.5" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>268</v>
+        <v>351</v>
       </c>
       <c r="C24" s="5">
         <v>12</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="264.5" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="C25" s="5">
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>271</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="264.5" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>272</v>
+        <v>355</v>
       </c>
       <c r="C26" s="5">
         <v>7</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="264.5" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>274</v>
+        <v>357</v>
       </c>
       <c r="C27" s="5">
         <v>15</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="264.5" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>276</v>
+        <v>359</v>
       </c>
       <c r="C28" s="5">
         <v>22</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>277</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="264.5" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="C29" s="5">
         <v>7</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>279</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="264.5" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>280</v>
+        <v>363</v>
       </c>
       <c r="C30" s="10">
         <v>7</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>281</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5487,408 +5357,408 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="53" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="A2" s="54" t="s">
+        <v>366</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1">
       <c r="A4" s="16" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>227</v>
+        <v>310</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="72" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>288</v>
+        <v>220</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5">
         <v>200</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="72" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5">
         <v>405</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="72" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5">
         <v>200</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5">
         <v>405</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="72" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="F9" s="5">
         <v>200</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="72" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>380</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>371</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5">
         <v>400</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F11" s="5">
         <v>200</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="72" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F12" s="5">
         <v>400</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="72" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5">
         <v>405</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="72" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>332</v>
+        <v>278</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F14" s="5">
         <v>404</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="72" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="F15" s="5">
         <v>201</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="72" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>343</v>
+        <v>291</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>393</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="F16" s="5">
         <v>200</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="72" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="F17" s="5">
         <v>200</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="J17" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="72" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F18" s="5">
         <v>200</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R418e862b16844f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R6de2d55eaec045a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R3e480d97a2424b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="R745b47c2b10c46e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdf42f5a42e8b4d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rc58a075d306d4760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rec1381cd85f94dd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rddb34e481cee40c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1150,60 +1150,15 @@
         <x:color indexed="64"/>
       </x:top>
     </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1577,7 +1532,7 @@
     <x:cellStyle name="Hyperlink" xfId="1"/>
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="6">
+  <x:dxfs count="86">
     <x:dxf>
       <x:font>
         <x:color rgb="FF595959"/>
@@ -1640,6 +1595,856 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C5700"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF595959"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE7E6E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF7F7F7F"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1822,7 +2627,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf3c835c84e35479e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c7d0dc3d8234d3f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2399,7 +3204,7 @@
     <x:mergeCell ref="M5:N6"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3dc9e12634949ab"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re99bb098e4dd4f7d"/>
 </x:worksheet>
 </file>
 
@@ -2593,7 +3398,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N8" s="107" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O8" s="116" t="str">
         <x:v>Pass</x:v>
@@ -2650,7 +3455,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N9" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O9" s="117" t="str">
         <x:v>Pass</x:v>
@@ -2706,7 +3511,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N10" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O10" s="117" t="str">
         <x:v>Pass</x:v>
@@ -2761,7 +3566,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N11" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="O11" s="118" t="str">
         <x:v>Fail</x:v>
@@ -2818,7 +3623,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N12" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O12" s="117" t="str">
         <x:v>Pass</x:v>
@@ -2872,7 +3677,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N13" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O13" s="117" t="str">
         <x:v>Pass</x:v>
@@ -2926,7 +3731,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N14" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O14" s="117" t="str">
         <x:v>Pass</x:v>
@@ -2980,7 +3785,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N15" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O15" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3034,7 +3839,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N16" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O16" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3088,7 +3893,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N17" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O17" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3142,7 +3947,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N18" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O18" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3196,7 +4001,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N19" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="O19" s="118" t="str">
         <x:v>Fail</x:v>
@@ -3252,7 +4057,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N20" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O20" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3306,7 +4111,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N21" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O21" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3356,7 +4161,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N22" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O22" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3406,7 +4211,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N23" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O23" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3458,7 +4263,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N24" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O24" s="117" t="str">
         <x:v>Pass</x:v>
@@ -3510,7 +4315,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N25" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O25" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3560,7 +4365,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N26" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O26" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3610,7 +4415,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N27" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O27" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3660,7 +4465,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N28" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O28" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3710,7 +4515,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N29" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O29" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3760,7 +4565,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N30" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O30" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3810,7 +4615,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N31" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O31" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3860,7 +4665,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N32" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O32" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3910,7 +4715,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N33" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O33" s="120" t="str">
         <x:v>Not Run</x:v>
@@ -3962,7 +4767,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N34" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O34" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4016,7 +4821,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N35" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O35" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4070,7 +4875,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N36" s="109" t="str">
-        <x:v>Implemented; see automation evidence</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O36" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4124,7 +4929,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N37" s="109" t="str">
-        <x:v>Not automated</x:v>
+        <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O37" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4175,7 +4980,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M38" s="109" t="str">
-        <x:v>Historical: Error (script/no response); corrected rerun pending</x:v>
+        <x:v>Error</x:v>
       </x:c>
       <x:c r="N38" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4191,7 +4996,9 @@
       <x:c r="Q38" s="93"/>
       <x:c r="R38" s="94" t="str">
         <x:v>Current verification passed: 200 | products list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: script error / no response.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="96" customHeight="1">
@@ -4232,7 +5039,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M39" s="109" t="str">
-        <x:v>Historical: Not evaluated (no tests); corrected rerun pending</x:v>
+        <x:v>Not Run</x:v>
       </x:c>
       <x:c r="N39" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4248,7 +5055,9 @@
       <x:c r="Q39" s="93"/>
       <x:c r="R39" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: request executed without automated tests.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="96" customHeight="1">
@@ -4289,7 +5098,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M40" s="109" t="str">
-        <x:v>Historical: Pass; corrected rerun pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N40" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4305,7 +5114,9 @@
       <x:c r="Q40" s="93"/>
       <x:c r="R40" s="94" t="str">
         <x:v>Current verification passed: 200 | brands list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertions passed.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="96" customHeight="1">
@@ -4346,7 +5157,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M41" s="109" t="str">
-        <x:v>Historical: Error (script/no response); corrected rerun pending</x:v>
+        <x:v>Error</x:v>
       </x:c>
       <x:c r="N41" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4362,7 +5173,9 @@
       <x:c r="Q41" s="93"/>
       <x:c r="R41" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: script error / no response.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="96" customHeight="1">
@@ -4403,7 +5216,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M42" s="109" t="str">
-        <x:v>Historical: Pass; corrected rerun pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N42" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4419,7 +5232,9 @@
       <x:c r="Q42" s="93"/>
       <x:c r="R42" s="94" t="str">
         <x:v>Current verification passed: 200 | searched products list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertions passed.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="96" customHeight="1">
@@ -4461,7 +5276,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M43" s="109" t="str">
-        <x:v>Historical: Inconclusive (not visible); corrected rerun pending</x:v>
+        <x:v>Inconclusive</x:v>
       </x:c>
       <x:c r="N43" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4477,7 +5292,9 @@
       <x:c r="Q43" s="93"/>
       <x:c r="R43" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 400 | missing search_product message returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: result was not visible in the supplied runner screenshots.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="96" customHeight="1">
@@ -4518,7 +5335,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M44" s="109" t="str">
-        <x:v>Historical: Fail (stale credentials); corrected rerun pending</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="N44" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4534,7 +5351,9 @@
       <x:c r="Q44" s="93"/>
       <x:c r="R44" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 200 | User exists!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: valid-login scenario failed because the supplied credentials were stale or invalid.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="96" customHeight="1">
@@ -4575,7 +5394,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M45" s="109" t="str">
-        <x:v>Historical: Fail (transport assertion); corrected rerun pending</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="N45" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4591,7 +5410,9 @@
       <x:c r="Q45" s="93"/>
       <x:c r="R45" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 400 | missing credential message returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 400.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="96" customHeight="1">
@@ -4632,7 +5453,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M46" s="109" t="str">
-        <x:v>Historical: Fail (transport assertion); corrected rerun pending</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="N46" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4648,7 +5469,9 @@
       <x:c r="Q46" s="93"/>
       <x:c r="R46" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 405.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="96" customHeight="1">
@@ -4689,7 +5512,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M47" s="109" t="str">
-        <x:v>Historical: Fail (transport assertion); corrected rerun pending</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="N47" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4705,7 +5528,9 @@
       <x:c r="Q47" s="93"/>
       <x:c r="R47" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 404 | User not found!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 404.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="96" customHeight="1">
@@ -4746,7 +5571,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M48" s="109" t="str">
-        <x:v>Historical: Fail (transport assertion); corrected rerun pending</x:v>
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="N48" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4762,7 +5587,9 @@
       <x:c r="Q48" s="93"/>
       <x:c r="R48" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 201 | User created!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 201.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="96" customHeight="1">
@@ -4803,7 +5630,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M49" s="109" t="str">
-        <x:v>Historical: Pass; corrected rerun pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N49" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4819,7 +5646,9 @@
       <x:c r="Q49" s="93"/>
       <x:c r="R49" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 200 | Account deleted!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertions passed.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="96" customHeight="1">
@@ -4860,7 +5689,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M50" s="109" t="str">
-        <x:v>Historical: Pass; corrected rerun pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N50" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4876,7 +5705,9 @@
       <x:c r="Q50" s="93"/>
       <x:c r="R50" s="94" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 200 | User updated!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertions passed.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="96" customHeight="1">
@@ -4917,7 +5748,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M51" s="111" t="str">
-        <x:v>Historical: Pass; corrected rerun pending</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N51" s="121" t="str">
         <x:v>Pass</x:v>
@@ -4933,7 +5764,9 @@
       <x:c r="Q51" s="97"/>
       <x:c r="R51" s="98" t="str">
         <x:v>Current verification passed: 200 transport | responseCode 200 | user detail returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.</x:v>
+Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
+Historical Postman detail: assertions passed.
+Corrected native Postman rerun: pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="57" customHeight="1">
@@ -4972,7 +5805,111 @@
     <x:cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Fail"/>
     <x:cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Not Run"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="5">
+  <x:conditionalFormatting sqref="L8:L107">
+    <x:cfRule type="expression" dxfId="54" priority="47">
+      <x:formula>L8="Pass"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="55" priority="48">
+      <x:formula>L8="Fail"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="56" priority="49">
+      <x:formula>L8="Error"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="57" priority="50">
+      <x:formula>L8="Blocked"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="58" priority="51">
+      <x:formula>L8="Inconclusive"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="59" priority="52">
+      <x:formula>L8="Not Run"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="60" priority="53">
+      <x:formula>L8="Not Automated"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="61" priority="54">
+      <x:formula>L8="N/A"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="M8:M107">
+    <x:cfRule type="expression" dxfId="62" priority="55">
+      <x:formula>M8="Pass"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="63" priority="56">
+      <x:formula>M8="Fail"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="64" priority="57">
+      <x:formula>M8="Error"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="65" priority="58">
+      <x:formula>M8="Blocked"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="66" priority="59">
+      <x:formula>M8="Inconclusive"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="67" priority="60">
+      <x:formula>M8="Not Run"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="68" priority="61">
+      <x:formula>M8="Not Automated"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="69" priority="62">
+      <x:formula>M8="N/A"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="N8:N107">
+    <x:cfRule type="expression" dxfId="70" priority="63">
+      <x:formula>N8="Pass"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="71" priority="64">
+      <x:formula>N8="Fail"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="72" priority="65">
+      <x:formula>N8="Error"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="73" priority="66">
+      <x:formula>N8="Blocked"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="74" priority="67">
+      <x:formula>N8="Inconclusive"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="75" priority="68">
+      <x:formula>N8="Not Run"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="76" priority="69">
+      <x:formula>N8="Not Automated"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="77" priority="70">
+      <x:formula>N8="N/A"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="O8:O107">
+    <x:cfRule type="expression" dxfId="78" priority="71">
+      <x:formula>O8="Pass"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="79" priority="72">
+      <x:formula>O8="Fail"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="80" priority="73">
+      <x:formula>O8="Error"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="81" priority="74">
+      <x:formula>O8="Blocked"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="82" priority="75">
+      <x:formula>O8="Inconclusive"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="83" priority="76">
+      <x:formula>O8="Not Run"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="84" priority="77">
+      <x:formula>O8="Not Automated"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="85" priority="78">
+      <x:formula>O8="N/A"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="G8:G107">
       <x:formula1>"Fully Covered,Partially Covered,Not Covered"</x:formula1>
     </x:dataValidation>
@@ -4980,7 +5917,7 @@
       <x:formula1>"Critical,High,Medium,Low"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="K8:K107">
-      <x:formula1>"Pass,Fail,Blocked,Not Run"</x:formula1>
+      <x:formula1>"QA"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="B8:B107">
       <x:formula1>"Site Scenario,Site API Scenario,Tester-Derived"</x:formula1>
@@ -4988,10 +5925,22 @@
     <x:dataValidation type="list" sqref="I8:I107">
       <x:formula1>"Functional — Positive,Functional — Negative,Security — Negative,End-to-End — Positive,API — Positive,API — Negative"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="L8:L107">
+      <x:formula1>"Pass,Fail,Blocked,Not Run,N/A"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M8:M107">
+      <x:formula1>"Pass,Fail,Error,Inconclusive,Not Run,N/A"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N8:N107">
+      <x:formula1>"Pass,Fail,Error,Blocked,Not Run,Not Automated,N/A"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O8:O107">
+      <x:formula1>"Pass,Fail,Blocked,Inconclusive,Not Run"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c53bf124d784b72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc1097e19eab4b4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5407,7 +6356,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aab54e4963e4b13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc20094945a241ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5843,7 +6792,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddb8845b73984fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re844ae0a5db044fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdf42f5a42e8b4d7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rc58a075d306d4760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rec1381cd85f94dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rddb34e481cee40c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R0439ba4267a34574"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rbd0e9c0662c0433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R5a9c1fd025cc4645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rcb813b7245a64355"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2114,7 +2114,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -2125,7 +2125,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2136,7 +2136,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2147,7 +2147,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2158,7 +2158,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEB9C"/>
         </x:patternFill>
       </x:fill>
@@ -2168,7 +2168,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2178,7 +2178,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2188,7 +2188,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -2199,7 +2199,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -2210,7 +2210,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2221,7 +2221,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2232,7 +2232,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2243,7 +2243,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEB9C"/>
         </x:patternFill>
       </x:fill>
@@ -2253,7 +2253,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2263,7 +2263,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2273,7 +2273,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -2284,7 +2284,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -2295,7 +2295,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2306,7 +2306,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2317,7 +2317,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2328,7 +2328,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEB9C"/>
         </x:patternFill>
       </x:fill>
@@ -2338,7 +2338,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2348,7 +2348,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2358,7 +2358,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -2369,7 +2369,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFC6EFCE"/>
         </x:patternFill>
       </x:fill>
@@ -2380,7 +2380,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2391,7 +2391,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -2402,7 +2402,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2413,7 +2413,7 @@
         <x:color rgb="FF9C6500"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEB9C"/>
         </x:patternFill>
       </x:fill>
@@ -2423,7 +2423,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2433,7 +2433,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -2443,7 +2443,7 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -2627,7 +2627,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c7d0dc3d8234d3f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rda9167370d9a4583"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3105,10 +3105,10 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Current strength: all 14 official API requirements are fully mapped and independently verified by Playwright. Coverage status is kept separate from runner outcome.
-API execution history: the 2026-08-01 Postman baseline recorded 37 assertions, 28 passes, 9 assertion failures, and 2 runner errors. Those results remain historical and are shown separately from the current Playwright result.
-Current API status: Playwright passed 14 of 14 scenarios; the corrected native Postman collection rerun is still pending. BUG-API-001 and BUG-API-002 remain rejected after reconciliation/retest.
-Interpretation rule: a disagreement between tools is an execution discrepancy requiring reconciliation, not partial coverage unless required behavior or assertions are actually missing.</x:v>
+        <x:v>Current strength: all 14 official API requirements are fully mapped and independently verified by both Postman and Playwright. Coverage status remains separate from execution outcome.
+Fresh Postman verification: the corrected 14-request collection ran on 2026-08-09 with one iteration, 42 of 42 assertions passed, zero failures, and zero errors.
+Historical baseline: the 2026-08-01 Postman run recorded 37 assertions, 28 passes, 9 assertion failures, and 2 runner errors. It remains preserved separately to show the original test-script, credential, and request-configuration reconciliation.
+Current API status: Postman 14/14 Pass; Playwright 14/14 Pass; confirmed open API defects 0. BUG-API-001 and BUG-API-002 remain rejected and auditable.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3204,7 +3204,7 @@
     <x:mergeCell ref="M5:N6"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re99bb098e4dd4f7d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35491727d0644fec"/>
 </x:worksheet>
 </file>
 
@@ -4965,7 +4965,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H38" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I38" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -4980,7 +4980,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M38" s="109" t="str">
-        <x:v>Error</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N38" s="117" t="str">
         <x:v>Pass</x:v>
@@ -4989,16 +4989,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P38" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-PRODUCT-001.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-PRODUCT-001.png
 ..\Automation\Execution Evidence\API-PRODUCT-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q38" s="93"/>
       <x:c r="R38" s="94" t="str">
-        <x:v>Current verification passed: 200 | products list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: script error / no response.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 | products list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="96" customHeight="1">
@@ -5024,7 +5023,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H39" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I39" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5039,7 +5038,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M39" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N39" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5048,16 +5047,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P39" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-PRODUCT-002.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-PRODUCT-002.png
 ..\Automation\Execution Evidence\API-PRODUCT-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q39" s="93"/>
       <x:c r="R39" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: request executed without automated tests.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="96" customHeight="1">
@@ -5083,7 +5081,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H40" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I40" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5107,16 +5105,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P40" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-BRAND-001.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-BRAND-001.png
 ..\Automation\Execution Evidence\API-BRAND-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q40" s="93"/>
       <x:c r="R40" s="94" t="str">
-        <x:v>Current verification passed: 200 | brands list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertions passed.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 | brands list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="96" customHeight="1">
@@ -5142,7 +5139,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H41" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I41" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5157,7 +5154,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M41" s="109" t="str">
-        <x:v>Error</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N41" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5166,16 +5163,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P41" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-BRAND-002.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-BRAND-002.png
 ..\Automation\Execution Evidence\API-BRAND-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q41" s="93"/>
       <x:c r="R41" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: script error / no response.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="96" customHeight="1">
@@ -5201,7 +5197,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H42" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I42" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5225,16 +5221,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P42" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-SEARCH-001.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-SEARCH-001.png
 ..\Automation\Execution Evidence\API-SEARCH-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q42" s="93"/>
       <x:c r="R42" s="94" t="str">
-        <x:v>Current verification passed: 200 | searched products list returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertions passed.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 | searched products list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="96" customHeight="1">
@@ -5261,7 +5256,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H43" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I43" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5276,7 +5271,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M43" s="109" t="str">
-        <x:v>Inconclusive</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N43" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5285,16 +5280,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P43" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-SEARCH-002.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-SEARCH-002.png
 ..\Automation\Execution Evidence\API-SEARCH-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q43" s="93"/>
       <x:c r="R43" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 400 | missing search_product message returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: result was not visible in the supplied runner screenshots.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 400 | missing search_product message returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="96" customHeight="1">
@@ -5320,7 +5314,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H44" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I44" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5335,7 +5329,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M44" s="109" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N44" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5344,16 +5338,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P44" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-AUTH-001.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-AUTH-001.png
 ..\Automation\Execution Evidence\API-AUTH-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q44" s="93"/>
       <x:c r="R44" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 200 | User exists!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: valid-login scenario failed because the supplied credentials were stale or invalid.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 200 | User exists!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="96" customHeight="1">
@@ -5379,7 +5372,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H45" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I45" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5394,7 +5387,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M45" s="109" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N45" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5403,16 +5396,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P45" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-AUTH-002.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-AUTH-002.png
 ..\Automation\Execution Evidence\API-AUTH-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q45" s="93"/>
       <x:c r="R45" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 400 | missing credential message returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 400.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 400 | missing credential message returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="96" customHeight="1">
@@ -5438,7 +5430,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H46" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I46" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5453,7 +5445,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M46" s="109" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N46" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5462,16 +5454,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P46" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-AUTH-003.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-AUTH-003.png
 ..\Automation\Execution Evidence\API-AUTH-003.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q46" s="93"/>
       <x:c r="R46" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 405 | method not supported. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 405.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="96" customHeight="1">
@@ -5497,7 +5488,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H47" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I47" s="109" t="str">
         <x:v>API — Negative</x:v>
@@ -5512,7 +5503,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M47" s="109" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N47" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5521,16 +5512,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P47" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-AUTH-004.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-AUTH-004.png
 ..\Automation\Execution Evidence\API-AUTH-004.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q47" s="93"/>
       <x:c r="R47" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 404 | User not found!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 404.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 404 | User not found!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="96" customHeight="1">
@@ -5556,7 +5546,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H48" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I48" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5571,7 +5561,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="M48" s="109" t="str">
-        <x:v>Fail</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="N48" s="117" t="str">
         <x:v>Pass</x:v>
@@ -5580,16 +5570,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P48" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-ACCOUNT-001.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-ACCOUNT-001.png
 ..\Automation\Execution Evidence\API-ACCOUNT-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q48" s="93"/>
       <x:c r="R48" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 201 | User created!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertion incorrectly compared HTTP transport status with JSON responseCode 201.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 201 | User created!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="96" customHeight="1">
@@ -5615,7 +5604,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H49" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I49" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5639,16 +5628,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P49" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-ACCOUNT-002.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-ACCOUNT-002.png
 ..\Automation\Execution Evidence\API-ACCOUNT-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q49" s="93"/>
       <x:c r="R49" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 200 | Account deleted!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertions passed.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 200 | Account deleted!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="96" customHeight="1">
@@ -5674,7 +5662,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H50" s="93" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I50" s="109" t="str">
         <x:v>API — Positive</x:v>
@@ -5698,16 +5686,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P50" s="93" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-ACCOUNT-003.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-ACCOUNT-003.png
 ..\Automation\Execution Evidence\API-ACCOUNT-003.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q50" s="93"/>
       <x:c r="R50" s="94" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 200 | User updated!. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertions passed.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 200 | User updated!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="96" customHeight="1">
@@ -5733,7 +5720,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H51" s="97" t="str">
-        <x:v>Current Playwright execution passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions. The corrected Postman collection is ready for a fresh native runner execution.</x:v>
+        <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
       <x:c r="I51" s="111" t="str">
         <x:v>API — Positive</x:v>
@@ -5757,16 +5744,15 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P51" s="97" t="str">
-        <x:v>..\API Testing\Execution Results\Screenshots\API-ACCOUNT-004.png
+        <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
+..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
+..\API Testing\Execution Results\Screenshots\API-ACCOUNT-004.png
 ..\Automation\Execution Evidence\API-ACCOUNT-004.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
       <x:c r="Q51" s="97"/>
       <x:c r="R51" s="98" t="str">
-        <x:v>Current verification passed: 200 transport | responseCode 200 | user detail returned. Historical Postman baseline is retained separately for auditability.
-Reconciliation classification: historical tool/assertion discrepancy, not partial requirement coverage.
-Historical Postman detail: assertions passed.
-Corrected native Postman rerun: pending.</x:v>
+        <x:v>200 transport | responseCode 200 | user detail returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="57" customHeight="1">
@@ -5940,7 +5926,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc1097e19eab4b4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a8c95dde81b4b9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6356,7 +6342,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc20094945a241ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b945217db314ad5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6792,7 +6778,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re844ae0a5db044fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c3d434b098435a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R0439ba4267a34574"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rbd0e9c0662c0433f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R5a9c1fd025cc4645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rcb813b7245a64355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R1f8f25853fd34c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rf8c3609043084288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R9dd2c21f25964194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="R6cac6f94c04c4059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R6efc6d26ea694578"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,12 +14,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">Automation Exercise | Requirements Traceability Matrix</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cross-reference of 26 official UI scenarios, 14 official API scenarios, and 4 tester-derived requirements against the current 21-case manual UI test repository</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Total Requirements</x:t>
   </x:si>
   <x:si>
@@ -77,9 +72,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Requirements Traceability Matrix</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coverage is synchronized with the 21-case manual test repository and current defect log. Source scenario wording and exact steps are preserved on the Source Scenarios worksheet.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Coverage rule: Fully Covered means every material behavior in the requirement is mapped to one or more existing test cases. Partially Covered means some, but not all material behavior is mapped. Not Covered means no existing case verifies the requirement.</x:t>
@@ -804,7 +796,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="13">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -875,8 +867,20 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0F172A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -961,6 +965,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF173B63"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0C4A6E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE0F2FE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0369A1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1164,7 +1193,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="122">
+  <x:cellXfs count="140">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1525,6 +1554,48 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="14" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1532,7 +1603,7 @@
     <x:cellStyle name="Hyperlink" xfId="1"/>
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="86">
+  <x:dxfs count="90">
     <x:dxf>
       <x:font>
         <x:color rgb="FF595959"/>
@@ -2448,6 +2519,46 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -2627,7 +2738,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rda9167370d9a4583"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R83b4f8ed2e614914"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2688,6 +2799,28 @@
     <x:tableColumn id="6" name="Response Code"/>
     <x:tableColumn id="7" name="Response Type"/>
     <x:tableColumn id="8" name="Exact Expected Response"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="JiraSyncTable" displayName="JiraSyncTable" ref="A4:N122" headerRowCount="1">
+  <x:tableColumns count="14">
+    <x:tableColumn id="1" name="Jira Key"/>
+    <x:tableColumn id="2" name="Work Type"/>
+    <x:tableColumn id="3" name="Summary"/>
+    <x:tableColumn id="4" name="Workflow Status"/>
+    <x:tableColumn id="5" name="Priority"/>
+    <x:tableColumn id="6" name="Assignee"/>
+    <x:tableColumn id="7" name="Requirement ID"/>
+    <x:tableColumn id="8" name="Test Case ID"/>
+    <x:tableColumn id="9" name="Defect ID"/>
+    <x:tableColumn id="10" name="Execution Status"/>
+    <x:tableColumn id="11" name="Automation Status"/>
+    <x:tableColumn id="12" name="Testing Link(s)"/>
+    <x:tableColumn id="13" name="Parent Key"/>
+    <x:tableColumn id="14" name="Jira Updated"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -2848,85 +2981,85 @@
     <x:col min="6" max="14" width="13" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="36" customHeight="1">
-      <x:c r="A1" s="38" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="38"/>
-      <x:c r="C1" s="38"/>
-      <x:c r="D1" s="38"/>
-      <x:c r="E1" s="38"/>
-      <x:c r="F1" s="38"/>
-      <x:c r="G1" s="38"/>
-      <x:c r="H1" s="38"/>
-      <x:c r="I1" s="38"/>
-      <x:c r="J1" s="38"/>
-      <x:c r="K1" s="38"/>
-      <x:c r="L1" s="38"/>
-      <x:c r="M1" s="38"/>
+    <x:row r="1" ht="25.5" customHeight="1">
+      <x:c r="A1" s="122" t="str">
+        <x:v>Automation Exercise | Requirements Traceability Matrix</x:v>
+      </x:c>
+      <x:c r="B1" s="122"/>
+      <x:c r="C1" s="122"/>
+      <x:c r="D1" s="122"/>
+      <x:c r="E1" s="122"/>
+      <x:c r="F1" s="122"/>
+      <x:c r="G1" s="122"/>
+      <x:c r="H1" s="122"/>
+      <x:c r="I1" s="122"/>
+      <x:c r="J1" s="122"/>
+      <x:c r="K1" s="122"/>
+      <x:c r="L1" s="122"/>
+      <x:c r="M1" s="122"/>
       <x:c r="N1" s="38"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="39" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="39"/>
-      <x:c r="C2" s="39"/>
-      <x:c r="D2" s="39"/>
-      <x:c r="E2" s="39"/>
-      <x:c r="F2" s="39"/>
-      <x:c r="G2" s="39"/>
-      <x:c r="H2" s="39"/>
-      <x:c r="I2" s="39"/>
-      <x:c r="J2" s="39"/>
-      <x:c r="K2" s="39"/>
-      <x:c r="L2" s="39"/>
-      <x:c r="M2" s="39"/>
+    <x:row r="2" ht="22.5" customHeight="1">
+      <x:c r="A2" s="125" t="str">
+        <x:v>Traceability across 44 requirements and 48 Jira Test Cases, with coverage design kept separate from execution outcome</x:v>
+      </x:c>
+      <x:c r="B2" s="125"/>
+      <x:c r="C2" s="125"/>
+      <x:c r="D2" s="125"/>
+      <x:c r="E2" s="125"/>
+      <x:c r="F2" s="125"/>
+      <x:c r="G2" s="125"/>
+      <x:c r="H2" s="125"/>
+      <x:c r="I2" s="125"/>
+      <x:c r="J2" s="125"/>
+      <x:c r="K2" s="125"/>
+      <x:c r="L2" s="125"/>
+      <x:c r="M2" s="125"/>
       <x:c r="N2" s="39"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="40" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="40"/>
       <x:c r="C4" s="40"/>
       <x:c r="E4" s="40" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="40"/>
       <x:c r="G4" s="40"/>
       <x:c r="I4" s="40" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J4" s="40"/>
       <x:c r="K4" s="40"/>
       <x:c r="M4" s="40" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N4" s="40"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="41" t="n">
-        <x:f>COUNTA(RTM!A8:A107)</x:f>
+        <x:f>COUNTA(RTM!$A$8:$A$51)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="42"/>
       <x:c r="C5" s="43"/>
       <x:c r="E5" s="41" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Fully Covered")</x:f>
-        <x:v>31</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,"Fully Covered")</x:f>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F5" s="42"/>
       <x:c r="G5" s="43"/>
       <x:c r="I5" s="41" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Partially Covered")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,"Partially Covered")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J5" s="42"/>
       <x:c r="K5" s="43"/>
       <x:c r="M5" s="41" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Not Covered")</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,"Not Covered")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="43"/>
     </x:row>
@@ -2945,120 +3078,120 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="s">
+      <x:c r="D8" s="17" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C8" s="17" t="s">
+      <x:c r="E8" s="17" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E8" s="17" t="s">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Fully Covered")</x:f>
-        <x:v>31</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,$A9)</x:f>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Fully Covered")</x:f>
-        <x:v>13</x:v>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A9,RTM!$B$8:$B$51,"Site Scenario")</x:f>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Fully Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A9,RTM!$B$8:$B$51,"Site API Scenario")</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Fully Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A9,RTM!$B$8:$B$51,"Tester-Derived")</x:f>
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="18" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="18" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Partially Covered")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,$A10)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Partially Covered")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A10,RTM!$B$8:$B$51,"Site Scenario")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Partially Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A10,RTM!$B$8:$B$51,"Site API Scenario")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Partially Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A10,RTM!$B$8:$B$51,"Tester-Derived")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="18" t="n">
-        <x:f>COUNTIF(RTM!G8:G107,"Not Covered")</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(RTM!$G$8:$G$51,$A11)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site Scenario",RTM!G8:G107,"Not Covered")</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A11,RTM!$B$8:$B$51,"Site Scenario")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Site API Scenario",RTM!G8:G107,"Not Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A11,RTM!$B$8:$B$51,"Site API Scenario")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="18" t="n">
-        <x:f>COUNTIFS(RTM!B8:B107,"Tester-Derived",RTM!G8:G107,"Not Covered")</x:f>
+        <x:f>COUNTIFS(RTM!$G$8:$G$51,$A11,RTM!$B$8:$B$51,"Tester-Derived")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="19" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="19" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="37.5">
       <x:c r="A15" s="20" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:f>COUNTIF(RTM!O8:O107,"Pass")</x:f>
-        <x:v>30</x:v>
+        <x:f>COUNTIF(RTM!$O$8:$O$51,$A15)</x:f>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="20" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5">
       <x:c r="A16" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="20" t="n">
-        <x:f>COUNTIF(RTM!O8:O107,"Fail")</x:f>
+        <x:f>COUNTIF(RTM!$O$8:$O$51,$A16)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="20" t="n">
@@ -3066,28 +3199,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D16" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25">
       <x:c r="A17" s="20" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:f>COUNTIF(RTM!O8:O107,"Not Run")</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(RTM!$O$8:$O$51,$A17)</x:f>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15.5">
       <x:c r="A20" s="28" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="28"/>
       <x:c r="C20" s="28"/>
@@ -3105,10 +3238,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Current strength: all 14 official API requirements are fully mapped and independently verified by both Postman and Playwright. Coverage status remains separate from execution outcome.
-Fresh Postman verification: the corrected 14-request collection ran on 2026-08-09 with one iteration, 42 of 42 assertions passed, zero failures, and zero errors.
-Historical baseline: the 2026-08-01 Postman run recorded 37 assertions, 28 passes, 9 assertion failures, and 2 runner errors. It remains preserved separately to show the original test-script, credential, and request-configuration reconciliation.
-Current API status: Postman 14/14 Pass; Playwright 14/14 Pass; confirmed open API defects 0. BUG-API-001 and BUG-API-002 remain rejected and auditable.</x:v>
+        <x:v>Coverage design is now complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. Thirteen newly linked manual cases remain Not Run; they must not be presented as passed until execution evidence is captured. Current reconciled requirement execution: 29 Pass, 2 Fail, and 13 Not Run. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3192,8 +3322,6 @@
   <x:mergeCells>
     <x:mergeCell ref="A20:N20"/>
     <x:mergeCell ref="A21:N25"/>
-    <x:mergeCell ref="A1:N1"/>
-    <x:mergeCell ref="A2:N2"/>
     <x:mergeCell ref="A4:C4"/>
     <x:mergeCell ref="A5:C6"/>
     <x:mergeCell ref="E4:G4"/>
@@ -3202,9 +3330,11 @@
     <x:mergeCell ref="I5:K6"/>
     <x:mergeCell ref="M4:N4"/>
     <x:mergeCell ref="M5:N6"/>
+    <x:mergeCell ref="A1:M1"/>
+    <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35491727d0644fec"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d4bd5a162f24728"/>
 </x:worksheet>
 </file>
 
@@ -3235,7 +3365,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="38" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -3251,8 +3381,8 @@
       <x:c r="M1" s="38"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="39" t="s">
-        <x:v>22</x:v>
+      <x:c r="A2" s="39" t="str">
+        <x:v>Coverage synchronized with 48 Jira Test Cases: 35 executed UI/API cases plus 13 linked manual cases awaiting execution.</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -3266,10 +3396,15 @@
       <x:c r="K2" s="39"/>
       <x:c r="L2" s="39"/>
       <x:c r="M2" s="39"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="47" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="48"/>
       <x:c r="C4" s="48"/>
@@ -3374,13 +3509,14 @@
       <x:c r="F8" s="107" t="str">
         <x:v>AE-SIGNUP-001
 AE-SIGNUP-002
-AE-ACCOUNT-001</x:v>
+AE-ACCOUNT-001
+AE-SIGNUP-006</x:v>
       </x:c>
       <x:c r="G8" s="115" t="str">
-        <x:v>Partially Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H8" s="89" t="str">
-        <x:v>Registration and deletion are covered, but the complete continuous workflow and optional newsletter/partner selections are not documented.</x:v>
+        <x:v>Test design is complete. Jira AEQA-106 (AE-SIGNUP-006) is linked to AEQA-1; execution remains pending.</x:v>
       </x:c>
       <x:c r="I8" s="107" t="str">
         <x:v>Functional — Positive</x:v>
@@ -3392,7 +3528,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L8" s="107" t="str">
-        <x:v>Pass</x:v>
+        <x:v>Not Run</x:v>
       </x:c>
       <x:c r="M8" s="107" t="str">
         <x:v>N/A</x:v>
@@ -3401,7 +3537,7 @@
         <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O8" s="116" t="str">
-        <x:v>Pass</x:v>
+        <x:v>Not Run</x:v>
       </x:c>
       <x:c r="P8" s="89" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-001.png
@@ -3410,7 +3546,7 @@
       </x:c>
       <x:c r="Q8" s="89"/>
       <x:c r="R8" s="90" t="str">
-        <x:v>Add an end-to-end registration case or explicitly document why the workflow is decomposed. Verify newsletter and partner selections if they are in scope.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-SIGNUP-006 (AEQA-106) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -4088,12 +4224,14 @@
       <x:c r="E21" s="109" t="str">
         <x:v>Place Order: Register while Checkout</x:v>
       </x:c>
-      <x:c r="F21" s="109"/>
+      <x:c r="F21" s="109" t="str">
+        <x:v>AE-ORDER-001</x:v>
+      </x:c>
       <x:c r="G21" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H21" s="93" t="str">
-        <x:v>No checkout registration-during-order workflow exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-107 (AE-ORDER-001) is linked to AEQA-14; execution remains pending.</x:v>
       </x:c>
       <x:c r="I21" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4119,7 +4257,7 @@
       <x:c r="P21" s="93"/>
       <x:c r="Q21" s="93"/>
       <x:c r="R21" s="94" t="str">
-        <x:v>Create an end-to-end checkout case for registration during checkout.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-ORDER-001 (AEQA-107) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -4138,12 +4276,14 @@
       <x:c r="E22" s="109" t="str">
         <x:v>Place Order: Register before Checkout</x:v>
       </x:c>
-      <x:c r="F22" s="109"/>
+      <x:c r="F22" s="109" t="str">
+        <x:v>AE-ORDER-002</x:v>
+      </x:c>
       <x:c r="G22" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H22" s="93" t="str">
-        <x:v>No register-before-checkout workflow exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-108 (AE-ORDER-002) is linked to AEQA-15; execution remains pending.</x:v>
       </x:c>
       <x:c r="I22" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4169,7 +4309,7 @@
       <x:c r="P22" s="93"/>
       <x:c r="Q22" s="93"/>
       <x:c r="R22" s="94" t="str">
-        <x:v>Create an end-to-end checkout case for registration before checkout.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-ORDER-002 (AEQA-108) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -4188,12 +4328,14 @@
       <x:c r="E23" s="109" t="str">
         <x:v>Place Order: Login before Checkout</x:v>
       </x:c>
-      <x:c r="F23" s="109"/>
+      <x:c r="F23" s="109" t="str">
+        <x:v>AE-ORDER-003</x:v>
+      </x:c>
       <x:c r="G23" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H23" s="93" t="str">
-        <x:v>No login-before-checkout workflow exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-109 (AE-ORDER-003) is linked to AEQA-16; execution remains pending.</x:v>
       </x:c>
       <x:c r="I23" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4219,7 +4361,7 @@
       <x:c r="P23" s="93"/>
       <x:c r="Q23" s="93"/>
       <x:c r="R23" s="94" t="str">
-        <x:v>Create an end-to-end checkout case for login before checkout.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-ORDER-003 (AEQA-109) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -4292,12 +4434,14 @@
       <x:c r="E25" s="109" t="str">
         <x:v>View Category Products</x:v>
       </x:c>
-      <x:c r="F25" s="109"/>
+      <x:c r="F25" s="109" t="str">
+        <x:v>AE-CATALOG-001</x:v>
+      </x:c>
       <x:c r="G25" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H25" s="93" t="str">
-        <x:v>No category-navigation test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-110 (AE-CATALOG-001) is linked to AEQA-18; execution remains pending.</x:v>
       </x:c>
       <x:c r="I25" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4323,7 +4467,7 @@
       <x:c r="P25" s="93"/>
       <x:c r="Q25" s="93"/>
       <x:c r="R25" s="94" t="str">
-        <x:v>Create category and subcategory navigation coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-CATALOG-001 (AEQA-110) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -4342,12 +4486,14 @@
       <x:c r="E26" s="109" t="str">
         <x:v>View &amp; Cart Brand Products</x:v>
       </x:c>
-      <x:c r="F26" s="109"/>
+      <x:c r="F26" s="109" t="str">
+        <x:v>AE-CATALOG-002</x:v>
+      </x:c>
       <x:c r="G26" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H26" s="93" t="str">
-        <x:v>No brand-navigation test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-111 (AE-CATALOG-002) is linked to AEQA-19; execution remains pending.</x:v>
       </x:c>
       <x:c r="I26" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4373,7 +4519,7 @@
       <x:c r="P26" s="93"/>
       <x:c r="Q26" s="93"/>
       <x:c r="R26" s="94" t="str">
-        <x:v>Create brand-list and brand-switching coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-CATALOG-002 (AEQA-111) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -4392,12 +4538,14 @@
       <x:c r="E27" s="109" t="str">
         <x:v>Search Products and Verify Cart After Login</x:v>
       </x:c>
-      <x:c r="F27" s="109"/>
+      <x:c r="F27" s="109" t="str">
+        <x:v>AE-CART-004</x:v>
+      </x:c>
       <x:c r="G27" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H27" s="93" t="str">
-        <x:v>No cart-persistence-after-login workflow exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-112 (AE-CART-004) is linked to AEQA-20; execution remains pending.</x:v>
       </x:c>
       <x:c r="I27" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4423,7 +4571,7 @@
       <x:c r="P27" s="93"/>
       <x:c r="Q27" s="93"/>
       <x:c r="R27" s="94" t="str">
-        <x:v>Create search, cart, login, and cart-persistence coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-CART-004 (AEQA-112) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -4442,12 +4590,14 @@
       <x:c r="E28" s="109" t="str">
         <x:v>Add review on product</x:v>
       </x:c>
-      <x:c r="F28" s="109"/>
+      <x:c r="F28" s="109" t="str">
+        <x:v>AE-REVIEW-001</x:v>
+      </x:c>
       <x:c r="G28" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H28" s="93" t="str">
-        <x:v>No product-review test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-113 (AE-REVIEW-001) is linked to AEQA-21; execution remains pending.</x:v>
       </x:c>
       <x:c r="I28" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4473,7 +4623,7 @@
       <x:c r="P28" s="93"/>
       <x:c r="Q28" s="93"/>
       <x:c r="R28" s="94" t="str">
-        <x:v>Create product-review submission coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-REVIEW-001 (AEQA-113) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -4492,12 +4642,14 @@
       <x:c r="E29" s="109" t="str">
         <x:v>Add to cart from Recommended items</x:v>
       </x:c>
-      <x:c r="F29" s="109"/>
+      <x:c r="F29" s="109" t="str">
+        <x:v>AE-CART-005</x:v>
+      </x:c>
       <x:c r="G29" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H29" s="93" t="str">
-        <x:v>No recommended-item cart test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-114 (AE-CART-005) is linked to AEQA-22; execution remains pending.</x:v>
       </x:c>
       <x:c r="I29" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4523,7 +4675,7 @@
       <x:c r="P29" s="93"/>
       <x:c r="Q29" s="93"/>
       <x:c r="R29" s="94" t="str">
-        <x:v>Create recommended-item cart coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-CART-005 (AEQA-114) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -4542,12 +4694,14 @@
       <x:c r="E30" s="109" t="str">
         <x:v>Verify address details in checkout page</x:v>
       </x:c>
-      <x:c r="F30" s="109"/>
+      <x:c r="F30" s="109" t="str">
+        <x:v>AE-ORDER-004</x:v>
+      </x:c>
       <x:c r="G30" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H30" s="93" t="str">
-        <x:v>No billing/delivery address verification exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-115 (AE-ORDER-004) is linked to AEQA-23; execution remains pending.</x:v>
       </x:c>
       <x:c r="I30" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4573,7 +4727,7 @@
       <x:c r="P30" s="93"/>
       <x:c r="Q30" s="93"/>
       <x:c r="R30" s="94" t="str">
-        <x:v>Create checkout-address verification coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-ORDER-004 (AEQA-115) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -4592,12 +4746,14 @@
       <x:c r="E31" s="109" t="str">
         <x:v>Download Invoice after purchase order</x:v>
       </x:c>
-      <x:c r="F31" s="109"/>
+      <x:c r="F31" s="109" t="str">
+        <x:v>AE-ORDER-005</x:v>
+      </x:c>
       <x:c r="G31" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H31" s="93" t="str">
-        <x:v>No invoice-download test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-116 (AE-ORDER-005) is linked to AEQA-24; execution remains pending.</x:v>
       </x:c>
       <x:c r="I31" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4623,7 +4779,7 @@
       <x:c r="P31" s="93"/>
       <x:c r="Q31" s="93"/>
       <x:c r="R31" s="94" t="str">
-        <x:v>Create purchase and invoice-download coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-ORDER-005 (AEQA-116) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -4642,12 +4798,14 @@
       <x:c r="E32" s="109" t="str">
         <x:v>Verify Scroll Up using 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
-      <x:c r="F32" s="109"/>
+      <x:c r="F32" s="109" t="str">
+        <x:v>AE-NAV-002</x:v>
+      </x:c>
       <x:c r="G32" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H32" s="93" t="str">
-        <x:v>No arrow-assisted scrolling test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-117 (AE-NAV-002) is linked to AEQA-25; execution remains pending.</x:v>
       </x:c>
       <x:c r="I32" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4673,7 +4831,7 @@
       <x:c r="P32" s="93"/>
       <x:c r="Q32" s="93"/>
       <x:c r="R32" s="94" t="str">
-        <x:v>Create scroll-down and arrow-assisted scroll-up coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-NAV-002 (AEQA-117) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
@@ -4692,12 +4850,14 @@
       <x:c r="E33" s="109" t="str">
         <x:v>Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
-      <x:c r="F33" s="109"/>
+      <x:c r="F33" s="109" t="str">
+        <x:v>AE-NAV-003</x:v>
+      </x:c>
       <x:c r="G33" s="119" t="str">
-        <x:v>Not Covered</x:v>
+        <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H33" s="93" t="str">
-        <x:v>No manual scroll-up test exists.</x:v>
+        <x:v>Test design is complete. Jira AEQA-118 (AE-NAV-003) is linked to AEQA-26; execution remains pending.</x:v>
       </x:c>
       <x:c r="I33" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4723,7 +4883,7 @@
       <x:c r="P33" s="93"/>
       <x:c r="Q33" s="93"/>
       <x:c r="R33" s="94" t="str">
-        <x:v>Create manual scroll-down and scroll-up coverage.</x:v>
+        <x:v>Design gap closed in Jira. Execute AE-NAV-003 (AEQA-118) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
@@ -5926,7 +6086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a8c95dde81b4b9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08e6f7acea6b4f0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5943,7 +6103,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="38" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -5951,7 +6111,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -5959,380 +6119,380 @@
     </x:row>
     <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="264.5" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="5">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="264.5" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="264.5" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="264.5" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C8" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="264.5" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="264.5" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="5">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="264.5" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C11" s="5">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="264.5" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C12" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D12" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="264.5" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="264.5" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="264.5" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="264.5" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="264.5" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D17" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="264.5" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C18" s="5">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D18" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="264.5" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C19" s="5">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D19" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="264.5" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C20" s="5">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="264.5" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C21" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D21" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="264.5" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C22" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D22" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="264.5" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C23" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="264.5" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C24" s="5">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="264.5" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="264.5" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="264.5" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C27" s="5">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="264.5" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B28" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C28" s="5">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D28" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="264.5" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B29" s="5" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C29" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="264.5" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C30" s="10">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6342,7 +6502,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b945217db314ad5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e24b4ce862246c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6363,7 +6523,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="53" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B1" s="53"/>
       <x:c r="C1" s="53"/>
@@ -6375,7 +6535,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="54" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B2" s="54"/>
       <x:c r="C2" s="54"/>
@@ -6392,383 +6552,383 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="16" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="s">
+      <x:c r="F4" s="16" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="s">
+      <x:c r="G4" s="16" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="s">
+      <x:c r="H4" s="16" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="s">
-        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="E5" s="5"/>
       <x:c r="F5" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G6" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E8" s="5"/>
       <x:c r="F8" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G8" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H8" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="72" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="F9" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G9" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H9" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
         <x:v>400</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
       <x:c r="A11" s="5" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="F11" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E12" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F12" s="5">
         <x:v>400</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D13" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="72" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="F14" s="5">
         <x:v>404</x:v>
       </x:c>
       <x:c r="G14" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H14" s="5" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
       <x:c r="A15" s="5" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="C15" s="5" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D15" s="5" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E15" s="5" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="E15" s="5" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="F15" s="5">
         <x:v>201</x:v>
       </x:c>
       <x:c r="G15" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H15" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="72" customHeight="1">
       <x:c r="A16" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F16" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G16" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H16" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="72" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D17" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E17" s="5" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F17" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G17" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H17" s="5" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J17" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="72" customHeight="1">
       <x:c r="A18" s="5" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="s">
-        <x:v>176</x:v>
       </x:c>
       <x:c r="F18" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G18" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H18" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6778,7 +6938,4132 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74c3d434b098435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc340310bf6e344a6"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="41.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="25.5" customHeight="1">
+      <x:c r="A1" s="129" t="str">
+        <x:v>AEQA Jira Traceability Snapshot</x:v>
+      </x:c>
+      <x:c r="B1" s="129"/>
+      <x:c r="C1" s="129"/>
+      <x:c r="D1" s="129"/>
+      <x:c r="E1" s="129"/>
+      <x:c r="F1" s="129"/>
+      <x:c r="G1" s="129"/>
+      <x:c r="H1" s="129"/>
+      <x:c r="I1" s="129"/>
+      <x:c r="J1" s="129"/>
+      <x:c r="K1" s="129"/>
+      <x:c r="L1" s="129"/>
+      <x:c r="M1" s="129"/>
+      <x:c r="N1" s="129"/>
+    </x:row>
+    <x:row r="2" ht="25.5" customHeight="1">
+      <x:c r="A2" s="134" t="str">
+        <x:v>Source: live Jira Cloud AEQA all-fields export captured 2026-08-11. Re-export Jira before each formal RTM reconciliation.</x:v>
+      </x:c>
+      <x:c r="B2" s="134"/>
+      <x:c r="C2" s="134"/>
+      <x:c r="D2" s="134"/>
+      <x:c r="E2" s="134"/>
+      <x:c r="F2" s="134"/>
+      <x:c r="G2" s="134"/>
+      <x:c r="H2" s="134"/>
+      <x:c r="I2" s="134"/>
+      <x:c r="J2" s="134"/>
+      <x:c r="K2" s="134"/>
+      <x:c r="L2" s="134"/>
+      <x:c r="M2" s="134"/>
+      <x:c r="N2" s="134"/>
+    </x:row>
+    <x:row r="4" ht="25.5" customHeight="1">
+      <x:c r="A4" s="139" t="str">
+        <x:v>Jira Key</x:v>
+      </x:c>
+      <x:c r="B4" s="139" t="str">
+        <x:v>Work Type</x:v>
+      </x:c>
+      <x:c r="C4" s="139" t="str">
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="D4" s="139" t="str">
+        <x:v>Workflow Status</x:v>
+      </x:c>
+      <x:c r="E4" s="139" t="str">
+        <x:v>Priority</x:v>
+      </x:c>
+      <x:c r="F4" s="139" t="str">
+        <x:v>Assignee</x:v>
+      </x:c>
+      <x:c r="G4" s="139" t="str">
+        <x:v>Requirement ID</x:v>
+      </x:c>
+      <x:c r="H4" s="139" t="str">
+        <x:v>Test Case ID</x:v>
+      </x:c>
+      <x:c r="I4" s="139" t="str">
+        <x:v>Defect ID</x:v>
+      </x:c>
+      <x:c r="J4" s="139" t="str">
+        <x:v>Execution Status</x:v>
+      </x:c>
+      <x:c r="K4" s="139" t="str">
+        <x:v>Automation Status</x:v>
+      </x:c>
+      <x:c r="L4" s="139" t="str">
+        <x:v>Testing Link(s)</x:v>
+      </x:c>
+      <x:c r="M4" s="139" t="str">
+        <x:v>Parent Key</x:v>
+      </x:c>
+      <x:c r="N4" s="139" t="str">
+        <x:v>Jira Updated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="31.5" customHeight="1">
+      <x:c r="A5" s="76" t="str">
+        <x:v>AEQA-1</x:v>
+      </x:c>
+      <x:c r="B5" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C5" s="76" t="str">
+        <x:v>REQ-AUTH-001 - Register User</x:v>
+      </x:c>
+      <x:c r="D5" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E5" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F5" s="76" t="str"/>
+      <x:c r="G5" s="76" t="str">
+        <x:v>REQ-AUTH-001</x:v>
+      </x:c>
+      <x:c r="H5" s="76" t="str"/>
+      <x:c r="I5" s="76" t="str"/>
+      <x:c r="J5" s="76" t="str"/>
+      <x:c r="K5" s="76" t="str"/>
+      <x:c r="L5" s="76" t="str">
+        <x:v>AEQA-45
+AEQA-46
+AEQA-53
+AEQA-106</x:v>
+      </x:c>
+      <x:c r="M5" s="76" t="str"/>
+      <x:c r="N5" s="76" t="str">
+        <x:v>10/Aug/26 8:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="31.5" customHeight="1">
+      <x:c r="A6" s="76" t="str">
+        <x:v>AEQA-2</x:v>
+      </x:c>
+      <x:c r="B6" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C6" s="76" t="str">
+        <x:v>REQ-AUTH-002 - Login User with correct email and password</x:v>
+      </x:c>
+      <x:c r="D6" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E6" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F6" s="76" t="str"/>
+      <x:c r="G6" s="76" t="str">
+        <x:v>REQ-AUTH-002</x:v>
+      </x:c>
+      <x:c r="H6" s="76" t="str"/>
+      <x:c r="I6" s="76" t="str"/>
+      <x:c r="J6" s="76" t="str"/>
+      <x:c r="K6" s="76" t="str"/>
+      <x:c r="L6" s="76" t="str">
+        <x:v>AEQA-49
+AEQA-53</x:v>
+      </x:c>
+      <x:c r="M6" s="76" t="str"/>
+      <x:c r="N6" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="31.5" customHeight="1">
+      <x:c r="A7" s="76" t="str">
+        <x:v>AEQA-3</x:v>
+      </x:c>
+      <x:c r="B7" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C7" s="76" t="str">
+        <x:v>REQ-AUTH-003 - Login User with incorrect email and password</x:v>
+      </x:c>
+      <x:c r="D7" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E7" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F7" s="76" t="str"/>
+      <x:c r="G7" s="76" t="str">
+        <x:v>REQ-AUTH-003</x:v>
+      </x:c>
+      <x:c r="H7" s="76" t="str"/>
+      <x:c r="I7" s="76" t="str"/>
+      <x:c r="J7" s="76" t="str"/>
+      <x:c r="K7" s="76" t="str"/>
+      <x:c r="L7" s="76" t="str">
+        <x:v>AEQA-51
+AEQA-56</x:v>
+      </x:c>
+      <x:c r="M7" s="76" t="str"/>
+      <x:c r="N7" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="31.5" customHeight="1">
+      <x:c r="A8" s="76" t="str">
+        <x:v>AEQA-4</x:v>
+      </x:c>
+      <x:c r="B8" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C8" s="76" t="str">
+        <x:v>REQ-AUTH-004 - Logout User</x:v>
+      </x:c>
+      <x:c r="D8" s="76" t="str">
+        <x:v>Selected for Development</x:v>
+      </x:c>
+      <x:c r="E8" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F8" s="76" t="str"/>
+      <x:c r="G8" s="76" t="str">
+        <x:v>REQ-AUTH-004</x:v>
+      </x:c>
+      <x:c r="H8" s="76" t="str"/>
+      <x:c r="I8" s="76" t="str"/>
+      <x:c r="J8" s="76" t="str"/>
+      <x:c r="K8" s="76" t="str"/>
+      <x:c r="L8" s="76" t="str">
+        <x:v>AEQA-52</x:v>
+      </x:c>
+      <x:c r="M8" s="76" t="str"/>
+      <x:c r="N8" s="76" t="str">
+        <x:v>11/Aug/26 7:35 AM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="31.5" customHeight="1">
+      <x:c r="A9" s="76" t="str">
+        <x:v>AEQA-5</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="str">
+        <x:v>REQ-AUTH-005 - Register User with existing email</x:v>
+      </x:c>
+      <x:c r="D9" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E9" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F9" s="76" t="str"/>
+      <x:c r="G9" s="76" t="str">
+        <x:v>REQ-AUTH-005</x:v>
+      </x:c>
+      <x:c r="H9" s="76" t="str"/>
+      <x:c r="I9" s="76" t="str"/>
+      <x:c r="J9" s="76" t="str"/>
+      <x:c r="K9" s="76" t="str"/>
+      <x:c r="L9" s="76" t="str">
+        <x:v>AEQA-55</x:v>
+      </x:c>
+      <x:c r="M9" s="76" t="str"/>
+      <x:c r="N9" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="31.5" customHeight="1">
+      <x:c r="A10" s="76" t="str">
+        <x:v>AEQA-6</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C10" s="76" t="str">
+        <x:v>REQ-CONTACT-001 - Contact Us Form</x:v>
+      </x:c>
+      <x:c r="D10" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E10" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F10" s="76" t="str"/>
+      <x:c r="G10" s="76" t="str">
+        <x:v>REQ-CONTACT-001</x:v>
+      </x:c>
+      <x:c r="H10" s="76" t="str"/>
+      <x:c r="I10" s="76" t="str"/>
+      <x:c r="J10" s="76" t="str"/>
+      <x:c r="K10" s="76" t="str"/>
+      <x:c r="L10" s="76" t="str">
+        <x:v>AEQA-62</x:v>
+      </x:c>
+      <x:c r="M10" s="76" t="str"/>
+      <x:c r="N10" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="31.5" customHeight="1">
+      <x:c r="A11" s="76" t="str">
+        <x:v>AEQA-7</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="str">
+        <x:v>REQ-NAV-001 - Verify Test Cases Page</x:v>
+      </x:c>
+      <x:c r="D11" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E11" s="76" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="F11" s="76" t="str"/>
+      <x:c r="G11" s="76" t="str">
+        <x:v>REQ-NAV-001</x:v>
+      </x:c>
+      <x:c r="H11" s="76" t="str"/>
+      <x:c r="I11" s="76" t="str"/>
+      <x:c r="J11" s="76" t="str"/>
+      <x:c r="K11" s="76" t="str"/>
+      <x:c r="L11" s="76" t="str">
+        <x:v>AEQA-63</x:v>
+      </x:c>
+      <x:c r="M11" s="76" t="str"/>
+      <x:c r="N11" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="31.5" customHeight="1">
+      <x:c r="A12" s="76" t="str">
+        <x:v>AEQA-8</x:v>
+      </x:c>
+      <x:c r="B12" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C12" s="76" t="str">
+        <x:v>REQ-PRODUCT-001 - Verify All Products and product detail page</x:v>
+      </x:c>
+      <x:c r="D12" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E12" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F12" s="76" t="str"/>
+      <x:c r="G12" s="76" t="str">
+        <x:v>REQ-PRODUCT-001</x:v>
+      </x:c>
+      <x:c r="H12" s="76" t="str"/>
+      <x:c r="I12" s="76" t="str"/>
+      <x:c r="J12" s="76" t="str"/>
+      <x:c r="K12" s="76" t="str"/>
+      <x:c r="L12" s="76" t="str">
+        <x:v>AEQA-57</x:v>
+      </x:c>
+      <x:c r="M12" s="76" t="str"/>
+      <x:c r="N12" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="31.5" customHeight="1">
+      <x:c r="A13" s="76" t="str">
+        <x:v>AEQA-9</x:v>
+      </x:c>
+      <x:c r="B13" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C13" s="76" t="str">
+        <x:v>REQ-PRODUCT-002 - Search Product</x:v>
+      </x:c>
+      <x:c r="D13" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E13" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F13" s="76" t="str"/>
+      <x:c r="G13" s="76" t="str">
+        <x:v>REQ-PRODUCT-002</x:v>
+      </x:c>
+      <x:c r="H13" s="76" t="str"/>
+      <x:c r="I13" s="76" t="str"/>
+      <x:c r="J13" s="76" t="str"/>
+      <x:c r="K13" s="76" t="str"/>
+      <x:c r="L13" s="76" t="str">
+        <x:v>AEQA-58</x:v>
+      </x:c>
+      <x:c r="M13" s="76" t="str"/>
+      <x:c r="N13" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="31.5" customHeight="1">
+      <x:c r="A14" s="76" t="str">
+        <x:v>AEQA-10</x:v>
+      </x:c>
+      <x:c r="B14" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C14" s="76" t="str">
+        <x:v>REQ-SUB-001 - Verify Subscription in home page</x:v>
+      </x:c>
+      <x:c r="D14" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E14" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F14" s="76" t="str"/>
+      <x:c r="G14" s="76" t="str">
+        <x:v>REQ-SUB-001</x:v>
+      </x:c>
+      <x:c r="H14" s="76" t="str"/>
+      <x:c r="I14" s="76" t="str"/>
+      <x:c r="J14" s="76" t="str"/>
+      <x:c r="K14" s="76" t="str"/>
+      <x:c r="L14" s="76" t="str">
+        <x:v>AEQA-64</x:v>
+      </x:c>
+      <x:c r="M14" s="76" t="str"/>
+      <x:c r="N14" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="31.5" customHeight="1">
+      <x:c r="A15" s="76" t="str">
+        <x:v>AEQA-11</x:v>
+      </x:c>
+      <x:c r="B15" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C15" s="76" t="str">
+        <x:v>REQ-SUB-002 - Verify Subscription in Cart page</x:v>
+      </x:c>
+      <x:c r="D15" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E15" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F15" s="76" t="str"/>
+      <x:c r="G15" s="76" t="str">
+        <x:v>REQ-SUB-002</x:v>
+      </x:c>
+      <x:c r="H15" s="76" t="str"/>
+      <x:c r="I15" s="76" t="str"/>
+      <x:c r="J15" s="76" t="str"/>
+      <x:c r="K15" s="76" t="str"/>
+      <x:c r="L15" s="76" t="str">
+        <x:v>AEQA-65</x:v>
+      </x:c>
+      <x:c r="M15" s="76" t="str"/>
+      <x:c r="N15" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="31.5" customHeight="1">
+      <x:c r="A16" s="76" t="str">
+        <x:v>AEQA-12</x:v>
+      </x:c>
+      <x:c r="B16" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C16" s="76" t="str">
+        <x:v>REQ-CART-001 - Add Products in Cart</x:v>
+      </x:c>
+      <x:c r="D16" s="76" t="str">
+        <x:v>Selected for Development</x:v>
+      </x:c>
+      <x:c r="E16" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F16" s="76" t="str"/>
+      <x:c r="G16" s="76" t="str">
+        <x:v>REQ-CART-001</x:v>
+      </x:c>
+      <x:c r="H16" s="76" t="str"/>
+      <x:c r="I16" s="76" t="str"/>
+      <x:c r="J16" s="76" t="str"/>
+      <x:c r="K16" s="76" t="str"/>
+      <x:c r="L16" s="76" t="str">
+        <x:v>AEQA-59</x:v>
+      </x:c>
+      <x:c r="M16" s="76" t="str"/>
+      <x:c r="N16" s="76" t="str">
+        <x:v>10/Aug/26 8:26 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="31.5" customHeight="1">
+      <x:c r="A17" s="76" t="str">
+        <x:v>AEQA-13</x:v>
+      </x:c>
+      <x:c r="B17" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C17" s="76" t="str">
+        <x:v>REQ-CART-002 - Verify Product quantity in Cart</x:v>
+      </x:c>
+      <x:c r="D17" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E17" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F17" s="76" t="str"/>
+      <x:c r="G17" s="76" t="str">
+        <x:v>REQ-CART-002</x:v>
+      </x:c>
+      <x:c r="H17" s="76" t="str"/>
+      <x:c r="I17" s="76" t="str"/>
+      <x:c r="J17" s="76" t="str"/>
+      <x:c r="K17" s="76" t="str"/>
+      <x:c r="L17" s="76" t="str">
+        <x:v>AEQA-60</x:v>
+      </x:c>
+      <x:c r="M17" s="76" t="str"/>
+      <x:c r="N17" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="31.5" customHeight="1">
+      <x:c r="A18" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="B18" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C18" s="76" t="str">
+        <x:v>REQ-ORDER-001 - Place Order: Register while Checkout</x:v>
+      </x:c>
+      <x:c r="D18" s="76" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="E18" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F18" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G18" s="76" t="str">
+        <x:v>REQ-ORDER-001</x:v>
+      </x:c>
+      <x:c r="H18" s="76" t="str"/>
+      <x:c r="I18" s="76" t="str"/>
+      <x:c r="J18" s="76" t="str"/>
+      <x:c r="K18" s="76" t="str"/>
+      <x:c r="L18" s="76" t="str">
+        <x:v>AEQA-107</x:v>
+      </x:c>
+      <x:c r="M18" s="76" t="str"/>
+      <x:c r="N18" s="76" t="str">
+        <x:v>11/Aug/26 7:41 AM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="31.5" customHeight="1">
+      <x:c r="A19" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="B19" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C19" s="76" t="str">
+        <x:v>REQ-ORDER-002 - Place Order: Register before Checkout</x:v>
+      </x:c>
+      <x:c r="D19" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E19" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F19" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G19" s="76" t="str">
+        <x:v>REQ-ORDER-002</x:v>
+      </x:c>
+      <x:c r="H19" s="76" t="str"/>
+      <x:c r="I19" s="76" t="str"/>
+      <x:c r="J19" s="76" t="str"/>
+      <x:c r="K19" s="76" t="str"/>
+      <x:c r="L19" s="76" t="str">
+        <x:v>AEQA-108</x:v>
+      </x:c>
+      <x:c r="M19" s="76" t="str"/>
+      <x:c r="N19" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="31.5" customHeight="1">
+      <x:c r="A20" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="B20" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C20" s="76" t="str">
+        <x:v>REQ-ORDER-003 - Place Order: Login before Checkout</x:v>
+      </x:c>
+      <x:c r="D20" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E20" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F20" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G20" s="76" t="str">
+        <x:v>REQ-ORDER-003</x:v>
+      </x:c>
+      <x:c r="H20" s="76" t="str"/>
+      <x:c r="I20" s="76" t="str"/>
+      <x:c r="J20" s="76" t="str"/>
+      <x:c r="K20" s="76" t="str"/>
+      <x:c r="L20" s="76" t="str">
+        <x:v>AEQA-109</x:v>
+      </x:c>
+      <x:c r="M20" s="76" t="str"/>
+      <x:c r="N20" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="31.5" customHeight="1">
+      <x:c r="A21" s="76" t="str">
+        <x:v>AEQA-17</x:v>
+      </x:c>
+      <x:c r="B21" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C21" s="76" t="str">
+        <x:v>REQ-CART-003 - Remove Products From Cart</x:v>
+      </x:c>
+      <x:c r="D21" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E21" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F21" s="76" t="str"/>
+      <x:c r="G21" s="76" t="str">
+        <x:v>REQ-CART-003</x:v>
+      </x:c>
+      <x:c r="H21" s="76" t="str"/>
+      <x:c r="I21" s="76" t="str"/>
+      <x:c r="J21" s="76" t="str"/>
+      <x:c r="K21" s="76" t="str"/>
+      <x:c r="L21" s="76" t="str">
+        <x:v>AEQA-61</x:v>
+      </x:c>
+      <x:c r="M21" s="76" t="str"/>
+      <x:c r="N21" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="31.5" customHeight="1">
+      <x:c r="A22" s="76" t="str">
+        <x:v>AEQA-18</x:v>
+      </x:c>
+      <x:c r="B22" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C22" s="76" t="str">
+        <x:v>REQ-CATALOG-001 - View Category Products</x:v>
+      </x:c>
+      <x:c r="D22" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E22" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F22" s="76" t="str"/>
+      <x:c r="G22" s="76" t="str">
+        <x:v>REQ-CATALOG-001</x:v>
+      </x:c>
+      <x:c r="H22" s="76" t="str"/>
+      <x:c r="I22" s="76" t="str"/>
+      <x:c r="J22" s="76" t="str"/>
+      <x:c r="K22" s="76" t="str"/>
+      <x:c r="L22" s="76" t="str">
+        <x:v>AEQA-110</x:v>
+      </x:c>
+      <x:c r="M22" s="76" t="str"/>
+      <x:c r="N22" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="31.5" customHeight="1">
+      <x:c r="A23" s="76" t="str">
+        <x:v>AEQA-19</x:v>
+      </x:c>
+      <x:c r="B23" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C23" s="76" t="str">
+        <x:v>REQ-CATALOG-002 - View &amp; Cart Brand Products</x:v>
+      </x:c>
+      <x:c r="D23" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E23" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F23" s="76" t="str"/>
+      <x:c r="G23" s="76" t="str">
+        <x:v>REQ-CATALOG-002</x:v>
+      </x:c>
+      <x:c r="H23" s="76" t="str"/>
+      <x:c r="I23" s="76" t="str"/>
+      <x:c r="J23" s="76" t="str"/>
+      <x:c r="K23" s="76" t="str"/>
+      <x:c r="L23" s="76" t="str">
+        <x:v>AEQA-111</x:v>
+      </x:c>
+      <x:c r="M23" s="76" t="str"/>
+      <x:c r="N23" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="31.5" customHeight="1">
+      <x:c r="A24" s="76" t="str">
+        <x:v>AEQA-20</x:v>
+      </x:c>
+      <x:c r="B24" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C24" s="76" t="str">
+        <x:v>REQ-CART-004 - Search Products and Verify Cart After Login</x:v>
+      </x:c>
+      <x:c r="D24" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E24" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F24" s="76" t="str"/>
+      <x:c r="G24" s="76" t="str">
+        <x:v>REQ-CART-004</x:v>
+      </x:c>
+      <x:c r="H24" s="76" t="str"/>
+      <x:c r="I24" s="76" t="str"/>
+      <x:c r="J24" s="76" t="str"/>
+      <x:c r="K24" s="76" t="str"/>
+      <x:c r="L24" s="76" t="str">
+        <x:v>AEQA-112</x:v>
+      </x:c>
+      <x:c r="M24" s="76" t="str"/>
+      <x:c r="N24" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="31.5" customHeight="1">
+      <x:c r="A25" s="76" t="str">
+        <x:v>AEQA-21</x:v>
+      </x:c>
+      <x:c r="B25" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C25" s="76" t="str">
+        <x:v>REQ-REVIEW-001 - Add review on product</x:v>
+      </x:c>
+      <x:c r="D25" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E25" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F25" s="76" t="str"/>
+      <x:c r="G25" s="76" t="str">
+        <x:v>REQ-REVIEW-001</x:v>
+      </x:c>
+      <x:c r="H25" s="76" t="str"/>
+      <x:c r="I25" s="76" t="str"/>
+      <x:c r="J25" s="76" t="str"/>
+      <x:c r="K25" s="76" t="str"/>
+      <x:c r="L25" s="76" t="str">
+        <x:v>AEQA-113</x:v>
+      </x:c>
+      <x:c r="M25" s="76" t="str"/>
+      <x:c r="N25" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="31.5" customHeight="1">
+      <x:c r="A26" s="76" t="str">
+        <x:v>AEQA-22</x:v>
+      </x:c>
+      <x:c r="B26" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C26" s="76" t="str">
+        <x:v>REQ-CART-005 - Add to cart from Recommended items</x:v>
+      </x:c>
+      <x:c r="D26" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E26" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F26" s="76" t="str"/>
+      <x:c r="G26" s="76" t="str">
+        <x:v>REQ-CART-005</x:v>
+      </x:c>
+      <x:c r="H26" s="76" t="str"/>
+      <x:c r="I26" s="76" t="str"/>
+      <x:c r="J26" s="76" t="str"/>
+      <x:c r="K26" s="76" t="str"/>
+      <x:c r="L26" s="76" t="str">
+        <x:v>AEQA-114</x:v>
+      </x:c>
+      <x:c r="M26" s="76" t="str"/>
+      <x:c r="N26" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="31.5" customHeight="1">
+      <x:c r="A27" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="B27" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C27" s="76" t="str">
+        <x:v>REQ-ORDER-004 - Verify address details in checkout page</x:v>
+      </x:c>
+      <x:c r="D27" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E27" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F27" s="76" t="str"/>
+      <x:c r="G27" s="76" t="str">
+        <x:v>REQ-ORDER-004</x:v>
+      </x:c>
+      <x:c r="H27" s="76" t="str"/>
+      <x:c r="I27" s="76" t="str"/>
+      <x:c r="J27" s="76" t="str"/>
+      <x:c r="K27" s="76" t="str"/>
+      <x:c r="L27" s="76" t="str">
+        <x:v>AEQA-115</x:v>
+      </x:c>
+      <x:c r="M27" s="76" t="str"/>
+      <x:c r="N27" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="31.5" customHeight="1">
+      <x:c r="A28" s="76" t="str">
+        <x:v>AEQA-24</x:v>
+      </x:c>
+      <x:c r="B28" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C28" s="76" t="str">
+        <x:v>REQ-ORDER-005 - Download Invoice after purchase order</x:v>
+      </x:c>
+      <x:c r="D28" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E28" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F28" s="76" t="str"/>
+      <x:c r="G28" s="76" t="str">
+        <x:v>REQ-ORDER-005</x:v>
+      </x:c>
+      <x:c r="H28" s="76" t="str"/>
+      <x:c r="I28" s="76" t="str"/>
+      <x:c r="J28" s="76" t="str"/>
+      <x:c r="K28" s="76" t="str"/>
+      <x:c r="L28" s="76" t="str">
+        <x:v>AEQA-116</x:v>
+      </x:c>
+      <x:c r="M28" s="76" t="str"/>
+      <x:c r="N28" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="31.5" customHeight="1">
+      <x:c r="A29" s="76" t="str">
+        <x:v>AEQA-25</x:v>
+      </x:c>
+      <x:c r="B29" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C29" s="76" t="str">
+        <x:v>REQ-NAV-002 - Verify Scroll Up using 'Arrow' button and Scroll Down functionality</x:v>
+      </x:c>
+      <x:c r="D29" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E29" s="76" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="F29" s="76" t="str"/>
+      <x:c r="G29" s="76" t="str">
+        <x:v>REQ-NAV-002</x:v>
+      </x:c>
+      <x:c r="H29" s="76" t="str"/>
+      <x:c r="I29" s="76" t="str"/>
+      <x:c r="J29" s="76" t="str"/>
+      <x:c r="K29" s="76" t="str"/>
+      <x:c r="L29" s="76" t="str">
+        <x:v>AEQA-117</x:v>
+      </x:c>
+      <x:c r="M29" s="76" t="str"/>
+      <x:c r="N29" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="31.5" customHeight="1">
+      <x:c r="A30" s="76" t="str">
+        <x:v>AEQA-26</x:v>
+      </x:c>
+      <x:c r="B30" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C30" s="76" t="str">
+        <x:v>REQ-NAV-003 - Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
+      </x:c>
+      <x:c r="D30" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E30" s="76" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="F30" s="76" t="str"/>
+      <x:c r="G30" s="76" t="str">
+        <x:v>REQ-NAV-003</x:v>
+      </x:c>
+      <x:c r="H30" s="76" t="str"/>
+      <x:c r="I30" s="76" t="str"/>
+      <x:c r="J30" s="76" t="str"/>
+      <x:c r="K30" s="76" t="str"/>
+      <x:c r="L30" s="76" t="str">
+        <x:v>AEQA-118</x:v>
+      </x:c>
+      <x:c r="M30" s="76" t="str"/>
+      <x:c r="N30" s="76" t="str">
+        <x:v>10/Aug/26 9:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="31.5" customHeight="1">
+      <x:c r="A31" s="76" t="str">
+        <x:v>AEQA-27</x:v>
+      </x:c>
+      <x:c r="B31" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C31" s="76" t="str">
+        <x:v>REQ-EXT-001 - Reject invalid email format during registration</x:v>
+      </x:c>
+      <x:c r="D31" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E31" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F31" s="76" t="str"/>
+      <x:c r="G31" s="76" t="str">
+        <x:v>REQ-EXT-001</x:v>
+      </x:c>
+      <x:c r="H31" s="76" t="str"/>
+      <x:c r="I31" s="76" t="str"/>
+      <x:c r="J31" s="76" t="str"/>
+      <x:c r="K31" s="76" t="str"/>
+      <x:c r="L31" s="76" t="str">
+        <x:v>AEQA-47</x:v>
+      </x:c>
+      <x:c r="M31" s="76" t="str"/>
+      <x:c r="N31" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="31.5" customHeight="1">
+      <x:c r="A32" s="76" t="str">
+        <x:v>AEQA-28</x:v>
+      </x:c>
+      <x:c r="B32" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C32" s="76" t="str">
+        <x:v>REQ-EXT-002 - Prevent account creation when required fields are blank</x:v>
+      </x:c>
+      <x:c r="D32" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E32" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F32" s="76" t="str"/>
+      <x:c r="G32" s="76" t="str">
+        <x:v>REQ-EXT-002</x:v>
+      </x:c>
+      <x:c r="H32" s="76" t="str"/>
+      <x:c r="I32" s="76" t="str"/>
+      <x:c r="J32" s="76" t="str"/>
+      <x:c r="K32" s="76" t="str"/>
+      <x:c r="L32" s="76" t="str">
+        <x:v>AEQA-48</x:v>
+      </x:c>
+      <x:c r="M32" s="76" t="str"/>
+      <x:c r="N32" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="31.5" customHeight="1">
+      <x:c r="A33" s="76" t="str">
+        <x:v>AEQA-29</x:v>
+      </x:c>
+      <x:c r="B33" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C33" s="76" t="str">
+        <x:v>REQ-EXT-003 - Reject SQL injection input without authenticating the user</x:v>
+      </x:c>
+      <x:c r="D33" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E33" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F33" s="76" t="str"/>
+      <x:c r="G33" s="76" t="str">
+        <x:v>REQ-EXT-003</x:v>
+      </x:c>
+      <x:c r="H33" s="76" t="str"/>
+      <x:c r="I33" s="76" t="str"/>
+      <x:c r="J33" s="76" t="str"/>
+      <x:c r="K33" s="76" t="str"/>
+      <x:c r="L33" s="76" t="str">
+        <x:v>AEQA-50</x:v>
+      </x:c>
+      <x:c r="M33" s="76" t="str"/>
+      <x:c r="N33" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="31.5" customHeight="1">
+      <x:c r="A34" s="76" t="str">
+        <x:v>AEQA-30</x:v>
+      </x:c>
+      <x:c r="B34" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C34" s="76" t="str">
+        <x:v>REQ-EXT-004 - Preserve an active account across logout and a new browser tab</x:v>
+      </x:c>
+      <x:c r="D34" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E34" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F34" s="76" t="str"/>
+      <x:c r="G34" s="76" t="str">
+        <x:v>REQ-EXT-004</x:v>
+      </x:c>
+      <x:c r="H34" s="76" t="str"/>
+      <x:c r="I34" s="76" t="str"/>
+      <x:c r="J34" s="76" t="str"/>
+      <x:c r="K34" s="76" t="str"/>
+      <x:c r="L34" s="76" t="str">
+        <x:v>AEQA-54</x:v>
+      </x:c>
+      <x:c r="M34" s="76" t="str"/>
+      <x:c r="N34" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="31.5" customHeight="1">
+      <x:c r="A35" s="76" t="str">
+        <x:v>AEQA-31</x:v>
+      </x:c>
+      <x:c r="B35" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C35" s="76" t="str">
+        <x:v>REQ-API-001 - Get All Products List</x:v>
+      </x:c>
+      <x:c r="D35" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E35" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F35" s="76" t="str"/>
+      <x:c r="G35" s="76" t="str">
+        <x:v>REQ-API-001</x:v>
+      </x:c>
+      <x:c r="H35" s="76" t="str"/>
+      <x:c r="I35" s="76" t="str"/>
+      <x:c r="J35" s="76" t="str"/>
+      <x:c r="K35" s="76" t="str"/>
+      <x:c r="L35" s="76" t="str">
+        <x:v>AEQA-66</x:v>
+      </x:c>
+      <x:c r="M35" s="76" t="str"/>
+      <x:c r="N35" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="31.5" customHeight="1">
+      <x:c r="A36" s="76" t="str">
+        <x:v>AEQA-32</x:v>
+      </x:c>
+      <x:c r="B36" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C36" s="76" t="str">
+        <x:v>REQ-API-002 - POST To All Products List</x:v>
+      </x:c>
+      <x:c r="D36" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E36" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F36" s="76" t="str"/>
+      <x:c r="G36" s="76" t="str">
+        <x:v>REQ-API-002</x:v>
+      </x:c>
+      <x:c r="H36" s="76" t="str"/>
+      <x:c r="I36" s="76" t="str"/>
+      <x:c r="J36" s="76" t="str"/>
+      <x:c r="K36" s="76" t="str"/>
+      <x:c r="L36" s="76" t="str">
+        <x:v>AEQA-67</x:v>
+      </x:c>
+      <x:c r="M36" s="76" t="str"/>
+      <x:c r="N36" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="31.5" customHeight="1">
+      <x:c r="A37" s="76" t="str">
+        <x:v>AEQA-33</x:v>
+      </x:c>
+      <x:c r="B37" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C37" s="76" t="str">
+        <x:v>REQ-API-003 - Get All Brands List</x:v>
+      </x:c>
+      <x:c r="D37" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E37" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F37" s="76" t="str"/>
+      <x:c r="G37" s="76" t="str">
+        <x:v>REQ-API-003</x:v>
+      </x:c>
+      <x:c r="H37" s="76" t="str"/>
+      <x:c r="I37" s="76" t="str"/>
+      <x:c r="J37" s="76" t="str"/>
+      <x:c r="K37" s="76" t="str"/>
+      <x:c r="L37" s="76" t="str">
+        <x:v>AEQA-68</x:v>
+      </x:c>
+      <x:c r="M37" s="76" t="str"/>
+      <x:c r="N37" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="31.5" customHeight="1">
+      <x:c r="A38" s="76" t="str">
+        <x:v>AEQA-34</x:v>
+      </x:c>
+      <x:c r="B38" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C38" s="76" t="str">
+        <x:v>REQ-API-004 - PUT To All Brands List</x:v>
+      </x:c>
+      <x:c r="D38" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E38" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F38" s="76" t="str"/>
+      <x:c r="G38" s="76" t="str">
+        <x:v>REQ-API-004</x:v>
+      </x:c>
+      <x:c r="H38" s="76" t="str"/>
+      <x:c r="I38" s="76" t="str"/>
+      <x:c r="J38" s="76" t="str"/>
+      <x:c r="K38" s="76" t="str"/>
+      <x:c r="L38" s="76" t="str">
+        <x:v>AEQA-69</x:v>
+      </x:c>
+      <x:c r="M38" s="76" t="str"/>
+      <x:c r="N38" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="31.5" customHeight="1">
+      <x:c r="A39" s="76" t="str">
+        <x:v>AEQA-35</x:v>
+      </x:c>
+      <x:c r="B39" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C39" s="76" t="str">
+        <x:v>REQ-API-005 - POST To Search Product</x:v>
+      </x:c>
+      <x:c r="D39" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E39" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F39" s="76" t="str"/>
+      <x:c r="G39" s="76" t="str">
+        <x:v>REQ-API-005</x:v>
+      </x:c>
+      <x:c r="H39" s="76" t="str"/>
+      <x:c r="I39" s="76" t="str"/>
+      <x:c r="J39" s="76" t="str"/>
+      <x:c r="K39" s="76" t="str"/>
+      <x:c r="L39" s="76" t="str">
+        <x:v>AEQA-70</x:v>
+      </x:c>
+      <x:c r="M39" s="76" t="str"/>
+      <x:c r="N39" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="31.5" customHeight="1">
+      <x:c r="A40" s="76" t="str">
+        <x:v>AEQA-36</x:v>
+      </x:c>
+      <x:c r="B40" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C40" s="76" t="str">
+        <x:v>REQ-API-006 - POST To Search Product without search_product 
+parameter</x:v>
+      </x:c>
+      <x:c r="D40" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E40" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F40" s="76" t="str"/>
+      <x:c r="G40" s="76" t="str">
+        <x:v>REQ-API-006</x:v>
+      </x:c>
+      <x:c r="H40" s="76" t="str"/>
+      <x:c r="I40" s="76" t="str"/>
+      <x:c r="J40" s="76" t="str"/>
+      <x:c r="K40" s="76" t="str"/>
+      <x:c r="L40" s="76" t="str">
+        <x:v>AEQA-71</x:v>
+      </x:c>
+      <x:c r="M40" s="76" t="str"/>
+      <x:c r="N40" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="31.5" customHeight="1">
+      <x:c r="A41" s="76" t="str">
+        <x:v>AEQA-37</x:v>
+      </x:c>
+      <x:c r="B41" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C41" s="76" t="str">
+        <x:v>REQ-API-007 - POST To Verify Login with valid details</x:v>
+      </x:c>
+      <x:c r="D41" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E41" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F41" s="76" t="str"/>
+      <x:c r="G41" s="76" t="str">
+        <x:v>REQ-API-007</x:v>
+      </x:c>
+      <x:c r="H41" s="76" t="str"/>
+      <x:c r="I41" s="76" t="str"/>
+      <x:c r="J41" s="76" t="str"/>
+      <x:c r="K41" s="76" t="str"/>
+      <x:c r="L41" s="76" t="str">
+        <x:v>AEQA-72</x:v>
+      </x:c>
+      <x:c r="M41" s="76" t="str"/>
+      <x:c r="N41" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="31.5" customHeight="1">
+      <x:c r="A42" s="76" t="str">
+        <x:v>AEQA-38</x:v>
+      </x:c>
+      <x:c r="B42" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C42" s="76" t="str">
+        <x:v>REQ-API-008 - POST To Verify Login without email parameter</x:v>
+      </x:c>
+      <x:c r="D42" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E42" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F42" s="76" t="str"/>
+      <x:c r="G42" s="76" t="str">
+        <x:v>REQ-API-008</x:v>
+      </x:c>
+      <x:c r="H42" s="76" t="str"/>
+      <x:c r="I42" s="76" t="str"/>
+      <x:c r="J42" s="76" t="str"/>
+      <x:c r="K42" s="76" t="str"/>
+      <x:c r="L42" s="76" t="str">
+        <x:v>AEQA-73</x:v>
+      </x:c>
+      <x:c r="M42" s="76" t="str"/>
+      <x:c r="N42" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="31.5" customHeight="1">
+      <x:c r="A43" s="76" t="str">
+        <x:v>AEQA-39</x:v>
+      </x:c>
+      <x:c r="B43" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C43" s="76" t="str">
+        <x:v>REQ-API-009 - DELETE To Verify Login</x:v>
+      </x:c>
+      <x:c r="D43" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E43" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F43" s="76" t="str"/>
+      <x:c r="G43" s="76" t="str">
+        <x:v>REQ-API-009</x:v>
+      </x:c>
+      <x:c r="H43" s="76" t="str"/>
+      <x:c r="I43" s="76" t="str"/>
+      <x:c r="J43" s="76" t="str"/>
+      <x:c r="K43" s="76" t="str"/>
+      <x:c r="L43" s="76" t="str">
+        <x:v>AEQA-74</x:v>
+      </x:c>
+      <x:c r="M43" s="76" t="str"/>
+      <x:c r="N43" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="31.5" customHeight="1">
+      <x:c r="A44" s="76" t="str">
+        <x:v>AEQA-40</x:v>
+      </x:c>
+      <x:c r="B44" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C44" s="76" t="str">
+        <x:v>REQ-API-010 - POST To Verify Login with invalid details</x:v>
+      </x:c>
+      <x:c r="D44" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E44" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F44" s="76" t="str"/>
+      <x:c r="G44" s="76" t="str">
+        <x:v>REQ-API-010</x:v>
+      </x:c>
+      <x:c r="H44" s="76" t="str"/>
+      <x:c r="I44" s="76" t="str"/>
+      <x:c r="J44" s="76" t="str"/>
+      <x:c r="K44" s="76" t="str"/>
+      <x:c r="L44" s="76" t="str">
+        <x:v>AEQA-75</x:v>
+      </x:c>
+      <x:c r="M44" s="76" t="str"/>
+      <x:c r="N44" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="31.5" customHeight="1">
+      <x:c r="A45" s="76" t="str">
+        <x:v>AEQA-41</x:v>
+      </x:c>
+      <x:c r="B45" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C45" s="76" t="str">
+        <x:v>REQ-API-011 - POST To Create/Register User Account</x:v>
+      </x:c>
+      <x:c r="D45" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E45" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F45" s="76" t="str"/>
+      <x:c r="G45" s="76" t="str">
+        <x:v>REQ-API-011</x:v>
+      </x:c>
+      <x:c r="H45" s="76" t="str"/>
+      <x:c r="I45" s="76" t="str"/>
+      <x:c r="J45" s="76" t="str"/>
+      <x:c r="K45" s="76" t="str"/>
+      <x:c r="L45" s="76" t="str">
+        <x:v>AEQA-76</x:v>
+      </x:c>
+      <x:c r="M45" s="76" t="str"/>
+      <x:c r="N45" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="31.5" customHeight="1">
+      <x:c r="A46" s="76" t="str">
+        <x:v>AEQA-42</x:v>
+      </x:c>
+      <x:c r="B46" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C46" s="76" t="str">
+        <x:v>REQ-API-012 - DELETE METHOD To Delete User Account</x:v>
+      </x:c>
+      <x:c r="D46" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E46" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F46" s="76" t="str"/>
+      <x:c r="G46" s="76" t="str">
+        <x:v>REQ-API-012</x:v>
+      </x:c>
+      <x:c r="H46" s="76" t="str"/>
+      <x:c r="I46" s="76" t="str"/>
+      <x:c r="J46" s="76" t="str"/>
+      <x:c r="K46" s="76" t="str"/>
+      <x:c r="L46" s="76" t="str">
+        <x:v>AEQA-77</x:v>
+      </x:c>
+      <x:c r="M46" s="76" t="str"/>
+      <x:c r="N46" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="31.5" customHeight="1">
+      <x:c r="A47" s="76" t="str">
+        <x:v>AEQA-43</x:v>
+      </x:c>
+      <x:c r="B47" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C47" s="76" t="str">
+        <x:v>REQ-API-013 - PUT METHOD To Update User Account</x:v>
+      </x:c>
+      <x:c r="D47" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E47" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F47" s="76" t="str"/>
+      <x:c r="G47" s="76" t="str">
+        <x:v>REQ-API-013</x:v>
+      </x:c>
+      <x:c r="H47" s="76" t="str"/>
+      <x:c r="I47" s="76" t="str"/>
+      <x:c r="J47" s="76" t="str"/>
+      <x:c r="K47" s="76" t="str"/>
+      <x:c r="L47" s="76" t="str">
+        <x:v>AEQA-78</x:v>
+      </x:c>
+      <x:c r="M47" s="76" t="str"/>
+      <x:c r="N47" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="31.5" customHeight="1">
+      <x:c r="A48" s="76" t="str">
+        <x:v>AEQA-44</x:v>
+      </x:c>
+      <x:c r="B48" s="76" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C48" s="76" t="str">
+        <x:v>REQ-API-014 - GET user account detail by email</x:v>
+      </x:c>
+      <x:c r="D48" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E48" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F48" s="76" t="str"/>
+      <x:c r="G48" s="76" t="str">
+        <x:v>REQ-API-014</x:v>
+      </x:c>
+      <x:c r="H48" s="76" t="str"/>
+      <x:c r="I48" s="76" t="str"/>
+      <x:c r="J48" s="76" t="str"/>
+      <x:c r="K48" s="76" t="str"/>
+      <x:c r="L48" s="76" t="str">
+        <x:v>AEQA-79</x:v>
+      </x:c>
+      <x:c r="M48" s="76" t="str"/>
+      <x:c r="N48" s="76" t="str">
+        <x:v>10/Aug/26 8:02 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="31.5" customHeight="1">
+      <x:c r="A49" s="76" t="str">
+        <x:v>AEQA-45</x:v>
+      </x:c>
+      <x:c r="B49" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C49" s="76" t="str">
+        <x:v>AE-SIGNUP-001 - Verify a new user can begin registration using a valid name and unregistered email address</x:v>
+      </x:c>
+      <x:c r="D49" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E49" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F49" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G49" s="76" t="str"/>
+      <x:c r="H49" s="76" t="str">
+        <x:v>AE-SIGNUP-001</x:v>
+      </x:c>
+      <x:c r="I49" s="76" t="str"/>
+      <x:c r="J49" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K49" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L49" s="76" t="str">
+        <x:v>AEQA-1</x:v>
+      </x:c>
+      <x:c r="M49" s="76" t="str"/>
+      <x:c r="N49" s="76" t="str">
+        <x:v>10/Aug/26 7:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="31.5" customHeight="1">
+      <x:c r="A50" s="76" t="str">
+        <x:v>AEQA-46</x:v>
+      </x:c>
+      <x:c r="B50" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C50" s="76" t="str">
+        <x:v>AE-SIGNUP-002 - Verify a new user can create an account using valid required information</x:v>
+      </x:c>
+      <x:c r="D50" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E50" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F50" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G50" s="76" t="str"/>
+      <x:c r="H50" s="76" t="str">
+        <x:v>AE-SIGNUP-002</x:v>
+      </x:c>
+      <x:c r="I50" s="76" t="str"/>
+      <x:c r="J50" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K50" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L50" s="76" t="str">
+        <x:v>AEQA-1</x:v>
+      </x:c>
+      <x:c r="M50" s="76" t="str"/>
+      <x:c r="N50" s="76" t="str">
+        <x:v>10/Aug/26 7:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="31.5" customHeight="1">
+      <x:c r="A51" s="76" t="str">
+        <x:v>AEQA-47</x:v>
+      </x:c>
+      <x:c r="B51" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C51" s="76" t="str">
+        <x:v>AE-SIGNUP-003 - Verify that registration is prevented when a user enters invalid email address</x:v>
+      </x:c>
+      <x:c r="D51" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E51" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F51" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G51" s="76" t="str"/>
+      <x:c r="H51" s="76" t="str">
+        <x:v>AE-SIGNUP-003</x:v>
+      </x:c>
+      <x:c r="I51" s="76" t="str"/>
+      <x:c r="J51" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K51" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L51" s="76" t="str">
+        <x:v>AEQA-27</x:v>
+      </x:c>
+      <x:c r="M51" s="76" t="str"/>
+      <x:c r="N51" s="76" t="str">
+        <x:v>10/Aug/26 7:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="31.5" customHeight="1">
+      <x:c r="A52" s="76" t="str">
+        <x:v>AEQA-48</x:v>
+      </x:c>
+      <x:c r="B52" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C52" s="76" t="str">
+        <x:v>AE-SIGNUP-004 - Verify that account creation is prevented when required fields are left blank</x:v>
+      </x:c>
+      <x:c r="D52" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E52" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F52" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G52" s="76" t="str"/>
+      <x:c r="H52" s="76" t="str">
+        <x:v>AE-SIGNUP-004</x:v>
+      </x:c>
+      <x:c r="I52" s="76" t="str"/>
+      <x:c r="J52" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K52" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L52" s="76" t="str">
+        <x:v>AEQA-28</x:v>
+      </x:c>
+      <x:c r="M52" s="76" t="str"/>
+      <x:c r="N52" s="76" t="str">
+        <x:v>10/Aug/26 7:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="31.5" customHeight="1">
+      <x:c r="A53" s="76" t="str">
+        <x:v>AEQA-49</x:v>
+      </x:c>
+      <x:c r="B53" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C53" s="76" t="str">
+        <x:v>AE-LOGIN-001 - Verify that a registered user can login using valid credentials</x:v>
+      </x:c>
+      <x:c r="D53" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E53" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F53" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G53" s="76" t="str"/>
+      <x:c r="H53" s="76" t="str">
+        <x:v>AE-LOGIN-001</x:v>
+      </x:c>
+      <x:c r="I53" s="76" t="str"/>
+      <x:c r="J53" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K53" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L53" s="76" t="str">
+        <x:v>AEQA-2</x:v>
+      </x:c>
+      <x:c r="M53" s="76" t="str"/>
+      <x:c r="N53" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="31.5" customHeight="1">
+      <x:c r="A54" s="76" t="str">
+        <x:v>AEQA-50</x:v>
+      </x:c>
+      <x:c r="B54" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C54" s="76" t="str">
+        <x:v>AE-LOGIN-002 - Verify that the login form rejects SQL injection input without authenticating the user</x:v>
+      </x:c>
+      <x:c r="D54" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E54" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F54" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G54" s="76" t="str"/>
+      <x:c r="H54" s="76" t="str">
+        <x:v>AE-LOGIN-002</x:v>
+      </x:c>
+      <x:c r="I54" s="76" t="str"/>
+      <x:c r="J54" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K54" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L54" s="76" t="str">
+        <x:v>AEQA-29</x:v>
+      </x:c>
+      <x:c r="M54" s="76" t="str"/>
+      <x:c r="N54" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="31.5" customHeight="1">
+      <x:c r="A55" s="76" t="str">
+        <x:v>AEQA-51</x:v>
+      </x:c>
+      <x:c r="B55" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C55" s="76" t="str">
+        <x:v>AE-LOGIN-003 - Verify that login is rejected when a registered email address is entered with an incorrect password</x:v>
+      </x:c>
+      <x:c r="D55" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E55" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F55" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G55" s="76" t="str"/>
+      <x:c r="H55" s="76" t="str">
+        <x:v>AE-LOGIN-003</x:v>
+      </x:c>
+      <x:c r="I55" s="76" t="str"/>
+      <x:c r="J55" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K55" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L55" s="76" t="str">
+        <x:v>AEQA-3</x:v>
+      </x:c>
+      <x:c r="M55" s="76" t="str"/>
+      <x:c r="N55" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="31.5" customHeight="1">
+      <x:c r="A56" s="76" t="str">
+        <x:v>AEQA-52</x:v>
+      </x:c>
+      <x:c r="B56" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C56" s="76" t="str">
+        <x:v>AE-LOGOUT-001 - Verify that an authenticated user can successfully logout</x:v>
+      </x:c>
+      <x:c r="D56" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E56" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F56" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G56" s="76" t="str"/>
+      <x:c r="H56" s="76" t="str">
+        <x:v>AE-LOGOUT-001</x:v>
+      </x:c>
+      <x:c r="I56" s="76" t="str"/>
+      <x:c r="J56" s="76" t="str">
+        <x:v>Fail</x:v>
+      </x:c>
+      <x:c r="K56" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L56" s="76" t="str">
+        <x:v>AEQA-4</x:v>
+      </x:c>
+      <x:c r="M56" s="76" t="str"/>
+      <x:c r="N56" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="31.5" customHeight="1">
+      <x:c r="A57" s="76" t="str">
+        <x:v>AEQA-53</x:v>
+      </x:c>
+      <x:c r="B57" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C57" s="76" t="str">
+        <x:v>AE-ACCOUNT-001 - Verify that an authenticated user can permanently delete their account</x:v>
+      </x:c>
+      <x:c r="D57" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E57" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F57" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G57" s="76" t="str"/>
+      <x:c r="H57" s="76" t="str">
+        <x:v>AE-ACCOUNT-001</x:v>
+      </x:c>
+      <x:c r="I57" s="76" t="str"/>
+      <x:c r="J57" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K57" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L57" s="76" t="str">
+        <x:v>AEQA-1
+AEQA-2</x:v>
+      </x:c>
+      <x:c r="M57" s="76" t="str"/>
+      <x:c r="N57" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="31.5" customHeight="1">
+      <x:c r="A58" s="76" t="str">
+        <x:v>AEQA-54</x:v>
+      </x:c>
+      <x:c r="B58" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C58" s="76" t="str">
+        <x:v>AE-ACCOUNT-002 - Verify that a registered account remains active and accessible after the user logs out</x:v>
+      </x:c>
+      <x:c r="D58" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E58" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F58" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G58" s="76" t="str"/>
+      <x:c r="H58" s="76" t="str">
+        <x:v>AE-ACCOUNT-002</x:v>
+      </x:c>
+      <x:c r="I58" s="76" t="str"/>
+      <x:c r="J58" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K58" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L58" s="76" t="str">
+        <x:v>AEQA-30</x:v>
+      </x:c>
+      <x:c r="M58" s="76" t="str"/>
+      <x:c r="N58" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="31.5" customHeight="1">
+      <x:c r="A59" s="76" t="str">
+        <x:v>AEQA-55</x:v>
+      </x:c>
+      <x:c r="B59" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C59" s="76" t="str">
+        <x:v>AE-SIGNUP-005 - Verify that registration is rejected when an existing email address is used</x:v>
+      </x:c>
+      <x:c r="D59" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E59" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F59" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G59" s="76" t="str"/>
+      <x:c r="H59" s="76" t="str">
+        <x:v>AE-SIGNUP-005</x:v>
+      </x:c>
+      <x:c r="I59" s="76" t="str"/>
+      <x:c r="J59" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K59" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L59" s="76" t="str">
+        <x:v>AEQA-5</x:v>
+      </x:c>
+      <x:c r="M59" s="76" t="str"/>
+      <x:c r="N59" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="31.5" customHeight="1">
+      <x:c r="A60" s="76" t="str">
+        <x:v>AEQA-56</x:v>
+      </x:c>
+      <x:c r="B60" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C60" s="76" t="str">
+        <x:v>AE-LOGIN-004 - Verify that login is rejected when an unregistered email address is entered</x:v>
+      </x:c>
+      <x:c r="D60" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E60" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F60" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G60" s="76" t="str"/>
+      <x:c r="H60" s="76" t="str">
+        <x:v>AE-LOGIN-004</x:v>
+      </x:c>
+      <x:c r="I60" s="76" t="str"/>
+      <x:c r="J60" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K60" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L60" s="76" t="str">
+        <x:v>AEQA-3</x:v>
+      </x:c>
+      <x:c r="M60" s="76" t="str"/>
+      <x:c r="N60" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="31.5" customHeight="1">
+      <x:c r="A61" s="76" t="str">
+        <x:v>AEQA-57</x:v>
+      </x:c>
+      <x:c r="B61" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C61" s="76" t="str">
+        <x:v>AE-PRODUCT-001 - Verify that the All Products page and product details display correctly</x:v>
+      </x:c>
+      <x:c r="D61" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E61" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F61" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G61" s="76" t="str"/>
+      <x:c r="H61" s="76" t="str">
+        <x:v>AE-PRODUCT-001</x:v>
+      </x:c>
+      <x:c r="I61" s="76" t="str"/>
+      <x:c r="J61" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K61" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L61" s="76" t="str">
+        <x:v>AEQA-8</x:v>
+      </x:c>
+      <x:c r="M61" s="76" t="str"/>
+      <x:c r="N61" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="31.5" customHeight="1">
+      <x:c r="A62" s="76" t="str">
+        <x:v>AEQA-58</x:v>
+      </x:c>
+      <x:c r="B62" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C62" s="76" t="str">
+        <x:v>AE-PRODUCT-002 - Verify that product search returns relevant products</x:v>
+      </x:c>
+      <x:c r="D62" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E62" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F62" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G62" s="76" t="str"/>
+      <x:c r="H62" s="76" t="str">
+        <x:v>AE-PRODUCT-002</x:v>
+      </x:c>
+      <x:c r="I62" s="76" t="str"/>
+      <x:c r="J62" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K62" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L62" s="76" t="str">
+        <x:v>AEQA-9</x:v>
+      </x:c>
+      <x:c r="M62" s="76" t="str"/>
+      <x:c r="N62" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="31.5" customHeight="1">
+      <x:c r="A63" s="76" t="str">
+        <x:v>AEQA-59</x:v>
+      </x:c>
+      <x:c r="B63" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C63" s="76" t="str">
+        <x:v>AE-CART-001 - Verify that two products can be added to the cart with correct prices, quantities, and totals</x:v>
+      </x:c>
+      <x:c r="D63" s="76" t="str">
+        <x:v>Selected for Development</x:v>
+      </x:c>
+      <x:c r="E63" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F63" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G63" s="76" t="str"/>
+      <x:c r="H63" s="76" t="str">
+        <x:v>AE-CART-001</x:v>
+      </x:c>
+      <x:c r="I63" s="76" t="str"/>
+      <x:c r="J63" s="76" t="str">
+        <x:v>Fail</x:v>
+      </x:c>
+      <x:c r="K63" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L63" s="76" t="str">
+        <x:v>AEQA-12</x:v>
+      </x:c>
+      <x:c r="M63" s="76" t="str"/>
+      <x:c r="N63" s="76" t="str">
+        <x:v>10/Aug/26 8:34 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="31.5" customHeight="1">
+      <x:c r="A64" s="76" t="str">
+        <x:v>AEQA-60</x:v>
+      </x:c>
+      <x:c r="B64" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C64" s="76" t="str">
+        <x:v>AE-CART-002 - Verify that a product is displayed in the cart with the selected quantity</x:v>
+      </x:c>
+      <x:c r="D64" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E64" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F64" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G64" s="76" t="str"/>
+      <x:c r="H64" s="76" t="str">
+        <x:v>AE-CART-002</x:v>
+      </x:c>
+      <x:c r="I64" s="76" t="str"/>
+      <x:c r="J64" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K64" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L64" s="76" t="str">
+        <x:v>AEQA-13</x:v>
+      </x:c>
+      <x:c r="M64" s="76" t="str"/>
+      <x:c r="N64" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="31.5" customHeight="1">
+      <x:c r="A65" s="76" t="str">
+        <x:v>AEQA-61</x:v>
+      </x:c>
+      <x:c r="B65" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C65" s="76" t="str">
+        <x:v>AE-CART-003 - Verify that a product can be removed from the cart</x:v>
+      </x:c>
+      <x:c r="D65" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E65" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F65" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G65" s="76" t="str"/>
+      <x:c r="H65" s="76" t="str">
+        <x:v>AE-CART-003</x:v>
+      </x:c>
+      <x:c r="I65" s="76" t="str"/>
+      <x:c r="J65" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K65" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L65" s="76" t="str">
+        <x:v>AEQA-17</x:v>
+      </x:c>
+      <x:c r="M65" s="76" t="str"/>
+      <x:c r="N65" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="31.5" customHeight="1">
+      <x:c r="A66" s="76" t="str">
+        <x:v>AEQA-62</x:v>
+      </x:c>
+      <x:c r="B66" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C66" s="76" t="str">
+        <x:v>AE-CONTACT-001 - Verify that a logged-out user can submit the Contact Us form successfully with a file attachment</x:v>
+      </x:c>
+      <x:c r="D66" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E66" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F66" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G66" s="76" t="str"/>
+      <x:c r="H66" s="76" t="str">
+        <x:v>AE-CONTACT-001</x:v>
+      </x:c>
+      <x:c r="I66" s="76" t="str"/>
+      <x:c r="J66" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K66" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L66" s="76" t="str">
+        <x:v>AEQA-6</x:v>
+      </x:c>
+      <x:c r="M66" s="76" t="str"/>
+      <x:c r="N66" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="31.5" customHeight="1">
+      <x:c r="A67" s="76" t="str">
+        <x:v>AEQA-63</x:v>
+      </x:c>
+      <x:c r="B67" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C67" s="76" t="str">
+        <x:v>AE-NAV-001 - Verify that a logged-out user can navigate to the Test Cases page successfully</x:v>
+      </x:c>
+      <x:c r="D67" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E67" s="76" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="F67" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G67" s="76" t="str"/>
+      <x:c r="H67" s="76" t="str">
+        <x:v>AE-NAV-001</x:v>
+      </x:c>
+      <x:c r="I67" s="76" t="str"/>
+      <x:c r="J67" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K67" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L67" s="76" t="str">
+        <x:v>AEQA-7</x:v>
+      </x:c>
+      <x:c r="M67" s="76" t="str"/>
+      <x:c r="N67" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="31.5" customHeight="1">
+      <x:c r="A68" s="76" t="str">
+        <x:v>AEQA-64</x:v>
+      </x:c>
+      <x:c r="B68" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C68" s="76" t="str">
+        <x:v>AE-SUB-001 - Verify that a logged-out user can subscribe successfully from the home-page footer</x:v>
+      </x:c>
+      <x:c r="D68" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E68" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F68" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G68" s="76" t="str"/>
+      <x:c r="H68" s="76" t="str">
+        <x:v>AE-SUB-001</x:v>
+      </x:c>
+      <x:c r="I68" s="76" t="str"/>
+      <x:c r="J68" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K68" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L68" s="76" t="str">
+        <x:v>AEQA-10</x:v>
+      </x:c>
+      <x:c r="M68" s="76" t="str"/>
+      <x:c r="N68" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="31.5" customHeight="1">
+      <x:c r="A69" s="76" t="str">
+        <x:v>AEQA-65</x:v>
+      </x:c>
+      <x:c r="B69" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C69" s="76" t="str">
+        <x:v>AE-SUB-002 - Verify that a logged-out user can subscribe successfully from the cart-page footer</x:v>
+      </x:c>
+      <x:c r="D69" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E69" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F69" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G69" s="76" t="str"/>
+      <x:c r="H69" s="76" t="str">
+        <x:v>AE-SUB-002</x:v>
+      </x:c>
+      <x:c r="I69" s="76" t="str"/>
+      <x:c r="J69" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K69" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L69" s="76" t="str">
+        <x:v>AEQA-11</x:v>
+      </x:c>
+      <x:c r="M69" s="76" t="str"/>
+      <x:c r="N69" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="31.5" customHeight="1">
+      <x:c r="A70" s="76" t="str">
+        <x:v>AEQA-66</x:v>
+      </x:c>
+      <x:c r="B70" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C70" s="76" t="str">
+        <x:v>API-PRODUCT-001 - Verify retrieval of the complete products list</x:v>
+      </x:c>
+      <x:c r="D70" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E70" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F70" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G70" s="76" t="str"/>
+      <x:c r="H70" s="76" t="str">
+        <x:v>API-PRODUCT-001</x:v>
+      </x:c>
+      <x:c r="I70" s="76" t="str"/>
+      <x:c r="J70" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K70" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L70" s="76" t="str">
+        <x:v>AEQA-31</x:v>
+      </x:c>
+      <x:c r="M70" s="76" t="str"/>
+      <x:c r="N70" s="76" t="str">
+        <x:v>10/Aug/26 7:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="31.5" customHeight="1">
+      <x:c r="A71" s="76" t="str">
+        <x:v>AEQA-67</x:v>
+      </x:c>
+      <x:c r="B71" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C71" s="76" t="str">
+        <x:v>API-PRODUCT-002 - Verify POST is rejected for the products-list endpoint</x:v>
+      </x:c>
+      <x:c r="D71" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E71" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F71" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G71" s="76" t="str"/>
+      <x:c r="H71" s="76" t="str">
+        <x:v>API-PRODUCT-002</x:v>
+      </x:c>
+      <x:c r="I71" s="76" t="str"/>
+      <x:c r="J71" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K71" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L71" s="76" t="str">
+        <x:v>AEQA-32</x:v>
+      </x:c>
+      <x:c r="M71" s="76" t="str"/>
+      <x:c r="N71" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="31.5" customHeight="1">
+      <x:c r="A72" s="76" t="str">
+        <x:v>AEQA-68</x:v>
+      </x:c>
+      <x:c r="B72" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C72" s="76" t="str">
+        <x:v>API-BRAND-001 - Verify retrieval of the complete brands list</x:v>
+      </x:c>
+      <x:c r="D72" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E72" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F72" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G72" s="76" t="str"/>
+      <x:c r="H72" s="76" t="str">
+        <x:v>API-BRAND-001</x:v>
+      </x:c>
+      <x:c r="I72" s="76" t="str"/>
+      <x:c r="J72" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K72" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L72" s="76" t="str">
+        <x:v>AEQA-33</x:v>
+      </x:c>
+      <x:c r="M72" s="76" t="str"/>
+      <x:c r="N72" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="31.5" customHeight="1">
+      <x:c r="A73" s="76" t="str">
+        <x:v>AEQA-69</x:v>
+      </x:c>
+      <x:c r="B73" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C73" s="76" t="str">
+        <x:v>API-BRAND-002 - Verify PUT is rejected for the brands-list endpoint</x:v>
+      </x:c>
+      <x:c r="D73" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E73" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F73" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G73" s="76" t="str"/>
+      <x:c r="H73" s="76" t="str">
+        <x:v>API-BRAND-002</x:v>
+      </x:c>
+      <x:c r="I73" s="76" t="str"/>
+      <x:c r="J73" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K73" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L73" s="76" t="str">
+        <x:v>AEQA-34</x:v>
+      </x:c>
+      <x:c r="M73" s="76" t="str"/>
+      <x:c r="N73" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="31.5" customHeight="1">
+      <x:c r="A74" s="76" t="str">
+        <x:v>AEQA-70</x:v>
+      </x:c>
+      <x:c r="B74" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C74" s="76" t="str">
+        <x:v>API-SEARCH-001 - Verify products can be searched using a valid search_product value</x:v>
+      </x:c>
+      <x:c r="D74" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E74" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F74" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G74" s="76" t="str"/>
+      <x:c r="H74" s="76" t="str">
+        <x:v>API-SEARCH-001</x:v>
+      </x:c>
+      <x:c r="I74" s="76" t="str"/>
+      <x:c r="J74" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K74" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L74" s="76" t="str">
+        <x:v>AEQA-35</x:v>
+      </x:c>
+      <x:c r="M74" s="76" t="str"/>
+      <x:c r="N74" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="31.5" customHeight="1">
+      <x:c r="A75" s="76" t="str">
+        <x:v>AEQA-71</x:v>
+      </x:c>
+      <x:c r="B75" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C75" s="76" t="str">
+        <x:v>API-SEARCH-002 - Verify search validation when search_product value is omitted</x:v>
+      </x:c>
+      <x:c r="D75" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E75" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F75" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G75" s="76" t="str"/>
+      <x:c r="H75" s="76" t="str">
+        <x:v>API-SEARCH-002</x:v>
+      </x:c>
+      <x:c r="I75" s="76" t="str"/>
+      <x:c r="J75" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K75" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L75" s="76" t="str">
+        <x:v>AEQA-36</x:v>
+      </x:c>
+      <x:c r="M75" s="76" t="str"/>
+      <x:c r="N75" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="31.5" customHeight="1">
+      <x:c r="A76" s="76" t="str">
+        <x:v>AEQA-72</x:v>
+      </x:c>
+      <x:c r="B76" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C76" s="76" t="str">
+        <x:v>API-AUTH-001 - Verify login API with valid credentials</x:v>
+      </x:c>
+      <x:c r="D76" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E76" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F76" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G76" s="76" t="str"/>
+      <x:c r="H76" s="76" t="str">
+        <x:v>API-AUTH-001</x:v>
+      </x:c>
+      <x:c r="I76" s="76" t="str"/>
+      <x:c r="J76" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K76" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L76" s="76" t="str">
+        <x:v>AEQA-37</x:v>
+      </x:c>
+      <x:c r="M76" s="76" t="str"/>
+      <x:c r="N76" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="31.5" customHeight="1">
+      <x:c r="A77" s="76" t="str">
+        <x:v>AEQA-73</x:v>
+      </x:c>
+      <x:c r="B77" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C77" s="76" t="str">
+        <x:v>API-AUTH-002 - Verify login validation when email is omitted</x:v>
+      </x:c>
+      <x:c r="D77" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E77" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F77" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G77" s="76" t="str"/>
+      <x:c r="H77" s="76" t="str">
+        <x:v>API-AUTH-002</x:v>
+      </x:c>
+      <x:c r="I77" s="76" t="str"/>
+      <x:c r="J77" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K77" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L77" s="76" t="str">
+        <x:v>AEQA-38</x:v>
+      </x:c>
+      <x:c r="M77" s="76" t="str"/>
+      <x:c r="N77" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="31.5" customHeight="1">
+      <x:c r="A78" s="76" t="str">
+        <x:v>AEQA-74</x:v>
+      </x:c>
+      <x:c r="B78" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C78" s="76" t="str">
+        <x:v>API-AUTH-003 - Verify DELETE is rejected for the login-verification endpoint</x:v>
+      </x:c>
+      <x:c r="D78" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E78" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F78" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G78" s="76" t="str"/>
+      <x:c r="H78" s="76" t="str">
+        <x:v>API-AUTH-003</x:v>
+      </x:c>
+      <x:c r="I78" s="76" t="str"/>
+      <x:c r="J78" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K78" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L78" s="76" t="str">
+        <x:v>AEQA-39</x:v>
+      </x:c>
+      <x:c r="M78" s="76" t="str"/>
+      <x:c r="N78" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="31.5" customHeight="1">
+      <x:c r="A79" s="76" t="str">
+        <x:v>AEQA-75</x:v>
+      </x:c>
+      <x:c r="B79" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C79" s="76" t="str">
+        <x:v>API-AUTH-004 - Verify login API rejects invalid credentials</x:v>
+      </x:c>
+      <x:c r="D79" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E79" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F79" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G79" s="76" t="str"/>
+      <x:c r="H79" s="76" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="I79" s="76" t="str"/>
+      <x:c r="J79" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K79" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L79" s="76" t="str">
+        <x:v>AEQA-40</x:v>
+      </x:c>
+      <x:c r="M79" s="76" t="str"/>
+      <x:c r="N79" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="31.5" customHeight="1">
+      <x:c r="A80" s="76" t="str">
+        <x:v>AEQA-76</x:v>
+      </x:c>
+      <x:c r="B80" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C80" s="76" t="str">
+        <x:v>API-ACCOUNT-001 - Verify a user account can be created through the API</x:v>
+      </x:c>
+      <x:c r="D80" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E80" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F80" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G80" s="76" t="str"/>
+      <x:c r="H80" s="76" t="str">
+        <x:v>API-ACCOUNT-001</x:v>
+      </x:c>
+      <x:c r="I80" s="76" t="str"/>
+      <x:c r="J80" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K80" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L80" s="76" t="str">
+        <x:v>AEQA-41</x:v>
+      </x:c>
+      <x:c r="M80" s="76" t="str"/>
+      <x:c r="N80" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="31.5" customHeight="1">
+      <x:c r="A81" s="76" t="str">
+        <x:v>AEQA-77</x:v>
+      </x:c>
+      <x:c r="B81" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C81" s="76" t="str">
+        <x:v>API-ACCOUNT-002 - Verify a user account can be deleted through the API</x:v>
+      </x:c>
+      <x:c r="D81" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E81" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F81" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G81" s="76" t="str"/>
+      <x:c r="H81" s="76" t="str">
+        <x:v>API-ACCOUNT-002</x:v>
+      </x:c>
+      <x:c r="I81" s="76" t="str"/>
+      <x:c r="J81" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K81" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L81" s="76" t="str">
+        <x:v>AEQA-42</x:v>
+      </x:c>
+      <x:c r="M81" s="76" t="str"/>
+      <x:c r="N81" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="31.5" customHeight="1">
+      <x:c r="A82" s="76" t="str">
+        <x:v>AEQA-78</x:v>
+      </x:c>
+      <x:c r="B82" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C82" s="76" t="str">
+        <x:v>API-ACCOUNT-003 - Verify a user account can be updated through the API</x:v>
+      </x:c>
+      <x:c r="D82" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E82" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F82" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G82" s="76" t="str"/>
+      <x:c r="H82" s="76" t="str">
+        <x:v>API-ACCOUNT-003</x:v>
+      </x:c>
+      <x:c r="I82" s="76" t="str"/>
+      <x:c r="J82" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K82" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L82" s="76" t="str">
+        <x:v>AEQA-43</x:v>
+      </x:c>
+      <x:c r="M82" s="76" t="str"/>
+      <x:c r="N82" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="31.5" customHeight="1">
+      <x:c r="A83" s="76" t="str">
+        <x:v>AEQA-79</x:v>
+      </x:c>
+      <x:c r="B83" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C83" s="76" t="str">
+        <x:v>API-ACCOUNT-004 - Verify user-account details can be retrieved by email</x:v>
+      </x:c>
+      <x:c r="D83" s="76" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E83" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F83" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G83" s="76" t="str"/>
+      <x:c r="H83" s="76" t="str">
+        <x:v>API-ACCOUNT-004</x:v>
+      </x:c>
+      <x:c r="I83" s="76" t="str"/>
+      <x:c r="J83" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K83" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L83" s="76" t="str">
+        <x:v>AEQA-44</x:v>
+      </x:c>
+      <x:c r="M83" s="76" t="str"/>
+      <x:c r="N83" s="76" t="str">
+        <x:v>10/Aug/26 8:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="31.5" customHeight="1">
+      <x:c r="A84" s="76" t="str">
+        <x:v>AEQA-80</x:v>
+      </x:c>
+      <x:c r="B84" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C84" s="76" t="str">
+        <x:v>AE-BUG-001 - Authenticated user information remains visible after logout when navigating back</x:v>
+      </x:c>
+      <x:c r="D84" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E84" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F84" s="76" t="str"/>
+      <x:c r="G84" s="76" t="str"/>
+      <x:c r="H84" s="76" t="str"/>
+      <x:c r="I84" s="76" t="str">
+        <x:v>AE-BUG-001</x:v>
+      </x:c>
+      <x:c r="J84" s="76" t="str"/>
+      <x:c r="K84" s="76" t="str"/>
+      <x:c r="L84" s="76" t="str"/>
+      <x:c r="M84" s="76" t="str"/>
+      <x:c r="N84" s="76" t="str">
+        <x:v>10/Aug/26 7:08 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="31.5" customHeight="1">
+      <x:c r="A85" s="76" t="str">
+        <x:v>AEQA-81</x:v>
+      </x:c>
+      <x:c r="B85" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C85" s="76" t="str">
+        <x:v>AE-BUG-002 - Repeated logout request causes an unhandled KeyError and exposes internal debugging information</x:v>
+      </x:c>
+      <x:c r="D85" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E85" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F85" s="76" t="str"/>
+      <x:c r="G85" s="76" t="str"/>
+      <x:c r="H85" s="76" t="str"/>
+      <x:c r="I85" s="76" t="str">
+        <x:v>AE-BUG-002</x:v>
+      </x:c>
+      <x:c r="J85" s="76" t="str"/>
+      <x:c r="K85" s="76" t="str"/>
+      <x:c r="L85" s="76" t="str"/>
+      <x:c r="M85" s="76" t="str"/>
+      <x:c r="N85" s="76" t="str">
+        <x:v>10/Aug/26 7:08 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="31.5" customHeight="1">
+      <x:c r="A86" s="76" t="str">
+        <x:v>AEQA-82</x:v>
+      </x:c>
+      <x:c r="B86" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C86" s="76" t="str">
+        <x:v>AE-BUG-003 - Cart does not display the overall total after multiple products are added</x:v>
+      </x:c>
+      <x:c r="D86" s="76" t="str">
+        <x:v>Selected for Development</x:v>
+      </x:c>
+      <x:c r="E86" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F86" s="76" t="str"/>
+      <x:c r="G86" s="76" t="str"/>
+      <x:c r="H86" s="76" t="str"/>
+      <x:c r="I86" s="76" t="str">
+        <x:v>AE-BUG-003</x:v>
+      </x:c>
+      <x:c r="J86" s="76" t="str"/>
+      <x:c r="K86" s="76" t="str"/>
+      <x:c r="L86" s="76" t="str"/>
+      <x:c r="M86" s="76" t="str"/>
+      <x:c r="N86" s="76" t="str">
+        <x:v>10/Aug/26 8:36 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="31.5" customHeight="1">
+      <x:c r="A87" s="76" t="str">
+        <x:v>AEQA-83</x:v>
+      </x:c>
+      <x:c r="B87" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C87" s="76" t="str">
+        <x:v>AE-BUG-004 - The quantity field on the product-detail page does not respond when the user attempts to edit it. As a result, the user cannot select the desired quantity before adding the product to the cart.</x:v>
+      </x:c>
+      <x:c r="D87" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E87" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F87" s="76" t="str"/>
+      <x:c r="G87" s="76" t="str"/>
+      <x:c r="H87" s="76" t="str"/>
+      <x:c r="I87" s="76" t="str">
+        <x:v>AE-BUG-004</x:v>
+      </x:c>
+      <x:c r="J87" s="76" t="str"/>
+      <x:c r="K87" s="76" t="str"/>
+      <x:c r="L87" s="76" t="str"/>
+      <x:c r="M87" s="76" t="str"/>
+      <x:c r="N87" s="76" t="str">
+        <x:v>10/Aug/26 7:09 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="31.5" customHeight="1">
+      <x:c r="A88" s="76" t="str">
+        <x:v>AEQA-84</x:v>
+      </x:c>
+      <x:c r="B88" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C88" s="76" t="str">
+        <x:v>BUG-API-001 - Products List API returns HTTP 200 instead of 405 for unsupported POST request</x:v>
+      </x:c>
+      <x:c r="D88" s="76" t="str">
+        <x:v>Selected for Development</x:v>
+      </x:c>
+      <x:c r="E88" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F88" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G88" s="76" t="str"/>
+      <x:c r="H88" s="76" t="str"/>
+      <x:c r="I88" s="76" t="str">
+        <x:v>BUG-API-001</x:v>
+      </x:c>
+      <x:c r="J88" s="76" t="str"/>
+      <x:c r="K88" s="76" t="str"/>
+      <x:c r="L88" s="76" t="str"/>
+      <x:c r="M88" s="76" t="str"/>
+      <x:c r="N88" s="76" t="str">
+        <x:v>11/Aug/26 9:29 AM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="31.5" customHeight="1">
+      <x:c r="A89" s="76" t="str">
+        <x:v>AEQA-85</x:v>
+      </x:c>
+      <x:c r="B89" s="76" t="str">
+        <x:v>Bug</x:v>
+      </x:c>
+      <x:c r="C89" s="76" t="str">
+        <x:v>BUG-API-002 - Search Product API returns all products when required search_product parameter is omitted</x:v>
+      </x:c>
+      <x:c r="D89" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E89" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F89" s="76" t="str"/>
+      <x:c r="G89" s="76" t="str"/>
+      <x:c r="H89" s="76" t="str"/>
+      <x:c r="I89" s="76" t="str">
+        <x:v>BUG-API-002</x:v>
+      </x:c>
+      <x:c r="J89" s="76" t="str"/>
+      <x:c r="K89" s="76" t="str"/>
+      <x:c r="L89" s="76" t="str"/>
+      <x:c r="M89" s="76" t="str"/>
+      <x:c r="N89" s="76" t="str">
+        <x:v>10/Aug/26 7:37 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="31.5" customHeight="1">
+      <x:c r="A90" s="76" t="str">
+        <x:v>AEQA-86</x:v>
+      </x:c>
+      <x:c r="B90" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C90" s="76" t="str">
+        <x:v>Define the register-during-checkout end-to-end test flow</x:v>
+      </x:c>
+      <x:c r="D90" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E90" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F90" s="76" t="str"/>
+      <x:c r="G90" s="76" t="str"/>
+      <x:c r="H90" s="76" t="str"/>
+      <x:c r="I90" s="76" t="str"/>
+      <x:c r="J90" s="76" t="str"/>
+      <x:c r="K90" s="76" t="str"/>
+      <x:c r="L90" s="76" t="str"/>
+      <x:c r="M90" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="N90" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="31.5" customHeight="1">
+      <x:c r="A91" s="76" t="str">
+        <x:v>AEQA-87</x:v>
+      </x:c>
+      <x:c r="B91" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C91" s="76" t="str">
+        <x:v>Prepare test data and checkout prerequisites</x:v>
+      </x:c>
+      <x:c r="D91" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E91" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F91" s="76" t="str"/>
+      <x:c r="G91" s="76" t="str"/>
+      <x:c r="H91" s="76" t="str"/>
+      <x:c r="I91" s="76" t="str"/>
+      <x:c r="J91" s="76" t="str"/>
+      <x:c r="K91" s="76" t="str"/>
+      <x:c r="L91" s="76" t="str"/>
+      <x:c r="M91" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="N91" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="31.5" customHeight="1">
+      <x:c r="A92" s="76" t="str">
+        <x:v>AEQA-88</x:v>
+      </x:c>
+      <x:c r="B92" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C92" s="76" t="str">
+        <x:v>Run and validate the new checkout test in QA</x:v>
+      </x:c>
+      <x:c r="D92" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E92" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F92" s="76" t="str"/>
+      <x:c r="G92" s="76" t="str"/>
+      <x:c r="H92" s="76" t="str"/>
+      <x:c r="I92" s="76" t="str"/>
+      <x:c r="J92" s="76" t="str"/>
+      <x:c r="K92" s="76" t="str"/>
+      <x:c r="L92" s="76" t="str"/>
+      <x:c r="M92" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="N92" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="31.5" customHeight="1">
+      <x:c r="A93" s="76" t="str">
+        <x:v>AEQA-89</x:v>
+      </x:c>
+      <x:c r="B93" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C93" s="76" t="str">
+        <x:v>Automate the register-while-checking-out scenario in Playwright</x:v>
+      </x:c>
+      <x:c r="D93" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E93" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F93" s="76" t="str"/>
+      <x:c r="G93" s="76" t="str"/>
+      <x:c r="H93" s="76" t="str"/>
+      <x:c r="I93" s="76" t="str"/>
+      <x:c r="J93" s="76" t="str"/>
+      <x:c r="K93" s="76" t="str"/>
+      <x:c r="L93" s="76" t="str"/>
+      <x:c r="M93" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="N93" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="31.5" customHeight="1">
+      <x:c r="A94" s="76" t="str">
+        <x:v>AEQA-90</x:v>
+      </x:c>
+      <x:c r="B94" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C94" s="76" t="str">
+        <x:v>Add assertions for successful registration and order completion</x:v>
+      </x:c>
+      <x:c r="D94" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E94" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F94" s="76" t="str"/>
+      <x:c r="G94" s="76" t="str"/>
+      <x:c r="H94" s="76" t="str"/>
+      <x:c r="I94" s="76" t="str"/>
+      <x:c r="J94" s="76" t="str"/>
+      <x:c r="K94" s="76" t="str"/>
+      <x:c r="L94" s="76" t="str"/>
+      <x:c r="M94" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="N94" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="31.5" customHeight="1">
+      <x:c r="A95" s="76" t="str">
+        <x:v>AEQA-91</x:v>
+      </x:c>
+      <x:c r="B95" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C95" s="76" t="str">
+        <x:v>Prepare test data and QA prerequisites for registration and checkout</x:v>
+      </x:c>
+      <x:c r="D95" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E95" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F95" s="76" t="str"/>
+      <x:c r="G95" s="76" t="str"/>
+      <x:c r="H95" s="76" t="str"/>
+      <x:c r="I95" s="76" t="str"/>
+      <x:c r="J95" s="76" t="str"/>
+      <x:c r="K95" s="76" t="str"/>
+      <x:c r="L95" s="76" t="str"/>
+      <x:c r="M95" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="N95" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="31.5" customHeight="1">
+      <x:c r="A96" s="76" t="str">
+        <x:v>AEQA-92</x:v>
+      </x:c>
+      <x:c r="B96" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C96" s="76" t="str">
+        <x:v>Add assertions for successful registration, checkout, and order completion</x:v>
+      </x:c>
+      <x:c r="D96" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E96" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F96" s="76" t="str"/>
+      <x:c r="G96" s="76" t="str"/>
+      <x:c r="H96" s="76" t="str"/>
+      <x:c r="I96" s="76" t="str"/>
+      <x:c r="J96" s="76" t="str"/>
+      <x:c r="K96" s="76" t="str"/>
+      <x:c r="L96" s="76" t="str"/>
+      <x:c r="M96" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="N96" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="31.5" customHeight="1">
+      <x:c r="A97" s="76" t="str">
+        <x:v>AEQA-93</x:v>
+      </x:c>
+      <x:c r="B97" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C97" s="76" t="str">
+        <x:v>Automate the register-before-checkout scenario in Playwright</x:v>
+      </x:c>
+      <x:c r="D97" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E97" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F97" s="76" t="str"/>
+      <x:c r="G97" s="76" t="str"/>
+      <x:c r="H97" s="76" t="str"/>
+      <x:c r="I97" s="76" t="str"/>
+      <x:c r="J97" s="76" t="str"/>
+      <x:c r="K97" s="76" t="str"/>
+      <x:c r="L97" s="76" t="str"/>
+      <x:c r="M97" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="N97" s="76" t="str">
+        <x:v>10/Aug/26 8:31 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="31.5" customHeight="1">
+      <x:c r="A98" s="76" t="str">
+        <x:v>AEQA-94</x:v>
+      </x:c>
+      <x:c r="B98" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C98" s="76" t="str">
+        <x:v>Run and validate the new register-before-checkout test in QA</x:v>
+      </x:c>
+      <x:c r="D98" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E98" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F98" s="76" t="str"/>
+      <x:c r="G98" s="76" t="str"/>
+      <x:c r="H98" s="76" t="str"/>
+      <x:c r="I98" s="76" t="str"/>
+      <x:c r="J98" s="76" t="str"/>
+      <x:c r="K98" s="76" t="str"/>
+      <x:c r="L98" s="76" t="str"/>
+      <x:c r="M98" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="N98" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="31.5" customHeight="1">
+      <x:c r="A99" s="76" t="str">
+        <x:v>AEQA-95</x:v>
+      </x:c>
+      <x:c r="B99" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C99" s="76" t="str">
+        <x:v>Define the register-before-checkout end-to-end test flow</x:v>
+      </x:c>
+      <x:c r="D99" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E99" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F99" s="76" t="str"/>
+      <x:c r="G99" s="76" t="str"/>
+      <x:c r="H99" s="76" t="str"/>
+      <x:c r="I99" s="76" t="str"/>
+      <x:c r="J99" s="76" t="str"/>
+      <x:c r="K99" s="76" t="str"/>
+      <x:c r="L99" s="76" t="str"/>
+      <x:c r="M99" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="N99" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="31.5" customHeight="1">
+      <x:c r="A100" s="76" t="str">
+        <x:v>AEQA-96</x:v>
+      </x:c>
+      <x:c r="B100" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C100" s="76" t="str">
+        <x:v>Define the login-before-checkout end-to-end test flow</x:v>
+      </x:c>
+      <x:c r="D100" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E100" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F100" s="76" t="str"/>
+      <x:c r="G100" s="76" t="str"/>
+      <x:c r="H100" s="76" t="str"/>
+      <x:c r="I100" s="76" t="str"/>
+      <x:c r="J100" s="76" t="str"/>
+      <x:c r="K100" s="76" t="str"/>
+      <x:c r="L100" s="76" t="str"/>
+      <x:c r="M100" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="N100" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="31.5" customHeight="1">
+      <x:c r="A101" s="76" t="str">
+        <x:v>AEQA-97</x:v>
+      </x:c>
+      <x:c r="B101" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C101" s="76" t="str">
+        <x:v>Prepare test data and QA prerequisites for login and checkout</x:v>
+      </x:c>
+      <x:c r="D101" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E101" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F101" s="76" t="str"/>
+      <x:c r="G101" s="76" t="str"/>
+      <x:c r="H101" s="76" t="str"/>
+      <x:c r="I101" s="76" t="str"/>
+      <x:c r="J101" s="76" t="str"/>
+      <x:c r="K101" s="76" t="str"/>
+      <x:c r="L101" s="76" t="str"/>
+      <x:c r="M101" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="N101" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="31.5" customHeight="1">
+      <x:c r="A102" s="76" t="str">
+        <x:v>AEQA-98</x:v>
+      </x:c>
+      <x:c r="B102" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C102" s="76" t="str">
+        <x:v>Add assertions for successful login, checkout, and order completion</x:v>
+      </x:c>
+      <x:c r="D102" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E102" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F102" s="76" t="str"/>
+      <x:c r="G102" s="76" t="str"/>
+      <x:c r="H102" s="76" t="str"/>
+      <x:c r="I102" s="76" t="str"/>
+      <x:c r="J102" s="76" t="str"/>
+      <x:c r="K102" s="76" t="str"/>
+      <x:c r="L102" s="76" t="str"/>
+      <x:c r="M102" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="N102" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="31.5" customHeight="1">
+      <x:c r="A103" s="76" t="str">
+        <x:v>AEQA-99</x:v>
+      </x:c>
+      <x:c r="B103" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C103" s="76" t="str">
+        <x:v>Run and validate the new login-before-checkout test in QA</x:v>
+      </x:c>
+      <x:c r="D103" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E103" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F103" s="76" t="str"/>
+      <x:c r="G103" s="76" t="str"/>
+      <x:c r="H103" s="76" t="str"/>
+      <x:c r="I103" s="76" t="str"/>
+      <x:c r="J103" s="76" t="str"/>
+      <x:c r="K103" s="76" t="str"/>
+      <x:c r="L103" s="76" t="str"/>
+      <x:c r="M103" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="N103" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="31.5" customHeight="1">
+      <x:c r="A104" s="76" t="str">
+        <x:v>AEQA-100</x:v>
+      </x:c>
+      <x:c r="B104" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C104" s="76" t="str">
+        <x:v>Automate the login-before-checkout scenario in Playwright</x:v>
+      </x:c>
+      <x:c r="D104" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E104" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F104" s="76" t="str"/>
+      <x:c r="G104" s="76" t="str"/>
+      <x:c r="H104" s="76" t="str"/>
+      <x:c r="I104" s="76" t="str"/>
+      <x:c r="J104" s="76" t="str"/>
+      <x:c r="K104" s="76" t="str"/>
+      <x:c r="L104" s="76" t="str"/>
+      <x:c r="M104" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="N104" s="76" t="str">
+        <x:v>10/Aug/26 8:32 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="31.5" customHeight="1">
+      <x:c r="A105" s="76" t="str">
+        <x:v>AEQA-101</x:v>
+      </x:c>
+      <x:c r="B105" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C105" s="76" t="str">
+        <x:v>Prepare test data and QA prerequisites for checkout address validation</x:v>
+      </x:c>
+      <x:c r="D105" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E105" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F105" s="76" t="str"/>
+      <x:c r="G105" s="76" t="str"/>
+      <x:c r="H105" s="76" t="str"/>
+      <x:c r="I105" s="76" t="str"/>
+      <x:c r="J105" s="76" t="str"/>
+      <x:c r="K105" s="76" t="str"/>
+      <x:c r="L105" s="76" t="str"/>
+      <x:c r="M105" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="N105" s="76" t="str">
+        <x:v>10/Aug/26 8:33 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="31.5" customHeight="1">
+      <x:c r="A106" s="76" t="str">
+        <x:v>AEQA-102</x:v>
+      </x:c>
+      <x:c r="B106" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C106" s="76" t="str">
+        <x:v>Automate the checkout address verification scenario in Playwright</x:v>
+      </x:c>
+      <x:c r="D106" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E106" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F106" s="76" t="str"/>
+      <x:c r="G106" s="76" t="str"/>
+      <x:c r="H106" s="76" t="str"/>
+      <x:c r="I106" s="76" t="str"/>
+      <x:c r="J106" s="76" t="str"/>
+      <x:c r="K106" s="76" t="str"/>
+      <x:c r="L106" s="76" t="str"/>
+      <x:c r="M106" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="N106" s="76" t="str">
+        <x:v>10/Aug/26 8:33 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="31.5" customHeight="1">
+      <x:c r="A107" s="76" t="str">
+        <x:v>AEQA-103</x:v>
+      </x:c>
+      <x:c r="B107" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C107" s="76" t="str">
+        <x:v>Define the checkout address verification test flow</x:v>
+      </x:c>
+      <x:c r="D107" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E107" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F107" s="76" t="str"/>
+      <x:c r="G107" s="76" t="str"/>
+      <x:c r="H107" s="76" t="str"/>
+      <x:c r="I107" s="76" t="str"/>
+      <x:c r="J107" s="76" t="str"/>
+      <x:c r="K107" s="76" t="str"/>
+      <x:c r="L107" s="76" t="str"/>
+      <x:c r="M107" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="N107" s="76" t="str">
+        <x:v>10/Aug/26 8:33 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="31.5" customHeight="1">
+      <x:c r="A108" s="76" t="str">
+        <x:v>AEQA-104</x:v>
+      </x:c>
+      <x:c r="B108" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C108" s="76" t="str">
+        <x:v>Run and validate the new checkout address verification test in QA</x:v>
+      </x:c>
+      <x:c r="D108" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E108" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F108" s="76" t="str"/>
+      <x:c r="G108" s="76" t="str"/>
+      <x:c r="H108" s="76" t="str"/>
+      <x:c r="I108" s="76" t="str"/>
+      <x:c r="J108" s="76" t="str"/>
+      <x:c r="K108" s="76" t="str"/>
+      <x:c r="L108" s="76" t="str"/>
+      <x:c r="M108" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="N108" s="76" t="str">
+        <x:v>10/Aug/26 8:33 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="31.5" customHeight="1">
+      <x:c r="A109" s="76" t="str">
+        <x:v>AEQA-105</x:v>
+      </x:c>
+      <x:c r="B109" s="76" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C109" s="76" t="str">
+        <x:v>Add assertions for billing and delivery address details on the checkout page</x:v>
+      </x:c>
+      <x:c r="D109" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E109" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F109" s="76" t="str"/>
+      <x:c r="G109" s="76" t="str"/>
+      <x:c r="H109" s="76" t="str"/>
+      <x:c r="I109" s="76" t="str"/>
+      <x:c r="J109" s="76" t="str"/>
+      <x:c r="K109" s="76" t="str"/>
+      <x:c r="L109" s="76" t="str"/>
+      <x:c r="M109" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="N109" s="76" t="str">
+        <x:v>10/Aug/26 8:33 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="31.5" customHeight="1">
+      <x:c r="A110" s="76" t="str">
+        <x:v>AEQA-106</x:v>
+      </x:c>
+      <x:c r="B110" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C110" s="76" t="str">
+        <x:v>AE-SIGNUP-006 - Verify the complete registration workflow including optional subscription selections</x:v>
+      </x:c>
+      <x:c r="D110" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E110" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F110" s="76" t="str"/>
+      <x:c r="G110" s="76" t="str"/>
+      <x:c r="H110" s="76" t="str">
+        <x:v>AE-SIGNUP-006</x:v>
+      </x:c>
+      <x:c r="I110" s="76" t="str"/>
+      <x:c r="J110" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K110" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L110" s="76" t="str">
+        <x:v>AEQA-1</x:v>
+      </x:c>
+      <x:c r="M110" s="76" t="str"/>
+      <x:c r="N110" s="76" t="str">
+        <x:v>10/Aug/26 8:58 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="31.5" customHeight="1">
+      <x:c r="A111" s="76" t="str">
+        <x:v>AEQA-107</x:v>
+      </x:c>
+      <x:c r="B111" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C111" s="76" t="str">
+        <x:v>AE-ORDER-001 - Verify an order can be placed after registering during checkout</x:v>
+      </x:c>
+      <x:c r="D111" s="76" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="E111" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F111" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G111" s="76" t="str"/>
+      <x:c r="H111" s="76" t="str">
+        <x:v>AE-ORDER-001</x:v>
+      </x:c>
+      <x:c r="I111" s="76" t="str"/>
+      <x:c r="J111" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K111" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L111" s="76" t="str">
+        <x:v>AEQA-14</x:v>
+      </x:c>
+      <x:c r="M111" s="76" t="str"/>
+      <x:c r="N111" s="76" t="str">
+        <x:v>11/Aug/26 7:43 AM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="31.5" customHeight="1">
+      <x:c r="A112" s="76" t="str">
+        <x:v>AEQA-108</x:v>
+      </x:c>
+      <x:c r="B112" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C112" s="76" t="str">
+        <x:v>AE-ORDER-002 - Verify an order can be placed after registering before checkout</x:v>
+      </x:c>
+      <x:c r="D112" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E112" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F112" s="76" t="str"/>
+      <x:c r="G112" s="76" t="str"/>
+      <x:c r="H112" s="76" t="str">
+        <x:v>AE-ORDER-002</x:v>
+      </x:c>
+      <x:c r="I112" s="76" t="str"/>
+      <x:c r="J112" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K112" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L112" s="76" t="str">
+        <x:v>AEQA-15</x:v>
+      </x:c>
+      <x:c r="M112" s="76" t="str"/>
+      <x:c r="N112" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="31.5" customHeight="1">
+      <x:c r="A113" s="76" t="str">
+        <x:v>AEQA-109</x:v>
+      </x:c>
+      <x:c r="B113" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C113" s="76" t="str">
+        <x:v>AE-ORDER-003 - Verify an existing user can log in before checkout and place an order</x:v>
+      </x:c>
+      <x:c r="D113" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E113" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F113" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G113" s="76" t="str"/>
+      <x:c r="H113" s="76" t="str">
+        <x:v>AE-ORDER-003</x:v>
+      </x:c>
+      <x:c r="I113" s="76" t="str"/>
+      <x:c r="J113" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K113" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L113" s="76" t="str">
+        <x:v>AEQA-16</x:v>
+      </x:c>
+      <x:c r="M113" s="76" t="str"/>
+      <x:c r="N113" s="76" t="str">
+        <x:v>11/Aug/26 9:31 AM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="31.5" customHeight="1">
+      <x:c r="A114" s="76" t="str">
+        <x:v>AEQA-110</x:v>
+      </x:c>
+      <x:c r="B114" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C114" s="76" t="str">
+        <x:v>AE-CATALOG-001 - Verify category and subcategory navigation displays matching products</x:v>
+      </x:c>
+      <x:c r="D114" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E114" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F114" s="76" t="str"/>
+      <x:c r="G114" s="76" t="str"/>
+      <x:c r="H114" s="76" t="str">
+        <x:v>AE-CATALOG-001</x:v>
+      </x:c>
+      <x:c r="I114" s="76" t="str"/>
+      <x:c r="J114" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K114" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L114" s="76" t="str">
+        <x:v>AEQA-18</x:v>
+      </x:c>
+      <x:c r="M114" s="76" t="str"/>
+      <x:c r="N114" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="31.5" customHeight="1">
+      <x:c r="A115" s="76" t="str">
+        <x:v>AEQA-111</x:v>
+      </x:c>
+      <x:c r="B115" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C115" s="76" t="str">
+        <x:v>AE-CATALOG-002 - Verify brand navigation and switching displays products for the selected brand</x:v>
+      </x:c>
+      <x:c r="D115" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E115" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F115" s="76" t="str"/>
+      <x:c r="G115" s="76" t="str"/>
+      <x:c r="H115" s="76" t="str">
+        <x:v>AE-CATALOG-002</x:v>
+      </x:c>
+      <x:c r="I115" s="76" t="str"/>
+      <x:c r="J115" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K115" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L115" s="76" t="str">
+        <x:v>AEQA-19</x:v>
+      </x:c>
+      <x:c r="M115" s="76" t="str"/>
+      <x:c r="N115" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="31.5" customHeight="1">
+      <x:c r="A116" s="76" t="str">
+        <x:v>AEQA-112</x:v>
+      </x:c>
+      <x:c r="B116" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C116" s="76" t="str">
+        <x:v>AE-CART-004 - Verify searched products remain in the cart after login</x:v>
+      </x:c>
+      <x:c r="D116" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E116" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F116" s="76" t="str"/>
+      <x:c r="G116" s="76" t="str"/>
+      <x:c r="H116" s="76" t="str">
+        <x:v>AE-CART-004</x:v>
+      </x:c>
+      <x:c r="I116" s="76" t="str"/>
+      <x:c r="J116" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K116" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L116" s="76" t="str">
+        <x:v>AEQA-20</x:v>
+      </x:c>
+      <x:c r="M116" s="76" t="str"/>
+      <x:c r="N116" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="31.5" customHeight="1">
+      <x:c r="A117" s="76" t="str">
+        <x:v>AEQA-113</x:v>
+      </x:c>
+      <x:c r="B117" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C117" s="76" t="str">
+        <x:v>AE-REVIEW-001 - Verify a visitor can submit a review from a product-details page</x:v>
+      </x:c>
+      <x:c r="D117" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E117" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F117" s="76" t="str"/>
+      <x:c r="G117" s="76" t="str"/>
+      <x:c r="H117" s="76" t="str">
+        <x:v>AE-REVIEW-001</x:v>
+      </x:c>
+      <x:c r="I117" s="76" t="str"/>
+      <x:c r="J117" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K117" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L117" s="76" t="str">
+        <x:v>AEQA-21</x:v>
+      </x:c>
+      <x:c r="M117" s="76" t="str"/>
+      <x:c r="N117" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="31.5" customHeight="1">
+      <x:c r="A118" s="76" t="str">
+        <x:v>AEQA-114</x:v>
+      </x:c>
+      <x:c r="B118" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C118" s="76" t="str">
+        <x:v>AE-CART-005 - Verify a product can be added to the cart from Recommended Items</x:v>
+      </x:c>
+      <x:c r="D118" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E118" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F118" s="76" t="str"/>
+      <x:c r="G118" s="76" t="str"/>
+      <x:c r="H118" s="76" t="str">
+        <x:v>AE-CART-005</x:v>
+      </x:c>
+      <x:c r="I118" s="76" t="str"/>
+      <x:c r="J118" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K118" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L118" s="76" t="str">
+        <x:v>AEQA-22</x:v>
+      </x:c>
+      <x:c r="M118" s="76" t="str"/>
+      <x:c r="N118" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="31.5" customHeight="1">
+      <x:c r="A119" s="76" t="str">
+        <x:v>AEQA-115</x:v>
+      </x:c>
+      <x:c r="B119" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C119" s="76" t="str">
+        <x:v>AE-ORDER-004 - Verify checkout delivery and billing addresses match the registered account</x:v>
+      </x:c>
+      <x:c r="D119" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E119" s="76" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F119" s="76" t="str"/>
+      <x:c r="G119" s="76" t="str"/>
+      <x:c r="H119" s="76" t="str">
+        <x:v>AE-ORDER-004</x:v>
+      </x:c>
+      <x:c r="I119" s="76" t="str"/>
+      <x:c r="J119" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K119" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L119" s="76" t="str">
+        <x:v>AEQA-23</x:v>
+      </x:c>
+      <x:c r="M119" s="76" t="str"/>
+      <x:c r="N119" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="31.5" customHeight="1">
+      <x:c r="A120" s="76" t="str">
+        <x:v>AEQA-116</x:v>
+      </x:c>
+      <x:c r="B120" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C120" s="76" t="str">
+        <x:v>AE-ORDER-005 - Verify an invoice can be downloaded after a successful purchase</x:v>
+      </x:c>
+      <x:c r="D120" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E120" s="76" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F120" s="76" t="str"/>
+      <x:c r="G120" s="76" t="str"/>
+      <x:c r="H120" s="76" t="str">
+        <x:v>AE-ORDER-005</x:v>
+      </x:c>
+      <x:c r="I120" s="76" t="str"/>
+      <x:c r="J120" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K120" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L120" s="76" t="str">
+        <x:v>AEQA-24</x:v>
+      </x:c>
+      <x:c r="M120" s="76" t="str"/>
+      <x:c r="N120" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="31.5" customHeight="1">
+      <x:c r="A121" s="76" t="str">
+        <x:v>AEQA-117</x:v>
+      </x:c>
+      <x:c r="B121" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C121" s="76" t="str">
+        <x:v>AE-NAV-002 - Verify scrolling down and returning to the top with the arrow button</x:v>
+      </x:c>
+      <x:c r="D121" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E121" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F121" s="76" t="str"/>
+      <x:c r="G121" s="76" t="str"/>
+      <x:c r="H121" s="76" t="str">
+        <x:v>AE-NAV-002</x:v>
+      </x:c>
+      <x:c r="I121" s="76" t="str"/>
+      <x:c r="J121" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K121" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L121" s="76" t="str">
+        <x:v>AEQA-25</x:v>
+      </x:c>
+      <x:c r="M121" s="76" t="str"/>
+      <x:c r="N121" s="76" t="str">
+        <x:v>10/Aug/26 8:59 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="31.5" customHeight="1">
+      <x:c r="A122" s="76" t="str">
+        <x:v>AEQA-118</x:v>
+      </x:c>
+      <x:c r="B122" s="76" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C122" s="76" t="str">
+        <x:v>AE-NAV-003 - Verify manual scrolling down and back to the top without the arrow button</x:v>
+      </x:c>
+      <x:c r="D122" s="76" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E122" s="76" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F122" s="76" t="str"/>
+      <x:c r="G122" s="76" t="str"/>
+      <x:c r="H122" s="76" t="str">
+        <x:v>AE-NAV-003</x:v>
+      </x:c>
+      <x:c r="I122" s="76" t="str"/>
+      <x:c r="J122" s="76" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K122" s="76" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="L122" s="76" t="str">
+        <x:v>AEQA-26</x:v>
+      </x:c>
+      <x:c r="M122" s="76" t="str"/>
+      <x:c r="N122" s="76" t="str">
+        <x:v>10/Aug/26 9:00 PM</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="D5:D122">
+    <x:cfRule type="containsText" dxfId="86" priority="1" operator="containsText" text="Done"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J5:J122">
+    <x:cfRule type="containsText" dxfId="87" priority="2" operator="containsText" text="Passed"/>
+    <x:cfRule type="containsText" dxfId="88" priority="3" operator="containsText" text="Failed"/>
+    <x:cfRule type="containsText" dxfId="89" priority="4" operator="containsText" text="Not Run"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c90dd95bca54b73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R1f8f25853fd34c8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rf8c3609043084288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R9dd2c21f25964194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="R6cac6f94c04c4059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R6efc6d26ea694578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdf8cf360182f4f7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R396ee8a6882b4899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rc73d54d173db40a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rfe20f315ce404bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R2648f26daf7944f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2524,7 +2524,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2534,7 +2534,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2544,7 +2544,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -2554,7 +2554,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -2576,7 +2576,6 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:rPr/>
               <a:t>Overall Requirement Coverage</a:t>
             </a:r>
           </a:p>
@@ -2586,7 +2585,6 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -2669,9 +2667,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -2738,7 +2734,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R83b4f8ed2e614914"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f335f33282c44bb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2869,9 +2865,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3176,7 +3172,7 @@
       </x:c>
       <x:c r="B15" s="20" t="n">
         <x:f>COUNTIF(RTM!$O$8:$O$51,$A15)</x:f>
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
@@ -3208,7 +3204,7 @@
       </x:c>
       <x:c r="B17" s="20" t="n">
         <x:f>COUNTIF(RTM!$O$8:$O$51,$A17)</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
@@ -3238,7 +3234,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Coverage design is now complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. Thirteen newly linked manual cases remain Not Run; they must not be presented as passed until execution evidence is captured. Current reconciled requirement execution: 29 Pass, 2 Fail, and 13 Not Run. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+        <x:v>Coverage design is complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. AEQA-107 / AE-ORDER-001 is now reconciled as Passed with screenshot evidence; 12 newly linked manual cases remain Not Run. Current reconciled requirement execution: 30 Pass, 2 Fail, and 12 Not Run. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3334,7 +3330,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d4bd5a162f24728"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f821d65c964aef"/>
 </x:worksheet>
 </file>
 
@@ -3382,7 +3378,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="str">
-        <x:v>Coverage synchronized with 48 Jira Test Cases: 35 executed UI/API cases plus 13 linked manual cases awaiting execution.</x:v>
+        <x:v>Coverage synchronized with 48 Jira Test Cases: 36 executed UI/API cases plus 12 linked manual cases awaiting execution.</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -4231,7 +4227,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H21" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-107 (AE-ORDER-001) is linked to AEQA-14; execution remains pending.</x:v>
+        <x:v>Executed through Jira Test Case AEQA-107 / AE-ORDER-001. Registration during checkout completed successfully and the expected order confirmation was displayed.</x:v>
       </x:c>
       <x:c r="I21" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4243,7 +4239,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L21" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M21" s="109" t="str">
         <x:v>N/A</x:v>
@@ -4252,12 +4248,14 @@
         <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O21" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P21" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P21" s="93" t="str">
+        <x:v>..\Screenshots\AE-ORDER-001.png</x:v>
+      </x:c>
       <x:c r="Q21" s="93"/>
       <x:c r="R21" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-ORDER-001 (AEQA-107) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execution synchronized from Jira AEQA-107 on 2026-08-12. Passed result, actual outcome, and screenshot evidence are retained in Jira and this RTM.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="48" customHeight="1">
@@ -6086,7 +6084,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08e6f7acea6b4f0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca4fa6edd20f4149"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6502,7 +6500,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e24b4ce862246c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8ae5d44b584bbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6938,7 +6936,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc340310bf6e344a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e6afe27f5a4189"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6983,7 +6981,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="134" t="str">
-        <x:v>Source: live Jira Cloud AEQA all-fields export captured 2026-08-11. Re-export Jira before each formal RTM reconciliation.</x:v>
+        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-12. Re-export Jira before each formal RTM reconciliation.</x:v>
       </x:c>
       <x:c r="B2" s="134"/>
       <x:c r="C2" s="134"/>
@@ -10623,7 +10621,7 @@
         <x:v>AE-ORDER-001 - Verify an order can be placed after registering during checkout</x:v>
       </x:c>
       <x:c r="D111" s="76" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E111" s="76" t="str">
         <x:v>Highest</x:v>
@@ -10637,7 +10635,7 @@
       </x:c>
       <x:c r="I111" s="76" t="str"/>
       <x:c r="J111" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K111" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10647,7 +10645,7 @@
       </x:c>
       <x:c r="M111" s="76" t="str"/>
       <x:c r="N111" s="76" t="str">
-        <x:v>11/Aug/26 7:43 AM</x:v>
+        <x:v>2026-08-12 22:27 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="31.5" customHeight="1">
@@ -11063,7 +11061,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c90dd95bca54b73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7282cf0489fa4380"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdf8cf360182f4f7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R396ee8a6882b4899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rc73d54d173db40a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rfe20f315ce404bcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R2648f26daf7944f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra498d7e7cfcb45fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R4fca51c3816243c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rf877c9ec1917439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Reba76d289c7941c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Rb4593fb3b4a0459a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,19 +50,10 @@
     <x:t xml:space="preserve">Notes</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Pass</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mapped requirements whose linked tests passed</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Fail</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Mapped requirements whose linked tests failed</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not Run</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Requirements without executed coverage</x:t>
@@ -2734,7 +2725,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f335f33282c44bb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf578a5de224f44a7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2997,7 +2988,7 @@
     </x:row>
     <x:row r="2" ht="22.5" customHeight="1">
       <x:c r="A2" s="125" t="str">
-        <x:v>Traceability across 44 requirements and 48 Jira Test Cases, with coverage design kept separate from execution outcome</x:v>
+        <x:v>Traceability across 44 requirements and 48 Jira Test Cases, synchronized with Jira Cloud through 2026-08-16</x:v>
       </x:c>
       <x:c r="B2" s="125"/>
       <x:c r="C2" s="125"/>
@@ -3167,27 +3158,25 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="37.5">
-      <x:c r="A15" s="20" t="s">
-        <x:v>12</x:v>
+      <x:c r="A15" s="20" t="str">
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:f>COUNTIF(RTM!$O$8:$O$51,$A15)</x:f>
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="20" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="37.5">
-      <x:c r="A16" s="20" t="s">
-        <x:v>14</x:v>
+      <x:c r="A16" s="20" t="str">
+        <x:v>Fail</x:v>
       </x:c>
       <x:c r="B16" s="20" t="n">
-        <x:f>COUNTIF(RTM!$O$8:$O$51,$A16)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="20" t="n">
@@ -3195,28 +3184,27 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D16" s="20" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25">
-      <x:c r="A17" s="20" t="s">
-        <x:v>16</x:v>
+      <x:c r="A17" s="20" t="str">
+        <x:v>Not Run</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:f>COUNTIF(RTM!$O$8:$O$51,$A17)</x:f>
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15.5">
       <x:c r="A20" s="28" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="28"/>
       <x:c r="C20" s="28"/>
@@ -3234,7 +3222,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Coverage design is complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. AEQA-107 / AE-ORDER-001 is now reconciled as Passed with screenshot evidence; 12 newly linked manual cases remain Not Run. Current reconciled requirement execution: 30 Pass, 2 Fail, and 12 Not Run. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+        <x:v>Coverage design remains complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. AEQA-107 / AE-ORDER-001, AEQA-110 / AE-CATALOG-001, and AEQA-115 / AE-ORDER-004 are reconciled as Passed. Current requirement execution: 32 Pass, 2 Fail, and 10 Not Run. AEQA-121 tracks Playwright automation for REQ-AUTH-001 and remains In Progress / Not Run until execution evidence exists. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3330,7 +3318,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f821d65c964aef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89df9d2d5c514b92"/>
 </x:worksheet>
 </file>
 
@@ -3361,7 +3349,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="38" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -3400,7 +3388,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="47" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="48"/>
       <x:c r="C4" s="48"/>
@@ -3512,7 +3500,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H8" s="89" t="str">
-        <x:v>Test design is complete. Jira AEQA-106 (AE-SIGNUP-006) is linked to AEQA-1; execution remains pending.</x:v>
+        <x:v>Test design is complete. Jira AEQA-106 is workflow-complete but its Execution Status remains Not Run; AEQA-121 tracks the Playwright implementation now In Progress.</x:v>
       </x:c>
       <x:c r="I8" s="107" t="str">
         <x:v>Functional — Positive</x:v>
@@ -3542,7 +3530,7 @@
       </x:c>
       <x:c r="Q8" s="89"/>
       <x:c r="R8" s="90" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-SIGNUP-006 (AEQA-106) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Do not treat Jira workflow Done as a passed execution. Run AE-SIGNUP-006 / AEQA-121, attach sanitized evidence, then reconcile the result here.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -4439,7 +4427,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H25" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-110 (AE-CATALOG-001) is linked to AEQA-18; execution remains pending.</x:v>
+        <x:v>Executed through Jira Test Case AEQA-110 / AE-CATALOG-001. Women &gt; Dress and Men &gt; Tshirts navigation displayed the expected category headings and matching product lists.</x:v>
       </x:c>
       <x:c r="I25" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4451,7 +4439,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L25" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M25" s="109" t="str">
         <x:v>N/A</x:v>
@@ -4460,12 +4448,14 @@
         <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O25" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P25" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P25" s="93" t="str">
+        <x:v>Jira native attachment (AEQA-110)</x:v>
+      </x:c>
       <x:c r="Q25" s="93"/>
       <x:c r="R25" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-CATALOG-001 (AEQA-110) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execution synchronized from Jira on 2026-08-16. Passed result and screenshot evidence are retained on AEQA-110.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="48" customHeight="1">
@@ -4699,7 +4689,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H30" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-115 (AE-ORDER-004) is linked to AEQA-23; execution remains pending.</x:v>
+        <x:v>Executed through Jira Test Case AEQA-115 / AE-ORDER-004 and automated under AEQA-102 / AEQA-105. Delivery and billing address details matched the registered QA account.</x:v>
       </x:c>
       <x:c r="I30" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4711,21 +4701,25 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L30" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M30" s="109" t="str">
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N30" s="109" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O30" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P30" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P30" s="93" t="str">
+        <x:v>..\Automation\Execution Evidence\AE-ORDER-004.png
+..\Automation\Execution Evidence\AE-ORDER-004-evidence.html
+..\Automation\Execution Evidence\AE-ORDER-004-evidence.pdf</x:v>
+      </x:c>
       <x:c r="Q30" s="93"/>
       <x:c r="R30" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-ORDER-004 (AEQA-115) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Manual and Playwright results synchronized from Jira and local evidence on 2026-08-16.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="48" customHeight="1">
@@ -6084,7 +6078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca4fa6edd20f4149"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623569e2157841c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6101,7 +6095,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="38" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="38"/>
       <x:c r="C1" s="38"/>
@@ -6109,7 +6103,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -6117,380 +6111,380 @@
     </x:row>
     <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="264.5" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="5">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="264.5" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="264.5" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="264.5" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="264.5" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="264.5" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C10" s="5">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="264.5" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="5">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="264.5" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D12" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="264.5" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="264.5" customHeight="1">
       <x:c r="A14" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="264.5" customHeight="1">
       <x:c r="A15" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="264.5" customHeight="1">
       <x:c r="A16" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C16" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D16" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="264.5" customHeight="1">
       <x:c r="A17" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D17" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="264.5" customHeight="1">
       <x:c r="A18" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="5">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D18" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="264.5" customHeight="1">
       <x:c r="A19" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="5">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D19" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="264.5" customHeight="1">
       <x:c r="A20" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="5">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="264.5" customHeight="1">
       <x:c r="A21" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C21" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D21" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="264.5" customHeight="1">
       <x:c r="A22" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C22" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D22" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="264.5" customHeight="1">
       <x:c r="A23" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C23" s="5">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="264.5" customHeight="1">
       <x:c r="A24" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C24" s="5">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D24" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="264.5" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B25" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C25" s="5">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="264.5" customHeight="1">
       <x:c r="A26" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B26" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C26" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="264.5" customHeight="1">
       <x:c r="A27" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C27" s="5">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="264.5" customHeight="1">
       <x:c r="A28" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B28" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="5">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D28" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="264.5" customHeight="1">
       <x:c r="A29" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B29" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C29" s="5">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D29" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="264.5" customHeight="1">
       <x:c r="A30" s="9" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B30" s="10" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C30" s="10">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6500,7 +6494,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a8ae5d44b584bbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aa5d8b218d4bbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6521,7 +6515,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="53" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B1" s="53"/>
       <x:c r="C1" s="53"/>
@@ -6533,7 +6527,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="54" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B2" s="54"/>
       <x:c r="C2" s="54"/>
@@ -6550,383 +6544,383 @@
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="16" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="s">
+      <x:c r="F4" s="16" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="s">
+      <x:c r="G4" s="16" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="s">
+      <x:c r="H4" s="16" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="s">
-        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="E5" s="5"/>
       <x:c r="F5" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="72" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G6" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="72" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D8" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E8" s="5"/>
       <x:c r="F8" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G8" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H8" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="72" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="F9" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G9" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H9" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="72" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D10" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E10" s="5"/>
       <x:c r="F10" s="5">
         <x:v>400</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="72" customHeight="1">
       <x:c r="A11" s="5" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="F11" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D12" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E12" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F12" s="5">
         <x:v>400</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="72" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D13" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E13" s="5"/>
       <x:c r="F13" s="5">
         <x:v>405</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="72" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D14" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E14" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F14" s="5">
         <x:v>404</x:v>
       </x:c>
       <x:c r="G14" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H14" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="72" customHeight="1">
       <x:c r="A15" s="5" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="C15" s="5" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="D15" s="5" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E15" s="5" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="E15" s="5" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="F15" s="5">
         <x:v>201</x:v>
       </x:c>
       <x:c r="G15" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H15" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="72" customHeight="1">
       <x:c r="A16" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D16" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E16" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F16" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G16" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H16" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="72" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D17" s="5" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E17" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F17" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G17" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H17" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="J17" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="72" customHeight="1">
       <x:c r="A18" s="5" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C18" s="5" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D18" s="5" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="C18" s="5" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="E18" s="5" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="F18" s="5">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G18" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H18" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6936,7 +6930,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e6afe27f5a4189"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf150350fb8204e9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6981,7 +6975,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="134" t="str">
-        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-12. Re-export Jira before each formal RTM reconciliation.</x:v>
+        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-16. Jira remains the operational layer; re-export before each formal RTM reconciliation.</x:v>
       </x:c>
       <x:c r="B2" s="134"/>
       <x:c r="C2" s="134"/>
@@ -7052,12 +7046,14 @@
         <x:v>REQ-AUTH-001 - Register User</x:v>
       </x:c>
       <x:c r="D5" s="76" t="str">
-        <x:v>Done</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="E5" s="76" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F5" s="76" t="str"/>
+      <x:c r="F5" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G5" s="76" t="str">
         <x:v>REQ-AUTH-001</x:v>
       </x:c>
@@ -7073,7 +7069,7 @@
       </x:c>
       <x:c r="M5" s="76" t="str"/>
       <x:c r="N5" s="76" t="str">
-        <x:v>10/Aug/26 8:58 PM</x:v>
+        <x:v>16/Aug/26 12:54 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -7473,7 +7469,7 @@
         <x:v>REQ-ORDER-001 - Place Order: Register while Checkout</x:v>
       </x:c>
       <x:c r="D18" s="76" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E18" s="76" t="str">
         <x:v>Highest</x:v>
@@ -7493,7 +7489,7 @@
       </x:c>
       <x:c r="M18" s="76" t="str"/>
       <x:c r="N18" s="76" t="str">
-        <x:v>11/Aug/26 7:41 AM</x:v>
+        <x:v>16/Aug/26 12:36 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="31.5" customHeight="1">
@@ -7607,12 +7603,14 @@
         <x:v>REQ-CATALOG-001 - View Category Products</x:v>
       </x:c>
       <x:c r="D22" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E22" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F22" s="76" t="str"/>
+      <x:c r="F22" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G22" s="76" t="str">
         <x:v>REQ-CATALOG-001</x:v>
       </x:c>
@@ -7625,7 +7623,7 @@
       </x:c>
       <x:c r="M22" s="76" t="str"/>
       <x:c r="N22" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>16/Aug/26 12:41 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="31.5" customHeight="1">
@@ -7767,12 +7765,14 @@
         <x:v>REQ-ORDER-004 - Verify address details in checkout page</x:v>
       </x:c>
       <x:c r="D27" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E27" s="76" t="str">
-        <x:v>Highest</x:v>
-      </x:c>
-      <x:c r="F27" s="76" t="str"/>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F27" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G27" s="76" t="str">
         <x:v>REQ-ORDER-004</x:v>
       </x:c>
@@ -7785,7 +7785,7 @@
       </x:c>
       <x:c r="M27" s="76" t="str"/>
       <x:c r="N27" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>15/Aug/26 11:27 PM</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="31.5" customHeight="1">
@@ -10015,12 +10015,14 @@
         <x:v>Prepare test data and checkout prerequisites</x:v>
       </x:c>
       <x:c r="D91" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E91" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F91" s="76" t="str"/>
+      <x:c r="F91" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G91" s="76" t="str"/>
       <x:c r="H91" s="76" t="str"/>
       <x:c r="I91" s="76" t="str"/>
@@ -10031,7 +10033,7 @@
         <x:v>AEQA-14</x:v>
       </x:c>
       <x:c r="N91" s="76" t="str">
-        <x:v>10/Aug/26 8:31 PM</x:v>
+        <x:v>14/Aug/26 8:22 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="31.5" customHeight="1">
@@ -10045,12 +10047,14 @@
         <x:v>Run and validate the new checkout test in QA</x:v>
       </x:c>
       <x:c r="D92" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E92" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F92" s="76" t="str"/>
+      <x:c r="F92" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G92" s="76" t="str"/>
       <x:c r="H92" s="76" t="str"/>
       <x:c r="I92" s="76" t="str"/>
@@ -10061,7 +10065,7 @@
         <x:v>AEQA-14</x:v>
       </x:c>
       <x:c r="N92" s="76" t="str">
-        <x:v>10/Aug/26 8:31 PM</x:v>
+        <x:v>14/Aug/26 8:22 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="31.5" customHeight="1">
@@ -10075,12 +10079,14 @@
         <x:v>Automate the register-while-checking-out scenario in Playwright</x:v>
       </x:c>
       <x:c r="D93" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E93" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F93" s="76" t="str"/>
+      <x:c r="F93" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G93" s="76" t="str"/>
       <x:c r="H93" s="76" t="str"/>
       <x:c r="I93" s="76" t="str"/>
@@ -10091,7 +10097,7 @@
         <x:v>AEQA-14</x:v>
       </x:c>
       <x:c r="N93" s="76" t="str">
-        <x:v>10/Aug/26 8:31 PM</x:v>
+        <x:v>16/Aug/26 12:34 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="31.5" customHeight="1">
@@ -10105,12 +10111,14 @@
         <x:v>Add assertions for successful registration and order completion</x:v>
       </x:c>
       <x:c r="D94" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E94" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F94" s="76" t="str"/>
+      <x:c r="F94" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G94" s="76" t="str"/>
       <x:c r="H94" s="76" t="str"/>
       <x:c r="I94" s="76" t="str"/>
@@ -10121,7 +10129,7 @@
         <x:v>AEQA-14</x:v>
       </x:c>
       <x:c r="N94" s="76" t="str">
-        <x:v>10/Aug/26 8:31 PM</x:v>
+        <x:v>16/Aug/26 12:34 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="31.5" customHeight="1">
@@ -10465,12 +10473,14 @@
         <x:v>Automate the checkout address verification scenario in Playwright</x:v>
       </x:c>
       <x:c r="D106" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E106" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F106" s="76" t="str"/>
+      <x:c r="F106" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G106" s="76" t="str"/>
       <x:c r="H106" s="76" t="str"/>
       <x:c r="I106" s="76" t="str"/>
@@ -10481,7 +10491,7 @@
         <x:v>AEQA-23</x:v>
       </x:c>
       <x:c r="N106" s="76" t="str">
-        <x:v>10/Aug/26 8:33 PM</x:v>
+        <x:v>15/Aug/26 11:23 PM</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="31.5" customHeight="1">
@@ -10555,12 +10565,14 @@
         <x:v>Add assertions for billing and delivery address details on the checkout page</x:v>
       </x:c>
       <x:c r="D109" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E109" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F109" s="76" t="str"/>
+      <x:c r="F109" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G109" s="76" t="str"/>
       <x:c r="H109" s="76" t="str"/>
       <x:c r="I109" s="76" t="str"/>
@@ -10571,7 +10583,7 @@
         <x:v>AEQA-23</x:v>
       </x:c>
       <x:c r="N109" s="76" t="str">
-        <x:v>10/Aug/26 8:33 PM</x:v>
+        <x:v>15/Aug/26 11:27 PM</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="31.5" customHeight="1">
@@ -10585,12 +10597,14 @@
         <x:v>AE-SIGNUP-006 - Verify the complete registration workflow including optional subscription selections</x:v>
       </x:c>
       <x:c r="D110" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E110" s="76" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F110" s="76" t="str"/>
+      <x:c r="F110" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G110" s="76" t="str"/>
       <x:c r="H110" s="76" t="str">
         <x:v>AE-SIGNUP-006</x:v>
@@ -10607,7 +10621,7 @@
       </x:c>
       <x:c r="M110" s="76" t="str"/>
       <x:c r="N110" s="76" t="str">
-        <x:v>10/Aug/26 8:58 PM</x:v>
+        <x:v>16/Aug/26 12:50 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="31.5" customHeight="1">
@@ -10733,19 +10747,21 @@
         <x:v>AE-CATALOG-001 - Verify category and subcategory navigation displays matching products</x:v>
       </x:c>
       <x:c r="D114" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E114" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F114" s="76" t="str"/>
+      <x:c r="F114" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G114" s="76" t="str"/>
       <x:c r="H114" s="76" t="str">
         <x:v>AE-CATALOG-001</x:v>
       </x:c>
       <x:c r="I114" s="76" t="str"/>
       <x:c r="J114" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K114" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10755,7 +10771,7 @@
       </x:c>
       <x:c r="M114" s="76" t="str"/>
       <x:c r="N114" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>16/Aug/26 12:46 AM</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="31.5" customHeight="1">
@@ -10913,19 +10929,21 @@
         <x:v>AE-ORDER-004 - Verify checkout delivery and billing addresses match the registered account</x:v>
       </x:c>
       <x:c r="D119" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E119" s="76" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F119" s="76" t="str"/>
+      <x:c r="F119" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G119" s="76" t="str"/>
       <x:c r="H119" s="76" t="str">
         <x:v>AE-ORDER-004</x:v>
       </x:c>
       <x:c r="I119" s="76" t="str"/>
       <x:c r="J119" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K119" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10935,7 +10953,7 @@
       </x:c>
       <x:c r="M119" s="76" t="str"/>
       <x:c r="N119" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>15/Aug/26 11:14 PM</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="31.5" customHeight="1">
@@ -11044,6 +11062,102 @@
       <x:c r="M122" s="76" t="str"/>
       <x:c r="N122" s="76" t="str">
         <x:v>10/Aug/26 9:00 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>AEQA-119</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>QA-ADMIN-001 - Validate manual Requirement form workflow</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F123"/>
+      <x:c r="G123" t="str">
+        <x:v>QA-ADMIN-001</x:v>
+      </x:c>
+      <x:c r="H123"/>
+      <x:c r="I123"/>
+      <x:c r="J123"/>
+      <x:c r="K123"/>
+      <x:c r="L123"/>
+      <x:c r="M123"/>
+      <x:c r="N123" t="str">
+        <x:v>12/Aug/26 9:18 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>AEQA-120</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>QA Maintenance - Reconcile and re-upload missing execution evidence</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G124"/>
+      <x:c r="H124"/>
+      <x:c r="I124"/>
+      <x:c r="J124"/>
+      <x:c r="K124"/>
+      <x:c r="L124"/>
+      <x:c r="M124"/>
+      <x:c r="N124" t="str">
+        <x:v>12/Aug/26 10:27 PM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>AEQA-121</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>Automate end-to-end user registration with Playwright</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>Highest</x:v>
+      </x:c>
+      <x:c r="F125" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>REQ-AUTH-001</x:v>
+      </x:c>
+      <x:c r="H125"/>
+      <x:c r="I125"/>
+      <x:c r="J125" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K125"/>
+      <x:c r="L125"/>
+      <x:c r="M125" t="str">
+        <x:v>AEQA-1</x:v>
+      </x:c>
+      <x:c r="N125" t="str">
+        <x:v>16/Aug/26 1:03 AM</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11061,7 +11175,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7282cf0489fa4380"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra012d6f785db4be3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra498d7e7cfcb45fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R4fca51c3816243c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rf877c9ec1917439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Reba76d289c7941c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Rb4593fb3b4a0459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rb1f82aaa1c864070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd3df77b818f14a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rbecefb8ec2a64707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Raeb525563ac14c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Re758762039af4438"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2725,7 +2725,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf578a5de224f44a7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e45ad3acfdf4e9e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2988,7 +2988,7 @@
     </x:row>
     <x:row r="2" ht="22.5" customHeight="1">
       <x:c r="A2" s="125" t="str">
-        <x:v>Traceability across 44 requirements and 48 Jira Test Cases, synchronized with Jira Cloud through 2026-08-16</x:v>
+        <x:v>Traceability across 44 portfolio requirements and 53 Jira Test Cases, synchronized with Jira Cloud through 2026-08-17</x:v>
       </x:c>
       <x:c r="B2" s="125"/>
       <x:c r="C2" s="125"/>
@@ -3162,7 +3162,7 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
@@ -3192,7 +3192,7 @@
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
@@ -3222,7 +3222,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Coverage design remains complete for all 44 requirements. Jira is the operational traceability layer, and this workbook is the formal synchronized record. AEQA-107 / AE-ORDER-001, AEQA-110 / AE-CATALOG-001, and AEQA-115 / AE-ORDER-004 are reconciled as Passed. Current requirement execution: 32 Pass, 2 Fail, and 10 Not Run. AEQA-121 tracks Playwright automation for REQ-AUTH-001 and remains In Progress / Not Run until execution evidence exists. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 33 Pass, 2 Fail, and 9 Not Run. REQ-CART-004 now has passing Playwright evidence under AEQA-122 while the separate manual case AEQA-112 remains Not Run. AEQA-121 is workflow Done, but registration execution remains Not Run until an explicit result is recorded. Five new automation Test Cases (AEQA-124 through AEQA-128) extend Jira traceability without changing execution results. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3318,7 +3318,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89df9d2d5c514b92"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39ade9095d9c4b7d"/>
 </x:worksheet>
 </file>
 
@@ -3366,7 +3366,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="str">
-        <x:v>Coverage synchronized with 48 Jira Test Cases: 36 executed UI/API cases plus 12 linked manual cases awaiting execution.</x:v>
+        <x:v>Coverage synchronized with 53 Jira Test Cases through 2026-08-17; Jira workflow and test execution status remain independently reconciled.</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -3500,7 +3500,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H8" s="89" t="str">
-        <x:v>Test design is complete. Jira AEQA-106 is workflow-complete but its Execution Status remains Not Run; AEQA-121 tracks the Playwright implementation now In Progress.</x:v>
+        <x:v>Test design is complete. Jira AEQA-106 is workflow-complete but its Execution Status remains Not Run. Automation implementation AEQA-121 is Done; do not infer a passing execution without an explicit recorded result.</x:v>
       </x:c>
       <x:c r="I8" s="107" t="str">
         <x:v>Functional — Positive</x:v>
@@ -3530,7 +3530,7 @@
       </x:c>
       <x:c r="Q8" s="89"/>
       <x:c r="R8" s="90" t="str">
-        <x:v>Do not treat Jira workflow Done as a passed execution. Run AE-SIGNUP-006 / AEQA-121, attach sanitized evidence, then reconcile the result here.</x:v>
+        <x:v>AEQA-121 is Done and evidence is attached, but AE-SIGNUP-006 / AEQA-106 remains Not Run. Record an explicit execution result before changing this row.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -4481,7 +4481,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H26" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-111 (AE-CATALOG-002) is linked to AEQA-19; execution remains pending.</x:v>
+        <x:v>Manual design is complete in AEQA-111 / AE-CATALOG-002. AEQA-123 is the linked Playwright implementation sub-task and remains Backlog.</x:v>
       </x:c>
       <x:c r="I26" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4507,7 +4507,7 @@
       <x:c r="P26" s="93"/>
       <x:c r="Q26" s="93"/>
       <x:c r="R26" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-CATALOG-002 (AEQA-111) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-CATALOG-002 manually and complete AEQA-123 automation; reconcile each result and its evidence independently.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="48" customHeight="1">
@@ -4533,7 +4533,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H27" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-112 (AE-CART-004) is linked to AEQA-20; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-112 / AE-CART-004 remains Not Run. The Playwright implementation under AEQA-122 is Done and the saved 1/1 Chromium report plus before/after cart screenshots passed.</x:v>
       </x:c>
       <x:c r="I27" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4551,15 +4551,19 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N27" s="109" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O27" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P27" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P27" s="93" t="str">
+        <x:v>..\Automation\Execution Evidence\AE-CART-004(1).png
+..\Automation\Execution Evidence\AE-CART-004(2).png
+..\Automation\test-results\html-report\index.html</x:v>
+      </x:c>
       <x:c r="Q27" s="93"/>
       <x:c r="R27" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-CART-004 (AEQA-112) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Automation passed under AEQA-122 on 2026-08-17. Keep the manual AEQA-112 result separate and Not Run until that case is executed.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -4579,13 +4583,14 @@
         <x:v>Add review on product</x:v>
       </x:c>
       <x:c r="F28" s="109" t="str">
-        <x:v>AE-REVIEW-001</x:v>
+        <x:v>AE-REVIEW-001
+AE-AUTO-REVIEW-001</x:v>
       </x:c>
       <x:c r="G28" s="119" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H28" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-113 (AE-REVIEW-001) is linked to AEQA-21; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-113 and automation case AEQA-124 are linked to AEQA-21. Both remain Not Run; Playwright implementation is planned.</x:v>
       </x:c>
       <x:c r="I28" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4611,7 +4616,7 @@
       <x:c r="P28" s="93"/>
       <x:c r="Q28" s="93"/>
       <x:c r="R28" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-REVIEW-001 (AEQA-113) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-REVIEW-001 and implement AE-AUTO-REVIEW-001 independently; attach result-specific evidence to each Jira Test Case.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -4631,13 +4636,14 @@
         <x:v>Add to cart from Recommended items</x:v>
       </x:c>
       <x:c r="F29" s="109" t="str">
-        <x:v>AE-CART-005</x:v>
+        <x:v>AE-CART-005
+AE-AUTO-CART-005</x:v>
       </x:c>
       <x:c r="G29" s="119" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H29" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-114 (AE-CART-005) is linked to AEQA-22; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-114 and automation case AEQA-125 are linked to AEQA-22. Both remain Not Run; Playwright implementation is planned.</x:v>
       </x:c>
       <x:c r="I29" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4663,7 +4669,7 @@
       <x:c r="P29" s="93"/>
       <x:c r="Q29" s="93"/>
       <x:c r="R29" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-CART-005 (AEQA-114) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-CART-005 and implement AE-AUTO-CART-005 independently; attach matching Recommended Items and cart evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="48" customHeight="1">
@@ -4739,13 +4745,14 @@
         <x:v>Download Invoice after purchase order</x:v>
       </x:c>
       <x:c r="F31" s="109" t="str">
-        <x:v>AE-ORDER-005</x:v>
+        <x:v>AE-ORDER-005
+AE-AUTO-ORDER-005</x:v>
       </x:c>
       <x:c r="G31" s="119" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H31" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-116 (AE-ORDER-005) is linked to AEQA-24; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-116 and automation case AEQA-126 are linked to AEQA-24. Both remain Not Run; end-to-end invoice automation is planned.</x:v>
       </x:c>
       <x:c r="I31" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4771,7 +4778,7 @@
       <x:c r="P31" s="93"/>
       <x:c r="Q31" s="93"/>
       <x:c r="R31" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-ORDER-005 (AEQA-116) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-ORDER-005 and implement AE-AUTO-ORDER-005 independently; retain sanitized order and invoice evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="48" customHeight="1">
@@ -4791,13 +4798,14 @@
         <x:v>Verify Scroll Up using 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
       <x:c r="F32" s="109" t="str">
-        <x:v>AE-NAV-002</x:v>
+        <x:v>AE-NAV-002
+AE-AUTO-NAV-002</x:v>
       </x:c>
       <x:c r="G32" s="119" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H32" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-117 (AE-NAV-002) is linked to AEQA-25; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-117 and automation case AEQA-127 are linked to AEQA-25. Both remain Not Run; arrow return-to-top automation is planned.</x:v>
       </x:c>
       <x:c r="I32" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4823,7 +4831,7 @@
       <x:c r="P32" s="93"/>
       <x:c r="Q32" s="93"/>
       <x:c r="R32" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-NAV-002 (AEQA-117) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-NAV-002 and implement AE-AUTO-NAV-002 independently; capture footer and returned-to-top evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="48" customHeight="1">
@@ -4843,13 +4851,14 @@
         <x:v>Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
       <x:c r="F33" s="109" t="str">
-        <x:v>AE-NAV-003</x:v>
+        <x:v>AE-NAV-003
+AE-AUTO-NAV-003</x:v>
       </x:c>
       <x:c r="G33" s="119" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H33" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-118 (AE-NAV-003) is linked to AEQA-26; execution remains pending.</x:v>
+        <x:v>Manual case AEQA-118 and automation case AEQA-128 are linked to AEQA-26. Both remain Not Run; browser-scroll automation is planned.</x:v>
       </x:c>
       <x:c r="I33" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4875,7 +4884,7 @@
       <x:c r="P33" s="93"/>
       <x:c r="Q33" s="93"/>
       <x:c r="R33" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-NAV-003 (AEQA-118) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Execute AE-NAV-003 and implement AE-AUTO-NAV-003 independently; confirm the site arrow is not used.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="48" customHeight="1">
@@ -6078,7 +6087,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623569e2157841c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16276633df5845d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6494,7 +6503,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aa5d8b218d4bbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77669e5cd87d4e0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6930,7 +6939,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf150350fb8204e9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R695a17ac7ad147e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6975,7 +6984,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="134" t="str">
-        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-16. Jira remains the operational layer; re-export before each formal RTM reconciliation.</x:v>
+        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-17 | Workflow status, traceability links, and execution metadata remain independently reconciled</x:v>
       </x:c>
       <x:c r="B2" s="134"/>
       <x:c r="C2" s="134"/>
@@ -7046,7 +7055,7 @@
         <x:v>REQ-AUTH-001 - Register User</x:v>
       </x:c>
       <x:c r="D5" s="76" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E5" s="76" t="str">
         <x:v>Highest</x:v>
@@ -7069,7 +7078,7 @@
       </x:c>
       <x:c r="M5" s="76" t="str"/>
       <x:c r="N5" s="76" t="str">
-        <x:v>16/Aug/26 12:54 AM</x:v>
+        <x:v>2026-08-16 23:42 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -7642,7 +7651,9 @@
       <x:c r="E23" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F23" s="76" t="str"/>
+      <x:c r="F23" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G23" s="76" t="str">
         <x:v>REQ-CATALOG-002</x:v>
       </x:c>
@@ -7655,7 +7666,7 @@
       </x:c>
       <x:c r="M23" s="76" t="str"/>
       <x:c r="N23" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 15:14 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="31.5" customHeight="1">
@@ -7669,12 +7680,14 @@
         <x:v>REQ-CART-004 - Search Products and Verify Cart After Login</x:v>
       </x:c>
       <x:c r="D24" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E24" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F24" s="76" t="str"/>
+      <x:c r="F24" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G24" s="76" t="str">
         <x:v>REQ-CART-004</x:v>
       </x:c>
@@ -7687,7 +7700,7 @@
       </x:c>
       <x:c r="M24" s="76" t="str"/>
       <x:c r="N24" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 13:05 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">
@@ -7706,7 +7719,9 @@
       <x:c r="E25" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F25" s="76" t="str"/>
+      <x:c r="F25" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G25" s="76" t="str">
         <x:v>REQ-REVIEW-001</x:v>
       </x:c>
@@ -7715,11 +7730,12 @@
       <x:c r="J25" s="76" t="str"/>
       <x:c r="K25" s="76" t="str"/>
       <x:c r="L25" s="76" t="str">
-        <x:v>AEQA-113</x:v>
+        <x:v>AEQA-113
+AEQA-124</x:v>
       </x:c>
       <x:c r="M25" s="76" t="str"/>
       <x:c r="N25" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 15:30 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="31.5" customHeight="1">
@@ -7738,7 +7754,9 @@
       <x:c r="E26" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F26" s="76" t="str"/>
+      <x:c r="F26" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G26" s="76" t="str">
         <x:v>REQ-CART-005</x:v>
       </x:c>
@@ -7747,11 +7765,12 @@
       <x:c r="J26" s="76" t="str"/>
       <x:c r="K26" s="76" t="str"/>
       <x:c r="L26" s="76" t="str">
-        <x:v>AEQA-114</x:v>
+        <x:v>AEQA-114
+AEQA-125</x:v>
       </x:c>
       <x:c r="M26" s="76" t="str"/>
       <x:c r="N26" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 15:31 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="31.5" customHeight="1">
@@ -7804,7 +7823,9 @@
       <x:c r="E28" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F28" s="76" t="str"/>
+      <x:c r="F28" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G28" s="76" t="str">
         <x:v>REQ-ORDER-005</x:v>
       </x:c>
@@ -7813,11 +7834,12 @@
       <x:c r="J28" s="76" t="str"/>
       <x:c r="K28" s="76" t="str"/>
       <x:c r="L28" s="76" t="str">
-        <x:v>AEQA-116</x:v>
+        <x:v>AEQA-116
+AEQA-126</x:v>
       </x:c>
       <x:c r="M28" s="76" t="str"/>
       <x:c r="N28" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 15:31 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="31.5" customHeight="1">
@@ -7836,7 +7858,9 @@
       <x:c r="E29" s="76" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="F29" s="76" t="str"/>
+      <x:c r="F29" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G29" s="76" t="str">
         <x:v>REQ-NAV-002</x:v>
       </x:c>
@@ -7845,11 +7869,12 @@
       <x:c r="J29" s="76" t="str"/>
       <x:c r="K29" s="76" t="str"/>
       <x:c r="L29" s="76" t="str">
-        <x:v>AEQA-117</x:v>
+        <x:v>AEQA-117
+AEQA-127</x:v>
       </x:c>
       <x:c r="M29" s="76" t="str"/>
       <x:c r="N29" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 15:31 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="31.5" customHeight="1">
@@ -7868,7 +7893,9 @@
       <x:c r="E30" s="76" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="F30" s="76" t="str"/>
+      <x:c r="F30" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G30" s="76" t="str">
         <x:v>REQ-NAV-003</x:v>
       </x:c>
@@ -7877,11 +7904,12 @@
       <x:c r="J30" s="76" t="str"/>
       <x:c r="K30" s="76" t="str"/>
       <x:c r="L30" s="76" t="str">
-        <x:v>AEQA-118</x:v>
+        <x:v>AEQA-118
+AEQA-128</x:v>
       </x:c>
       <x:c r="M30" s="76" t="str"/>
       <x:c r="N30" s="76" t="str">
-        <x:v>10/Aug/26 9:00 PM</x:v>
+        <x:v>2026-08-17 15:31 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="31.5" customHeight="1">
@@ -9803,12 +9831,14 @@
         <x:v>AE-BUG-001 - Authenticated user information remains visible after logout when navigating back</x:v>
       </x:c>
       <x:c r="D84" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Selected for Development</x:v>
       </x:c>
       <x:c r="E84" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F84" s="76" t="str"/>
+      <x:c r="F84" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G84" s="76" t="str"/>
       <x:c r="H84" s="76" t="str"/>
       <x:c r="I84" s="76" t="str">
@@ -9819,7 +9849,7 @@
       <x:c r="L84" s="76" t="str"/>
       <x:c r="M84" s="76" t="str"/>
       <x:c r="N84" s="76" t="str">
-        <x:v>10/Aug/26 7:08 PM</x:v>
+        <x:v>2026-08-15 23:29 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="31.5" customHeight="1">
@@ -9833,12 +9863,14 @@
         <x:v>AE-BUG-002 - Repeated logout request causes an unhandled KeyError and exposes internal debugging information</x:v>
       </x:c>
       <x:c r="D85" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Selected for Development</x:v>
       </x:c>
       <x:c r="E85" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F85" s="76" t="str"/>
+      <x:c r="F85" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G85" s="76" t="str"/>
       <x:c r="H85" s="76" t="str"/>
       <x:c r="I85" s="76" t="str">
@@ -9849,7 +9881,7 @@
       <x:c r="L85" s="76" t="str"/>
       <x:c r="M85" s="76" t="str"/>
       <x:c r="N85" s="76" t="str">
-        <x:v>10/Aug/26 7:08 PM</x:v>
+        <x:v>2026-08-15 23:28 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="31.5" customHeight="1">
@@ -9868,7 +9900,9 @@
       <x:c r="E86" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F86" s="76" t="str"/>
+      <x:c r="F86" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G86" s="76" t="str"/>
       <x:c r="H86" s="76" t="str"/>
       <x:c r="I86" s="76" t="str">
@@ -9879,7 +9913,7 @@
       <x:c r="L86" s="76" t="str"/>
       <x:c r="M86" s="76" t="str"/>
       <x:c r="N86" s="76" t="str">
-        <x:v>10/Aug/26 8:36 PM</x:v>
+        <x:v>2026-08-12 22:25 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="31.5" customHeight="1">
@@ -9893,12 +9927,14 @@
         <x:v>AE-BUG-004 - The quantity field on the product-detail page does not respond when the user attempts to edit it. As a result, the user cannot select the desired quantity before adding the product to the cart.</x:v>
       </x:c>
       <x:c r="D87" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E87" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F87" s="76" t="str"/>
+      <x:c r="F87" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G87" s="76" t="str"/>
       <x:c r="H87" s="76" t="str"/>
       <x:c r="I87" s="76" t="str">
@@ -9909,7 +9945,7 @@
       <x:c r="L87" s="76" t="str"/>
       <x:c r="M87" s="76" t="str"/>
       <x:c r="N87" s="76" t="str">
-        <x:v>10/Aug/26 7:09 PM</x:v>
+        <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="31.5" customHeight="1">
@@ -9923,7 +9959,7 @@
         <x:v>BUG-API-001 - Products List API returns HTTP 200 instead of 405 for unsupported POST request</x:v>
       </x:c>
       <x:c r="D88" s="76" t="str">
-        <x:v>Selected for Development</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E88" s="76" t="str">
         <x:v>Medium</x:v>
@@ -9941,7 +9977,7 @@
       <x:c r="L88" s="76" t="str"/>
       <x:c r="M88" s="76" t="str"/>
       <x:c r="N88" s="76" t="str">
-        <x:v>11/Aug/26 9:29 AM</x:v>
+        <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="31.5" customHeight="1">
@@ -9955,12 +9991,14 @@
         <x:v>BUG-API-002 - Search Product API returns all products when required search_product parameter is omitted</x:v>
       </x:c>
       <x:c r="D89" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E89" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F89" s="76" t="str"/>
+      <x:c r="F89" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G89" s="76" t="str"/>
       <x:c r="H89" s="76" t="str"/>
       <x:c r="I89" s="76" t="str">
@@ -9971,7 +10009,7 @@
       <x:c r="L89" s="76" t="str"/>
       <x:c r="M89" s="76" t="str"/>
       <x:c r="N89" s="76" t="str">
-        <x:v>10/Aug/26 7:37 PM</x:v>
+        <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="31.5" customHeight="1">
@@ -10621,7 +10659,7 @@
       </x:c>
       <x:c r="M110" s="76" t="str"/>
       <x:c r="N110" s="76" t="str">
-        <x:v>16/Aug/26 12:50 AM</x:v>
+        <x:v>2026-08-17 13:22 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="31.5" customHeight="1">
@@ -10790,7 +10828,9 @@
       <x:c r="E115" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F115" s="76" t="str"/>
+      <x:c r="F115" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G115" s="76" t="str"/>
       <x:c r="H115" s="76" t="str">
         <x:v>AE-CATALOG-002</x:v>
@@ -10807,7 +10847,7 @@
       </x:c>
       <x:c r="M115" s="76" t="str"/>
       <x:c r="N115" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:17 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="31.5" customHeight="1">
@@ -10821,12 +10861,14 @@
         <x:v>AE-CART-004 - Verify searched products remain in the cart after login</x:v>
       </x:c>
       <x:c r="D116" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E116" s="76" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F116" s="76" t="str"/>
+      <x:c r="F116" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G116" s="76" t="str"/>
       <x:c r="H116" s="76" t="str">
         <x:v>AE-CART-004</x:v>
@@ -10843,7 +10885,7 @@
       </x:c>
       <x:c r="M116" s="76" t="str"/>
       <x:c r="N116" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-17 13:21 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="31.5" customHeight="1">
@@ -10862,7 +10904,9 @@
       <x:c r="E117" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F117" s="76" t="str"/>
+      <x:c r="F117" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G117" s="76" t="str"/>
       <x:c r="H117" s="76" t="str">
         <x:v>AE-REVIEW-001</x:v>
@@ -10879,7 +10923,7 @@
       </x:c>
       <x:c r="M117" s="76" t="str"/>
       <x:c r="N117" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:18 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="31.5" customHeight="1">
@@ -10898,7 +10942,9 @@
       <x:c r="E118" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F118" s="76" t="str"/>
+      <x:c r="F118" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G118" s="76" t="str"/>
       <x:c r="H118" s="76" t="str">
         <x:v>AE-CART-005</x:v>
@@ -10915,7 +10961,7 @@
       </x:c>
       <x:c r="M118" s="76" t="str"/>
       <x:c r="N118" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:18 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="31.5" customHeight="1">
@@ -10972,7 +11018,9 @@
       <x:c r="E120" s="76" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F120" s="76" t="str"/>
+      <x:c r="F120" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G120" s="76" t="str"/>
       <x:c r="H120" s="76" t="str">
         <x:v>AE-ORDER-005</x:v>
@@ -10989,7 +11037,7 @@
       </x:c>
       <x:c r="M120" s="76" t="str"/>
       <x:c r="N120" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:18 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="31.5" customHeight="1">
@@ -11008,7 +11056,9 @@
       <x:c r="E121" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F121" s="76" t="str"/>
+      <x:c r="F121" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G121" s="76" t="str"/>
       <x:c r="H121" s="76" t="str">
         <x:v>AE-NAV-002</x:v>
@@ -11025,7 +11075,7 @@
       </x:c>
       <x:c r="M121" s="76" t="str"/>
       <x:c r="N121" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:18 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="31.5" customHeight="1">
@@ -11044,7 +11094,9 @@
       <x:c r="E122" s="76" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F122" s="76" t="str"/>
+      <x:c r="F122" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G122" s="76" t="str"/>
       <x:c r="H122" s="76" t="str">
         <x:v>AE-NAV-003</x:v>
@@ -11061,7 +11113,7 @@
       </x:c>
       <x:c r="M122" s="76" t="str"/>
       <x:c r="N122" s="76" t="str">
-        <x:v>10/Aug/26 9:00 PM</x:v>
+        <x:v>2026-08-12 22:18 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -11135,7 +11187,7 @@
         <x:v>Automate end-to-end user registration with Playwright</x:v>
       </x:c>
       <x:c r="D125" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E125" t="str">
         <x:v>Highest</x:v>
@@ -11146,18 +11198,274 @@
       <x:c r="G125" t="str">
         <x:v>REQ-AUTH-001</x:v>
       </x:c>
-      <x:c r="H125"/>
-      <x:c r="I125"/>
+      <x:c r="H125" t="str"/>
+      <x:c r="I125" t="str"/>
       <x:c r="J125" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="K125"/>
-      <x:c r="L125"/>
+      <x:c r="K125" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L125" t="str"/>
       <x:c r="M125" t="str">
         <x:v>AEQA-1</x:v>
       </x:c>
       <x:c r="N125" t="str">
-        <x:v>16/Aug/26 1:03 AM</x:v>
+        <x:v>2026-08-16 23:42 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>AEQA-122</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>Automate the search and cart persistence scenario in Playwright</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F126" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G126" t="str">
+        <x:v>REQ-CART-004</x:v>
+      </x:c>
+      <x:c r="H126" t="str"/>
+      <x:c r="I126" t="str"/>
+      <x:c r="J126" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L126" t="str"/>
+      <x:c r="M126" t="str">
+        <x:v>AEQA-20</x:v>
+      </x:c>
+      <x:c r="N126" t="str">
+        <x:v>2026-08-17 13:03 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>AEQA-123</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Sub-task</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>Automate brand-based product navigation in Playwright</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F127" t="str"/>
+      <x:c r="G127" t="str">
+        <x:v>REQ-CATALOG-002</x:v>
+      </x:c>
+      <x:c r="H127" t="str"/>
+      <x:c r="I127" t="str"/>
+      <x:c r="J127" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L127" t="str"/>
+      <x:c r="M127" t="str">
+        <x:v>AEQA-19</x:v>
+      </x:c>
+      <x:c r="N127" t="str">
+        <x:v>2026-08-17 15:14 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>AEQA-124</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>AE-AUTO-REVIEW-001 - Automate product review submission in Playwright</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F128" t="str"/>
+      <x:c r="G128" t="str"/>
+      <x:c r="H128" t="str">
+        <x:v>AE-AUTO-REVIEW-001</x:v>
+      </x:c>
+      <x:c r="I128" t="str"/>
+      <x:c r="J128" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L128" t="str">
+        <x:v>AEQA-21</x:v>
+      </x:c>
+      <x:c r="M128" t="str"/>
+      <x:c r="N128" t="str">
+        <x:v>2026-08-17 15:30 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>AEQA-125</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>AE-AUTO-CART-005 - Automate Recommended Items add-to-cart in Playwright</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F129" t="str"/>
+      <x:c r="G129" t="str"/>
+      <x:c r="H129" t="str">
+        <x:v>AE-AUTO-CART-005</x:v>
+      </x:c>
+      <x:c r="I129" t="str"/>
+      <x:c r="J129" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L129" t="str">
+        <x:v>AEQA-22</x:v>
+      </x:c>
+      <x:c r="M129" t="str"/>
+      <x:c r="N129" t="str">
+        <x:v>2026-08-17 15:31 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>AEQA-126</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>AE-AUTO-ORDER-005 - Automate invoice download after purchase in Playwright</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="F130" t="str"/>
+      <x:c r="G130" t="str"/>
+      <x:c r="H130" t="str">
+        <x:v>AE-AUTO-ORDER-005</x:v>
+      </x:c>
+      <x:c r="I130" t="str"/>
+      <x:c r="J130" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L130" t="str">
+        <x:v>AEQA-24</x:v>
+      </x:c>
+      <x:c r="M130" t="str"/>
+      <x:c r="N130" t="str">
+        <x:v>2026-08-17 15:31 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>AEQA-127</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>AE-AUTO-NAV-002 - Automate scroll-down and arrow return-to-top in Playwright</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F131" t="str"/>
+      <x:c r="G131" t="str"/>
+      <x:c r="H131" t="str">
+        <x:v>AE-AUTO-NAV-002</x:v>
+      </x:c>
+      <x:c r="I131" t="str"/>
+      <x:c r="J131" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K131" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L131" t="str">
+        <x:v>AEQA-25</x:v>
+      </x:c>
+      <x:c r="M131" t="str"/>
+      <x:c r="N131" t="str">
+        <x:v>2026-08-17 15:31 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>AEQA-128</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>Test Case</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>AE-AUTO-NAV-003 - Automate scroll-down and scroll-up without the arrow in Playwright</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>Backlog</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F132" t="str"/>
+      <x:c r="G132" t="str"/>
+      <x:c r="H132" t="str">
+        <x:v>AE-AUTO-NAV-003</x:v>
+      </x:c>
+      <x:c r="I132" t="str"/>
+      <x:c r="J132" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K132" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="L132" t="str">
+        <x:v>AEQA-26</x:v>
+      </x:c>
+      <x:c r="M132" t="str"/>
+      <x:c r="N132" t="str">
+        <x:v>2026-08-17 15:31 EDT</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11175,7 +11483,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra012d6f785db4be3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c63327ba8b94eb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rb1f82aaa1c864070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rd3df77b818f14a28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="Rbecefb8ec2a64707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Raeb525563ac14c09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Re758762039af4438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R31a47194b1604f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R30dfb5f0c36542e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R47541595e75c48cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rf14c1f7314274f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Rf078edf6ab4c4192"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2725,7 +2725,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4e45ad3acfdf4e9e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4e053601d8740aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3162,7 +3162,7 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
@@ -3192,7 +3192,7 @@
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
@@ -3222,7 +3222,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="29" t="str">
-        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 33 Pass, 2 Fail, and 9 Not Run. REQ-CART-004 now has passing Playwright evidence under AEQA-122 while the separate manual case AEQA-112 remains Not Run. AEQA-121 is workflow Done, but registration execution remains Not Run until an explicit result is recorded. Five new automation Test Cases (AEQA-124 through AEQA-128) extend Jira traceability without changing execution results. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 37 Pass, 2 Fail, and 5 Not Run. REQ-AUTH-001, REQ-ORDER-002, REQ-ORDER-003, REQ-CART-004, and REQ-REVIEW-001 are reconciled to their latest passing Jira results. Result-specific evidence is attached to the correct Jira work items. Planned automation Test Cases AEQA-125 through AEQA-128 remain Not Run and do not change requirement execution results. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
       </x:c>
       <x:c r="B21" s="30"/>
       <x:c r="C21" s="30"/>
@@ -3318,7 +3318,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39ade9095d9c4b7d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R641f1d3bb0734382"/>
 </x:worksheet>
 </file>
 
@@ -3500,7 +3500,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H8" s="89" t="str">
-        <x:v>Test design is complete. Jira AEQA-106 is workflow-complete but its Execution Status remains Not Run. Automation implementation AEQA-121 is Done; do not infer a passing execution without an explicit recorded result.</x:v>
+        <x:v>Jira Test Case AEQA-106 passed the complete registration workflow. Playwright implementation AEQA-121 is Done, and the registration evidence is attached.</x:v>
       </x:c>
       <x:c r="I8" s="107" t="str">
         <x:v>Functional — Positive</x:v>
@@ -3512,25 +3512,26 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L8" s="107" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M8" s="107" t="str">
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N8" s="107" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O8" s="116" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="P8" s="89" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-001.png
 ..\Screenshots\AE-SIGNUP-002.png
-..\Screenshots\AE-ACCOUNT-001.png</x:v>
+..\Screenshots\AE-ACCOUNT-001.png
+..\Automation\Execution Evidence\AE-SIGNUP-006.png</x:v>
       </x:c>
       <x:c r="Q8" s="89"/>
       <x:c r="R8" s="90" t="str">
-        <x:v>AEQA-121 is Done and evidence is attached, but AE-SIGNUP-006 / AEQA-106 remains Not Run. Record an explicit execution result before changing this row.</x:v>
+        <x:v>AEQA-106 passed and AEQA-121 is Done. Registration coverage includes the optional newsletter and partner-offer selections plus account cleanup.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -4269,7 +4270,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H22" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-108 (AE-ORDER-002) is linked to AEQA-15; execution remains pending.</x:v>
+        <x:v>Jira Test Case AEQA-108 passed. A user registered before shopping, completed checkout, and received the order confirmation.</x:v>
       </x:c>
       <x:c r="I22" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4281,7 +4282,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L22" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M22" s="109" t="str">
         <x:v>N/A</x:v>
@@ -4290,12 +4291,14 @@
         <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O22" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P22" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P22" s="93" t="str">
+        <x:v>Jira AEQA-108 attachments: image_2026-08-11_232841897.png; image_2026-08-11_233013612.png; image_2026-08-11_233046264.png; invoice (1).txt</x:v>
+      </x:c>
       <x:c r="Q22" s="93"/>
       <x:c r="R22" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-ORDER-002 (AEQA-108) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Manual execution passed in AEQA-108. Evidence and invoice output remain attached to the Jira Test Case.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="48" customHeight="1">
@@ -4321,7 +4324,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H23" s="93" t="str">
-        <x:v>Test design is complete. Jira AEQA-109 (AE-ORDER-003) is linked to AEQA-16; execution remains pending.</x:v>
+        <x:v>Jira Test Case AEQA-109 passed. An existing user logged in before checkout, completed the order, and received the success confirmation.</x:v>
       </x:c>
       <x:c r="I23" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4333,7 +4336,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L23" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M23" s="109" t="str">
         <x:v>N/A</x:v>
@@ -4342,12 +4345,14 @@
         <x:v>Not Automated</x:v>
       </x:c>
       <x:c r="O23" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P23" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P23" s="93" t="str">
+        <x:v>Jira AEQA-109 attachments: image_2026-08-11_234034965.png; image_2026-08-11_234130953.png; image_2026-08-11_234238291.png; invoice (2).txt</x:v>
+      </x:c>
       <x:c r="Q23" s="93"/>
       <x:c r="R23" s="94" t="str">
-        <x:v>Design gap closed in Jira. Execute AE-ORDER-003 (AEQA-109) and reconcile the result, evidence, and any defect back to this RTM.</x:v>
+        <x:v>Manual execution passed in AEQA-109. Evidence and invoice output remain attached to the Jira Test Case.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="48" customHeight="1">
@@ -4533,7 +4538,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H27" s="93" t="str">
-        <x:v>Manual case AEQA-112 / AE-CART-004 remains Not Run. The Playwright implementation under AEQA-122 is Done and the saved 1/1 Chromium report plus before/after cart screenshots passed.</x:v>
+        <x:v>Manual case AEQA-112 and Playwright task AEQA-122 are linked to AEQA-20. Both passed, and their before-login and after-login cart evidence is attached to the correct Jira work items.</x:v>
       </x:c>
       <x:c r="I27" s="109" t="str">
         <x:v>End-to-End — Positive</x:v>
@@ -4545,7 +4550,7 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L27" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M27" s="109" t="str">
         <x:v>N/A</x:v>
@@ -4557,13 +4562,12 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P27" s="93" t="str">
-        <x:v>..\Automation\Execution Evidence\AE-CART-004(1).png
-..\Automation\Execution Evidence\AE-CART-004(2).png
-..\Automation\test-results\html-report\index.html</x:v>
+        <x:v>Manual evidence: Jira AEQA-112 attachments AE-CART-004(1).png and AE-CART-004(2).png
+Automation evidence: ..\Automation\Execution Evidence\AE-CART-004(1).png; ..\Automation\Execution Evidence\AE-CART-004(2).png</x:v>
       </x:c>
       <x:c r="Q27" s="93"/>
       <x:c r="R27" s="94" t="str">
-        <x:v>Automation passed under AEQA-122 on 2026-08-17. Keep the manual AEQA-112 result separate and Not Run until that case is executed.</x:v>
+        <x:v>Manual testing and Playwright automation passed on 2026-08-17. Keep the manual and automation evidence attached to their separate Jira work items.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="48" customHeight="1">
@@ -4590,7 +4594,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H28" s="93" t="str">
-        <x:v>Manual case AEQA-113 and automation case AEQA-124 are linked to AEQA-21. Both remain Not Run; Playwright implementation is planned.</x:v>
+        <x:v>Manual case AEQA-113 and automation case AEQA-124 are linked to AEQA-21. Both passed, and their result-specific evidence is attached to the correct Jira Test Cases.</x:v>
       </x:c>
       <x:c r="I28" s="109" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4602,21 +4606,24 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L28" s="109" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M28" s="109" t="str">
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N28" s="109" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O28" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P28" s="93"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P28" s="93" t="str">
+        <x:v>Manual evidence: Jira AEQA-113 attachments (2 screenshots)
+Automation evidence: ..\Automation\Execution Evidence\AE-REVIEW-001(1).png; ..\Automation\Execution Evidence\AE-REVIEW-001(2).png</x:v>
+      </x:c>
       <x:c r="Q28" s="93"/>
       <x:c r="R28" s="94" t="str">
-        <x:v>Execute AE-REVIEW-001 and implement AE-AUTO-REVIEW-001 independently; attach result-specific evidence to each Jira Test Case.</x:v>
+        <x:v>Manual testing and Playwright automation passed on 2026-08-17. Keep the manual and automation evidence attached to their separate Jira Test Cases.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="48" customHeight="1">
@@ -6087,7 +6094,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16276633df5845d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8bb945c7a446e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6503,7 +6510,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77669e5cd87d4e0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc505a24c44634916"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6939,7 +6946,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R695a17ac7ad147e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4308aa48128447b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7068,7 +7075,9 @@
       </x:c>
       <x:c r="H5" s="76" t="str"/>
       <x:c r="I5" s="76" t="str"/>
-      <x:c r="J5" s="76" t="str"/>
+      <x:c r="J5" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K5" s="76" t="str"/>
       <x:c r="L5" s="76" t="str">
         <x:v>AEQA-45
@@ -7078,7 +7087,7 @@
       </x:c>
       <x:c r="M5" s="76" t="str"/>
       <x:c r="N5" s="76" t="str">
-        <x:v>2026-08-16 23:42 EDT</x:v>
+        <x:v>2026-08-17 19:33 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="31.5" customHeight="1">
@@ -7512,7 +7521,7 @@
         <x:v>REQ-ORDER-002 - Place Order: Register before Checkout</x:v>
       </x:c>
       <x:c r="D19" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E19" s="76" t="str">
         <x:v>Highest</x:v>
@@ -7525,14 +7534,16 @@
       </x:c>
       <x:c r="H19" s="76" t="str"/>
       <x:c r="I19" s="76" t="str"/>
-      <x:c r="J19" s="76" t="str"/>
+      <x:c r="J19" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K19" s="76" t="str"/>
       <x:c r="L19" s="76" t="str">
         <x:v>AEQA-108</x:v>
       </x:c>
       <x:c r="M19" s="76" t="str"/>
       <x:c r="N19" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 21:22 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="31.5" customHeight="1">
@@ -7546,7 +7557,7 @@
         <x:v>REQ-ORDER-003 - Place Order: Login before Checkout</x:v>
       </x:c>
       <x:c r="D20" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E20" s="76" t="str">
         <x:v>Highest</x:v>
@@ -7559,14 +7570,16 @@
       </x:c>
       <x:c r="H20" s="76" t="str"/>
       <x:c r="I20" s="76" t="str"/>
-      <x:c r="J20" s="76" t="str"/>
+      <x:c r="J20" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K20" s="76" t="str"/>
       <x:c r="L20" s="76" t="str">
         <x:v>AEQA-109</x:v>
       </x:c>
       <x:c r="M20" s="76" t="str"/>
       <x:c r="N20" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:10 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="31.5" customHeight="1">
@@ -7693,14 +7706,16 @@
       </x:c>
       <x:c r="H24" s="76" t="str"/>
       <x:c r="I24" s="76" t="str"/>
-      <x:c r="J24" s="76" t="str"/>
+      <x:c r="J24" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K24" s="76" t="str"/>
       <x:c r="L24" s="76" t="str">
         <x:v>AEQA-112</x:v>
       </x:c>
       <x:c r="M24" s="76" t="str"/>
       <x:c r="N24" s="76" t="str">
-        <x:v>2026-08-17 13:05 EDT</x:v>
+        <x:v>2026-08-17 19:22 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="31.5" customHeight="1">
@@ -7714,7 +7729,7 @@
         <x:v>REQ-REVIEW-001 - Add review on product</x:v>
       </x:c>
       <x:c r="D25" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E25" s="76" t="str">
         <x:v>Medium</x:v>
@@ -7727,7 +7742,9 @@
       </x:c>
       <x:c r="H25" s="76" t="str"/>
       <x:c r="I25" s="76" t="str"/>
-      <x:c r="J25" s="76" t="str"/>
+      <x:c r="J25" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K25" s="76" t="str"/>
       <x:c r="L25" s="76" t="str">
         <x:v>AEQA-113
@@ -7735,7 +7752,7 @@
       </x:c>
       <x:c r="M25" s="76" t="str"/>
       <x:c r="N25" s="76" t="str">
-        <x:v>2026-08-17 15:30 EDT</x:v>
+        <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="31.5" customHeight="1">
@@ -10649,7 +10666,7 @@
       </x:c>
       <x:c r="I110" s="76" t="str"/>
       <x:c r="J110" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K110" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10657,7 +10674,7 @@
       <x:c r="L110" s="76" t="str">
         <x:v>AEQA-1</x:v>
       </x:c>
-      <x:c r="M110" s="76" t="str"/>
+      <x:c r="M110" s="76"/>
       <x:c r="N110" s="76" t="str">
         <x:v>2026-08-17 13:22 EDT</x:v>
       </x:c>
@@ -10711,19 +10728,21 @@
         <x:v>AE-ORDER-002 - Verify an order can be placed after registering before checkout</x:v>
       </x:c>
       <x:c r="D112" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E112" s="76" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F112" s="76" t="str"/>
+      <x:c r="F112" s="76" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G112" s="76" t="str"/>
       <x:c r="H112" s="76" t="str">
         <x:v>AE-ORDER-002</x:v>
       </x:c>
       <x:c r="I112" s="76" t="str"/>
       <x:c r="J112" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K112" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10731,9 +10750,9 @@
       <x:c r="L112" s="76" t="str">
         <x:v>AEQA-15</x:v>
       </x:c>
-      <x:c r="M112" s="76" t="str"/>
+      <x:c r="M112" s="76"/>
       <x:c r="N112" s="76" t="str">
-        <x:v>10/Aug/26 8:59 PM</x:v>
+        <x:v>2026-08-12 22:28 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="31.5" customHeight="1">
@@ -10747,7 +10766,7 @@
         <x:v>AE-ORDER-003 - Verify an existing user can log in before checkout and place an order</x:v>
       </x:c>
       <x:c r="D113" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E113" s="76" t="str">
         <x:v>Highest</x:v>
@@ -10761,7 +10780,7 @@
       </x:c>
       <x:c r="I113" s="76" t="str"/>
       <x:c r="J113" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K113" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10769,9 +10788,9 @@
       <x:c r="L113" s="76" t="str">
         <x:v>AEQA-16</x:v>
       </x:c>
-      <x:c r="M113" s="76" t="str"/>
+      <x:c r="M113" s="76"/>
       <x:c r="N113" s="76" t="str">
-        <x:v>11/Aug/26 9:31 AM</x:v>
+        <x:v>2026-08-12 22:28 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="31.5" customHeight="1">
@@ -10875,7 +10894,7 @@
       </x:c>
       <x:c r="I116" s="76" t="str"/>
       <x:c r="J116" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K116" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10883,9 +10902,9 @@
       <x:c r="L116" s="76" t="str">
         <x:v>AEQA-20</x:v>
       </x:c>
-      <x:c r="M116" s="76" t="str"/>
+      <x:c r="M116" s="76"/>
       <x:c r="N116" s="76" t="str">
-        <x:v>2026-08-17 13:21 EDT</x:v>
+        <x:v>2026-08-17 19:22 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="31.5" customHeight="1">
@@ -10899,7 +10918,7 @@
         <x:v>AE-REVIEW-001 - Verify a visitor can submit a review from a product-details page</x:v>
       </x:c>
       <x:c r="D117" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E117" s="76" t="str">
         <x:v>Medium</x:v>
@@ -10913,7 +10932,7 @@
       </x:c>
       <x:c r="I117" s="76" t="str"/>
       <x:c r="J117" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K117" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10921,9 +10940,9 @@
       <x:c r="L117" s="76" t="str">
         <x:v>AEQA-21</x:v>
       </x:c>
-      <x:c r="M117" s="76" t="str"/>
+      <x:c r="M117" s="76"/>
       <x:c r="N117" s="76" t="str">
-        <x:v>2026-08-12 22:18 EDT</x:v>
+        <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="31.5" customHeight="1">
@@ -11299,19 +11318,21 @@
         <x:v>AE-AUTO-REVIEW-001 - Automate product review submission in Playwright</x:v>
       </x:c>
       <x:c r="D128" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E128" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F128" t="str"/>
+      <x:c r="F128" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G128" t="str"/>
       <x:c r="H128" t="str">
         <x:v>AE-AUTO-REVIEW-001</x:v>
       </x:c>
       <x:c r="I128" t="str"/>
       <x:c r="J128" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K128" t="str">
         <x:v>Playwright</x:v>
@@ -11319,9 +11340,9 @@
       <x:c r="L128" t="str">
         <x:v>AEQA-21</x:v>
       </x:c>
-      <x:c r="M128" t="str"/>
+      <x:c r="M128"/>
       <x:c r="N128" t="str">
-        <x:v>2026-08-17 15:30 EDT</x:v>
+        <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -11340,24 +11361,26 @@
       <x:c r="E129" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F129" t="str"/>
-      <x:c r="G129" t="str"/>
+      <x:c r="F129" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G129"/>
       <x:c r="H129" t="str">
         <x:v>AE-AUTO-CART-005</x:v>
       </x:c>
-      <x:c r="I129" t="str"/>
+      <x:c r="I129"/>
       <x:c r="J129" t="str">
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>Playwright</x:v>
+        <x:v>Automation Candidate</x:v>
       </x:c>
       <x:c r="L129" t="str">
         <x:v>AEQA-22</x:v>
       </x:c>
-      <x:c r="M129" t="str"/>
+      <x:c r="M129"/>
       <x:c r="N129" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
+        <x:v>2026-08-17 19:24 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -11376,24 +11399,26 @@
       <x:c r="E130" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F130" t="str"/>
-      <x:c r="G130" t="str"/>
+      <x:c r="F130" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G130"/>
       <x:c r="H130" t="str">
         <x:v>AE-AUTO-ORDER-005</x:v>
       </x:c>
-      <x:c r="I130" t="str"/>
+      <x:c r="I130"/>
       <x:c r="J130" t="str">
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="K130" t="str">
-        <x:v>Playwright</x:v>
+        <x:v>Automation Candidate</x:v>
       </x:c>
       <x:c r="L130" t="str">
         <x:v>AEQA-24</x:v>
       </x:c>
-      <x:c r="M130" t="str"/>
+      <x:c r="M130"/>
       <x:c r="N130" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
+        <x:v>2026-08-17 19:24 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -11412,24 +11437,26 @@
       <x:c r="E131" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F131" t="str"/>
-      <x:c r="G131" t="str"/>
+      <x:c r="F131" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G131"/>
       <x:c r="H131" t="str">
         <x:v>AE-AUTO-NAV-002</x:v>
       </x:c>
-      <x:c r="I131" t="str"/>
+      <x:c r="I131"/>
       <x:c r="J131" t="str">
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="K131" t="str">
-        <x:v>Playwright</x:v>
+        <x:v>Automation Candidate</x:v>
       </x:c>
       <x:c r="L131" t="str">
         <x:v>AEQA-25</x:v>
       </x:c>
-      <x:c r="M131" t="str"/>
+      <x:c r="M131"/>
       <x:c r="N131" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
+        <x:v>2026-08-17 19:24 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -11448,24 +11475,26 @@
       <x:c r="E132" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F132" t="str"/>
-      <x:c r="G132" t="str"/>
+      <x:c r="F132" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G132"/>
       <x:c r="H132" t="str">
         <x:v>AE-AUTO-NAV-003</x:v>
       </x:c>
-      <x:c r="I132" t="str"/>
+      <x:c r="I132"/>
       <x:c r="J132" t="str">
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="K132" t="str">
-        <x:v>Playwright</x:v>
+        <x:v>Automation Candidate</x:v>
       </x:c>
       <x:c r="L132" t="str">
         <x:v>AEQA-26</x:v>
       </x:c>
-      <x:c r="M132" t="str"/>
+      <x:c r="M132"/>
       <x:c r="N132" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
+        <x:v>2026-08-17 19:24 EDT</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11483,7 +11512,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c63327ba8b94eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a0d37e3cda84c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R31a47194b1604f54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R30dfb5f0c36542e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R47541595e75c48cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rf14c1f7314274f2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Rf078edf6ab4c4192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R56e8e386f27f41da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R30264579887248b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R2a6eca20ec7c4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rb5b9934d2bb44a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R0c0bdc12b1eb418a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1184,7 +1184,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="140">
+  <x:cellXfs count="151">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1588,6 +1588,39 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -2725,7 +2758,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4e053601d8740aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1742cb2ebb24793"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3162,7 +3195,7 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
@@ -3192,7 +3225,7 @@
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
@@ -3221,22 +3254,22 @@
       <x:c r="N20" s="28"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="29" t="str">
-        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 37 Pass, 2 Fail, and 5 Not Run. REQ-AUTH-001, REQ-ORDER-002, REQ-ORDER-003, REQ-CART-004, and REQ-REVIEW-001 are reconciled to their latest passing Jira results. Result-specific evidence is attached to the correct Jira work items. Planned automation Test Cases AEQA-125 through AEQA-128 remain Not Run and do not change requirement execution results. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
-      </x:c>
-      <x:c r="B21" s="30"/>
-      <x:c r="C21" s="30"/>
-      <x:c r="D21" s="30"/>
-      <x:c r="E21" s="30"/>
-      <x:c r="F21" s="30"/>
-      <x:c r="G21" s="30"/>
-      <x:c r="H21" s="30"/>
-      <x:c r="I21" s="30"/>
-      <x:c r="J21" s="30"/>
-      <x:c r="K21" s="30"/>
-      <x:c r="L21" s="30"/>
-      <x:c r="M21" s="30"/>
-      <x:c r="N21" s="31"/>
+      <x:c r="A21" s="140" t="str">
+        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 41 Pass, 2 Fail, and 1 Not Run. REQ-CART-005, REQ-ORDER-005, REQ-NAV-002, and REQ-NAV-003 are reconciled to their latest passing manual and automation results. AE-AUTO-NAV-003 / AEQA-128 remains Not Run and is not claimed as executed. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+      </x:c>
+      <x:c r="B21" s="141"/>
+      <x:c r="C21" s="141"/>
+      <x:c r="D21" s="141"/>
+      <x:c r="E21" s="141"/>
+      <x:c r="F21" s="141"/>
+      <x:c r="G21" s="141"/>
+      <x:c r="H21" s="141"/>
+      <x:c r="I21" s="141"/>
+      <x:c r="J21" s="141"/>
+      <x:c r="K21" s="141"/>
+      <x:c r="L21" s="141"/>
+      <x:c r="M21" s="141"/>
+      <x:c r="N21" s="142"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="32"/>
@@ -3318,7 +3351,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R641f1d3bb0734382"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57c505957ba24ed8"/>
 </x:worksheet>
 </file>
 
@@ -3366,7 +3399,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="str">
-        <x:v>Coverage synchronized with 53 Jira Test Cases through 2026-08-17; Jira workflow and test execution status remain independently reconciled.</x:v>
+        <x:v>Coverage synchronized with 53 Jira Test Cases through 2026-08-17; Jira workflow and test execution status remain independently reconciled</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -3474,7 +3507,7 @@
         <x:v>Gap / Reconciliation Note</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="48" customHeight="1">
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A8" s="106" t="str">
         <x:v>REQ-AUTH-001</x:v>
       </x:c>
@@ -3487,54 +3520,54 @@
       <x:c r="D8" s="107" t="str">
         <x:v>Registration</x:v>
       </x:c>
-      <x:c r="E8" s="107" t="str">
+      <x:c r="E8" s="143" t="str">
         <x:v>Register User</x:v>
       </x:c>
-      <x:c r="F8" s="107" t="str">
+      <x:c r="F8" s="143" t="str">
         <x:v>AE-SIGNUP-001
 AE-SIGNUP-002
 AE-ACCOUNT-001
 AE-SIGNUP-006</x:v>
       </x:c>
-      <x:c r="G8" s="115" t="str">
+      <x:c r="G8" s="144" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H8" s="89" t="str">
+      <x:c r="H8" s="82" t="str">
         <x:v>Jira Test Case AEQA-106 passed the complete registration workflow. Playwright implementation AEQA-121 is Done, and the registration evidence is attached.</x:v>
       </x:c>
-      <x:c r="I8" s="107" t="str">
+      <x:c r="I8" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J8" s="107" t="str">
+      <x:c r="J8" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K8" s="107" t="str">
+      <x:c r="K8" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L8" s="107" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M8" s="107" t="str">
+      <x:c r="L8" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M8" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N8" s="107" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O8" s="116" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P8" s="89" t="str">
+      <x:c r="N8" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O8" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P8" s="82" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-001.png
 ..\Screenshots\AE-SIGNUP-002.png
 ..\Screenshots\AE-ACCOUNT-001.png
 ..\Automation\Execution Evidence\AE-SIGNUP-006.png</x:v>
       </x:c>
-      <x:c r="Q8" s="89"/>
-      <x:c r="R8" s="90" t="str">
+      <x:c r="Q8" s="82"/>
+      <x:c r="R8" s="82" t="str">
         <x:v>AEQA-106 passed and AEQA-121 is Done. Registration coverage includes the optional newsletter and partner-offer selections plus account cleanup.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
+    <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A9" s="108" t="str">
         <x:v>REQ-AUTH-002</x:v>
       </x:c>
@@ -3547,50 +3580,50 @@
       <x:c r="D9" s="109" t="str">
         <x:v>Login / Account</x:v>
       </x:c>
-      <x:c r="E9" s="109" t="str">
+      <x:c r="E9" s="143" t="str">
         <x:v>Login User with correct email and password</x:v>
       </x:c>
-      <x:c r="F9" s="109" t="str">
+      <x:c r="F9" s="143" t="str">
         <x:v>AE-LOGIN-001
 AE-ACCOUNT-001</x:v>
       </x:c>
-      <x:c r="G9" s="117" t="str">
+      <x:c r="G9" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H9" s="93" t="str">
+      <x:c r="H9" s="82" t="str">
         <x:v>Valid login, username confirmation, and account deletion are covered across two focused test cases.</x:v>
       </x:c>
-      <x:c r="I9" s="109" t="str">
+      <x:c r="I9" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J9" s="109" t="str">
+      <x:c r="J9" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K9" s="109" t="str">
+      <x:c r="K9" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L9" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M9" s="109" t="str">
+      <x:c r="L9" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M9" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N9" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O9" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P9" s="93" t="str">
+      <x:c r="N9" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O9" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P9" s="82" t="str">
         <x:v>..\Screenshots\AE-LOGIN-001.png
 ..\Screenshots\AE-ACCOUNT-001.png</x:v>
       </x:c>
-      <x:c r="Q9" s="93"/>
-      <x:c r="R9" s="94" t="str">
+      <x:c r="Q9" s="82"/>
+      <x:c r="R9" s="82" t="str">
         <x:v>No immediate gap. Maintain cross-reference between the two focused cases.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
+    <x:row r="10" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A10" s="108" t="str">
         <x:v>REQ-AUTH-003</x:v>
       </x:c>
@@ -3603,50 +3636,50 @@
       <x:c r="D10" s="109" t="str">
         <x:v>Login</x:v>
       </x:c>
-      <x:c r="E10" s="109" t="str">
+      <x:c r="E10" s="143" t="str">
         <x:v>Login User with incorrect email and password</x:v>
       </x:c>
-      <x:c r="F10" s="109" t="str">
+      <x:c r="F10" s="143" t="str">
         <x:v>AE-LOGIN-003
 AE-LOGIN-004</x:v>
       </x:c>
-      <x:c r="G10" s="117" t="str">
+      <x:c r="G10" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H10" s="93" t="str">
+      <x:c r="H10" s="82" t="str">
         <x:v>Incorrect-password handling is covered by AE-LOGIN-003, and rejection of an unregistered email address is covered by AE-LOGIN-004.</x:v>
       </x:c>
-      <x:c r="I10" s="109" t="str">
+      <x:c r="I10" s="143" t="str">
         <x:v>Functional — Negative</x:v>
       </x:c>
-      <x:c r="J10" s="109" t="str">
+      <x:c r="J10" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K10" s="109" t="str">
+      <x:c r="K10" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L10" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M10" s="109" t="str">
+      <x:c r="L10" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M10" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N10" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O10" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P10" s="93" t="str">
+      <x:c r="N10" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O10" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P10" s="82" t="str">
         <x:v>..\Screenshots\AE-LOGIN-003.png
 ..\Screenshots\AE-LOGIN-004.png</x:v>
       </x:c>
-      <x:c r="Q10" s="93"/>
-      <x:c r="R10" s="94" t="str">
+      <x:c r="Q10" s="82"/>
+      <x:c r="R10" s="82" t="str">
         <x:v>No immediate coverage gap. Retain both cases so invalid-password and unregistered-email behavior remain independently traceable.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="48" customHeight="1">
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A11" s="108" t="str">
         <x:v>REQ-AUTH-004</x:v>
       </x:c>
@@ -3659,51 +3692,51 @@
       <x:c r="D11" s="109" t="str">
         <x:v>Logout</x:v>
       </x:c>
-      <x:c r="E11" s="109" t="str">
+      <x:c r="E11" s="143" t="str">
         <x:v>Logout User</x:v>
       </x:c>
-      <x:c r="F11" s="109" t="str">
+      <x:c r="F11" s="143" t="str">
         <x:v>AE-LOGOUT-001</x:v>
       </x:c>
-      <x:c r="G11" s="117" t="str">
+      <x:c r="G11" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H11" s="93" t="str">
+      <x:c r="H11" s="82" t="str">
         <x:v>The source logout flow and additional browser-back session behavior were executed.</x:v>
       </x:c>
-      <x:c r="I11" s="109" t="str">
+      <x:c r="I11" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J11" s="109" t="str">
+      <x:c r="J11" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K11" s="109" t="str">
+      <x:c r="K11" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L11" s="109" t="str">
+      <x:c r="L11" s="143" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="M11" s="109" t="str">
+      <x:c r="M11" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N11" s="109" t="str">
+      <x:c r="N11" s="143" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="O11" s="118" t="str">
+      <x:c r="O11" s="146" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="P11" s="93" t="str">
+      <x:c r="P11" s="82" t="str">
         <x:v>..\Screenshots\AE-LOGOUT-001.png</x:v>
       </x:c>
-      <x:c r="Q11" s="93" t="str">
+      <x:c r="Q11" s="82" t="str">
         <x:v>AE-BUG-001
 AE-BUG-002</x:v>
       </x:c>
-      <x:c r="R11" s="94" t="str">
+      <x:c r="R11" s="82" t="str">
         <x:v>Retest after defects are corrected. Keep the additional browser-back check as enhanced coverage.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="48" customHeight="1">
+    <x:row r="12" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A12" s="108" t="str">
         <x:v>REQ-AUTH-005</x:v>
       </x:c>
@@ -3716,48 +3749,48 @@
       <x:c r="D12" s="109" t="str">
         <x:v>Registration</x:v>
       </x:c>
-      <x:c r="E12" s="109" t="str">
+      <x:c r="E12" s="143" t="str">
         <x:v>Register User with existing email</x:v>
       </x:c>
-      <x:c r="F12" s="109" t="str">
+      <x:c r="F12" s="143" t="str">
         <x:v>AE-SIGNUP-005</x:v>
       </x:c>
-      <x:c r="G12" s="117" t="str">
+      <x:c r="G12" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H12" s="93" t="str">
+      <x:c r="H12" s="82" t="str">
         <x:v>Registration with an already registered email address was executed successfully and the expected duplicate-email error was displayed.</x:v>
       </x:c>
-      <x:c r="I12" s="109" t="str">
+      <x:c r="I12" s="143" t="str">
         <x:v>Functional — Negative</x:v>
       </x:c>
-      <x:c r="J12" s="109" t="str">
+      <x:c r="J12" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K12" s="109" t="str">
+      <x:c r="K12" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L12" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M12" s="109" t="str">
+      <x:c r="L12" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M12" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N12" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O12" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P12" s="93" t="str">
+      <x:c r="N12" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O12" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P12" s="82" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-005.png</x:v>
       </x:c>
-      <x:c r="Q12" s="93"/>
-      <x:c r="R12" s="94" t="str">
+      <x:c r="Q12" s="82"/>
+      <x:c r="R12" s="82" t="str">
         <x:v>No immediate gap. Continue using a dedicated QA account and sanitized evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
+    <x:row r="13" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A13" s="108" t="str">
         <x:v>REQ-CONTACT-001</x:v>
       </x:c>
@@ -3770,48 +3803,48 @@
       <x:c r="D13" s="109" t="str">
         <x:v>Contact</x:v>
       </x:c>
-      <x:c r="E13" s="109" t="str">
+      <x:c r="E13" s="143" t="str">
         <x:v>Contact Us Form</x:v>
       </x:c>
-      <x:c r="F13" s="109" t="str">
+      <x:c r="F13" s="143" t="str">
         <x:v>AE-CONTACT-001</x:v>
       </x:c>
-      <x:c r="G13" s="117" t="str">
+      <x:c r="G13" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H13" s="93" t="str">
+      <x:c r="H13" s="82" t="str">
         <x:v>Text entry, permitted file upload, the confirmation dialog, success messaging, and return to Home all matched the expected result.</x:v>
       </x:c>
-      <x:c r="I13" s="109" t="str">
+      <x:c r="I13" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J13" s="109" t="str">
+      <x:c r="J13" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K13" s="109" t="str">
+      <x:c r="K13" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L13" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M13" s="109" t="str">
+      <x:c r="L13" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M13" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N13" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O13" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P13" s="93" t="str">
+      <x:c r="N13" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O13" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P13" s="82" t="str">
         <x:v>..\Screenshots\AE-CONTACT-001.png</x:v>
       </x:c>
-      <x:c r="Q13" s="93"/>
-      <x:c r="R13" s="94" t="str">
+      <x:c r="Q13" s="82"/>
+      <x:c r="R13" s="82" t="str">
         <x:v>No immediate gap. Preserve the sanitized AE-CONTACT-001 screenshot and successful return-to-Home observation for regression evidence.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="48" customHeight="1">
+    <x:row r="14" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A14" s="108" t="str">
         <x:v>REQ-NAV-001</x:v>
       </x:c>
@@ -3824,48 +3857,48 @@
       <x:c r="D14" s="109" t="str">
         <x:v>Navigation</x:v>
       </x:c>
-      <x:c r="E14" s="109" t="str">
+      <x:c r="E14" s="143" t="str">
         <x:v>Verify Test Cases Page</x:v>
       </x:c>
-      <x:c r="F14" s="109" t="str">
+      <x:c r="F14" s="143" t="str">
         <x:v>AE-NAV-001</x:v>
       </x:c>
-      <x:c r="G14" s="117" t="str">
+      <x:c r="G14" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H14" s="93" t="str">
+      <x:c r="H14" s="82" t="str">
         <x:v> Navigation to the Test Cases page completed without error and the published scenarios were visible as expected.</x:v>
       </x:c>
-      <x:c r="I14" s="109" t="str">
+      <x:c r="I14" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J14" s="109" t="str">
+      <x:c r="J14" s="143" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="K14" s="109" t="str">
+      <x:c r="K14" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L14" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M14" s="109" t="str">
+      <x:c r="L14" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M14" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N14" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O14" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P14" s="93" t="str">
+      <x:c r="N14" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O14" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P14" s="82" t="str">
         <x:v>..\Screenshots\AE-NAV-001.png</x:v>
       </x:c>
-      <x:c r="Q14" s="93"/>
-      <x:c r="R14" s="94" t="str">
+      <x:c r="Q14" s="82"/>
+      <x:c r="R14" s="82" t="str">
         <x:v>No immediate gap. Retain AE-NAV-001 evidence showing both successful navigation and the published Test Cases page content.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="48" customHeight="1">
+    <x:row r="15" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A15" s="108" t="str">
         <x:v>REQ-PRODUCT-001</x:v>
       </x:c>
@@ -3878,48 +3911,48 @@
       <x:c r="D15" s="109" t="str">
         <x:v>Products</x:v>
       </x:c>
-      <x:c r="E15" s="109" t="str">
+      <x:c r="E15" s="143" t="str">
         <x:v>Verify All Products and product detail page</x:v>
       </x:c>
-      <x:c r="F15" s="109" t="str">
+      <x:c r="F15" s="143" t="str">
         <x:v>AE-PRODUCT-001</x:v>
       </x:c>
-      <x:c r="G15" s="117" t="str">
+      <x:c r="G15" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H15" s="93" t="str">
+      <x:c r="H15" s="82" t="str">
         <x:v>The All Products page, complete product list, product-detail navigation, and required product attributes were verified successfully.</x:v>
       </x:c>
-      <x:c r="I15" s="109" t="str">
+      <x:c r="I15" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J15" s="109" t="str">
+      <x:c r="J15" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K15" s="109" t="str">
+      <x:c r="K15" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L15" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M15" s="109" t="str">
+      <x:c r="L15" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M15" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N15" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O15" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P15" s="93" t="str">
+      <x:c r="N15" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O15" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P15" s="82" t="str">
         <x:v>..\Screenshots\AE-PRODUCT-001.png</x:v>
       </x:c>
-      <x:c r="Q15" s="93"/>
-      <x:c r="R15" s="94" t="str">
+      <x:c r="Q15" s="82"/>
+      <x:c r="R15" s="82" t="str">
         <x:v>No immediate gap. Preserve evidence showing both the product list and product-detail information.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="48" customHeight="1">
+    <x:row r="16" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A16" s="108" t="str">
         <x:v>REQ-PRODUCT-002</x:v>
       </x:c>
@@ -3932,48 +3965,48 @@
       <x:c r="D16" s="109" t="str">
         <x:v>Products</x:v>
       </x:c>
-      <x:c r="E16" s="109" t="str">
+      <x:c r="E16" s="143" t="str">
         <x:v>Search Product</x:v>
       </x:c>
-      <x:c r="F16" s="109" t="str">
+      <x:c r="F16" s="143" t="str">
         <x:v>AE-PRODUCT-002</x:v>
       </x:c>
-      <x:c r="G16" s="117" t="str">
+      <x:c r="G16" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H16" s="93" t="str">
+      <x:c r="H16" s="82" t="str">
         <x:v>Product search was executed successfully and the returned products were verified as relevant to the selected search term.</x:v>
       </x:c>
-      <x:c r="I16" s="109" t="str">
+      <x:c r="I16" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J16" s="109" t="str">
+      <x:c r="J16" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K16" s="109" t="str">
+      <x:c r="K16" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L16" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M16" s="109" t="str">
+      <x:c r="L16" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M16" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N16" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O16" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P16" s="93" t="str">
+      <x:c r="N16" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O16" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P16" s="82" t="str">
         <x:v>..\Screenshots\AE-PRODUCT-002.png</x:v>
       </x:c>
-      <x:c r="Q16" s="93"/>
-      <x:c r="R16" s="94" t="str">
+      <x:c r="Q16" s="82"/>
+      <x:c r="R16" s="82" t="str">
         <x:v>No immediate gap. Record the exact search term with each future execution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A17" s="108" t="str">
         <x:v>REQ-SUB-001</x:v>
       </x:c>
@@ -3986,48 +4019,48 @@
       <x:c r="D17" s="109" t="str">
         <x:v>Subscription</x:v>
       </x:c>
-      <x:c r="E17" s="109" t="str">
+      <x:c r="E17" s="143" t="str">
         <x:v>Verify Subscription in home page</x:v>
       </x:c>
-      <x:c r="F17" s="109" t="str">
+      <x:c r="F17" s="143" t="str">
         <x:v>AE-SUB-001</x:v>
       </x:c>
-      <x:c r="G17" s="117" t="str">
+      <x:c r="G17" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H17" s="93" t="str">
+      <x:c r="H17" s="82" t="str">
         <x:v>The home-page footer displayed the subscription heading, accepted the sanitized email, and showed the expected success message.</x:v>
       </x:c>
-      <x:c r="I17" s="109" t="str">
+      <x:c r="I17" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J17" s="109" t="str">
+      <x:c r="J17" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K17" s="109" t="str">
+      <x:c r="K17" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L17" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M17" s="109" t="str">
+      <x:c r="L17" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M17" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N17" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O17" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P17" s="93" t="str">
+      <x:c r="N17" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O17" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P17" s="82" t="str">
         <x:v>..\Screenshots\AE-SUB-001.png</x:v>
       </x:c>
-      <x:c r="Q17" s="93"/>
-      <x:c r="R17" s="94" t="str">
+      <x:c r="Q17" s="82"/>
+      <x:c r="R17" s="82" t="str">
         <x:v>No immediate gap. Retain the sanitized AE-SUB-001 screenshot and reuse a controlled email value during regression testing.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="48" customHeight="1">
+    <x:row r="18" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A18" s="108" t="str">
         <x:v>REQ-SUB-002</x:v>
       </x:c>
@@ -4040,48 +4073,48 @@
       <x:c r="D18" s="109" t="str">
         <x:v>Subscription</x:v>
       </x:c>
-      <x:c r="E18" s="109" t="str">
+      <x:c r="E18" s="143" t="str">
         <x:v>Verify Subscription in Cart page</x:v>
       </x:c>
-      <x:c r="F18" s="109" t="str">
+      <x:c r="F18" s="143" t="str">
         <x:v>AE-SUB-002</x:v>
       </x:c>
-      <x:c r="G18" s="117" t="str">
+      <x:c r="G18" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H18" s="93" t="str">
+      <x:c r="H18" s="82" t="str">
         <x:v>The cart-page footer displayed the subscription heading, accepted the sanitized email, showed the expected success message, and remained on the cart page.</x:v>
       </x:c>
-      <x:c r="I18" s="109" t="str">
+      <x:c r="I18" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J18" s="109" t="str">
+      <x:c r="J18" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K18" s="109" t="str">
+      <x:c r="K18" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L18" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M18" s="109" t="str">
+      <x:c r="L18" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M18" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N18" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O18" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P18" s="93" t="str">
+      <x:c r="N18" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O18" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P18" s="82" t="str">
         <x:v>..\Screenshots\AE-SUB-002.png</x:v>
       </x:c>
-      <x:c r="Q18" s="93"/>
-      <x:c r="R18" s="94" t="str">
+      <x:c r="Q18" s="82"/>
+      <x:c r="R18" s="82" t="str">
         <x:v>No immediate gap. Retain AE-SUB-002 evidence confirming both the success message and continued cart-page context.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="48" customHeight="1">
+    <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A19" s="108" t="str">
         <x:v>REQ-CART-001</x:v>
       </x:c>
@@ -4094,50 +4127,50 @@
       <x:c r="D19" s="109" t="str">
         <x:v>Cart</x:v>
       </x:c>
-      <x:c r="E19" s="109" t="str">
+      <x:c r="E19" s="143" t="str">
         <x:v>Add Products in Cart</x:v>
       </x:c>
-      <x:c r="F19" s="109" t="str">
+      <x:c r="F19" s="143" t="str">
         <x:v>AE-CART-001</x:v>
       </x:c>
-      <x:c r="G19" s="117" t="str">
+      <x:c r="G19" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H19" s="93" t="str">
+      <x:c r="H19" s="82" t="str">
         <x:v>Two products, their unit prices, default quantities, and line totals were verified. The case failed because the overall cart total was not displayed.</x:v>
       </x:c>
-      <x:c r="I19" s="109" t="str">
+      <x:c r="I19" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J19" s="109" t="str">
+      <x:c r="J19" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K19" s="109" t="str">
+      <x:c r="K19" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L19" s="109" t="str">
+      <x:c r="L19" s="143" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="M19" s="109" t="str">
+      <x:c r="M19" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N19" s="109" t="str">
+      <x:c r="N19" s="143" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="O19" s="118" t="str">
+      <x:c r="O19" s="146" t="str">
         <x:v>Fail</x:v>
       </x:c>
-      <x:c r="P19" s="93" t="str">
+      <x:c r="P19" s="82" t="str">
         <x:v>..\Screenshots\AE-CART-001.png</x:v>
       </x:c>
-      <x:c r="Q19" s="93" t="str">
+      <x:c r="Q19" s="82" t="str">
         <x:v>AE-BUG-003</x:v>
       </x:c>
-      <x:c r="R19" s="94" t="str">
+      <x:c r="R19" s="82" t="str">
         <x:v>Retest AE-CART-001 after AE-BUG-003 is corrected and confirm the overall total equals the sum of all line totals.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="48" customHeight="1">
+    <x:row r="20" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A20" s="108" t="str">
         <x:v>REQ-CART-002</x:v>
       </x:c>
@@ -4150,50 +4183,50 @@
       <x:c r="D20" s="109" t="str">
         <x:v>Cart</x:v>
       </x:c>
-      <x:c r="E20" s="109" t="str">
+      <x:c r="E20" s="143" t="str">
         <x:v>Verify Product quantity in Cart</x:v>
       </x:c>
-      <x:c r="F20" s="109" t="str">
+      <x:c r="F20" s="143" t="str">
         <x:v>AE-CART-002</x:v>
       </x:c>
-      <x:c r="G20" s="117" t="str">
+      <x:c r="G20" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H20" s="93" t="str">
+      <x:c r="H20" s="82" t="str">
         <x:v>Manual retest and corrected Playwright automation confirmed that quantity 4 can be selected on the product-detail page and is displayed correctly in the cart with the expected line total.</x:v>
       </x:c>
-      <x:c r="I20" s="109" t="str">
+      <x:c r="I20" s="143" t="str">
         <x:v>Functional | Positive</x:v>
       </x:c>
-      <x:c r="J20" s="109" t="str">
+      <x:c r="J20" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K20" s="109" t="str">
+      <x:c r="K20" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L20" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M20" s="109" t="str">
+      <x:c r="L20" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M20" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N20" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O20" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P20" s="93" t="str">
+      <x:c r="N20" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O20" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P20" s="82" t="str">
         <x:v>..\Screenshots\AE-CART-002.png</x:v>
       </x:c>
-      <x:c r="Q20" s="93" t="str">
+      <x:c r="Q20" s="82" t="str">
         <x:v>AE-BUG-004</x:v>
       </x:c>
-      <x:c r="R20" s="94" t="str">
+      <x:c r="R20" s="82" t="str">
         <x:v>No immediate coverage gap. Retain AE-CART-002 in regression and preserve AE-BUG-004 as a rejected defect record.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="48" customHeight="1">
+    <x:row r="21" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A21" s="108" t="str">
         <x:v>REQ-ORDER-001</x:v>
       </x:c>
@@ -4206,48 +4239,48 @@
       <x:c r="D21" s="109" t="str">
         <x:v>Checkout</x:v>
       </x:c>
-      <x:c r="E21" s="109" t="str">
+      <x:c r="E21" s="143" t="str">
         <x:v>Place Order: Register while Checkout</x:v>
       </x:c>
-      <x:c r="F21" s="109" t="str">
+      <x:c r="F21" s="143" t="str">
         <x:v>AE-ORDER-001</x:v>
       </x:c>
-      <x:c r="G21" s="119" t="str">
+      <x:c r="G21" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H21" s="93" t="str">
+      <x:c r="H21" s="82" t="str">
         <x:v>Executed through Jira Test Case AEQA-107 / AE-ORDER-001. Registration during checkout completed successfully and the expected order confirmation was displayed.</x:v>
       </x:c>
-      <x:c r="I21" s="109" t="str">
+      <x:c r="I21" s="143" t="str">
         <x:v>End-to-End — Positive</x:v>
       </x:c>
-      <x:c r="J21" s="109" t="str">
+      <x:c r="J21" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K21" s="109" t="str">
+      <x:c r="K21" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L21" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M21" s="109" t="str">
+      <x:c r="L21" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M21" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N21" s="109" t="str">
+      <x:c r="N21" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O21" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P21" s="93" t="str">
+      <x:c r="O21" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P21" s="82" t="str">
         <x:v>..\Screenshots\AE-ORDER-001.png</x:v>
       </x:c>
-      <x:c r="Q21" s="93"/>
-      <x:c r="R21" s="94" t="str">
+      <x:c r="Q21" s="82"/>
+      <x:c r="R21" s="82" t="str">
         <x:v>Execution synchronized from Jira AEQA-107 on 2026-08-12. Passed result, actual outcome, and screenshot evidence are retained in Jira and this RTM.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="48" customHeight="1">
+    <x:row r="22" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A22" s="108" t="str">
         <x:v>REQ-ORDER-002</x:v>
       </x:c>
@@ -4260,48 +4293,48 @@
       <x:c r="D22" s="109" t="str">
         <x:v>Checkout</x:v>
       </x:c>
-      <x:c r="E22" s="109" t="str">
+      <x:c r="E22" s="143" t="str">
         <x:v>Place Order: Register before Checkout</x:v>
       </x:c>
-      <x:c r="F22" s="109" t="str">
+      <x:c r="F22" s="143" t="str">
         <x:v>AE-ORDER-002</x:v>
       </x:c>
-      <x:c r="G22" s="119" t="str">
+      <x:c r="G22" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H22" s="93" t="str">
+      <x:c r="H22" s="82" t="str">
         <x:v>Jira Test Case AEQA-108 passed. A user registered before shopping, completed checkout, and received the order confirmation.</x:v>
       </x:c>
-      <x:c r="I22" s="109" t="str">
+      <x:c r="I22" s="143" t="str">
         <x:v>End-to-End — Positive</x:v>
       </x:c>
-      <x:c r="J22" s="109" t="str">
+      <x:c r="J22" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K22" s="109" t="str">
+      <x:c r="K22" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L22" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M22" s="109" t="str">
+      <x:c r="L22" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M22" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N22" s="109" t="str">
+      <x:c r="N22" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O22" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P22" s="93" t="str">
+      <x:c r="O22" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P22" s="82" t="str">
         <x:v>Jira AEQA-108 attachments: image_2026-08-11_232841897.png; image_2026-08-11_233013612.png; image_2026-08-11_233046264.png; invoice (1).txt</x:v>
       </x:c>
-      <x:c r="Q22" s="93"/>
-      <x:c r="R22" s="94" t="str">
+      <x:c r="Q22" s="82"/>
+      <x:c r="R22" s="82" t="str">
         <x:v>Manual execution passed in AEQA-108. Evidence and invoice output remain attached to the Jira Test Case.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="48" customHeight="1">
+    <x:row r="23" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A23" s="108" t="str">
         <x:v>REQ-ORDER-003</x:v>
       </x:c>
@@ -4314,48 +4347,48 @@
       <x:c r="D23" s="109" t="str">
         <x:v>Checkout</x:v>
       </x:c>
-      <x:c r="E23" s="109" t="str">
+      <x:c r="E23" s="143" t="str">
         <x:v>Place Order: Login before Checkout</x:v>
       </x:c>
-      <x:c r="F23" s="109" t="str">
+      <x:c r="F23" s="143" t="str">
         <x:v>AE-ORDER-003</x:v>
       </x:c>
-      <x:c r="G23" s="119" t="str">
+      <x:c r="G23" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H23" s="93" t="str">
+      <x:c r="H23" s="82" t="str">
         <x:v>Jira Test Case AEQA-109 passed. An existing user logged in before checkout, completed the order, and received the success confirmation.</x:v>
       </x:c>
-      <x:c r="I23" s="109" t="str">
+      <x:c r="I23" s="143" t="str">
         <x:v>End-to-End — Positive</x:v>
       </x:c>
-      <x:c r="J23" s="109" t="str">
+      <x:c r="J23" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K23" s="109" t="str">
+      <x:c r="K23" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L23" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M23" s="109" t="str">
+      <x:c r="L23" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M23" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N23" s="109" t="str">
+      <x:c r="N23" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O23" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P23" s="93" t="str">
+      <x:c r="O23" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P23" s="82" t="str">
         <x:v>Jira AEQA-109 attachments: image_2026-08-11_234034965.png; image_2026-08-11_234130953.png; image_2026-08-11_234238291.png; invoice (2).txt</x:v>
       </x:c>
-      <x:c r="Q23" s="93"/>
-      <x:c r="R23" s="94" t="str">
+      <x:c r="Q23" s="82"/>
+      <x:c r="R23" s="82" t="str">
         <x:v>Manual execution passed in AEQA-109. Evidence and invoice output remain attached to the Jira Test Case.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="48" customHeight="1">
+    <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A24" s="108" t="str">
         <x:v>REQ-CART-003</x:v>
       </x:c>
@@ -4368,48 +4401,48 @@
       <x:c r="D24" s="109" t="str">
         <x:v>Cart</x:v>
       </x:c>
-      <x:c r="E24" s="109" t="str">
+      <x:c r="E24" s="143" t="str">
         <x:v>Remove Products From Cart</x:v>
       </x:c>
-      <x:c r="F24" s="109" t="str">
+      <x:c r="F24" s="143" t="str">
         <x:v>AE-CART-003</x:v>
       </x:c>
-      <x:c r="G24" s="117" t="str">
+      <x:c r="G24" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H24" s="93" t="str">
+      <x:c r="H24" s="82" t="str">
         <x:v>A product was added to the cart, removed using the remove control, and verified as no longer displayed or included in cart totals.</x:v>
       </x:c>
-      <x:c r="I24" s="109" t="str">
+      <x:c r="I24" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J24" s="109" t="str">
+      <x:c r="J24" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K24" s="109" t="str">
+      <x:c r="K24" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L24" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M24" s="109" t="str">
+      <x:c r="L24" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M24" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N24" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O24" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P24" s="93" t="str">
+      <x:c r="N24" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O24" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P24" s="82" t="str">
         <x:v>..\Screenshots\AE-CART-003.png</x:v>
       </x:c>
-      <x:c r="Q24" s="93"/>
-      <x:c r="R24" s="94" t="str">
+      <x:c r="Q24" s="82"/>
+      <x:c r="R24" s="82" t="str">
         <x:v>No immediate gap. Retain before-and-after cart evidence for future executions.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="48" customHeight="1">
+    <x:row r="25" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A25" s="108" t="str">
         <x:v>REQ-CATALOG-001</x:v>
       </x:c>
@@ -4422,48 +4455,48 @@
       <x:c r="D25" s="109" t="str">
         <x:v>Catalog</x:v>
       </x:c>
-      <x:c r="E25" s="109" t="str">
+      <x:c r="E25" s="143" t="str">
         <x:v>View Category Products</x:v>
       </x:c>
-      <x:c r="F25" s="109" t="str">
+      <x:c r="F25" s="143" t="str">
         <x:v>AE-CATALOG-001</x:v>
       </x:c>
-      <x:c r="G25" s="119" t="str">
+      <x:c r="G25" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H25" s="93" t="str">
+      <x:c r="H25" s="82" t="str">
         <x:v>Executed through Jira Test Case AEQA-110 / AE-CATALOG-001. Women &gt; Dress and Men &gt; Tshirts navigation displayed the expected category headings and matching product lists.</x:v>
       </x:c>
-      <x:c r="I25" s="109" t="str">
+      <x:c r="I25" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J25" s="109" t="str">
+      <x:c r="J25" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K25" s="109" t="str">
+      <x:c r="K25" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L25" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M25" s="109" t="str">
+      <x:c r="L25" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M25" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N25" s="109" t="str">
+      <x:c r="N25" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O25" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P25" s="93" t="str">
+      <x:c r="O25" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P25" s="82" t="str">
         <x:v>Jira native attachment (AEQA-110)</x:v>
       </x:c>
-      <x:c r="Q25" s="93"/>
-      <x:c r="R25" s="94" t="str">
+      <x:c r="Q25" s="82"/>
+      <x:c r="R25" s="82" t="str">
         <x:v>Execution synchronized from Jira on 2026-08-16. Passed result and screenshot evidence are retained on AEQA-110.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="48" customHeight="1">
+    <x:row r="26" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A26" s="108" t="str">
         <x:v>REQ-CATALOG-002</x:v>
       </x:c>
@@ -4476,46 +4509,46 @@
       <x:c r="D26" s="109" t="str">
         <x:v>Catalog</x:v>
       </x:c>
-      <x:c r="E26" s="109" t="str">
+      <x:c r="E26" s="143" t="str">
         <x:v>View &amp; Cart Brand Products</x:v>
       </x:c>
-      <x:c r="F26" s="109" t="str">
+      <x:c r="F26" s="143" t="str">
         <x:v>AE-CATALOG-002</x:v>
       </x:c>
-      <x:c r="G26" s="119" t="str">
+      <x:c r="G26" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H26" s="93" t="str">
+      <x:c r="H26" s="82" t="str">
         <x:v>Manual design is complete in AEQA-111 / AE-CATALOG-002. AEQA-123 is the linked Playwright implementation sub-task and remains Backlog.</x:v>
       </x:c>
-      <x:c r="I26" s="109" t="str">
+      <x:c r="I26" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J26" s="109" t="str">
+      <x:c r="J26" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K26" s="109" t="str">
+      <x:c r="K26" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L26" s="109" t="str">
+      <x:c r="L26" s="143" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="M26" s="109" t="str">
+      <x:c r="M26" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N26" s="109" t="str">
+      <x:c r="N26" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O26" s="120" t="str">
+      <x:c r="O26" s="148" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="P26" s="93"/>
-      <x:c r="Q26" s="93"/>
-      <x:c r="R26" s="94" t="str">
+      <x:c r="P26" s="82"/>
+      <x:c r="Q26" s="82"/>
+      <x:c r="R26" s="82" t="str">
         <x:v>Execute AE-CATALOG-002 manually and complete AEQA-123 automation; reconcile each result and its evidence independently.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="48" customHeight="1">
+    <x:row r="27" ht="54" hidden="0" customHeight="1">
       <x:c r="A27" s="108" t="str">
         <x:v>REQ-CART-004</x:v>
       </x:c>
@@ -4528,49 +4561,49 @@
       <x:c r="D27" s="109" t="str">
         <x:v>Search / Cart</x:v>
       </x:c>
-      <x:c r="E27" s="109" t="str">
+      <x:c r="E27" s="143" t="str">
         <x:v>Search Products and Verify Cart After Login</x:v>
       </x:c>
-      <x:c r="F27" s="109" t="str">
+      <x:c r="F27" s="143" t="str">
         <x:v>AE-CART-004</x:v>
       </x:c>
-      <x:c r="G27" s="119" t="str">
+      <x:c r="G27" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H27" s="93" t="str">
+      <x:c r="H27" s="82" t="str">
         <x:v>Manual case AEQA-112 and Playwright task AEQA-122 are linked to AEQA-20. Both passed, and their before-login and after-login cart evidence is attached to the correct Jira work items.</x:v>
       </x:c>
-      <x:c r="I27" s="109" t="str">
+      <x:c r="I27" s="143" t="str">
         <x:v>End-to-End — Positive</x:v>
       </x:c>
-      <x:c r="J27" s="109" t="str">
+      <x:c r="J27" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K27" s="109" t="str">
+      <x:c r="K27" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L27" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M27" s="109" t="str">
+      <x:c r="L27" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M27" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N27" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O27" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P27" s="93" t="str">
+      <x:c r="N27" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O27" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P27" s="82" t="str">
         <x:v>Manual evidence: Jira AEQA-112 attachments AE-CART-004(1).png and AE-CART-004(2).png
 Automation evidence: ..\Automation\Execution Evidence\AE-CART-004(1).png; ..\Automation\Execution Evidence\AE-CART-004(2).png</x:v>
       </x:c>
-      <x:c r="Q27" s="93"/>
-      <x:c r="R27" s="94" t="str">
+      <x:c r="Q27" s="82"/>
+      <x:c r="R27" s="82" t="str">
         <x:v>Manual testing and Playwright automation passed on 2026-08-17. Keep the manual and automation evidence attached to their separate Jira work items.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="48" customHeight="1">
+    <x:row r="28" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A28" s="108" t="str">
         <x:v>REQ-REVIEW-001</x:v>
       </x:c>
@@ -4583,50 +4616,50 @@
       <x:c r="D28" s="109" t="str">
         <x:v>Product Review</x:v>
       </x:c>
-      <x:c r="E28" s="109" t="str">
+      <x:c r="E28" s="143" t="str">
         <x:v>Add review on product</x:v>
       </x:c>
-      <x:c r="F28" s="109" t="str">
+      <x:c r="F28" s="143" t="str">
         <x:v>AE-REVIEW-001
 AE-AUTO-REVIEW-001</x:v>
       </x:c>
-      <x:c r="G28" s="119" t="str">
+      <x:c r="G28" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H28" s="93" t="str">
+      <x:c r="H28" s="82" t="str">
         <x:v>Manual case AEQA-113 and automation case AEQA-124 are linked to AEQA-21. Both passed, and their result-specific evidence is attached to the correct Jira Test Cases.</x:v>
       </x:c>
-      <x:c r="I28" s="109" t="str">
+      <x:c r="I28" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J28" s="109" t="str">
+      <x:c r="J28" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K28" s="109" t="str">
+      <x:c r="K28" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L28" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M28" s="109" t="str">
+      <x:c r="L28" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M28" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N28" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O28" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P28" s="93" t="str">
+      <x:c r="N28" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O28" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P28" s="82" t="str">
         <x:v>Manual evidence: Jira AEQA-113 attachments (2 screenshots)
 Automation evidence: ..\Automation\Execution Evidence\AE-REVIEW-001(1).png; ..\Automation\Execution Evidence\AE-REVIEW-001(2).png</x:v>
       </x:c>
-      <x:c r="Q28" s="93"/>
-      <x:c r="R28" s="94" t="str">
+      <x:c r="Q28" s="82"/>
+      <x:c r="R28" s="82" t="str">
         <x:v>Manual testing and Playwright automation passed on 2026-08-17. Keep the manual and automation evidence attached to their separate Jira Test Cases.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="48" customHeight="1">
+    <x:row r="29" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A29" s="108" t="str">
         <x:v>REQ-CART-005</x:v>
       </x:c>
@@ -4639,47 +4672,50 @@
       <x:c r="D29" s="109" t="str">
         <x:v>Recommended Items</x:v>
       </x:c>
-      <x:c r="E29" s="109" t="str">
+      <x:c r="E29" s="143" t="str">
         <x:v>Add to cart from Recommended items</x:v>
       </x:c>
-      <x:c r="F29" s="109" t="str">
+      <x:c r="F29" s="143" t="str">
         <x:v>AE-CART-005
 AE-AUTO-CART-005</x:v>
       </x:c>
-      <x:c r="G29" s="119" t="str">
+      <x:c r="G29" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H29" s="93" t="str">
-        <x:v>Manual case AEQA-114 and automation case AEQA-125 are linked to AEQA-22. Both remain Not Run; Playwright implementation is planned.</x:v>
-      </x:c>
-      <x:c r="I29" s="109" t="str">
+      <x:c r="H29" s="82" t="str">
+        <x:v>Manual case AEQA-114 and automation case AEQA-125 both passed. Recommended Items add-to-cart behavior is covered by manual and Playwright evidence.</x:v>
+      </x:c>
+      <x:c r="I29" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J29" s="109" t="str">
+      <x:c r="J29" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K29" s="109" t="str">
+      <x:c r="K29" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L29" s="109" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="M29" s="109" t="str">
+      <x:c r="L29" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M29" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N29" s="109" t="str">
-        <x:v>Not Automated</x:v>
-      </x:c>
-      <x:c r="O29" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P29" s="93"/>
-      <x:c r="Q29" s="93"/>
-      <x:c r="R29" s="94" t="str">
-        <x:v>Execute AE-CART-005 and implement AE-AUTO-CART-005 independently; attach matching Recommended Items and cart evidence.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="48" customHeight="1">
+      <x:c r="N29" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O29" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P29" s="82" t="str">
+        <x:v>Jira AEQA-114: image_2026-08-17_205040181.png
+..\Automation\Execution Evidence\AE-AUTO-CART-005.png</x:v>
+      </x:c>
+      <x:c r="Q29" s="82"/>
+      <x:c r="R29" s="82" t="str">
+        <x:v>Coverage complete. Manual and Playwright results are independently recorded as Pass.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A30" s="108" t="str">
         <x:v>REQ-ORDER-004</x:v>
       </x:c>
@@ -4692,50 +4728,50 @@
       <x:c r="D30" s="109" t="str">
         <x:v>Checkout</x:v>
       </x:c>
-      <x:c r="E30" s="109" t="str">
+      <x:c r="E30" s="143" t="str">
         <x:v>Verify address details in checkout page</x:v>
       </x:c>
-      <x:c r="F30" s="109" t="str">
+      <x:c r="F30" s="143" t="str">
         <x:v>AE-ORDER-004</x:v>
       </x:c>
-      <x:c r="G30" s="119" t="str">
+      <x:c r="G30" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H30" s="93" t="str">
+      <x:c r="H30" s="82" t="str">
         <x:v>Executed through Jira Test Case AEQA-115 / AE-ORDER-004 and automated under AEQA-102 / AEQA-105. Delivery and billing address details matched the registered QA account.</x:v>
       </x:c>
-      <x:c r="I30" s="109" t="str">
+      <x:c r="I30" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J30" s="109" t="str">
+      <x:c r="J30" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K30" s="109" t="str">
+      <x:c r="K30" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L30" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M30" s="109" t="str">
+      <x:c r="L30" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M30" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N30" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O30" s="120" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P30" s="93" t="str">
+      <x:c r="N30" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O30" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P30" s="82" t="str">
         <x:v>..\Automation\Execution Evidence\AE-ORDER-004.png
 ..\Automation\Execution Evidence\AE-ORDER-004-evidence.html
 ..\Automation\Execution Evidence\AE-ORDER-004-evidence.pdf</x:v>
       </x:c>
-      <x:c r="Q30" s="93"/>
-      <x:c r="R30" s="94" t="str">
+      <x:c r="Q30" s="82"/>
+      <x:c r="R30" s="82" t="str">
         <x:v>Manual and Playwright results synchronized from Jira and local evidence on 2026-08-16.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="48" customHeight="1">
+    <x:row r="31" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A31" s="108" t="str">
         <x:v>REQ-ORDER-005</x:v>
       </x:c>
@@ -4748,47 +4784,51 @@
       <x:c r="D31" s="109" t="str">
         <x:v>Checkout / Invoice</x:v>
       </x:c>
-      <x:c r="E31" s="109" t="str">
+      <x:c r="E31" s="143" t="str">
         <x:v>Download Invoice after purchase order</x:v>
       </x:c>
-      <x:c r="F31" s="109" t="str">
+      <x:c r="F31" s="143" t="str">
         <x:v>AE-ORDER-005
 AE-AUTO-ORDER-005</x:v>
       </x:c>
-      <x:c r="G31" s="119" t="str">
+      <x:c r="G31" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H31" s="93" t="str">
-        <x:v>Manual case AEQA-116 and automation case AEQA-126 are linked to AEQA-24. Both remain Not Run; end-to-end invoice automation is planned.</x:v>
-      </x:c>
-      <x:c r="I31" s="109" t="str">
+      <x:c r="H31" s="82" t="str">
+        <x:v>Manual case AEQA-116 and automation case AEQA-126 both passed. The completed order and invoice download were verified with screenshot and invoice evidence.</x:v>
+      </x:c>
+      <x:c r="I31" s="143" t="str">
         <x:v>End-to-End — Positive</x:v>
       </x:c>
-      <x:c r="J31" s="109" t="str">
+      <x:c r="J31" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K31" s="109" t="str">
+      <x:c r="K31" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L31" s="109" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="M31" s="109" t="str">
+      <x:c r="L31" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M31" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N31" s="109" t="str">
-        <x:v>Not Automated</x:v>
-      </x:c>
-      <x:c r="O31" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P31" s="93"/>
-      <x:c r="Q31" s="93"/>
-      <x:c r="R31" s="94" t="str">
-        <x:v>Execute AE-ORDER-005 and implement AE-AUTO-ORDER-005 independently; retain sanitized order and invoice evidence.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="N31" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O31" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P31" s="82" t="str">
+        <x:v>Jira AEQA-116: image_2026-08-17_211426159.png; invoice (3).txt
+..\Automation\Execution Evidence\AE-AUTO-ORDER-005.png
+..\Automation\Execution Evidence\AE-AUTO-ORDER-005-invoice.txt</x:v>
+      </x:c>
+      <x:c r="Q31" s="82"/>
+      <x:c r="R31" s="82" t="str">
+        <x:v>Coverage complete. Manual and Playwright invoice evidence are retained separately.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A32" s="108" t="str">
         <x:v>REQ-NAV-002</x:v>
       </x:c>
@@ -4801,47 +4841,51 @@
       <x:c r="D32" s="109" t="str">
         <x:v>Navigation</x:v>
       </x:c>
-      <x:c r="E32" s="109" t="str">
+      <x:c r="E32" s="143" t="str">
         <x:v>Verify Scroll Up using 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
-      <x:c r="F32" s="109" t="str">
+      <x:c r="F32" s="143" t="str">
         <x:v>AE-NAV-002
 AE-AUTO-NAV-002</x:v>
       </x:c>
-      <x:c r="G32" s="119" t="str">
+      <x:c r="G32" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H32" s="93" t="str">
-        <x:v>Manual case AEQA-117 and automation case AEQA-127 are linked to AEQA-25. Both remain Not Run; arrow return-to-top automation is planned.</x:v>
-      </x:c>
-      <x:c r="I32" s="109" t="str">
+      <x:c r="H32" s="82" t="str">
+        <x:v>Manual case AEQA-117 and automation case AEQA-127 both passed. Footer visibility, arrow appearance, and return-to-top behavior were verified.</x:v>
+      </x:c>
+      <x:c r="I32" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J32" s="109" t="str">
+      <x:c r="J32" s="143" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="K32" s="109" t="str">
+      <x:c r="K32" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L32" s="109" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="M32" s="109" t="str">
+      <x:c r="L32" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M32" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N32" s="109" t="str">
-        <x:v>Not Automated</x:v>
-      </x:c>
-      <x:c r="O32" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P32" s="93"/>
-      <x:c r="Q32" s="93"/>
-      <x:c r="R32" s="94" t="str">
-        <x:v>Execute AE-NAV-002 and implement AE-AUTO-NAV-002 independently; capture footer and returned-to-top evidence.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="N32" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O32" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P32" s="82" t="str">
+        <x:v>Jira AEQA-117: image_2026-08-17_213605047.png; image_2026-08-17_213623066.png
+..\Automation\Execution Evidence\AE-AUTO-NAV-002.png
+..\Automation\Execution Evidence\AE-AUTO-NAV-002.webm</x:v>
+      </x:c>
+      <x:c r="Q32" s="82"/>
+      <x:c r="R32" s="82" t="str">
+        <x:v>Coverage complete. Manual screenshots and Playwright screenshot/video evidence are retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A33" s="108" t="str">
         <x:v>REQ-NAV-003</x:v>
       </x:c>
@@ -4854,47 +4898,49 @@
       <x:c r="D33" s="109" t="str">
         <x:v>Navigation</x:v>
       </x:c>
-      <x:c r="E33" s="109" t="str">
+      <x:c r="E33" s="143" t="str">
         <x:v>Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
-      <x:c r="F33" s="109" t="str">
+      <x:c r="F33" s="143" t="str">
         <x:v>AE-NAV-003
 AE-AUTO-NAV-003</x:v>
       </x:c>
-      <x:c r="G33" s="119" t="str">
+      <x:c r="G33" s="147" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H33" s="93" t="str">
-        <x:v>Manual case AEQA-118 and automation case AEQA-128 are linked to AEQA-26. Both remain Not Run; browser-scroll automation is planned.</x:v>
-      </x:c>
-      <x:c r="I33" s="109" t="str">
+      <x:c r="H33" s="82" t="str">
+        <x:v>Manual case AEQA-118 passed and automation case AEQA-128 remains Not Run. Manual scrolling down and back to the top without the arrow is verified.</x:v>
+      </x:c>
+      <x:c r="I33" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J33" s="109" t="str">
+      <x:c r="J33" s="143" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="K33" s="109" t="str">
+      <x:c r="K33" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L33" s="109" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="M33" s="109" t="str">
+      <x:c r="L33" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M33" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N33" s="109" t="str">
+      <x:c r="N33" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O33" s="120" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P33" s="93"/>
-      <x:c r="Q33" s="93"/>
-      <x:c r="R33" s="94" t="str">
-        <x:v>Execute AE-NAV-003 and implement AE-AUTO-NAV-003 independently; confirm the site arrow is not used.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="O33" s="148" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P33" s="82" t="str">
+        <x:v>Jira AEQA-118: image_2026-08-17_215326128.png; image_2026-08-17_215755766.png</x:v>
+      </x:c>
+      <x:c r="Q33" s="82"/>
+      <x:c r="R33" s="82" t="str">
+        <x:v>Manual coverage passed. AE-AUTO-NAV-003 / AEQA-128 remains In Progress and Not Run until executed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A34" s="108" t="str">
         <x:v>REQ-EXT-001</x:v>
       </x:c>
@@ -4907,48 +4953,48 @@
       <x:c r="D34" s="109" t="str">
         <x:v>Registration</x:v>
       </x:c>
-      <x:c r="E34" s="109" t="str">
+      <x:c r="E34" s="143" t="str">
         <x:v>Reject invalid email format during registration</x:v>
       </x:c>
-      <x:c r="F34" s="109" t="str">
+      <x:c r="F34" s="143" t="str">
         <x:v>AE-SIGNUP-003</x:v>
       </x:c>
-      <x:c r="G34" s="117" t="str">
+      <x:c r="G34" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H34" s="93" t="str">
+      <x:c r="H34" s="82" t="str">
         <x:v>Tester-derived negative validation coverage was executed successfully.</x:v>
       </x:c>
-      <x:c r="I34" s="109" t="str">
+      <x:c r="I34" s="143" t="str">
         <x:v>Functional — Negative</x:v>
       </x:c>
-      <x:c r="J34" s="109" t="str">
+      <x:c r="J34" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K34" s="109" t="str">
+      <x:c r="K34" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L34" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M34" s="109" t="str">
+      <x:c r="L34" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M34" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N34" s="109" t="str">
+      <x:c r="N34" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O34" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P34" s="93" t="str">
+      <x:c r="O34" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P34" s="82" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-003.png</x:v>
       </x:c>
-      <x:c r="Q34" s="93"/>
-      <x:c r="R34" s="94" t="str">
+      <x:c r="Q34" s="82"/>
+      <x:c r="R34" s="82" t="str">
         <x:v>Retain as enhanced coverage beyond the published scenarios.</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="48" customHeight="1">
+    <x:row r="35" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A35" s="108" t="str">
         <x:v>REQ-EXT-002</x:v>
       </x:c>
@@ -4961,48 +5007,48 @@
       <x:c r="D35" s="109" t="str">
         <x:v>Registration</x:v>
       </x:c>
-      <x:c r="E35" s="109" t="str">
+      <x:c r="E35" s="143" t="str">
         <x:v>Prevent account creation when required fields are blank</x:v>
       </x:c>
-      <x:c r="F35" s="109" t="str">
+      <x:c r="F35" s="143" t="str">
         <x:v>AE-SIGNUP-004</x:v>
       </x:c>
-      <x:c r="G35" s="117" t="str">
+      <x:c r="G35" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H35" s="93" t="str">
+      <x:c r="H35" s="82" t="str">
         <x:v>Tester-derived required-field validation was executed successfully.</x:v>
       </x:c>
-      <x:c r="I35" s="109" t="str">
+      <x:c r="I35" s="143" t="str">
         <x:v>Functional — Negative</x:v>
       </x:c>
-      <x:c r="J35" s="109" t="str">
+      <x:c r="J35" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K35" s="109" t="str">
+      <x:c r="K35" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L35" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M35" s="109" t="str">
+      <x:c r="L35" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M35" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N35" s="109" t="str">
+      <x:c r="N35" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O35" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P35" s="93" t="str">
+      <x:c r="O35" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P35" s="82" t="str">
         <x:v>..\Screenshots\AE-SIGNUP-004.png</x:v>
       </x:c>
-      <x:c r="Q35" s="93"/>
-      <x:c r="R35" s="94" t="str">
+      <x:c r="Q35" s="82"/>
+      <x:c r="R35" s="82" t="str">
         <x:v>Consider splitting each required field into an independently traceable case.</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="48" customHeight="1">
+    <x:row r="36" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A36" s="108" t="str">
         <x:v>REQ-EXT-003</x:v>
       </x:c>
@@ -5015,48 +5061,48 @@
       <x:c r="D36" s="109" t="str">
         <x:v>Login Security</x:v>
       </x:c>
-      <x:c r="E36" s="109" t="str">
+      <x:c r="E36" s="143" t="str">
         <x:v>Reject SQL injection input without authenticating the user</x:v>
       </x:c>
-      <x:c r="F36" s="109" t="str">
+      <x:c r="F36" s="143" t="str">
         <x:v>AE-LOGIN-002</x:v>
       </x:c>
-      <x:c r="G36" s="117" t="str">
+      <x:c r="G36" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H36" s="93" t="str">
+      <x:c r="H36" s="82" t="str">
         <x:v>Tester-derived security-focused input validation was executed successfully.</x:v>
       </x:c>
-      <x:c r="I36" s="109" t="str">
+      <x:c r="I36" s="143" t="str">
         <x:v>Security — Negative</x:v>
       </x:c>
-      <x:c r="J36" s="109" t="str">
+      <x:c r="J36" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K36" s="109" t="str">
+      <x:c r="K36" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L36" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M36" s="109" t="str">
+      <x:c r="L36" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M36" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N36" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O36" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P36" s="93" t="str">
+      <x:c r="N36" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O36" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P36" s="82" t="str">
         <x:v>..\Screenshots\AE-LOGIN-002.png</x:v>
       </x:c>
-      <x:c r="Q36" s="93"/>
-      <x:c r="R36" s="94" t="str">
+      <x:c r="Q36" s="82"/>
+      <x:c r="R36" s="82" t="str">
         <x:v>Retain as authorized security coverage; do not use destructive payloads.</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="48" customHeight="1">
+    <x:row r="37" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A37" s="108" t="str">
         <x:v>REQ-EXT-004</x:v>
       </x:c>
@@ -5069,48 +5115,48 @@
       <x:c r="D37" s="109" t="str">
         <x:v>Account Management</x:v>
       </x:c>
-      <x:c r="E37" s="109" t="str">
+      <x:c r="E37" s="143" t="str">
         <x:v>Preserve an active account across logout and a new browser tab</x:v>
       </x:c>
-      <x:c r="F37" s="109" t="str">
+      <x:c r="F37" s="143" t="str">
         <x:v>AE-ACCOUNT-002</x:v>
       </x:c>
-      <x:c r="G37" s="117" t="str">
+      <x:c r="G37" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H37" s="93" t="str">
+      <x:c r="H37" s="82" t="str">
         <x:v>Tester-derived account-persistence coverage was executed successfully.</x:v>
       </x:c>
-      <x:c r="I37" s="109" t="str">
+      <x:c r="I37" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
-      <x:c r="J37" s="109" t="str">
+      <x:c r="J37" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K37" s="109" t="str">
+      <x:c r="K37" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L37" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="M37" s="109" t="str">
+      <x:c r="L37" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="M37" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="N37" s="109" t="str">
+      <x:c r="N37" s="143" t="str">
         <x:v>Not Automated</x:v>
       </x:c>
-      <x:c r="O37" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P37" s="93" t="str">
+      <x:c r="O37" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P37" s="82" t="str">
         <x:v>..\Screenshots\AE-ACCOUNT-002.png</x:v>
       </x:c>
-      <x:c r="Q37" s="93"/>
-      <x:c r="R37" s="94" t="str">
+      <x:c r="Q37" s="82"/>
+      <x:c r="R37" s="82" t="str">
         <x:v>Retain as enhanced account-lifecycle coverage.</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="96" customHeight="1">
+    <x:row r="38" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A38" s="108" t="str">
         <x:v>REQ-API-001</x:v>
       </x:c>
@@ -5123,52 +5169,52 @@
       <x:c r="D38" s="109" t="str">
         <x:v>Product API</x:v>
       </x:c>
-      <x:c r="E38" s="109" t="str">
+      <x:c r="E38" s="143" t="str">
         <x:v>Get All Products List</x:v>
       </x:c>
-      <x:c r="F38" s="109" t="str">
+      <x:c r="F38" s="143" t="str">
         <x:v>API-PRODUCT-001</x:v>
       </x:c>
-      <x:c r="G38" s="117" t="str">
+      <x:c r="G38" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H38" s="93" t="str">
+      <x:c r="H38" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I38" s="109" t="str">
+      <x:c r="I38" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J38" s="109" t="str">
+      <x:c r="J38" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K38" s="109" t="str">
+      <x:c r="K38" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L38" s="109" t="str">
+      <x:c r="L38" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M38" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N38" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O38" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P38" s="93" t="str">
+      <x:c r="M38" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N38" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O38" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P38" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-PRODUCT-001.png
 ..\Automation\Execution Evidence\API-PRODUCT-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q38" s="93"/>
-      <x:c r="R38" s="94" t="str">
+      <x:c r="Q38" s="82"/>
+      <x:c r="R38" s="82" t="str">
         <x:v>200 | products list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="96" customHeight="1">
+    <x:row r="39" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A39" s="108" t="str">
         <x:v>REQ-API-002</x:v>
       </x:c>
@@ -5181,52 +5227,52 @@
       <x:c r="D39" s="109" t="str">
         <x:v>Product API</x:v>
       </x:c>
-      <x:c r="E39" s="109" t="str">
+      <x:c r="E39" s="143" t="str">
         <x:v>POST To All Products List</x:v>
       </x:c>
-      <x:c r="F39" s="109" t="str">
+      <x:c r="F39" s="143" t="str">
         <x:v>API-PRODUCT-002</x:v>
       </x:c>
-      <x:c r="G39" s="117" t="str">
+      <x:c r="G39" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H39" s="93" t="str">
+      <x:c r="H39" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I39" s="109" t="str">
+      <x:c r="I39" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J39" s="109" t="str">
+      <x:c r="J39" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K39" s="109" t="str">
+      <x:c r="K39" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L39" s="109" t="str">
+      <x:c r="L39" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M39" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N39" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O39" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P39" s="93" t="str">
+      <x:c r="M39" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N39" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O39" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P39" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-PRODUCT-002.png
 ..\Automation\Execution Evidence\API-PRODUCT-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q39" s="93"/>
-      <x:c r="R39" s="94" t="str">
+      <x:c r="Q39" s="82"/>
+      <x:c r="R39" s="82" t="str">
         <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="96" customHeight="1">
+    <x:row r="40" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A40" s="108" t="str">
         <x:v>REQ-API-003</x:v>
       </x:c>
@@ -5239,52 +5285,52 @@
       <x:c r="D40" s="109" t="str">
         <x:v>Brand API</x:v>
       </x:c>
-      <x:c r="E40" s="109" t="str">
+      <x:c r="E40" s="143" t="str">
         <x:v>Get All Brands List</x:v>
       </x:c>
-      <x:c r="F40" s="109" t="str">
+      <x:c r="F40" s="143" t="str">
         <x:v>API-BRAND-001</x:v>
       </x:c>
-      <x:c r="G40" s="117" t="str">
+      <x:c r="G40" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H40" s="93" t="str">
+      <x:c r="H40" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I40" s="109" t="str">
+      <x:c r="I40" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J40" s="109" t="str">
+      <x:c r="J40" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K40" s="109" t="str">
+      <x:c r="K40" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L40" s="109" t="str">
+      <x:c r="L40" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M40" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N40" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O40" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P40" s="93" t="str">
+      <x:c r="M40" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N40" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O40" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P40" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-BRAND-001.png
 ..\Automation\Execution Evidence\API-BRAND-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q40" s="93"/>
-      <x:c r="R40" s="94" t="str">
+      <x:c r="Q40" s="82"/>
+      <x:c r="R40" s="82" t="str">
         <x:v>200 | brands list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="96" customHeight="1">
+    <x:row r="41" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A41" s="108" t="str">
         <x:v>REQ-API-004</x:v>
       </x:c>
@@ -5297,52 +5343,52 @@
       <x:c r="D41" s="109" t="str">
         <x:v>Brand API</x:v>
       </x:c>
-      <x:c r="E41" s="109" t="str">
+      <x:c r="E41" s="143" t="str">
         <x:v>PUT To All Brands List</x:v>
       </x:c>
-      <x:c r="F41" s="109" t="str">
+      <x:c r="F41" s="143" t="str">
         <x:v>API-BRAND-002</x:v>
       </x:c>
-      <x:c r="G41" s="117" t="str">
+      <x:c r="G41" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H41" s="93" t="str">
+      <x:c r="H41" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I41" s="109" t="str">
+      <x:c r="I41" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J41" s="109" t="str">
+      <x:c r="J41" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K41" s="109" t="str">
+      <x:c r="K41" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L41" s="109" t="str">
+      <x:c r="L41" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M41" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N41" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O41" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P41" s="93" t="str">
+      <x:c r="M41" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N41" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O41" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P41" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-BRAND-002.png
 ..\Automation\Execution Evidence\API-BRAND-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q41" s="93"/>
-      <x:c r="R41" s="94" t="str">
+      <x:c r="Q41" s="82"/>
+      <x:c r="R41" s="82" t="str">
         <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="96" customHeight="1">
+    <x:row r="42" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A42" s="108" t="str">
         <x:v>REQ-API-005</x:v>
       </x:c>
@@ -5355,52 +5401,52 @@
       <x:c r="D42" s="109" t="str">
         <x:v>Search API</x:v>
       </x:c>
-      <x:c r="E42" s="109" t="str">
+      <x:c r="E42" s="143" t="str">
         <x:v>POST To Search Product</x:v>
       </x:c>
-      <x:c r="F42" s="109" t="str">
+      <x:c r="F42" s="143" t="str">
         <x:v>API-SEARCH-001</x:v>
       </x:c>
-      <x:c r="G42" s="117" t="str">
+      <x:c r="G42" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H42" s="93" t="str">
+      <x:c r="H42" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I42" s="109" t="str">
+      <x:c r="I42" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J42" s="109" t="str">
+      <x:c r="J42" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K42" s="109" t="str">
+      <x:c r="K42" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L42" s="109" t="str">
+      <x:c r="L42" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M42" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N42" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O42" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P42" s="93" t="str">
+      <x:c r="M42" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N42" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O42" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P42" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-SEARCH-001.png
 ..\Automation\Execution Evidence\API-SEARCH-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q42" s="93"/>
-      <x:c r="R42" s="94" t="str">
+      <x:c r="Q42" s="82"/>
+      <x:c r="R42" s="82" t="str">
         <x:v>200 | searched products list returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="96" customHeight="1">
+    <x:row r="43" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A43" s="108" t="str">
         <x:v>REQ-API-006</x:v>
       </x:c>
@@ -5413,53 +5459,53 @@
       <x:c r="D43" s="109" t="str">
         <x:v>Search API</x:v>
       </x:c>
-      <x:c r="E43" s="109" t="str">
+      <x:c r="E43" s="143" t="str">
         <x:v>POST To Search Product without search_product 
 parameter</x:v>
       </x:c>
-      <x:c r="F43" s="109" t="str">
+      <x:c r="F43" s="143" t="str">
         <x:v>API-SEARCH-002</x:v>
       </x:c>
-      <x:c r="G43" s="117" t="str">
+      <x:c r="G43" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H43" s="93" t="str">
+      <x:c r="H43" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I43" s="109" t="str">
+      <x:c r="I43" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J43" s="109" t="str">
+      <x:c r="J43" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K43" s="109" t="str">
+      <x:c r="K43" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L43" s="109" t="str">
+      <x:c r="L43" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M43" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N43" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O43" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P43" s="93" t="str">
+      <x:c r="M43" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N43" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O43" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P43" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-SEARCH-002.png
 ..\Automation\Execution Evidence\API-SEARCH-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q43" s="93"/>
-      <x:c r="R43" s="94" t="str">
+      <x:c r="Q43" s="82"/>
+      <x:c r="R43" s="82" t="str">
         <x:v>200 transport | responseCode 400 | missing search_product message returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="96" customHeight="1">
+    <x:row r="44" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A44" s="108" t="str">
         <x:v>REQ-API-007</x:v>
       </x:c>
@@ -5472,52 +5518,52 @@
       <x:c r="D44" s="109" t="str">
         <x:v>Authentication API</x:v>
       </x:c>
-      <x:c r="E44" s="109" t="str">
+      <x:c r="E44" s="143" t="str">
         <x:v>POST To Verify Login with valid details</x:v>
       </x:c>
-      <x:c r="F44" s="109" t="str">
+      <x:c r="F44" s="143" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
-      <x:c r="G44" s="117" t="str">
+      <x:c r="G44" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H44" s="93" t="str">
+      <x:c r="H44" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I44" s="109" t="str">
+      <x:c r="I44" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J44" s="109" t="str">
+      <x:c r="J44" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K44" s="109" t="str">
+      <x:c r="K44" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L44" s="109" t="str">
+      <x:c r="L44" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M44" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N44" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O44" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P44" s="93" t="str">
+      <x:c r="M44" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N44" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O44" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P44" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-AUTH-001.png
 ..\Automation\Execution Evidence\API-AUTH-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q44" s="93"/>
-      <x:c r="R44" s="94" t="str">
+      <x:c r="Q44" s="82"/>
+      <x:c r="R44" s="82" t="str">
         <x:v>200 transport | responseCode 200 | User exists!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="96" customHeight="1">
+    <x:row r="45" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A45" s="108" t="str">
         <x:v>REQ-API-008</x:v>
       </x:c>
@@ -5530,52 +5576,52 @@
       <x:c r="D45" s="109" t="str">
         <x:v>Authentication API</x:v>
       </x:c>
-      <x:c r="E45" s="109" t="str">
+      <x:c r="E45" s="143" t="str">
         <x:v>POST To Verify Login without email parameter</x:v>
       </x:c>
-      <x:c r="F45" s="109" t="str">
+      <x:c r="F45" s="143" t="str">
         <x:v>API-AUTH-002</x:v>
       </x:c>
-      <x:c r="G45" s="117" t="str">
+      <x:c r="G45" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H45" s="93" t="str">
+      <x:c r="H45" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I45" s="109" t="str">
+      <x:c r="I45" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J45" s="109" t="str">
+      <x:c r="J45" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K45" s="109" t="str">
+      <x:c r="K45" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L45" s="109" t="str">
+      <x:c r="L45" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M45" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N45" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O45" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P45" s="93" t="str">
+      <x:c r="M45" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N45" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O45" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P45" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-AUTH-002.png
 ..\Automation\Execution Evidence\API-AUTH-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q45" s="93"/>
-      <x:c r="R45" s="94" t="str">
+      <x:c r="Q45" s="82"/>
+      <x:c r="R45" s="82" t="str">
         <x:v>200 transport | responseCode 400 | missing credential message returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="96" customHeight="1">
+    <x:row r="46" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A46" s="108" t="str">
         <x:v>REQ-API-009</x:v>
       </x:c>
@@ -5588,52 +5634,52 @@
       <x:c r="D46" s="109" t="str">
         <x:v>Authentication API</x:v>
       </x:c>
-      <x:c r="E46" s="109" t="str">
+      <x:c r="E46" s="143" t="str">
         <x:v>DELETE To Verify Login</x:v>
       </x:c>
-      <x:c r="F46" s="109" t="str">
+      <x:c r="F46" s="143" t="str">
         <x:v>API-AUTH-003</x:v>
       </x:c>
-      <x:c r="G46" s="117" t="str">
+      <x:c r="G46" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H46" s="93" t="str">
+      <x:c r="H46" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I46" s="109" t="str">
+      <x:c r="I46" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J46" s="109" t="str">
+      <x:c r="J46" s="143" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="K46" s="109" t="str">
+      <x:c r="K46" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L46" s="109" t="str">
+      <x:c r="L46" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M46" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N46" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O46" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P46" s="93" t="str">
+      <x:c r="M46" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N46" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O46" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P46" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-AUTH-003.png
 ..\Automation\Execution Evidence\API-AUTH-003.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q46" s="93"/>
-      <x:c r="R46" s="94" t="str">
+      <x:c r="Q46" s="82"/>
+      <x:c r="R46" s="82" t="str">
         <x:v>200 transport | responseCode 405 | method not supported. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="96" customHeight="1">
+    <x:row r="47" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A47" s="108" t="str">
         <x:v>REQ-API-010</x:v>
       </x:c>
@@ -5646,52 +5692,52 @@
       <x:c r="D47" s="109" t="str">
         <x:v>Authentication API</x:v>
       </x:c>
-      <x:c r="E47" s="109" t="str">
+      <x:c r="E47" s="143" t="str">
         <x:v>POST To Verify Login with invalid details</x:v>
       </x:c>
-      <x:c r="F47" s="109" t="str">
+      <x:c r="F47" s="143" t="str">
         <x:v>API-AUTH-004</x:v>
       </x:c>
-      <x:c r="G47" s="117" t="str">
+      <x:c r="G47" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H47" s="93" t="str">
+      <x:c r="H47" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I47" s="109" t="str">
+      <x:c r="I47" s="143" t="str">
         <x:v>API — Negative</x:v>
       </x:c>
-      <x:c r="J47" s="109" t="str">
+      <x:c r="J47" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K47" s="109" t="str">
+      <x:c r="K47" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L47" s="109" t="str">
+      <x:c r="L47" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M47" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N47" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O47" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P47" s="93" t="str">
+      <x:c r="M47" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N47" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O47" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P47" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-AUTH-004.png
 ..\Automation\Execution Evidence\API-AUTH-004.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q47" s="93"/>
-      <x:c r="R47" s="94" t="str">
+      <x:c r="Q47" s="82"/>
+      <x:c r="R47" s="82" t="str">
         <x:v>200 transport | responseCode 404 | User not found!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="96" customHeight="1">
+    <x:row r="48" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A48" s="108" t="str">
         <x:v>REQ-API-011</x:v>
       </x:c>
@@ -5704,52 +5750,52 @@
       <x:c r="D48" s="109" t="str">
         <x:v>Account API</x:v>
       </x:c>
-      <x:c r="E48" s="109" t="str">
+      <x:c r="E48" s="143" t="str">
         <x:v>POST To Create/Register User Account</x:v>
       </x:c>
-      <x:c r="F48" s="109" t="str">
+      <x:c r="F48" s="143" t="str">
         <x:v>API-ACCOUNT-001</x:v>
       </x:c>
-      <x:c r="G48" s="117" t="str">
+      <x:c r="G48" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H48" s="93" t="str">
+      <x:c r="H48" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I48" s="109" t="str">
+      <x:c r="I48" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J48" s="109" t="str">
+      <x:c r="J48" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K48" s="109" t="str">
+      <x:c r="K48" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L48" s="109" t="str">
+      <x:c r="L48" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M48" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N48" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O48" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P48" s="93" t="str">
+      <x:c r="M48" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N48" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O48" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P48" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-ACCOUNT-001.png
 ..\Automation\Execution Evidence\API-ACCOUNT-001.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q48" s="93"/>
-      <x:c r="R48" s="94" t="str">
+      <x:c r="Q48" s="82"/>
+      <x:c r="R48" s="82" t="str">
         <x:v>200 transport | responseCode 201 | User created!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="96" customHeight="1">
+    <x:row r="49" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A49" s="108" t="str">
         <x:v>REQ-API-012</x:v>
       </x:c>
@@ -5762,52 +5808,52 @@
       <x:c r="D49" s="109" t="str">
         <x:v>Account API</x:v>
       </x:c>
-      <x:c r="E49" s="109" t="str">
+      <x:c r="E49" s="143" t="str">
         <x:v>DELETE METHOD To Delete User Account</x:v>
       </x:c>
-      <x:c r="F49" s="109" t="str">
+      <x:c r="F49" s="143" t="str">
         <x:v>API-ACCOUNT-002</x:v>
       </x:c>
-      <x:c r="G49" s="117" t="str">
+      <x:c r="G49" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H49" s="93" t="str">
+      <x:c r="H49" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I49" s="109" t="str">
+      <x:c r="I49" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J49" s="109" t="str">
+      <x:c r="J49" s="143" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="K49" s="109" t="str">
+      <x:c r="K49" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L49" s="109" t="str">
+      <x:c r="L49" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M49" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N49" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O49" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P49" s="93" t="str">
+      <x:c r="M49" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N49" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O49" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P49" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-ACCOUNT-002.png
 ..\Automation\Execution Evidence\API-ACCOUNT-002.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q49" s="93"/>
-      <x:c r="R49" s="94" t="str">
+      <x:c r="Q49" s="82"/>
+      <x:c r="R49" s="82" t="str">
         <x:v>200 transport | responseCode 200 | Account deleted!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="96" customHeight="1">
+    <x:row r="50" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A50" s="108" t="str">
         <x:v>REQ-API-013</x:v>
       </x:c>
@@ -5820,52 +5866,52 @@
       <x:c r="D50" s="109" t="str">
         <x:v>Account API</x:v>
       </x:c>
-      <x:c r="E50" s="109" t="str">
+      <x:c r="E50" s="143" t="str">
         <x:v>PUT METHOD To Update User Account</x:v>
       </x:c>
-      <x:c r="F50" s="109" t="str">
+      <x:c r="F50" s="143" t="str">
         <x:v>API-ACCOUNT-003</x:v>
       </x:c>
-      <x:c r="G50" s="117" t="str">
+      <x:c r="G50" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H50" s="93" t="str">
+      <x:c r="H50" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I50" s="109" t="str">
+      <x:c r="I50" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J50" s="109" t="str">
+      <x:c r="J50" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K50" s="109" t="str">
+      <x:c r="K50" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L50" s="109" t="str">
+      <x:c r="L50" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M50" s="109" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N50" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O50" s="117" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P50" s="93" t="str">
+      <x:c r="M50" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N50" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O50" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P50" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-ACCOUNT-003.png
 ..\Automation\Execution Evidence\API-ACCOUNT-003.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q50" s="93"/>
-      <x:c r="R50" s="94" t="str">
+      <x:c r="Q50" s="82"/>
+      <x:c r="R50" s="82" t="str">
         <x:v>200 transport | responseCode 200 | User updated!. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="96" customHeight="1">
+    <x:row r="51" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A51" s="110" t="str">
         <x:v>REQ-API-014</x:v>
       </x:c>
@@ -5878,48 +5924,48 @@
       <x:c r="D51" s="111" t="str">
         <x:v>Account API</x:v>
       </x:c>
-      <x:c r="E51" s="111" t="str">
+      <x:c r="E51" s="143" t="str">
         <x:v>GET user account detail by email</x:v>
       </x:c>
-      <x:c r="F51" s="111" t="str">
+      <x:c r="F51" s="143" t="str">
         <x:v>API-ACCOUNT-004</x:v>
       </x:c>
-      <x:c r="G51" s="121" t="str">
+      <x:c r="G51" s="145" t="str">
         <x:v>Fully Covered</x:v>
       </x:c>
-      <x:c r="H51" s="97" t="str">
+      <x:c r="H51" s="82" t="str">
         <x:v>Fresh Postman Collection Runner execution and independent Playwright verification both passed the HTTP transport, documented JSON responseCode, and scenario-specific payload or message assertions.</x:v>
       </x:c>
-      <x:c r="I51" s="111" t="str">
+      <x:c r="I51" s="143" t="str">
         <x:v>API — Positive</x:v>
       </x:c>
-      <x:c r="J51" s="111" t="str">
+      <x:c r="J51" s="143" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="K51" s="111" t="str">
+      <x:c r="K51" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
-      <x:c r="L51" s="111" t="str">
+      <x:c r="L51" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="M51" s="111" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="N51" s="121" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="O51" s="121" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="P51" s="97" t="str">
+      <x:c r="M51" s="143" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="N51" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="O51" s="145" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P51" s="82" t="str">
         <x:v>..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09-Run-Summary.md
 ..\API Testing\Execution Results\Postman Reports\AE-API_Full-Collection_QA_2026-08-09.reconstructed.postman_run.json
 ..\API Testing\Execution Results\Screenshots\API-ACCOUNT-004.png
 ..\Automation\Execution Evidence\API-ACCOUNT-004.png
 ..\Automation\test-results\qa-analytics\index.html</x:v>
       </x:c>
-      <x:c r="Q51" s="97"/>
-      <x:c r="R51" s="98" t="str">
+      <x:c r="Q51" s="82"/>
+      <x:c r="R51" s="82" t="str">
         <x:v>200 transport | responseCode 200 | user detail returned. Fresh Postman run: 3/3 assertions passed on 2026-08-09; full collection: 42/42 passed, 0 errors. Historical August 1 baseline remains retained separately for auditability.</x:v>
       </x:c>
     </x:row>
@@ -6094,7 +6140,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8bb945c7a446e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R686395056909448a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6139,7 +6185,7 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="264.5" customHeight="1">
+    <x:row r="5" ht="216" hidden="0" customHeight="1">
       <x:c r="A5" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
@@ -6149,11 +6195,11 @@
       <x:c r="C5" s="5">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D5" s="14" t="s">
+      <x:c r="D5" s="149" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="264.5" customHeight="1">
+    <x:row r="6" ht="120" hidden="0" customHeight="1">
       <x:c r="A6" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
@@ -6163,11 +6209,11 @@
       <x:c r="C6" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="s">
+      <x:c r="D6" s="149" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="264.5" customHeight="1">
+    <x:row r="7" ht="96" hidden="0" customHeight="1">
       <x:c r="A7" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -6177,11 +6223,11 @@
       <x:c r="C7" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="149" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="264.5" customHeight="1">
+    <x:row r="8" ht="120" hidden="0" customHeight="1">
       <x:c r="A8" s="4" t="s">
         <x:v>33</x:v>
       </x:c>
@@ -6191,11 +6237,11 @@
       <x:c r="C8" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="149" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="264.5" customHeight="1">
+    <x:row r="9" ht="96" hidden="0" customHeight="1">
       <x:c r="A9" s="4" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -6205,11 +6251,11 @@
       <x:c r="C9" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="149" t="s">
         <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="264.5" customHeight="1">
+    <x:row r="10" ht="132" hidden="0" customHeight="1">
       <x:c r="A10" s="4" t="s">
         <x:v>39</x:v>
       </x:c>
@@ -6219,11 +6265,11 @@
       <x:c r="C10" s="5">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="s">
+      <x:c r="D10" s="149" t="s">
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="264.5" customHeight="1">
+    <x:row r="11" ht="60" hidden="0" customHeight="1">
       <x:c r="A11" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -6233,11 +6279,11 @@
       <x:c r="C11" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="s">
+      <x:c r="D11" s="149" t="s">
         <x:v>44</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="264.5" customHeight="1">
+    <x:row r="12" ht="108" hidden="0" customHeight="1">
       <x:c r="A12" s="4" t="s">
         <x:v>45</x:v>
       </x:c>
@@ -6247,11 +6293,11 @@
       <x:c r="C12" s="5">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="s">
+      <x:c r="D12" s="149" t="s">
         <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="264.5" customHeight="1">
+    <x:row r="13" ht="96" hidden="0" customHeight="1">
       <x:c r="A13" s="4" t="s">
         <x:v>48</x:v>
       </x:c>
@@ -6261,11 +6307,11 @@
       <x:c r="C13" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="D13" s="149" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="264.5" customHeight="1">
+    <x:row r="14" ht="84" hidden="0" customHeight="1">
       <x:c r="A14" s="4" t="s">
         <x:v>51</x:v>
       </x:c>
@@ -6275,11 +6321,11 @@
       <x:c r="C14" s="5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="s">
+      <x:c r="D14" s="149" t="s">
         <x:v>53</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="264.5" customHeight="1">
+    <x:row r="15" ht="96" hidden="0" customHeight="1">
       <x:c r="A15" s="4" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -6289,11 +6335,11 @@
       <x:c r="C15" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="14" t="s">
+      <x:c r="D15" s="149" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="264.5" customHeight="1">
+    <x:row r="16" ht="120" hidden="0" customHeight="1">
       <x:c r="A16" s="4" t="s">
         <x:v>57</x:v>
       </x:c>
@@ -6303,11 +6349,11 @@
       <x:c r="C16" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D16" s="14" t="s">
+      <x:c r="D16" s="149" t="s">
         <x:v>59</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="264.5" customHeight="1">
+    <x:row r="17" ht="108" hidden="0" customHeight="1">
       <x:c r="A17" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -6317,11 +6363,11 @@
       <x:c r="C17" s="5">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D17" s="14" t="s">
+      <x:c r="D17" s="149" t="s">
         <x:v>62</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="264.5" customHeight="1">
+    <x:row r="18" ht="240" hidden="0" customHeight="1">
       <x:c r="A18" s="4" t="s">
         <x:v>63</x:v>
       </x:c>
@@ -6331,11 +6377,11 @@
       <x:c r="C18" s="5">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D18" s="14" t="s">
+      <x:c r="D18" s="149" t="s">
         <x:v>65</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="264.5" customHeight="1">
+    <x:row r="19" ht="216" hidden="0" customHeight="1">
       <x:c r="A19" s="4" t="s">
         <x:v>66</x:v>
       </x:c>
@@ -6345,11 +6391,11 @@
       <x:c r="C19" s="5">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D19" s="14" t="s">
+      <x:c r="D19" s="149" t="s">
         <x:v>68</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="264.5" customHeight="1">
+    <x:row r="20" ht="204" hidden="0" customHeight="1">
       <x:c r="A20" s="4" t="s">
         <x:v>69</x:v>
       </x:c>
@@ -6359,11 +6405,11 @@
       <x:c r="C20" s="5">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D20" s="14" t="s">
+      <x:c r="D20" s="149" t="s">
         <x:v>71</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="264.5" customHeight="1">
+    <x:row r="21" ht="96" hidden="0" customHeight="1">
       <x:c r="A21" s="4" t="s">
         <x:v>72</x:v>
       </x:c>
@@ -6373,11 +6419,11 @@
       <x:c r="C21" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="14" t="s">
+      <x:c r="D21" s="149" t="s">
         <x:v>74</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="264.5" customHeight="1">
+    <x:row r="22" ht="96" hidden="0" customHeight="1">
       <x:c r="A22" s="4" t="s">
         <x:v>75</x:v>
       </x:c>
@@ -6387,11 +6433,11 @@
       <x:c r="C22" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D22" s="14" t="s">
+      <x:c r="D22" s="149" t="s">
         <x:v>77</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="264.5" customHeight="1">
+    <x:row r="23" ht="96" hidden="0" customHeight="1">
       <x:c r="A23" s="4" t="s">
         <x:v>78</x:v>
       </x:c>
@@ -6401,11 +6447,11 @@
       <x:c r="C23" s="5">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="14" t="s">
+      <x:c r="D23" s="149" t="s">
         <x:v>80</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="264.5" customHeight="1">
+    <x:row r="24" ht="144" hidden="0" customHeight="1">
       <x:c r="A24" s="4" t="s">
         <x:v>81</x:v>
       </x:c>
@@ -6415,11 +6461,11 @@
       <x:c r="C24" s="5">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D24" s="14" t="s">
+      <x:c r="D24" s="149" t="s">
         <x:v>83</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="264.5" customHeight="1">
+    <x:row r="25" ht="108" hidden="0" customHeight="1">
       <x:c r="A25" s="4" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -6429,11 +6475,11 @@
       <x:c r="C25" s="5">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D25" s="14" t="s">
+      <x:c r="D25" s="149" t="s">
         <x:v>86</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="264.5" customHeight="1">
+    <x:row r="26" ht="84" hidden="0" customHeight="1">
       <x:c r="A26" s="4" t="s">
         <x:v>87</x:v>
       </x:c>
@@ -6443,11 +6489,11 @@
       <x:c r="C26" s="5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D26" s="14" t="s">
+      <x:c r="D26" s="149" t="s">
         <x:v>89</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="264.5" customHeight="1">
+    <x:row r="27" ht="180" hidden="0" customHeight="1">
       <x:c r="A27" s="4" t="s">
         <x:v>90</x:v>
       </x:c>
@@ -6457,11 +6503,11 @@
       <x:c r="C27" s="5">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D27" s="14" t="s">
+      <x:c r="D27" s="149" t="s">
         <x:v>92</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="264.5" customHeight="1">
+    <x:row r="28" ht="264" hidden="0" customHeight="1">
       <x:c r="A28" s="4" t="s">
         <x:v>93</x:v>
       </x:c>
@@ -6471,11 +6517,11 @@
       <x:c r="C28" s="5">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D28" s="14" t="s">
+      <x:c r="D28" s="149" t="s">
         <x:v>95</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="264.5" customHeight="1">
+    <x:row r="29" ht="84" hidden="0" customHeight="1">
       <x:c r="A29" s="4" t="s">
         <x:v>96</x:v>
       </x:c>
@@ -6485,11 +6531,11 @@
       <x:c r="C29" s="5">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D29" s="14" t="s">
+      <x:c r="D29" s="149" t="s">
         <x:v>98</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="264.5" customHeight="1">
+    <x:row r="30" ht="84" hidden="0" customHeight="1">
       <x:c r="A30" s="9" t="s">
         <x:v>99</x:v>
       </x:c>
@@ -6499,7 +6545,7 @@
       <x:c r="C30" s="10">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="s">
+      <x:c r="D30" s="150" t="s">
         <x:v>101</x:v>
       </x:c>
     </x:row>
@@ -6510,7 +6556,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc505a24c44634916"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6391d83bfc461d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6584,358 +6630,358 @@
         <x:v>110</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="72" customHeight="1">
+    <x:row r="5" ht="14" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s">
+      <x:c r="B5" s="62" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="C5" s="62" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D5" s="5" t="s">
+      <x:c r="D5" s="62" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5">
+      <x:c r="E5" s="62"/>
+      <x:c r="F5" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="s">
+      <x:c r="G5" s="62" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H5" s="5" t="s">
+      <x:c r="H5" s="62" t="s">
         <x:v>116</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="72" customHeight="1">
+    <x:row r="6" ht="14" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
+      <x:c r="B6" s="62" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
+      <x:c r="C6" s="62" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="s">
+      <x:c r="D6" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5">
+      <x:c r="E6" s="62"/>
+      <x:c r="F6" s="62">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="s">
+      <x:c r="G6" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H6" s="5" t="s">
+      <x:c r="H6" s="62" t="s">
         <x:v>121</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
+    <x:row r="7" ht="14" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="s">
+      <x:c r="B7" s="62" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="s">
+      <x:c r="C7" s="62" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="s">
+      <x:c r="D7" s="62" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5">
+      <x:c r="E7" s="62"/>
+      <x:c r="F7" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="s">
+      <x:c r="G7" s="62" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="s">
+      <x:c r="H7" s="62" t="s">
         <x:v>125</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="72" customHeight="1">
+    <x:row r="8" ht="14" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="s">
+      <x:c r="B8" s="62" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="C8" s="5" t="s">
+      <x:c r="C8" s="62" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="s">
+      <x:c r="D8" s="62" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5">
+      <x:c r="E8" s="62"/>
+      <x:c r="F8" s="62">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="G8" s="5" t="s">
+      <x:c r="G8" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H8" s="5" t="s">
+      <x:c r="H8" s="62" t="s">
         <x:v>121</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
+    <x:row r="9" ht="14" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="s">
+      <x:c r="B9" s="62" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="s">
+      <x:c r="C9" s="62" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D9" s="5" t="s">
+      <x:c r="D9" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E9" s="5" t="s">
+      <x:c r="E9" s="62" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="F9" s="5">
+      <x:c r="F9" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G9" s="5" t="s">
+      <x:c r="G9" s="62" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H9" s="5" t="s">
+      <x:c r="H9" s="62" t="s">
         <x:v>133</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
+    <x:row r="10" ht="14" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B10" s="5" t="s">
+      <x:c r="B10" s="62" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="s">
+      <x:c r="C10" s="62" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D10" s="5" t="s">
+      <x:c r="D10" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5">
+      <x:c r="E10" s="62"/>
+      <x:c r="F10" s="62">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="G10" s="5" t="s">
+      <x:c r="G10" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H10" s="5" t="s">
+      <x:c r="H10" s="62" t="s">
         <x:v>136</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="72" customHeight="1">
+    <x:row r="11" ht="14" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B11" s="5" t="s">
+      <x:c r="B11" s="62" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="C11" s="5" t="s">
+      <x:c r="C11" s="62" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D11" s="5" t="s">
+      <x:c r="D11" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E11" s="5" t="s">
+      <x:c r="E11" s="62" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="F11" s="5">
+      <x:c r="F11" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G11" s="5" t="s">
+      <x:c r="G11" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="s">
+      <x:c r="H11" s="62" t="s">
         <x:v>141</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="72" customHeight="1">
+    <x:row r="12" ht="14" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B12" s="5" t="s">
+      <x:c r="B12" s="62" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="C12" s="5" t="s">
+      <x:c r="C12" s="62" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D12" s="5" t="s">
+      <x:c r="D12" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E12" s="5" t="s">
+      <x:c r="E12" s="62" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="F12" s="5">
+      <x:c r="F12" s="62">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="G12" s="5" t="s">
+      <x:c r="G12" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H12" s="5" t="s">
+      <x:c r="H12" s="62" t="s">
         <x:v>145</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="72" customHeight="1">
+    <x:row r="13" ht="14" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B13" s="5" t="s">
+      <x:c r="B13" s="62" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="C13" s="5" t="s">
+      <x:c r="C13" s="62" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D13" s="5" t="s">
+      <x:c r="D13" s="62" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5">
+      <x:c r="E13" s="62"/>
+      <x:c r="F13" s="62">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="G13" s="5" t="s">
+      <x:c r="G13" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H13" s="5" t="s">
+      <x:c r="H13" s="62" t="s">
         <x:v>121</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="72" customHeight="1">
+    <x:row r="14" ht="14" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B14" s="5" t="s">
+      <x:c r="B14" s="62" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="C14" s="5" t="s">
+      <x:c r="C14" s="62" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="D14" s="5" t="s">
+      <x:c r="D14" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E14" s="5" t="s">
+      <x:c r="E14" s="62" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="F14" s="5">
+      <x:c r="F14" s="62">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="G14" s="5" t="s">
+      <x:c r="G14" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H14" s="5" t="s">
+      <x:c r="H14" s="62" t="s">
         <x:v>152</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="72" customHeight="1">
+    <x:row r="15" ht="36" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B15" s="5" t="s">
+      <x:c r="B15" s="62" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C15" s="5" t="s">
+      <x:c r="C15" s="62" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D15" s="5" t="s">
+      <x:c r="D15" s="62" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="E15" s="5" t="s">
+      <x:c r="E15" s="62" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F15" s="5">
+      <x:c r="F15" s="62">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G15" s="5" t="s">
+      <x:c r="G15" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H15" s="5" t="s">
+      <x:c r="H15" s="62" t="s">
         <x:v>157</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="72" customHeight="1">
+    <x:row r="16" ht="14" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B16" s="5" t="s">
+      <x:c r="B16" s="62" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C16" s="5" t="s">
+      <x:c r="C16" s="62" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="D16" s="5" t="s">
+      <x:c r="D16" s="62" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="E16" s="5" t="s">
+      <x:c r="E16" s="62" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="F16" s="5">
+      <x:c r="F16" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G16" s="5" t="s">
+      <x:c r="G16" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H16" s="5" t="s">
+      <x:c r="H16" s="62" t="s">
         <x:v>161</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="72" customHeight="1">
+    <x:row r="17" ht="36" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B17" s="5" t="s">
+      <x:c r="B17" s="62" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="C17" s="5" t="s">
+      <x:c r="C17" s="62" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="D17" s="5" t="s">
+      <x:c r="D17" s="62" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E17" s="5" t="s">
+      <x:c r="E17" s="62" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="F17" s="5">
+      <x:c r="F17" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G17" s="5" t="s">
+      <x:c r="G17" s="62" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="s">
+      <x:c r="H17" s="62" t="s">
         <x:v>165</x:v>
       </x:c>
       <x:c r="J17" t="s">
         <x:v>166</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="72" customHeight="1">
+    <x:row r="18" ht="14" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B18" s="5" t="s">
+      <x:c r="B18" s="62" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="C18" s="5" t="s">
+      <x:c r="C18" s="62" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D18" s="5" t="s">
+      <x:c r="D18" s="62" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="E18" s="5" t="s">
+      <x:c r="E18" s="62" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="F18" s="5">
+      <x:c r="F18" s="62">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G18" s="5" t="s">
+      <x:c r="G18" s="62" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H18" s="5" t="s">
+      <x:c r="H18" s="62" t="s">
         <x:v>171</x:v>
       </x:c>
     </x:row>
@@ -6946,7 +6992,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4308aa48128447b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc2c45f69ce4abf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7051,7 +7097,7 @@
         <x:v>Jira Updated</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="31.5" customHeight="1">
+    <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A5" s="76" t="str">
         <x:v>AEQA-1</x:v>
       </x:c>
@@ -7090,7 +7136,7 @@
         <x:v>2026-08-17 19:33 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="31.5" customHeight="1">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="76" t="str">
         <x:v>AEQA-2</x:v>
       </x:c>
@@ -7123,7 +7169,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="31.5" customHeight="1">
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="76" t="str">
         <x:v>AEQA-3</x:v>
       </x:c>
@@ -7156,7 +7202,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="31.5" customHeight="1">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="76" t="str">
         <x:v>AEQA-4</x:v>
       </x:c>
@@ -7188,7 +7234,7 @@
         <x:v>11/Aug/26 7:35 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="31.5" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="76" t="str">
         <x:v>AEQA-5</x:v>
       </x:c>
@@ -7220,7 +7266,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="31.5" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="76" t="str">
         <x:v>AEQA-6</x:v>
       </x:c>
@@ -7252,7 +7298,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="31.5" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="76" t="str">
         <x:v>AEQA-7</x:v>
       </x:c>
@@ -7284,7 +7330,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="31.5" customHeight="1">
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="76" t="str">
         <x:v>AEQA-8</x:v>
       </x:c>
@@ -7316,7 +7362,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="31.5" customHeight="1">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="76" t="str">
         <x:v>AEQA-9</x:v>
       </x:c>
@@ -7348,7 +7394,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="31.5" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="76" t="str">
         <x:v>AEQA-10</x:v>
       </x:c>
@@ -7380,7 +7426,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="31.5" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="76" t="str">
         <x:v>AEQA-11</x:v>
       </x:c>
@@ -7412,7 +7458,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="31.5" customHeight="1">
+    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="76" t="str">
         <x:v>AEQA-12</x:v>
       </x:c>
@@ -7444,7 +7490,7 @@
         <x:v>10/Aug/26 8:26 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="31.5" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="76" t="str">
         <x:v>AEQA-13</x:v>
       </x:c>
@@ -7476,7 +7522,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="31.5" customHeight="1">
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="76" t="str">
         <x:v>AEQA-14</x:v>
       </x:c>
@@ -7510,7 +7556,7 @@
         <x:v>16/Aug/26 12:36 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="31.5" customHeight="1">
+    <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A19" s="76" t="str">
         <x:v>AEQA-15</x:v>
       </x:c>
@@ -7546,7 +7592,7 @@
         <x:v>2026-08-12 21:22 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="31.5" customHeight="1">
+    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A20" s="76" t="str">
         <x:v>AEQA-16</x:v>
       </x:c>
@@ -7582,7 +7628,7 @@
         <x:v>2026-08-12 22:10 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="31.5" customHeight="1">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="76" t="str">
         <x:v>AEQA-17</x:v>
       </x:c>
@@ -7614,7 +7660,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="31.5" customHeight="1">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="76" t="str">
         <x:v>AEQA-18</x:v>
       </x:c>
@@ -7648,7 +7694,7 @@
         <x:v>16/Aug/26 12:41 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="31.5" customHeight="1">
+    <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A23" s="76" t="str">
         <x:v>AEQA-19</x:v>
       </x:c>
@@ -7682,7 +7728,7 @@
         <x:v>2026-08-17 15:14 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="31.5" customHeight="1">
+    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A24" s="76" t="str">
         <x:v>AEQA-20</x:v>
       </x:c>
@@ -7718,7 +7764,7 @@
         <x:v>2026-08-17 19:22 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="31.5" customHeight="1">
+    <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="76" t="str">
         <x:v>AEQA-21</x:v>
       </x:c>
@@ -7755,7 +7801,7 @@
         <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="31.5" customHeight="1">
+    <x:row r="26" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A26" s="76" t="str">
         <x:v>AEQA-22</x:v>
       </x:c>
@@ -7766,7 +7812,7 @@
         <x:v>REQ-CART-005 - Add to cart from Recommended items</x:v>
       </x:c>
       <x:c r="D26" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E26" s="76" t="str">
         <x:v>Medium</x:v>
@@ -7779,7 +7825,9 @@
       </x:c>
       <x:c r="H26" s="76" t="str"/>
       <x:c r="I26" s="76" t="str"/>
-      <x:c r="J26" s="76" t="str"/>
+      <x:c r="J26" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K26" s="76" t="str"/>
       <x:c r="L26" s="76" t="str">
         <x:v>AEQA-114
@@ -7787,10 +7835,10 @@
       </x:c>
       <x:c r="M26" s="76" t="str"/>
       <x:c r="N26" s="76" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A27" s="76" t="str">
         <x:v>AEQA-23</x:v>
       </x:c>
@@ -7824,7 +7872,7 @@
         <x:v>15/Aug/26 11:27 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="31.5" customHeight="1">
+    <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A28" s="76" t="str">
         <x:v>AEQA-24</x:v>
       </x:c>
@@ -7835,7 +7883,7 @@
         <x:v>REQ-ORDER-005 - Download Invoice after purchase order</x:v>
       </x:c>
       <x:c r="D28" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E28" s="76" t="str">
         <x:v>High</x:v>
@@ -7848,7 +7896,9 @@
       </x:c>
       <x:c r="H28" s="76" t="str"/>
       <x:c r="I28" s="76" t="str"/>
-      <x:c r="J28" s="76" t="str"/>
+      <x:c r="J28" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K28" s="76" t="str"/>
       <x:c r="L28" s="76" t="str">
         <x:v>AEQA-116
@@ -7856,10 +7906,10 @@
       </x:c>
       <x:c r="M28" s="76" t="str"/>
       <x:c r="N28" s="76" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A29" s="76" t="str">
         <x:v>AEQA-25</x:v>
       </x:c>
@@ -7870,7 +7920,7 @@
         <x:v>REQ-NAV-002 - Verify Scroll Up using 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
       <x:c r="D29" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" s="76" t="str">
         <x:v>Low</x:v>
@@ -7883,7 +7933,9 @@
       </x:c>
       <x:c r="H29" s="76" t="str"/>
       <x:c r="I29" s="76" t="str"/>
-      <x:c r="J29" s="76" t="str"/>
+      <x:c r="J29" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K29" s="76" t="str"/>
       <x:c r="L29" s="76" t="str">
         <x:v>AEQA-117
@@ -7891,10 +7943,10 @@
       </x:c>
       <x:c r="M29" s="76" t="str"/>
       <x:c r="N29" s="76" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A30" s="76" t="str">
         <x:v>AEQA-26</x:v>
       </x:c>
@@ -7905,7 +7957,7 @@
         <x:v>REQ-NAV-003 - Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
       <x:c r="D30" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="E30" s="76" t="str">
         <x:v>Low</x:v>
@@ -7918,7 +7970,9 @@
       </x:c>
       <x:c r="H30" s="76" t="str"/>
       <x:c r="I30" s="76" t="str"/>
-      <x:c r="J30" s="76" t="str"/>
+      <x:c r="J30" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
       <x:c r="K30" s="76" t="str"/>
       <x:c r="L30" s="76" t="str">
         <x:v>AEQA-118
@@ -7926,10 +7980,10 @@
       </x:c>
       <x:c r="M30" s="76" t="str"/>
       <x:c r="N30" s="76" t="str">
-        <x:v>2026-08-17 15:31 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A31" s="76" t="str">
         <x:v>AEQA-27</x:v>
       </x:c>
@@ -7961,7 +8015,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="31.5" customHeight="1">
+    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A32" s="76" t="str">
         <x:v>AEQA-28</x:v>
       </x:c>
@@ -7993,7 +8047,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="31.5" customHeight="1">
+    <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A33" s="76" t="str">
         <x:v>AEQA-29</x:v>
       </x:c>
@@ -8025,7 +8079,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="31.5" customHeight="1">
+    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A34" s="76" t="str">
         <x:v>AEQA-30</x:v>
       </x:c>
@@ -8057,7 +8111,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="31.5" customHeight="1">
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="76" t="str">
         <x:v>AEQA-31</x:v>
       </x:c>
@@ -8089,7 +8143,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="31.5" customHeight="1">
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="76" t="str">
         <x:v>AEQA-32</x:v>
       </x:c>
@@ -8121,7 +8175,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="31.5" customHeight="1">
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="76" t="str">
         <x:v>AEQA-33</x:v>
       </x:c>
@@ -8153,7 +8207,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="31.5" customHeight="1">
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="76" t="str">
         <x:v>AEQA-34</x:v>
       </x:c>
@@ -8185,7 +8239,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="31.5" customHeight="1">
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="76" t="str">
         <x:v>AEQA-35</x:v>
       </x:c>
@@ -8217,7 +8271,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="31.5" customHeight="1">
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A40" s="76" t="str">
         <x:v>AEQA-36</x:v>
       </x:c>
@@ -8250,7 +8304,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="31.5" customHeight="1">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="76" t="str">
         <x:v>AEQA-37</x:v>
       </x:c>
@@ -8282,7 +8336,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="31.5" customHeight="1">
+    <x:row r="42" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A42" s="76" t="str">
         <x:v>AEQA-38</x:v>
       </x:c>
@@ -8314,7 +8368,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="31.5" customHeight="1">
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="76" t="str">
         <x:v>AEQA-39</x:v>
       </x:c>
@@ -8346,7 +8400,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="31.5" customHeight="1">
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="76" t="str">
         <x:v>AEQA-40</x:v>
       </x:c>
@@ -8378,7 +8432,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="31.5" customHeight="1">
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="76" t="str">
         <x:v>AEQA-41</x:v>
       </x:c>
@@ -8410,7 +8464,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="31.5" customHeight="1">
+    <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="76" t="str">
         <x:v>AEQA-42</x:v>
       </x:c>
@@ -8442,7 +8496,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="31.5" customHeight="1">
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="76" t="str">
         <x:v>AEQA-43</x:v>
       </x:c>
@@ -8474,7 +8528,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="31.5" customHeight="1">
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="76" t="str">
         <x:v>AEQA-44</x:v>
       </x:c>
@@ -8506,7 +8560,7 @@
         <x:v>10/Aug/26 8:02 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="31.5" customHeight="1">
+    <x:row r="49" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A49" s="76" t="str">
         <x:v>AEQA-45</x:v>
       </x:c>
@@ -8544,7 +8598,7 @@
         <x:v>10/Aug/26 7:58 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="31.5" customHeight="1">
+    <x:row r="50" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A50" s="76" t="str">
         <x:v>AEQA-46</x:v>
       </x:c>
@@ -8582,7 +8636,7 @@
         <x:v>10/Aug/26 7:58 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="31.5" customHeight="1">
+    <x:row r="51" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A51" s="76" t="str">
         <x:v>AEQA-47</x:v>
       </x:c>
@@ -8620,7 +8674,7 @@
         <x:v>10/Aug/26 7:58 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="31.5" customHeight="1">
+    <x:row r="52" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A52" s="76" t="str">
         <x:v>AEQA-48</x:v>
       </x:c>
@@ -8658,7 +8712,7 @@
         <x:v>10/Aug/26 7:58 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="31.5" customHeight="1">
+    <x:row r="53" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A53" s="76" t="str">
         <x:v>AEQA-49</x:v>
       </x:c>
@@ -8696,7 +8750,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="31.5" customHeight="1">
+    <x:row r="54" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A54" s="76" t="str">
         <x:v>AEQA-50</x:v>
       </x:c>
@@ -8734,7 +8788,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="31.5" customHeight="1">
+    <x:row r="55" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A55" s="76" t="str">
         <x:v>AEQA-51</x:v>
       </x:c>
@@ -8772,7 +8826,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="31.5" customHeight="1">
+    <x:row r="56" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A56" s="76" t="str">
         <x:v>AEQA-52</x:v>
       </x:c>
@@ -8810,7 +8864,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="31.5" customHeight="1">
+    <x:row r="57" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A57" s="76" t="str">
         <x:v>AEQA-53</x:v>
       </x:c>
@@ -8849,7 +8903,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="31.5" customHeight="1">
+    <x:row r="58" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A58" s="76" t="str">
         <x:v>AEQA-54</x:v>
       </x:c>
@@ -8887,7 +8941,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="31.5" customHeight="1">
+    <x:row r="59" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A59" s="76" t="str">
         <x:v>AEQA-55</x:v>
       </x:c>
@@ -8925,7 +8979,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="31.5" customHeight="1">
+    <x:row r="60" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A60" s="76" t="str">
         <x:v>AEQA-56</x:v>
       </x:c>
@@ -8963,7 +9017,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="31.5" customHeight="1">
+    <x:row r="61" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A61" s="76" t="str">
         <x:v>AEQA-57</x:v>
       </x:c>
@@ -9001,7 +9055,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="31.5" customHeight="1">
+    <x:row r="62" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A62" s="76" t="str">
         <x:v>AEQA-58</x:v>
       </x:c>
@@ -9039,7 +9093,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="31.5" customHeight="1">
+    <x:row r="63" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A63" s="76" t="str">
         <x:v>AEQA-59</x:v>
       </x:c>
@@ -9077,7 +9131,7 @@
         <x:v>10/Aug/26 8:34 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="31.5" customHeight="1">
+    <x:row r="64" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A64" s="76" t="str">
         <x:v>AEQA-60</x:v>
       </x:c>
@@ -9115,7 +9169,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="31.5" customHeight="1">
+    <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A65" s="76" t="str">
         <x:v>AEQA-61</x:v>
       </x:c>
@@ -9153,7 +9207,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="31.5" customHeight="1">
+    <x:row r="66" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A66" s="76" t="str">
         <x:v>AEQA-62</x:v>
       </x:c>
@@ -9191,7 +9245,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="31.5" customHeight="1">
+    <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A67" s="76" t="str">
         <x:v>AEQA-63</x:v>
       </x:c>
@@ -9229,7 +9283,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="31.5" customHeight="1">
+    <x:row r="68" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A68" s="76" t="str">
         <x:v>AEQA-64</x:v>
       </x:c>
@@ -9267,7 +9321,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="31.5" customHeight="1">
+    <x:row r="69" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A69" s="76" t="str">
         <x:v>AEQA-65</x:v>
       </x:c>
@@ -9305,7 +9359,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="31.5" customHeight="1">
+    <x:row r="70" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A70" s="76" t="str">
         <x:v>AEQA-66</x:v>
       </x:c>
@@ -9343,7 +9397,7 @@
         <x:v>10/Aug/26 7:59 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="31.5" customHeight="1">
+    <x:row r="71" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A71" s="76" t="str">
         <x:v>AEQA-67</x:v>
       </x:c>
@@ -9381,7 +9435,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="31.5" customHeight="1">
+    <x:row r="72" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A72" s="76" t="str">
         <x:v>AEQA-68</x:v>
       </x:c>
@@ -9419,7 +9473,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="31.5" customHeight="1">
+    <x:row r="73" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A73" s="76" t="str">
         <x:v>AEQA-69</x:v>
       </x:c>
@@ -9457,7 +9511,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="31.5" customHeight="1">
+    <x:row r="74" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A74" s="76" t="str">
         <x:v>AEQA-70</x:v>
       </x:c>
@@ -9495,7 +9549,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="31.5" customHeight="1">
+    <x:row r="75" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A75" s="76" t="str">
         <x:v>AEQA-71</x:v>
       </x:c>
@@ -9533,7 +9587,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="31.5" customHeight="1">
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="76" t="str">
         <x:v>AEQA-72</x:v>
       </x:c>
@@ -9571,7 +9625,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="31.5" customHeight="1">
+    <x:row r="77" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A77" s="76" t="str">
         <x:v>AEQA-73</x:v>
       </x:c>
@@ -9609,7 +9663,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="31.5" customHeight="1">
+    <x:row r="78" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A78" s="76" t="str">
         <x:v>AEQA-74</x:v>
       </x:c>
@@ -9647,7 +9701,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="31.5" customHeight="1">
+    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A79" s="76" t="str">
         <x:v>AEQA-75</x:v>
       </x:c>
@@ -9685,7 +9739,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="31.5" customHeight="1">
+    <x:row r="80" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A80" s="76" t="str">
         <x:v>AEQA-76</x:v>
       </x:c>
@@ -9723,7 +9777,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="31.5" customHeight="1">
+    <x:row r="81" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A81" s="76" t="str">
         <x:v>AEQA-77</x:v>
       </x:c>
@@ -9761,7 +9815,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="31.5" customHeight="1">
+    <x:row r="82" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A82" s="76" t="str">
         <x:v>AEQA-78</x:v>
       </x:c>
@@ -9799,7 +9853,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="31.5" customHeight="1">
+    <x:row r="83" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A83" s="76" t="str">
         <x:v>AEQA-79</x:v>
       </x:c>
@@ -9837,7 +9891,7 @@
         <x:v>10/Aug/26 8:00 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="31.5" customHeight="1">
+    <x:row r="84" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A84" s="76" t="str">
         <x:v>AEQA-80</x:v>
       </x:c>
@@ -9869,7 +9923,7 @@
         <x:v>2026-08-15 23:29 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="31.5" customHeight="1">
+    <x:row r="85" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A85" s="76" t="str">
         <x:v>AEQA-81</x:v>
       </x:c>
@@ -9901,7 +9955,7 @@
         <x:v>2026-08-15 23:28 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="31.5" customHeight="1">
+    <x:row r="86" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A86" s="76" t="str">
         <x:v>AEQA-82</x:v>
       </x:c>
@@ -9933,7 +9987,7 @@
         <x:v>2026-08-12 22:25 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="31.5" customHeight="1">
+    <x:row r="87" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A87" s="76" t="str">
         <x:v>AEQA-83</x:v>
       </x:c>
@@ -9965,7 +10019,7 @@
         <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="31.5" customHeight="1">
+    <x:row r="88" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A88" s="76" t="str">
         <x:v>AEQA-84</x:v>
       </x:c>
@@ -9997,7 +10051,7 @@
         <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="31.5" customHeight="1">
+    <x:row r="89" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A89" s="76" t="str">
         <x:v>AEQA-85</x:v>
       </x:c>
@@ -10029,7 +10083,7 @@
         <x:v>2026-08-12 22:26 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="31.5" customHeight="1">
+    <x:row r="90" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A90" s="76" t="str">
         <x:v>AEQA-86</x:v>
       </x:c>
@@ -10059,7 +10113,7 @@
         <x:v>10/Aug/26 8:31 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="31.5" customHeight="1">
+    <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="76" t="str">
         <x:v>AEQA-87</x:v>
       </x:c>
@@ -10091,7 +10145,7 @@
         <x:v>14/Aug/26 8:22 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="31.5" customHeight="1">
+    <x:row r="92" ht="15" hidden="0" customHeight="1">
       <x:c r="A92" s="76" t="str">
         <x:v>AEQA-88</x:v>
       </x:c>
@@ -10123,7 +10177,7 @@
         <x:v>14/Aug/26 8:22 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="31.5" customHeight="1">
+    <x:row r="93" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A93" s="76" t="str">
         <x:v>AEQA-89</x:v>
       </x:c>
@@ -10155,7 +10209,7 @@
         <x:v>16/Aug/26 12:34 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="31.5" customHeight="1">
+    <x:row r="94" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A94" s="76" t="str">
         <x:v>AEQA-90</x:v>
       </x:c>
@@ -10187,7 +10241,7 @@
         <x:v>16/Aug/26 12:34 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="31.5" customHeight="1">
+    <x:row r="95" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A95" s="76" t="str">
         <x:v>AEQA-91</x:v>
       </x:c>
@@ -10217,7 +10271,7 @@
         <x:v>10/Aug/26 8:31 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="31.5" customHeight="1">
+    <x:row r="96" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A96" s="76" t="str">
         <x:v>AEQA-92</x:v>
       </x:c>
@@ -10247,7 +10301,7 @@
         <x:v>10/Aug/26 8:31 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="31.5" customHeight="1">
+    <x:row r="97" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A97" s="76" t="str">
         <x:v>AEQA-93</x:v>
       </x:c>
@@ -10277,7 +10331,7 @@
         <x:v>10/Aug/26 8:31 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="31.5" customHeight="1">
+    <x:row r="98" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A98" s="76" t="str">
         <x:v>AEQA-94</x:v>
       </x:c>
@@ -10307,7 +10361,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="31.5" customHeight="1">
+    <x:row r="99" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A99" s="76" t="str">
         <x:v>AEQA-95</x:v>
       </x:c>
@@ -10337,7 +10391,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="31.5" customHeight="1">
+    <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="76" t="str">
         <x:v>AEQA-96</x:v>
       </x:c>
@@ -10367,7 +10421,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="31.5" customHeight="1">
+    <x:row r="101" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A101" s="76" t="str">
         <x:v>AEQA-97</x:v>
       </x:c>
@@ -10397,7 +10451,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="31.5" customHeight="1">
+    <x:row r="102" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A102" s="76" t="str">
         <x:v>AEQA-98</x:v>
       </x:c>
@@ -10427,7 +10481,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="31.5" customHeight="1">
+    <x:row r="103" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A103" s="76" t="str">
         <x:v>AEQA-99</x:v>
       </x:c>
@@ -10457,7 +10511,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="31.5" customHeight="1">
+    <x:row r="104" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A104" s="76" t="str">
         <x:v>AEQA-100</x:v>
       </x:c>
@@ -10487,7 +10541,7 @@
         <x:v>10/Aug/26 8:32 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="31.5" customHeight="1">
+    <x:row r="105" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A105" s="76" t="str">
         <x:v>AEQA-101</x:v>
       </x:c>
@@ -10517,7 +10571,7 @@
         <x:v>10/Aug/26 8:33 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="31.5" customHeight="1">
+    <x:row r="106" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A106" s="76" t="str">
         <x:v>AEQA-102</x:v>
       </x:c>
@@ -10549,7 +10603,7 @@
         <x:v>15/Aug/26 11:23 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="31.5" customHeight="1">
+    <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="76" t="str">
         <x:v>AEQA-103</x:v>
       </x:c>
@@ -10579,7 +10633,7 @@
         <x:v>10/Aug/26 8:33 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="31.5" customHeight="1">
+    <x:row r="108" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A108" s="76" t="str">
         <x:v>AEQA-104</x:v>
       </x:c>
@@ -10609,7 +10663,7 @@
         <x:v>10/Aug/26 8:33 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="31.5" customHeight="1">
+    <x:row r="109" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A109" s="76" t="str">
         <x:v>AEQA-105</x:v>
       </x:c>
@@ -10641,7 +10695,7 @@
         <x:v>15/Aug/26 11:27 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="31.5" customHeight="1">
+    <x:row r="110" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A110" s="76" t="str">
         <x:v>AEQA-106</x:v>
       </x:c>
@@ -10679,7 +10733,7 @@
         <x:v>2026-08-17 13:22 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="31.5" customHeight="1">
+    <x:row r="111" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A111" s="76" t="str">
         <x:v>AEQA-107</x:v>
       </x:c>
@@ -10717,7 +10771,7 @@
         <x:v>2026-08-12 22:27 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="31.5" customHeight="1">
+    <x:row r="112" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A112" s="76" t="str">
         <x:v>AEQA-108</x:v>
       </x:c>
@@ -10755,7 +10809,7 @@
         <x:v>2026-08-12 22:28 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="31.5" customHeight="1">
+    <x:row r="113" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A113" s="76" t="str">
         <x:v>AEQA-109</x:v>
       </x:c>
@@ -10793,7 +10847,7 @@
         <x:v>2026-08-12 22:28 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="31.5" customHeight="1">
+    <x:row r="114" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A114" s="76" t="str">
         <x:v>AEQA-110</x:v>
       </x:c>
@@ -10831,7 +10885,7 @@
         <x:v>16/Aug/26 12:46 AM</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="31.5" customHeight="1">
+    <x:row r="115" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A115" s="76" t="str">
         <x:v>AEQA-111</x:v>
       </x:c>
@@ -10869,7 +10923,7 @@
         <x:v>2026-08-12 22:17 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="31.5" customHeight="1">
+    <x:row r="116" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A116" s="76" t="str">
         <x:v>AEQA-112</x:v>
       </x:c>
@@ -10907,7 +10961,7 @@
         <x:v>2026-08-17 19:22 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="31.5" customHeight="1">
+    <x:row r="117" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A117" s="76" t="str">
         <x:v>AEQA-113</x:v>
       </x:c>
@@ -10945,7 +10999,7 @@
         <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="31.5" customHeight="1">
+    <x:row r="118" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A118" s="76" t="str">
         <x:v>AEQA-114</x:v>
       </x:c>
@@ -10956,7 +11010,7 @@
         <x:v>AE-CART-005 - Verify a product can be added to the cart from Recommended Items</x:v>
       </x:c>
       <x:c r="D118" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E118" s="76" t="str">
         <x:v>High</x:v>
@@ -10970,7 +11024,7 @@
       </x:c>
       <x:c r="I118" s="76" t="str"/>
       <x:c r="J118" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K118" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10980,10 +11034,10 @@
       </x:c>
       <x:c r="M118" s="76" t="str"/>
       <x:c r="N118" s="76" t="str">
-        <x:v>2026-08-12 22:18 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A119" s="76" t="str">
         <x:v>AEQA-115</x:v>
       </x:c>
@@ -11021,7 +11075,7 @@
         <x:v>15/Aug/26 11:14 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="31.5" customHeight="1">
+    <x:row r="120" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A120" s="76" t="str">
         <x:v>AEQA-116</x:v>
       </x:c>
@@ -11032,7 +11086,7 @@
         <x:v>AE-ORDER-005 - Verify an invoice can be downloaded after a successful purchase</x:v>
       </x:c>
       <x:c r="D120" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E120" s="76" t="str">
         <x:v>High</x:v>
@@ -11046,7 +11100,7 @@
       </x:c>
       <x:c r="I120" s="76" t="str"/>
       <x:c r="J120" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K120" s="76" t="str">
         <x:v>Manual</x:v>
@@ -11056,10 +11110,10 @@
       </x:c>
       <x:c r="M120" s="76" t="str"/>
       <x:c r="N120" s="76" t="str">
-        <x:v>2026-08-12 22:18 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A121" s="76" t="str">
         <x:v>AEQA-117</x:v>
       </x:c>
@@ -11070,7 +11124,7 @@
         <x:v>AE-NAV-002 - Verify scrolling down and returning to the top with the arrow button</x:v>
       </x:c>
       <x:c r="D121" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E121" s="76" t="str">
         <x:v>Medium</x:v>
@@ -11084,7 +11138,7 @@
       </x:c>
       <x:c r="I121" s="76" t="str"/>
       <x:c r="J121" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K121" s="76" t="str">
         <x:v>Manual</x:v>
@@ -11094,10 +11148,10 @@
       </x:c>
       <x:c r="M121" s="76" t="str"/>
       <x:c r="N121" s="76" t="str">
-        <x:v>2026-08-12 22:18 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="31.5" customHeight="1">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A122" s="76" t="str">
         <x:v>AEQA-118</x:v>
       </x:c>
@@ -11108,7 +11162,7 @@
         <x:v>AE-NAV-003 - Verify manual scrolling down and back to the top without the arrow button</x:v>
       </x:c>
       <x:c r="D122" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E122" s="76" t="str">
         <x:v>Medium</x:v>
@@ -11122,7 +11176,7 @@
       </x:c>
       <x:c r="I122" s="76" t="str"/>
       <x:c r="J122" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K122" s="76" t="str">
         <x:v>Manual</x:v>
@@ -11132,369 +11186,369 @@
       </x:c>
       <x:c r="M122" s="76" t="str"/>
       <x:c r="N122" s="76" t="str">
-        <x:v>2026-08-12 22:18 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A123" t="str">
         <x:v>AEQA-119</x:v>
       </x:c>
       <x:c r="B123" t="str">
         <x:v>Requirement</x:v>
       </x:c>
-      <x:c r="C123" t="str">
+      <x:c r="C123" s="60" t="str">
         <x:v>QA-ADMIN-001 - Validate manual Requirement form workflow</x:v>
       </x:c>
-      <x:c r="D123" t="str">
+      <x:c r="D123" s="60" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="E123" t="str">
+      <x:c r="E123" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F123"/>
-      <x:c r="G123" t="str">
+      <x:c r="F123" s="60"/>
+      <x:c r="G123" s="60" t="str">
         <x:v>QA-ADMIN-001</x:v>
       </x:c>
-      <x:c r="H123"/>
-      <x:c r="I123"/>
-      <x:c r="J123"/>
-      <x:c r="K123"/>
-      <x:c r="L123"/>
-      <x:c r="M123"/>
-      <x:c r="N123" t="str">
+      <x:c r="H123" s="60"/>
+      <x:c r="I123" s="60"/>
+      <x:c r="J123" s="60"/>
+      <x:c r="K123" s="60"/>
+      <x:c r="L123" s="60"/>
+      <x:c r="M123" s="60"/>
+      <x:c r="N123" s="60" t="str">
         <x:v>12/Aug/26 9:18 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="124">
+    <x:row r="124" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A124" t="str">
         <x:v>AEQA-120</x:v>
       </x:c>
       <x:c r="B124" t="str">
         <x:v>Task</x:v>
       </x:c>
-      <x:c r="C124" t="str">
+      <x:c r="C124" s="60" t="str">
         <x:v>QA Maintenance - Reconcile and re-upload missing execution evidence</x:v>
       </x:c>
-      <x:c r="D124" t="str">
+      <x:c r="D124" s="60" t="str">
         <x:v>Backlog</x:v>
       </x:c>
-      <x:c r="E124" t="str">
+      <x:c r="E124" s="60" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F124" t="str">
+      <x:c r="F124" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G124"/>
-      <x:c r="H124"/>
-      <x:c r="I124"/>
-      <x:c r="J124"/>
-      <x:c r="K124"/>
-      <x:c r="L124"/>
-      <x:c r="M124"/>
-      <x:c r="N124" t="str">
+      <x:c r="G124" s="60"/>
+      <x:c r="H124" s="60"/>
+      <x:c r="I124" s="60"/>
+      <x:c r="J124" s="60"/>
+      <x:c r="K124" s="60"/>
+      <x:c r="L124" s="60"/>
+      <x:c r="M124" s="60"/>
+      <x:c r="N124" s="60" t="str">
         <x:v>12/Aug/26 10:27 PM</x:v>
       </x:c>
     </x:row>
-    <x:row r="125">
+    <x:row r="125" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A125" t="str">
         <x:v>AEQA-121</x:v>
       </x:c>
       <x:c r="B125" t="str">
         <x:v>Sub-task</x:v>
       </x:c>
-      <x:c r="C125" t="str">
+      <x:c r="C125" s="60" t="str">
         <x:v>Automate end-to-end user registration with Playwright</x:v>
       </x:c>
-      <x:c r="D125" t="str">
+      <x:c r="D125" s="60" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="E125" t="str">
+      <x:c r="E125" s="60" t="str">
         <x:v>Highest</x:v>
       </x:c>
-      <x:c r="F125" t="str">
+      <x:c r="F125" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G125" t="str">
+      <x:c r="G125" s="60" t="str">
         <x:v>REQ-AUTH-001</x:v>
       </x:c>
-      <x:c r="H125" t="str"/>
-      <x:c r="I125" t="str"/>
-      <x:c r="J125" t="str">
+      <x:c r="H125" s="60" t="str"/>
+      <x:c r="I125" s="60" t="str"/>
+      <x:c r="J125" s="60" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="K125" t="str">
+      <x:c r="K125" s="60" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="L125" t="str"/>
-      <x:c r="M125" t="str">
+      <x:c r="L125" s="60" t="str"/>
+      <x:c r="M125" s="60" t="str">
         <x:v>AEQA-1</x:v>
       </x:c>
-      <x:c r="N125" t="str">
+      <x:c r="N125" s="60" t="str">
         <x:v>2026-08-16 23:42 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="126">
+    <x:row r="126" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A126" t="str">
         <x:v>AEQA-122</x:v>
       </x:c>
       <x:c r="B126" t="str">
         <x:v>Sub-task</x:v>
       </x:c>
-      <x:c r="C126" t="str">
+      <x:c r="C126" s="60" t="str">
         <x:v>Automate the search and cart persistence scenario in Playwright</x:v>
       </x:c>
-      <x:c r="D126" t="str">
+      <x:c r="D126" s="60" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="E126" t="str">
+      <x:c r="E126" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F126" t="str">
+      <x:c r="F126" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G126" t="str">
+      <x:c r="G126" s="60" t="str">
         <x:v>REQ-CART-004</x:v>
       </x:c>
-      <x:c r="H126" t="str"/>
-      <x:c r="I126" t="str"/>
-      <x:c r="J126" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="K126" t="str">
+      <x:c r="H126" s="60" t="str"/>
+      <x:c r="I126" s="60" t="str"/>
+      <x:c r="J126" s="60" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K126" s="60" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="L126" t="str"/>
-      <x:c r="M126" t="str">
+      <x:c r="L126" s="60" t="str"/>
+      <x:c r="M126" s="60" t="str">
         <x:v>AEQA-20</x:v>
       </x:c>
-      <x:c r="N126" t="str">
+      <x:c r="N126" s="60" t="str">
         <x:v>2026-08-17 13:03 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="127">
+    <x:row r="127" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A127" t="str">
         <x:v>AEQA-123</x:v>
       </x:c>
       <x:c r="B127" t="str">
         <x:v>Sub-task</x:v>
       </x:c>
-      <x:c r="C127" t="str">
+      <x:c r="C127" s="60" t="str">
         <x:v>Automate brand-based product navigation in Playwright</x:v>
       </x:c>
-      <x:c r="D127" t="str">
+      <x:c r="D127" s="60" t="str">
         <x:v>Backlog</x:v>
       </x:c>
-      <x:c r="E127" t="str">
+      <x:c r="E127" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F127" t="str"/>
-      <x:c r="G127" t="str">
+      <x:c r="F127" s="60" t="str"/>
+      <x:c r="G127" s="60" t="str">
         <x:v>REQ-CATALOG-002</x:v>
       </x:c>
-      <x:c r="H127" t="str"/>
-      <x:c r="I127" t="str"/>
-      <x:c r="J127" t="str">
+      <x:c r="H127" s="60" t="str"/>
+      <x:c r="I127" s="60" t="str"/>
+      <x:c r="J127" s="60" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="K127" t="str">
+      <x:c r="K127" s="60" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="L127" t="str"/>
-      <x:c r="M127" t="str">
+      <x:c r="L127" s="60" t="str"/>
+      <x:c r="M127" s="60" t="str">
         <x:v>AEQA-19</x:v>
       </x:c>
-      <x:c r="N127" t="str">
+      <x:c r="N127" s="60" t="str">
         <x:v>2026-08-17 15:14 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="128">
+    <x:row r="128" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A128" t="str">
         <x:v>AEQA-124</x:v>
       </x:c>
       <x:c r="B128" t="str">
         <x:v>Test Case</x:v>
       </x:c>
-      <x:c r="C128" t="str">
+      <x:c r="C128" s="60" t="str">
         <x:v>AE-AUTO-REVIEW-001 - Automate product review submission in Playwright</x:v>
       </x:c>
-      <x:c r="D128" t="str">
+      <x:c r="D128" s="60" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="E128" t="str">
+      <x:c r="E128" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F128" t="str">
+      <x:c r="F128" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G128" t="str"/>
-      <x:c r="H128" t="str">
+      <x:c r="G128" s="60" t="str"/>
+      <x:c r="H128" s="60" t="str">
         <x:v>AE-AUTO-REVIEW-001</x:v>
       </x:c>
-      <x:c r="I128" t="str"/>
-      <x:c r="J128" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="K128" t="str">
+      <x:c r="I128" s="60" t="str"/>
+      <x:c r="J128" s="60" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K128" s="60" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="L128" t="str">
+      <x:c r="L128" s="60" t="str">
         <x:v>AEQA-21</x:v>
       </x:c>
-      <x:c r="M128"/>
-      <x:c r="N128" t="str">
+      <x:c r="M128" s="60"/>
+      <x:c r="N128" s="60" t="str">
         <x:v>2026-08-17 19:11 EDT</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
+    <x:row r="129" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A129" t="str">
         <x:v>AEQA-125</x:v>
       </x:c>
       <x:c r="B129" t="str">
         <x:v>Test Case</x:v>
       </x:c>
-      <x:c r="C129" t="str">
+      <x:c r="C129" s="60" t="str">
         <x:v>AE-AUTO-CART-005 - Automate Recommended Items add-to-cart in Playwright</x:v>
       </x:c>
-      <x:c r="D129" t="str">
-        <x:v>Backlog</x:v>
-      </x:c>
-      <x:c r="E129" t="str">
+      <x:c r="D129" s="60" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E129" s="60" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F129" t="str">
+      <x:c r="F129" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G129"/>
-      <x:c r="H129" t="str">
+      <x:c r="G129" s="60"/>
+      <x:c r="H129" s="60" t="str">
         <x:v>AE-AUTO-CART-005</x:v>
       </x:c>
-      <x:c r="I129"/>
-      <x:c r="J129" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="K129" t="str">
-        <x:v>Automation Candidate</x:v>
-      </x:c>
-      <x:c r="L129" t="str">
+      <x:c r="I129" s="60"/>
+      <x:c r="J129" s="60" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K129" s="60" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="L129" s="60" t="str">
         <x:v>AEQA-22</x:v>
       </x:c>
-      <x:c r="M129"/>
-      <x:c r="N129" t="str">
-        <x:v>2026-08-17 19:24 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130">
+      <x:c r="M129" s="60"/>
+      <x:c r="N129" s="60" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A130" t="str">
         <x:v>AEQA-126</x:v>
       </x:c>
       <x:c r="B130" t="str">
         <x:v>Test Case</x:v>
       </x:c>
-      <x:c r="C130" t="str">
+      <x:c r="C130" s="60" t="str">
         <x:v>AE-AUTO-ORDER-005 - Automate invoice download after purchase in Playwright</x:v>
       </x:c>
-      <x:c r="D130" t="str">
-        <x:v>Backlog</x:v>
-      </x:c>
-      <x:c r="E130" t="str">
+      <x:c r="D130" s="60" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E130" s="60" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="F130" t="str">
+      <x:c r="F130" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G130"/>
-      <x:c r="H130" t="str">
+      <x:c r="G130" s="60"/>
+      <x:c r="H130" s="60" t="str">
         <x:v>AE-AUTO-ORDER-005</x:v>
       </x:c>
-      <x:c r="I130"/>
-      <x:c r="J130" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="K130" t="str">
-        <x:v>Automation Candidate</x:v>
-      </x:c>
-      <x:c r="L130" t="str">
+      <x:c r="I130" s="60"/>
+      <x:c r="J130" s="60" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K130" s="60" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="L130" s="60" t="str">
         <x:v>AEQA-24</x:v>
       </x:c>
-      <x:c r="M130"/>
-      <x:c r="N130" t="str">
-        <x:v>2026-08-17 19:24 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131">
+      <x:c r="M130" s="60"/>
+      <x:c r="N130" s="60" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A131" t="str">
         <x:v>AEQA-127</x:v>
       </x:c>
       <x:c r="B131" t="str">
         <x:v>Test Case</x:v>
       </x:c>
-      <x:c r="C131" t="str">
+      <x:c r="C131" s="60" t="str">
         <x:v>AE-AUTO-NAV-002 - Automate scroll-down and arrow return-to-top in Playwright</x:v>
       </x:c>
-      <x:c r="D131" t="str">
-        <x:v>Backlog</x:v>
-      </x:c>
-      <x:c r="E131" t="str">
+      <x:c r="D131" s="60" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E131" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F131" t="str">
+      <x:c r="F131" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G131"/>
-      <x:c r="H131" t="str">
+      <x:c r="G131" s="60"/>
+      <x:c r="H131" s="60" t="str">
         <x:v>AE-AUTO-NAV-002</x:v>
       </x:c>
-      <x:c r="I131"/>
-      <x:c r="J131" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="K131" t="str">
-        <x:v>Automation Candidate</x:v>
-      </x:c>
-      <x:c r="L131" t="str">
+      <x:c r="I131" s="60"/>
+      <x:c r="J131" s="60" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K131" s="60" t="str">
+        <x:v>Automated</x:v>
+      </x:c>
+      <x:c r="L131" s="60" t="str">
         <x:v>AEQA-25</x:v>
       </x:c>
-      <x:c r="M131"/>
-      <x:c r="N131" t="str">
-        <x:v>2026-08-17 19:24 EDT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132">
+      <x:c r="M131" s="60"/>
+      <x:c r="N131" s="60" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A132" t="str">
         <x:v>AEQA-128</x:v>
       </x:c>
       <x:c r="B132" t="str">
         <x:v>Test Case</x:v>
       </x:c>
-      <x:c r="C132" t="str">
+      <x:c r="C132" s="60" t="str">
         <x:v>AE-AUTO-NAV-003 - Automate scroll-down and scroll-up without the arrow in Playwright</x:v>
       </x:c>
-      <x:c r="D132" t="str">
-        <x:v>Backlog</x:v>
-      </x:c>
-      <x:c r="E132" t="str">
+      <x:c r="D132" s="60" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="E132" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F132" t="str">
+      <x:c r="F132" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G132"/>
-      <x:c r="H132" t="str">
+      <x:c r="G132" s="60"/>
+      <x:c r="H132" s="60" t="str">
         <x:v>AE-AUTO-NAV-003</x:v>
       </x:c>
-      <x:c r="I132"/>
-      <x:c r="J132" t="str">
+      <x:c r="I132" s="60"/>
+      <x:c r="J132" s="60" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="K132" t="str">
+      <x:c r="K132" s="60" t="str">
         <x:v>Automation Candidate</x:v>
       </x:c>
-      <x:c r="L132" t="str">
+      <x:c r="L132" s="60" t="str">
         <x:v>AEQA-26</x:v>
       </x:c>
-      <x:c r="M132"/>
-      <x:c r="N132" t="str">
-        <x:v>2026-08-17 19:24 EDT</x:v>
+      <x:c r="M132" s="60"/>
+      <x:c r="N132" s="60" t="str">
+        <x:v>2026-08-17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11512,7 +11566,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a0d37e3cda84c84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c4b47c8de0c48a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
+++ b/Automation Exercise Project/Test Plan/Automation Exercise Requirements Traceability Matrix.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R56e8e386f27f41da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="R30264579887248b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R2a6eca20ec7c4472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rb5b9934d2bb44a62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="R0c0bdc12b1eb418a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra1a64a7f30f64ee7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="2" r:id="Rda0a3e813da94ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Scenarios" sheetId="3" r:id="R9c8e3978da924d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source APIs" sheetId="4" r:id="Rc74d5a2325b64335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Sync" sheetId="5" r:id="Re94e8fbe55694441"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2758,7 +2758,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1742cb2ebb24793"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfbab7b52a1c84668"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3021,7 +3021,7 @@
     </x:row>
     <x:row r="2" ht="22.5" customHeight="1">
       <x:c r="A2" s="125" t="str">
-        <x:v>Traceability across 44 portfolio requirements and 53 Jira Test Cases, synchronized with Jira Cloud through 2026-08-17</x:v>
+        <x:v>Traceability across 44 portfolio requirements and 53 Jira Test Cases, synchronized with Jira Cloud through 2026-08-21</x:v>
       </x:c>
       <x:c r="B2" s="125"/>
       <x:c r="C2" s="125"/>
@@ -3195,7 +3195,7 @@
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="B15" s="20" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="20" t="n">
         <x:f>0</x:f>
@@ -3225,7 +3225,7 @@
         <x:v>Not Run</x:v>
       </x:c>
       <x:c r="B17" s="20" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="20" t="n">
         <x:f>0</x:f>
@@ -3255,7 +3255,7 @@
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="140" t="str">
-        <x:v>Coverage design remains complete for all 44 portfolio requirements. Current requirement execution: 41 Pass, 2 Fail, and 1 Not Run. REQ-CART-005, REQ-ORDER-005, REQ-NAV-002, and REQ-NAV-003 are reconciled to their latest passing manual and automation results. AE-AUTO-NAV-003 / AEQA-128 remains Not Run and is not claimed as executed. All 14 official API requirements remain independently verified by Postman and Playwright.</x:v>
+        <x:v>Coverage design is complete for all 44 portfolio requirements. Current requirement execution: 42 Pass, 2 Fail, and 0 Not Run. Brand navigation and scroll-without-arrow coverage now include passing manual and Playwright results. Three open application defects remain linked to the two failed requirements. All 14 official API requirements remain independently verified by Postman and Playwright. GitHub Actions regression activity is tracked in Jira AEQA-129.</x:v>
       </x:c>
       <x:c r="B21" s="141"/>
       <x:c r="C21" s="141"/>
@@ -3351,7 +3351,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57c505957ba24ed8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16c40d1269c487e"/>
 </x:worksheet>
 </file>
 
@@ -3399,7 +3399,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="39" t="str">
-        <x:v>Coverage synchronized with 53 Jira Test Cases through 2026-08-17; Jira workflow and test execution status remain independently reconciled</x:v>
+        <x:v>Coverage synchronized with 53 Jira Test Cases through 2026-08-21; Jira workflow and test execution status remain independently reconciled</x:v>
       </x:c>
       <x:c r="B2" s="39"/>
       <x:c r="C2" s="39"/>
@@ -4519,7 +4519,7 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H26" s="82" t="str">
-        <x:v>Manual design is complete in AEQA-111 / AE-CATALOG-002. AEQA-123 is the linked Playwright implementation sub-task and remains Backlog.</x:v>
+        <x:v>Manual case AEQA-111 and Playwright implementation AEQA-123 passed. Selecting Polo and then H&amp;M displayed the expected brand headings and matching product lists.</x:v>
       </x:c>
       <x:c r="I26" s="143" t="str">
         <x:v>Functional — Positive</x:v>
@@ -4531,21 +4531,25 @@
         <x:v>QA | automationexercise.com</x:v>
       </x:c>
       <x:c r="L26" s="143" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="M26" s="143" t="str">
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N26" s="143" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O26" s="148" t="str">
-        <x:v>Not Run</x:v>
-      </x:c>
-      <x:c r="P26" s="82"/>
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P26" s="82" t="str">
+        <x:v>..\Automation\Execution Evidence\AE-CATALOG-002.png
+..\Automation\Execution Evidence\AE-CATALOG-002(1).png
+..\Automation\Execution Evidence\AE-CATALOG-002(2).png</x:v>
+      </x:c>
       <x:c r="Q26" s="82"/>
       <x:c r="R26" s="82" t="str">
-        <x:v>Execute AE-CATALOG-002 manually and complete AEQA-123 automation; reconcile each result and its evidence independently.</x:v>
+        <x:v>Manual and Playwright brand-navigation coverage are complete. Results were reconciled from Jira and local evidence on 2026-08-21.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" hidden="0" customHeight="1">
@@ -4909,13 +4913,13 @@
         <x:v>Fully Covered</x:v>
       </x:c>
       <x:c r="H33" s="82" t="str">
-        <x:v>Manual case AEQA-118 passed and automation case AEQA-128 remains Not Run. Manual scrolling down and back to the top without the arrow is verified.</x:v>
+        <x:v>Manual case AEQA-118 and automation case AEQA-128 passed. Browser scrolling reached the Subscription section and returned to the top without selecting the site arrow control.</x:v>
       </x:c>
       <x:c r="I33" s="143" t="str">
         <x:v>Functional — Positive</x:v>
       </x:c>
       <x:c r="J33" s="143" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="K33" s="143" t="str">
         <x:v>QA | automationexercise.com</x:v>
@@ -4927,17 +4931,18 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="N33" s="143" t="str">
-        <x:v>Not Automated</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="O33" s="148" t="str">
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="P33" s="82" t="str">
-        <x:v>Jira AEQA-118: image_2026-08-17_215326128.png; image_2026-08-17_215755766.png</x:v>
+        <x:v>..\Automation\Execution Evidence\AE-AUTO-NAV-003.png
+..\Automation\Execution Evidence\AE-AUTO-NAV-003.webm</x:v>
       </x:c>
       <x:c r="Q33" s="82"/>
       <x:c r="R33" s="82" t="str">
-        <x:v>Manual coverage passed. AE-AUTO-NAV-003 / AEQA-128 remains In Progress and Not Run until executed.</x:v>
+        <x:v>Manual and Playwright scroll-without-arrow coverage are complete. Jira and local evidence were reconciled on 2026-08-21.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -6140,7 +6145,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R686395056909448a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0707dcf78cee4f51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6556,7 +6561,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc6391d83bfc461d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R040bc858b7174588"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6992,7 +6997,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc2c45f69ce4abf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7251314ff14c485e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7037,7 +7042,7 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="134" t="str">
-        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-17 | Workflow status, traceability links, and execution metadata remain independently reconciled</x:v>
+        <x:v>Source: Jira Cloud AEQA reconciliation through 2026-08-21 | Workflow status, traceability links, and execution metadata remain independently reconciled</x:v>
       </x:c>
       <x:c r="B2" s="134"/>
       <x:c r="C2" s="134"/>
@@ -7705,7 +7710,7 @@
         <x:v>REQ-CATALOG-002 - View &amp; Cart Brand Products</x:v>
       </x:c>
       <x:c r="D23" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E23" s="76" t="str">
         <x:v>Medium</x:v>
@@ -7716,16 +7721,21 @@
       <x:c r="G23" s="76" t="str">
         <x:v>REQ-CATALOG-002</x:v>
       </x:c>
-      <x:c r="H23" s="76" t="str"/>
-      <x:c r="I23" s="76" t="str"/>
-      <x:c r="J23" s="76" t="str"/>
-      <x:c r="K23" s="76" t="str"/>
+      <x:c r="H23" s="76"/>
+      <x:c r="I23" s="76"/>
+      <x:c r="J23" s="76" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K23" s="76" t="str">
+        <x:v>Manual and Playwright</x:v>
+      </x:c>
       <x:c r="L23" s="76" t="str">
-        <x:v>AEQA-111</x:v>
-      </x:c>
-      <x:c r="M23" s="76" t="str"/>
+        <x:v>AEQA-111
+AEQA-123</x:v>
+      </x:c>
+      <x:c r="M23" s="76"/>
       <x:c r="N23" s="76" t="str">
-        <x:v>2026-08-17 15:14 EDT</x:v>
+        <x:v>2026-08-20 14:07 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -7957,7 +7967,7 @@
         <x:v>REQ-NAV-003 - Verify Scroll Up without 'Arrow' button and Scroll Down functionality</x:v>
       </x:c>
       <x:c r="D30" s="76" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E30" s="76" t="str">
         <x:v>Low</x:v>
@@ -7968,19 +7978,21 @@
       <x:c r="G30" s="76" t="str">
         <x:v>REQ-NAV-003</x:v>
       </x:c>
-      <x:c r="H30" s="76" t="str"/>
-      <x:c r="I30" s="76" t="str"/>
+      <x:c r="H30" s="76"/>
+      <x:c r="I30" s="76"/>
       <x:c r="J30" s="76" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K30" s="76" t="str"/>
+      <x:c r="K30" s="76" t="str">
+        <x:v>Manual and Playwright</x:v>
+      </x:c>
       <x:c r="L30" s="76" t="str">
         <x:v>AEQA-118
 AEQA-128</x:v>
       </x:c>
-      <x:c r="M30" s="76" t="str"/>
+      <x:c r="M30" s="76"/>
       <x:c r="N30" s="76" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20 14:07 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -10896,7 +10908,7 @@
         <x:v>AE-CATALOG-002 - Verify brand navigation and switching displays products for the selected brand</x:v>
       </x:c>
       <x:c r="D115" s="76" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E115" s="76" t="str">
         <x:v>High</x:v>
@@ -10904,13 +10916,13 @@
       <x:c r="F115" s="76" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G115" s="76" t="str"/>
+      <x:c r="G115" s="76"/>
       <x:c r="H115" s="76" t="str">
         <x:v>AE-CATALOG-002</x:v>
       </x:c>
-      <x:c r="I115" s="76" t="str"/>
+      <x:c r="I115" s="76"/>
       <x:c r="J115" s="76" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K115" s="76" t="str">
         <x:v>Manual</x:v>
@@ -10918,9 +10930,9 @@
       <x:c r="L115" s="76" t="str">
         <x:v>AEQA-19</x:v>
       </x:c>
-      <x:c r="M115" s="76" t="str"/>
+      <x:c r="M115" s="76"/>
       <x:c r="N115" s="76" t="str">
-        <x:v>2026-08-12 22:17 EDT</x:v>
+        <x:v>2026-08-20 14:06 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -11230,7 +11242,7 @@
         <x:v>QA Maintenance - Reconcile and re-upload missing execution evidence</x:v>
       </x:c>
       <x:c r="D124" s="60" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E124" s="60" t="str">
         <x:v>High</x:v>
@@ -11246,7 +11258,7 @@
       <x:c r="L124" s="60"/>
       <x:c r="M124" s="60"/>
       <x:c r="N124" s="60" t="str">
-        <x:v>12/Aug/26 10:27 PM</x:v>
+        <x:v>2026-08-20 14:12 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -11336,29 +11348,31 @@
         <x:v>Automate brand-based product navigation in Playwright</x:v>
       </x:c>
       <x:c r="D127" s="60" t="str">
-        <x:v>Backlog</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E127" s="60" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="F127" s="60" t="str"/>
+      <x:c r="F127" s="60" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
       <x:c r="G127" s="60" t="str">
         <x:v>REQ-CATALOG-002</x:v>
       </x:c>
-      <x:c r="H127" s="60" t="str"/>
-      <x:c r="I127" s="60" t="str"/>
+      <x:c r="H127" s="60"/>
+      <x:c r="I127" s="60"/>
       <x:c r="J127" s="60" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K127" s="60" t="str">
         <x:v>Playwright</x:v>
       </x:c>
-      <x:c r="L127" s="60" t="str"/>
+      <x:c r="L127" s="60"/>
       <x:c r="M127" s="60" t="str">
         <x:v>AEQA-19</x:v>
       </x:c>
       <x:c r="N127" s="60" t="str">
-        <x:v>2026-08-17 15:14 EDT</x:v>
+        <x:v>2026-08-17 16:53 EDT</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -11524,7 +11538,7 @@
         <x:v>AE-AUTO-NAV-003 - Automate scroll-down and scroll-up without the arrow in Playwright</x:v>
       </x:c>
       <x:c r="D132" s="60" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E132" s="60" t="str">
         <x:v>Medium</x:v>
@@ -11532,23 +11546,57 @@
       <x:c r="F132" s="60" t="str">
         <x:v>Kevin Mcmahon</x:v>
       </x:c>
-      <x:c r="G132" s="60"/>
+      <x:c r="G132" s="60" t="str">
+        <x:v>REQ-NAV-003</x:v>
+      </x:c>
       <x:c r="H132" s="60" t="str">
         <x:v>AE-AUTO-NAV-003</x:v>
       </x:c>
       <x:c r="I132" s="60"/>
       <x:c r="J132" s="60" t="str">
-        <x:v>Not Run</x:v>
+        <x:v>Pass</x:v>
       </x:c>
       <x:c r="K132" s="60" t="str">
-        <x:v>Automation Candidate</x:v>
+        <x:v>Playwright</x:v>
       </x:c>
       <x:c r="L132" s="60" t="str">
         <x:v>AEQA-26</x:v>
       </x:c>
       <x:c r="M132" s="60"/>
       <x:c r="N132" s="60" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20 14:11 EDT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>AEQA-129</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>Task</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>GitHub Actions QA Regression Run Ledger</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>In Progress</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="F133" t="str">
+        <x:v>Kevin Mcmahon</x:v>
+      </x:c>
+      <x:c r="G133"/>
+      <x:c r="H133"/>
+      <x:c r="I133"/>
+      <x:c r="J133"/>
+      <x:c r="K133" t="str">
+        <x:v>GitHub Actions</x:v>
+      </x:c>
+      <x:c r="L133"/>
+      <x:c r="M133"/>
+      <x:c r="N133" t="str">
+        <x:v>2026-08-21 03:11 EDT</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11566,7 +11614,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c4b47c8de0c48a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2538f2830344813"/>
   </x:tableParts>
 </x:worksheet>
 </file>